--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -3130,10 +3130,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119838885</v>
+        <v>119838597</v>
       </c>
       <c r="B25" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,45 +3142,41 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562977</v>
+        <v>562861</v>
       </c>
       <c r="R25" t="n">
-        <v>7061045</v>
+        <v>7061099</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3207,19 +3203,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3234,22 +3220,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119835350</v>
+        <v>119838885</v>
       </c>
       <c r="B26" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3258,41 +3244,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562801</v>
+        <v>562977</v>
       </c>
       <c r="R26" t="n">
-        <v>7061274</v>
+        <v>7061045</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3319,9 +3309,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3336,22 +3336,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119838597</v>
+        <v>119835350</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3360,25 +3360,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3388,10 +3388,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562861</v>
+        <v>562801</v>
       </c>
       <c r="R27" t="n">
-        <v>7061099</v>
+        <v>7061274</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3766,10 +3766,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119839184</v>
+        <v>119837074</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3778,41 +3778,45 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>563009</v>
+        <v>562940</v>
       </c>
       <c r="R31" t="n">
-        <v>7061040</v>
+        <v>7061272</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3839,9 +3843,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3856,22 +3870,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119837494</v>
+        <v>119839184</v>
       </c>
       <c r="B32" t="n">
-        <v>89633</v>
+        <v>91840</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3880,25 +3894,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3908,13 +3922,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562773</v>
+        <v>563009</v>
       </c>
       <c r="R32" t="n">
-        <v>7061158</v>
+        <v>7061040</v>
       </c>
       <c r="S32" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3970,10 +3984,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119835805</v>
+        <v>119835742</v>
       </c>
       <c r="B33" t="n">
-        <v>78526</v>
+        <v>56522</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3982,25 +3996,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4010,10 +4024,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562873</v>
+        <v>562853</v>
       </c>
       <c r="R33" t="n">
-        <v>7061226</v>
+        <v>7061243</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4072,10 +4086,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119835742</v>
+        <v>119837494</v>
       </c>
       <c r="B34" t="n">
-        <v>56522</v>
+        <v>89633</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4084,25 +4098,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100138</v>
+        <v>1962</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4112,13 +4126,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562853</v>
+        <v>562773</v>
       </c>
       <c r="R34" t="n">
-        <v>7061243</v>
+        <v>7061158</v>
       </c>
       <c r="S34" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4162,22 +4176,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119837074</v>
+        <v>119835805</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4186,45 +4200,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I35" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I35" t="inlineStr"/>
       <c r="P35" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562940</v>
+        <v>562873</v>
       </c>
       <c r="R35" t="n">
-        <v>7061272</v>
+        <v>7061226</v>
       </c>
       <c r="S35" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4251,19 +4261,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z35" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AA35" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB35" t="inlineStr">
-        <is>
-          <t>16:40</t>
         </is>
       </c>
       <c r="AD35" t="b">
@@ -4278,12 +4278,12 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
@@ -5278,10 +5278,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119836284</v>
+        <v>119836719</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>90562</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5290,45 +5290,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562903</v>
+        <v>562937</v>
       </c>
       <c r="R45" t="n">
-        <v>7061259</v>
+        <v>7061312</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5355,19 +5351,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5382,22 +5368,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119836719</v>
+        <v>119835470</v>
       </c>
       <c r="B46" t="n">
-        <v>90562</v>
+        <v>78526</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5410,21 +5396,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5434,10 +5420,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562937</v>
+        <v>562839</v>
       </c>
       <c r="R46" t="n">
-        <v>7061312</v>
+        <v>7061260</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5496,7 +5482,7 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119835470</v>
+        <v>119840354</v>
       </c>
       <c r="B47" t="n">
         <v>78526</v>
@@ -5536,13 +5522,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562839</v>
+        <v>562893</v>
       </c>
       <c r="R47" t="n">
-        <v>7061260</v>
+        <v>7061427</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5586,22 +5572,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119840354</v>
+        <v>119838859</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>91883</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5614,21 +5600,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5638,10 +5624,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562893</v>
+        <v>562897</v>
       </c>
       <c r="R48" t="n">
-        <v>7061427</v>
+        <v>7061087</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5700,10 +5686,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119838859</v>
+        <v>119837306</v>
       </c>
       <c r="B49" t="n">
-        <v>91883</v>
+        <v>79607</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5716,21 +5702,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5740,10 +5726,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562897</v>
+        <v>562793</v>
       </c>
       <c r="R49" t="n">
-        <v>7061087</v>
+        <v>7061251</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5776,6 +5762,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5802,7 +5793,7 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119837306</v>
+        <v>119835897</v>
       </c>
       <c r="B50" t="n">
         <v>79607</v>
@@ -5842,13 +5833,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562793</v>
+        <v>562851</v>
       </c>
       <c r="R50" t="n">
-        <v>7061251</v>
+        <v>7061350</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5878,11 +5869,6 @@
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC50" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5909,10 +5895,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119835897</v>
+        <v>119837066</v>
       </c>
       <c r="B51" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5921,25 +5907,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5949,10 +5935,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562851</v>
+        <v>562940</v>
       </c>
       <c r="R51" t="n">
-        <v>7061350</v>
+        <v>7061261</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5999,19 +5985,19 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119837066</v>
+        <v>119836284</v>
       </c>
       <c r="B52" t="n">
         <v>97907</v>
@@ -6044,20 +6030,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr"/>
+      <c r="I52" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562940</v>
+        <v>562903</v>
       </c>
       <c r="R52" t="n">
-        <v>7061261</v>
+        <v>7061259</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6084,9 +6074,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6101,12 +6101,12 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
@@ -7406,10 +7406,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119835654</v>
+        <v>119836491</v>
       </c>
       <c r="B65" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7418,25 +7418,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7446,10 +7446,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562838</v>
+        <v>563040</v>
       </c>
       <c r="R65" t="n">
-        <v>7061333</v>
+        <v>7061203</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7508,10 +7508,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119837999</v>
+        <v>119839243</v>
       </c>
       <c r="B66" t="n">
-        <v>79144</v>
+        <v>97907</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7520,41 +7520,45 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562848</v>
+        <v>563074</v>
       </c>
       <c r="R66" t="n">
-        <v>7061083</v>
+        <v>7061022</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7581,9 +7585,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7598,22 +7612,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119836373</v>
+        <v>119835654</v>
       </c>
       <c r="B67" t="n">
-        <v>97907</v>
+        <v>79636</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7622,45 +7636,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562910</v>
+        <v>562838</v>
       </c>
       <c r="R67" t="n">
-        <v>7061306</v>
+        <v>7061333</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7687,19 +7697,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7714,22 +7714,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119836533</v>
+        <v>119837999</v>
       </c>
       <c r="B68" t="n">
-        <v>97907</v>
+        <v>79144</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7738,45 +7738,41 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562927</v>
+        <v>562848</v>
       </c>
       <c r="R68" t="n">
-        <v>7061314</v>
+        <v>7061083</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7803,19 +7799,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7830,19 +7816,19 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119836491</v>
+        <v>119836373</v>
       </c>
       <c r="B69" t="n">
         <v>97907</v>
@@ -7875,20 +7861,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I69" t="inlineStr"/>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>563040</v>
+        <v>562910</v>
       </c>
       <c r="R69" t="n">
-        <v>7061203</v>
+        <v>7061306</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7915,9 +7905,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7932,19 +7932,19 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119839243</v>
+        <v>119836533</v>
       </c>
       <c r="B70" t="n">
         <v>97907</v>
@@ -7979,19 +7979,19 @@
       </c>
       <c r="I70" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>563074</v>
+        <v>562927</v>
       </c>
       <c r="R70" t="n">
-        <v>7061022</v>
+        <v>7061314</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8023,7 +8023,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -8033,7 +8033,7 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8060,10 +8060,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119837298</v>
+        <v>119838967</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8072,41 +8072,45 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562841</v>
+        <v>562990</v>
       </c>
       <c r="R71" t="n">
-        <v>7061196</v>
+        <v>7061060</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8133,9 +8137,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8150,22 +8164,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119835500</v>
+        <v>119836632</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8174,38 +8188,42 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562824</v>
+        <v>562948</v>
       </c>
       <c r="R72" t="n">
-        <v>7061319</v>
+        <v>7061323</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8252,22 +8270,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119837399</v>
+        <v>119835344</v>
       </c>
       <c r="B73" t="n">
-        <v>79607</v>
+        <v>90582</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8280,21 +8298,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8304,10 +8322,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562767</v>
+        <v>562790</v>
       </c>
       <c r="R73" t="n">
-        <v>7061188</v>
+        <v>7061258</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8337,9 +8355,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8354,22 +8382,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119840328</v>
+        <v>119838030</v>
       </c>
       <c r="B74" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8382,34 +8410,39 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
+      <c r="M74" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562922</v>
+        <v>562828</v>
       </c>
       <c r="R74" t="n">
-        <v>7061399</v>
+        <v>7061089</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8439,9 +8472,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8456,19 +8499,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119838030</v>
+        <v>119836807</v>
       </c>
       <c r="B75" t="n">
         <v>57310</v>
@@ -8502,21 +8545,16 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562828</v>
+        <v>562926</v>
       </c>
       <c r="R75" t="n">
-        <v>7061089</v>
+        <v>7061340</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8548,7 +8586,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8558,7 +8596,12 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8585,10 +8628,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119836807</v>
+        <v>119837298</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8601,21 +8644,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8625,13 +8668,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562926</v>
+        <v>562841</v>
       </c>
       <c r="R76" t="n">
-        <v>7061340</v>
+        <v>7061196</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8658,24 +8701,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8690,22 +8718,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119835344</v>
+        <v>119835500</v>
       </c>
       <c r="B77" t="n">
-        <v>90582</v>
+        <v>79607</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8718,21 +8746,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8742,13 +8770,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562790</v>
+        <v>562824</v>
       </c>
       <c r="R77" t="n">
-        <v>7061258</v>
+        <v>7061319</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8775,19 +8803,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8802,22 +8820,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119838967</v>
+        <v>119837399</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8826,42 +8844,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562990</v>
+        <v>562767</v>
       </c>
       <c r="R78" t="n">
-        <v>7061060</v>
+        <v>7061188</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8891,19 +8905,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8918,22 +8922,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119836632</v>
+        <v>119840328</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8942,45 +8946,41 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562948</v>
+        <v>562922</v>
       </c>
       <c r="R79" t="n">
-        <v>7061323</v>
+        <v>7061399</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9024,12 +9024,12 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
@@ -10533,10 +10533,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119840391</v>
+        <v>119836358</v>
       </c>
       <c r="B94" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10549,21 +10549,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10573,13 +10573,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562861</v>
+        <v>562901</v>
       </c>
       <c r="R94" t="n">
-        <v>7061439</v>
+        <v>7061289</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10623,22 +10623,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119836358</v>
+        <v>119838709</v>
       </c>
       <c r="B95" t="n">
-        <v>78526</v>
+        <v>91883</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10651,21 +10651,21 @@
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10675,10 +10675,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562901</v>
+        <v>562892</v>
       </c>
       <c r="R95" t="n">
-        <v>7061289</v>
+        <v>7061086</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10737,10 +10737,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119838709</v>
+        <v>119840373</v>
       </c>
       <c r="B96" t="n">
-        <v>91883</v>
+        <v>79607</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10753,21 +10753,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5448</v>
+        <v>6458</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10777,13 +10777,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>562892</v>
+        <v>562875</v>
       </c>
       <c r="R96" t="n">
-        <v>7061086</v>
+        <v>7061433</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10827,19 +10827,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119840373</v>
+        <v>119840391</v>
       </c>
       <c r="B97" t="n">
         <v>79607</v>
@@ -10879,10 +10879,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562875</v>
+        <v>562861</v>
       </c>
       <c r="R97" t="n">
-        <v>7061433</v>
+        <v>7061439</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11257,10 +11257,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119837424</v>
+        <v>119837761</v>
       </c>
       <c r="B101" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11269,25 +11269,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11297,13 +11297,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562774</v>
+        <v>562816</v>
       </c>
       <c r="R101" t="n">
-        <v>7061178</v>
+        <v>7061089</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11347,22 +11347,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119837761</v>
+        <v>119837424</v>
       </c>
       <c r="B102" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11371,25 +11371,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11399,13 +11399,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562816</v>
+        <v>562774</v>
       </c>
       <c r="R102" t="n">
-        <v>7061089</v>
+        <v>7061178</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11449,19 +11449,19 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119836521</v>
+        <v>119836512</v>
       </c>
       <c r="B103" t="n">
         <v>97907</v>
@@ -11494,20 +11494,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I103" t="inlineStr"/>
+      <c r="I103" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562928</v>
+        <v>562925</v>
       </c>
       <c r="R103" t="n">
-        <v>7061305</v>
+        <v>7061308</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11534,9 +11538,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11551,12 +11565,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12123,7 +12137,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119836512</v>
+        <v>119836521</v>
       </c>
       <c r="B109" t="n">
         <v>97907</v>
@@ -12156,24 +12170,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>562925</v>
+        <v>562928</v>
       </c>
       <c r="R109" t="n">
-        <v>7061308</v>
+        <v>7061305</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12200,19 +12210,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12227,12 +12227,12 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
@@ -12876,10 +12876,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119837560</v>
+        <v>119835360</v>
       </c>
       <c r="B116" t="n">
-        <v>79607</v>
+        <v>4766</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12888,25 +12888,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>100299</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12916,10 +12916,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562746</v>
+        <v>562801</v>
       </c>
       <c r="R116" t="n">
-        <v>7061142</v>
+        <v>7061292</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12954,6 +12954,11 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
+        </is>
+      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -12966,22 +12971,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119835514</v>
+        <v>119837193</v>
       </c>
       <c r="B117" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12994,21 +12999,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13018,10 +13023,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562849</v>
+        <v>562864</v>
       </c>
       <c r="R117" t="n">
-        <v>7061244</v>
+        <v>7061224</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13054,6 +13059,11 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13080,10 +13090,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119835360</v>
+        <v>119837560</v>
       </c>
       <c r="B118" t="n">
-        <v>4766</v>
+        <v>79607</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13092,25 +13102,25 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100299</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13120,10 +13130,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562801</v>
+        <v>562746</v>
       </c>
       <c r="R118" t="n">
-        <v>7061292</v>
+        <v>7061142</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13158,11 +13168,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
-        </is>
-      </c>
       <c r="AD118" t="b">
         <v>0</v>
       </c>
@@ -13175,22 +13180,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119837193</v>
+        <v>119837992</v>
       </c>
       <c r="B119" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13203,21 +13208,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13227,10 +13232,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>562864</v>
+        <v>562845</v>
       </c>
       <c r="R119" t="n">
-        <v>7061224</v>
+        <v>7061115</v>
       </c>
       <c r="S119" t="n">
         <v>15</v>
@@ -13263,11 +13268,6 @@
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13294,7 +13294,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119835751</v>
+        <v>119835531</v>
       </c>
       <c r="B120" t="n">
         <v>79607</v>
@@ -13334,13 +13334,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562833</v>
+        <v>562827</v>
       </c>
       <c r="R120" t="n">
-        <v>7061339</v>
+        <v>7061302</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13396,10 +13396,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119840300</v>
+        <v>119835514</v>
       </c>
       <c r="B121" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13412,21 +13412,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13436,13 +13436,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562938</v>
+        <v>562849</v>
       </c>
       <c r="R121" t="n">
-        <v>7061384</v>
+        <v>7061244</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13486,22 +13486,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119836005</v>
+        <v>119835751</v>
       </c>
       <c r="B122" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13514,21 +13514,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13538,13 +13538,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>562898</v>
+        <v>562833</v>
       </c>
       <c r="R122" t="n">
-        <v>7061215</v>
+        <v>7061339</v>
       </c>
       <c r="S122" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13588,22 +13588,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119837992</v>
+        <v>119836005</v>
       </c>
       <c r="B123" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13616,21 +13616,21 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>562845</v>
+        <v>562898</v>
       </c>
       <c r="R123" t="n">
-        <v>7061115</v>
+        <v>7061215</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13702,10 +13702,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119835531</v>
+        <v>119840300</v>
       </c>
       <c r="B124" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13718,21 +13718,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>562827</v>
+        <v>562938</v>
       </c>
       <c r="R124" t="n">
-        <v>7061302</v>
+        <v>7061384</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -4626,10 +4626,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119837299</v>
+        <v>119835697</v>
       </c>
       <c r="B39" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4642,21 +4642,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4666,10 +4666,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562843</v>
+        <v>562826</v>
       </c>
       <c r="R39" t="n">
-        <v>7061204</v>
+        <v>7061341</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -4699,19 +4699,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:52</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4726,12 +4716,12 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
@@ -4840,10 +4830,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119835697</v>
+        <v>119837299</v>
       </c>
       <c r="B41" t="n">
-        <v>79607</v>
+        <v>82305</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4856,21 +4846,21 @@
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4880,10 +4870,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562826</v>
+        <v>562843</v>
       </c>
       <c r="R41" t="n">
-        <v>7061341</v>
+        <v>7061204</v>
       </c>
       <c r="S41" t="n">
         <v>10</v>
@@ -4913,9 +4903,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z41" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB41" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4930,12 +4930,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -7090,10 +7090,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119838571</v>
+        <v>119836491</v>
       </c>
       <c r="B62" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7102,41 +7102,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562856</v>
+        <v>563040</v>
       </c>
       <c r="R62" t="n">
-        <v>7061099</v>
+        <v>7061203</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7163,19 +7163,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>17:44</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7190,22 +7180,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119835968</v>
+        <v>119839243</v>
       </c>
       <c r="B63" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7214,38 +7204,42 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562856</v>
+        <v>563074</v>
       </c>
       <c r="R63" t="n">
-        <v>7061341</v>
+        <v>7061022</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7275,9 +7269,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7292,22 +7296,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119835259</v>
+        <v>119838571</v>
       </c>
       <c r="B64" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7320,37 +7324,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562815</v>
+        <v>562856</v>
       </c>
       <c r="R64" t="n">
-        <v>7061302</v>
+        <v>7061099</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7377,9 +7381,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7394,22 +7408,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119836491</v>
+        <v>119835968</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7418,25 +7432,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7446,13 +7460,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563040</v>
+        <v>562856</v>
       </c>
       <c r="R65" t="n">
-        <v>7061203</v>
+        <v>7061341</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7508,10 +7522,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119839243</v>
+        <v>119835259</v>
       </c>
       <c r="B66" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7520,45 +7534,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563074</v>
+        <v>562815</v>
       </c>
       <c r="R66" t="n">
-        <v>7061022</v>
+        <v>7061302</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7585,19 +7595,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7612,12 +7612,12 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
@@ -8060,10 +8060,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119838967</v>
+        <v>119837298</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8072,45 +8072,41 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562990</v>
+        <v>562841</v>
       </c>
       <c r="R71" t="n">
-        <v>7061060</v>
+        <v>7061196</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8137,19 +8133,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8164,22 +8150,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119836632</v>
+        <v>119835500</v>
       </c>
       <c r="B72" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8188,42 +8174,38 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I72" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562948</v>
+        <v>562824</v>
       </c>
       <c r="R72" t="n">
-        <v>7061323</v>
+        <v>7061319</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8270,22 +8252,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119835344</v>
+        <v>119837399</v>
       </c>
       <c r="B73" t="n">
-        <v>90582</v>
+        <v>79607</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8298,21 +8280,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8322,10 +8304,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562790</v>
+        <v>562767</v>
       </c>
       <c r="R73" t="n">
-        <v>7061258</v>
+        <v>7061188</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8355,19 +8337,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8382,22 +8354,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119838030</v>
+        <v>119840328</v>
       </c>
       <c r="B74" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8410,39 +8382,34 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
-      <c r="M74" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562828</v>
+        <v>562922</v>
       </c>
       <c r="R74" t="n">
-        <v>7061089</v>
+        <v>7061399</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8472,19 +8439,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8499,19 +8456,19 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119836807</v>
+        <v>119838030</v>
       </c>
       <c r="B75" t="n">
         <v>57310</v>
@@ -8545,16 +8502,21 @@
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562926</v>
+        <v>562828</v>
       </c>
       <c r="R75" t="n">
-        <v>7061340</v>
+        <v>7061089</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8586,7 +8548,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8596,12 +8558,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8628,10 +8585,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119837298</v>
+        <v>119836807</v>
       </c>
       <c r="B76" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8644,21 +8601,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8668,13 +8625,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562841</v>
+        <v>562926</v>
       </c>
       <c r="R76" t="n">
-        <v>7061196</v>
+        <v>7061340</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8701,9 +8658,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8718,22 +8690,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119835500</v>
+        <v>119835344</v>
       </c>
       <c r="B77" t="n">
-        <v>79607</v>
+        <v>90582</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8746,21 +8718,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8770,13 +8742,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562824</v>
+        <v>562790</v>
       </c>
       <c r="R77" t="n">
-        <v>7061319</v>
+        <v>7061258</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8803,9 +8775,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8820,22 +8802,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119837399</v>
+        <v>119838967</v>
       </c>
       <c r="B78" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8844,38 +8826,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562767</v>
+        <v>562990</v>
       </c>
       <c r="R78" t="n">
-        <v>7061188</v>
+        <v>7061060</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8905,9 +8891,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8922,22 +8918,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119840328</v>
+        <v>119836632</v>
       </c>
       <c r="B79" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8946,41 +8942,45 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562922</v>
+        <v>562948</v>
       </c>
       <c r="R79" t="n">
-        <v>7061399</v>
+        <v>7061323</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9024,22 +9024,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119836367</v>
+        <v>119838064</v>
       </c>
       <c r="B80" t="n">
-        <v>95455</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9048,25 +9048,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9076,10 +9076,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562983</v>
+        <v>562850</v>
       </c>
       <c r="R80" t="n">
-        <v>7061268</v>
+        <v>7061098</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9138,10 +9138,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119837181</v>
+        <v>119837858</v>
       </c>
       <c r="B81" t="n">
-        <v>90527</v>
+        <v>91840</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9154,21 +9154,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5447</v>
+        <v>4364</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9178,10 +9178,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>562872</v>
+        <v>562847</v>
       </c>
       <c r="R81" t="n">
-        <v>7061246</v>
+        <v>7061096</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9240,10 +9240,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119837344</v>
+        <v>119836367</v>
       </c>
       <c r="B82" t="n">
-        <v>57463</v>
+        <v>95455</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9256,46 +9256,37 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I82" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M82" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I82" t="inlineStr"/>
       <c r="P82" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>562829</v>
+        <v>562983</v>
       </c>
       <c r="R82" t="n">
-        <v>7061182</v>
+        <v>7061268</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9322,19 +9313,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z82" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA82" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB82" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9349,22 +9330,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119838064</v>
+        <v>119837181</v>
       </c>
       <c r="B83" t="n">
-        <v>91840</v>
+        <v>90527</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9377,21 +9358,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>4364</v>
+        <v>5447</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9401,13 +9382,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562850</v>
+        <v>562872</v>
       </c>
       <c r="R83" t="n">
-        <v>7061098</v>
+        <v>7061246</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9463,10 +9444,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119837858</v>
+        <v>119835495</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9475,25 +9456,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9503,13 +9484,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562847</v>
+        <v>562822</v>
       </c>
       <c r="R84" t="n">
-        <v>7061096</v>
+        <v>7061305</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9565,10 +9546,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119835495</v>
+        <v>119837344</v>
       </c>
       <c r="B85" t="n">
-        <v>79607</v>
+        <v>57463</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9581,37 +9562,46 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M85" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>562822</v>
+        <v>562829</v>
       </c>
       <c r="R85" t="n">
-        <v>7061305</v>
+        <v>7061182</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9638,9 +9628,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9655,12 +9655,12 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839227</v>
+        <v>119838967</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,38 +2811,42 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563080</v>
+        <v>562990</v>
       </c>
       <c r="R22" t="n">
-        <v>7061030</v>
+        <v>7061060</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,9 +2876,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2889,22 +2903,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119835980</v>
+        <v>119835751</v>
       </c>
       <c r="B23" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2917,39 +2931,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562885</v>
+        <v>562833</v>
       </c>
       <c r="R23" t="n">
-        <v>7061225</v>
+        <v>7061339</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2979,19 +2988,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3006,22 +3005,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119838864</v>
+        <v>119840373</v>
       </c>
       <c r="B24" t="n">
-        <v>78263</v>
+        <v>79607</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3034,34 +3033,34 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
       <c r="P24" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562940</v>
+        <v>562875</v>
       </c>
       <c r="R24" t="n">
-        <v>7061021</v>
+        <v>7061433</v>
       </c>
       <c r="S24" t="n">
         <v>10</v>
@@ -3091,19 +3090,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>18:00</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3118,22 +3107,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119838597</v>
+        <v>119837992</v>
       </c>
       <c r="B25" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3142,25 +3131,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3170,10 +3159,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562861</v>
+        <v>562845</v>
       </c>
       <c r="R25" t="n">
-        <v>7061099</v>
+        <v>7061115</v>
       </c>
       <c r="S25" t="n">
         <v>15</v>
@@ -3232,10 +3221,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119838885</v>
+        <v>119837543</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3244,42 +3233,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562977</v>
+        <v>562745</v>
       </c>
       <c r="R26" t="n">
-        <v>7061045</v>
+        <v>7061152</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3311,7 +3296,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3321,7 +3306,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3348,10 +3333,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119835350</v>
+        <v>119835980</v>
       </c>
       <c r="B27" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3364,37 +3349,42 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562801</v>
+        <v>562885</v>
       </c>
       <c r="R27" t="n">
-        <v>7061274</v>
+        <v>7061225</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3421,9 +3411,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,22 +3438,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119837383</v>
+        <v>119838709</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>91883</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3466,21 +3466,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3490,13 +3490,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562779</v>
+        <v>562892</v>
       </c>
       <c r="R28" t="n">
-        <v>7061176</v>
+        <v>7061086</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3540,22 +3540,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119835431</v>
+        <v>119836896</v>
       </c>
       <c r="B29" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3568,21 +3568,21 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562853</v>
+        <v>562930</v>
       </c>
       <c r="R29" t="n">
-        <v>7061293</v>
+        <v>7061333</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3628,6 +3628,11 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,22 +3647,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119839135</v>
+        <v>119835259</v>
       </c>
       <c r="B30" t="n">
-        <v>78262</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3670,37 +3675,37 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562982</v>
+        <v>562815</v>
       </c>
       <c r="R30" t="n">
-        <v>7061063</v>
+        <v>7061302</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3727,19 +3732,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>18:21</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3754,22 +3749,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119837074</v>
+        <v>119835805</v>
       </c>
       <c r="B31" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3778,45 +3773,41 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562940</v>
+        <v>562873</v>
       </c>
       <c r="R31" t="n">
-        <v>7061272</v>
+        <v>7061226</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3843,19 +3834,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:40</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3870,22 +3851,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119839184</v>
+        <v>119837193</v>
       </c>
       <c r="B32" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3894,25 +3875,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3922,10 +3903,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563009</v>
+        <v>562864</v>
       </c>
       <c r="R32" t="n">
-        <v>7061040</v>
+        <v>7061224</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3960,6 +3941,11 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD32" t="b">
         <v>0</v>
       </c>
@@ -3972,22 +3958,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119835742</v>
+        <v>119837427</v>
       </c>
       <c r="B33" t="n">
-        <v>56522</v>
+        <v>91840</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -4000,21 +3986,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4024,13 +4010,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562853</v>
+        <v>562772</v>
       </c>
       <c r="R33" t="n">
-        <v>7061243</v>
+        <v>7061165</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4057,9 +4043,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z33" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB33" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4074,22 +4070,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119837494</v>
+        <v>119838859</v>
       </c>
       <c r="B34" t="n">
-        <v>89633</v>
+        <v>91883</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4102,21 +4098,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>1962</v>
+        <v>5448</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4126,13 +4122,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562773</v>
+        <v>562897</v>
       </c>
       <c r="R34" t="n">
-        <v>7061158</v>
+        <v>7061087</v>
       </c>
       <c r="S34" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4188,10 +4184,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119835805</v>
+        <v>119838102</v>
       </c>
       <c r="B35" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4204,37 +4200,42 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562873</v>
+        <v>562863</v>
       </c>
       <c r="R35" t="n">
-        <v>7061226</v>
+        <v>7061098</v>
       </c>
       <c r="S35" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4278,22 +4279,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119840261</v>
+        <v>119837560</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4306,37 +4307,37 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
       <c r="P36" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>563003</v>
+        <v>562746</v>
       </c>
       <c r="R36" t="n">
-        <v>7061318</v>
+        <v>7061142</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4363,24 +4364,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4395,22 +4381,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119836923</v>
+        <v>119835500</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4423,37 +4409,37 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
       <c r="P37" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562958</v>
+        <v>562824</v>
       </c>
       <c r="R37" t="n">
-        <v>7061345</v>
+        <v>7061319</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4480,24 +4466,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC37" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4512,22 +4483,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119837366</v>
+        <v>119837966</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>78171</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4540,21 +4511,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4564,13 +4535,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562815</v>
+        <v>562845</v>
       </c>
       <c r="R38" t="n">
-        <v>7061177</v>
+        <v>7061093</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4614,22 +4585,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119835697</v>
+        <v>119836719</v>
       </c>
       <c r="B39" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4642,21 +4613,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4666,13 +4637,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562826</v>
+        <v>562937</v>
       </c>
       <c r="R39" t="n">
-        <v>7061341</v>
+        <v>7061312</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4716,22 +4687,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119836179</v>
+        <v>119839228</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4744,34 +4715,34 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562966</v>
+        <v>563061</v>
       </c>
       <c r="R40" t="n">
-        <v>7061336</v>
+        <v>7061025</v>
       </c>
       <c r="S40" t="n">
         <v>10</v>
@@ -4801,9 +4772,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z40" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB40" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4818,22 +4804,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119837299</v>
+        <v>119835360</v>
       </c>
       <c r="B41" t="n">
-        <v>82305</v>
+        <v>4766</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4842,25 +4828,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>1312</v>
+        <v>100299</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4870,13 +4856,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562843</v>
+        <v>562801</v>
       </c>
       <c r="R41" t="n">
-        <v>7061204</v>
+        <v>7061292</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4903,19 +4889,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z41" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB41" t="inlineStr">
-        <is>
-          <t>16:52</t>
+      <c r="AC41" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -4930,22 +4911,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119836311</v>
+        <v>119840261</v>
       </c>
       <c r="B42" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4954,41 +4935,41 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562972</v>
+        <v>563003</v>
       </c>
       <c r="R42" t="n">
-        <v>7061274</v>
+        <v>7061318</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -5015,14 +4996,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
       <c r="AC42" t="inlineStr">
         <is>
-          <t>Spridd i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5037,22 +5028,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119837427</v>
+        <v>119837512</v>
       </c>
       <c r="B43" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5061,25 +5052,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5089,10 +5080,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562772</v>
+        <v>562769</v>
       </c>
       <c r="R43" t="n">
-        <v>7061165</v>
+        <v>7061157</v>
       </c>
       <c r="S43" t="n">
         <v>10</v>
@@ -5124,7 +5115,7 @@
       </c>
       <c r="Z43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA43" t="inlineStr">
@@ -5134,7 +5125,12 @@
       </c>
       <c r="AB43" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC43" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5161,10 +5157,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119837512</v>
+        <v>119837494</v>
       </c>
       <c r="B44" t="n">
-        <v>57310</v>
+        <v>89633</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5177,21 +5173,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5201,13 +5197,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562769</v>
+        <v>562773</v>
       </c>
       <c r="R44" t="n">
-        <v>7061157</v>
+        <v>7061158</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5234,24 +5230,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC44" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5266,22 +5247,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119836719</v>
+        <v>119839227</v>
       </c>
       <c r="B45" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5290,25 +5271,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5318,13 +5299,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562937</v>
+        <v>563080</v>
       </c>
       <c r="R45" t="n">
-        <v>7061312</v>
+        <v>7061030</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5368,22 +5349,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119835470</v>
+        <v>119838606</v>
       </c>
       <c r="B46" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5396,21 +5377,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5420,13 +5401,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562839</v>
+        <v>562879</v>
       </c>
       <c r="R46" t="n">
-        <v>7061260</v>
+        <v>7061091</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5470,22 +5451,22 @@
       <c r="AT46" t="inlineStr"/>
       <c r="AW46" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX46" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119840354</v>
+        <v>119835514</v>
       </c>
       <c r="B47" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5498,21 +5479,21 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5522,13 +5503,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562893</v>
+        <v>562849</v>
       </c>
       <c r="R47" t="n">
-        <v>7061427</v>
+        <v>7061244</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5572,22 +5553,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119838859</v>
+        <v>119840328</v>
       </c>
       <c r="B48" t="n">
-        <v>91883</v>
+        <v>79607</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5600,21 +5581,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>5448</v>
+        <v>6458</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5624,10 +5605,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562897</v>
+        <v>562922</v>
       </c>
       <c r="R48" t="n">
-        <v>7061087</v>
+        <v>7061399</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5686,10 +5667,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119837306</v>
+        <v>119836005</v>
       </c>
       <c r="B49" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5702,21 +5683,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5726,13 +5707,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562793</v>
+        <v>562898</v>
       </c>
       <c r="R49" t="n">
-        <v>7061251</v>
+        <v>7061215</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5762,11 +5743,6 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5781,22 +5757,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119835897</v>
+        <v>119837066</v>
       </c>
       <c r="B50" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5805,25 +5781,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5833,10 +5809,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562851</v>
+        <v>562940</v>
       </c>
       <c r="R50" t="n">
-        <v>7061350</v>
+        <v>7061261</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -5883,22 +5859,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119837066</v>
+        <v>119838064</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5907,25 +5883,25 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5935,10 +5911,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562940</v>
+        <v>562850</v>
       </c>
       <c r="R51" t="n">
-        <v>7061261</v>
+        <v>7061098</v>
       </c>
       <c r="S51" t="n">
         <v>15</v>
@@ -5985,22 +5961,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119836284</v>
+        <v>119838597</v>
       </c>
       <c r="B52" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6009,45 +5985,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I52" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562903</v>
+        <v>562861</v>
       </c>
       <c r="R52" t="n">
-        <v>7061259</v>
+        <v>7061099</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6074,19 +6046,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6101,22 +6063,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119836629</v>
+        <v>119838153</v>
       </c>
       <c r="B53" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6125,43 +6087,38 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562935</v>
+        <v>562865</v>
       </c>
       <c r="R53" t="n">
-        <v>7061315</v>
+        <v>7061107</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6191,19 +6148,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>16:20</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6218,19 +6170,19 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119838153</v>
+        <v>119837424</v>
       </c>
       <c r="B54" t="n">
         <v>91840</v>
@@ -6270,13 +6222,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562865</v>
+        <v>562774</v>
       </c>
       <c r="R54" t="n">
-        <v>7061107</v>
+        <v>7061178</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6306,11 +6258,6 @@
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6325,22 +6272,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119837899</v>
+        <v>119837084</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6349,25 +6296,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6377,13 +6324,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562848</v>
+        <v>562905</v>
       </c>
       <c r="R55" t="n">
-        <v>7061087</v>
+        <v>7061251</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6439,10 +6386,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119835763</v>
+        <v>119835638</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6455,21 +6402,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6479,13 +6426,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562859</v>
+        <v>562838</v>
       </c>
       <c r="R56" t="n">
-        <v>7061254</v>
+        <v>7061326</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6512,19 +6459,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6539,22 +6476,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119838625</v>
+        <v>119837216</v>
       </c>
       <c r="B57" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6567,37 +6504,37 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562899</v>
+        <v>562857</v>
       </c>
       <c r="R57" t="n">
-        <v>7061101</v>
+        <v>7061235</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6624,19 +6561,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z57" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB57" t="inlineStr">
-        <is>
-          <t>17:48</t>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6651,22 +6583,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119836424</v>
+        <v>119837383</v>
       </c>
       <c r="B58" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6675,45 +6607,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I58" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562902</v>
+        <v>562779</v>
       </c>
       <c r="R58" t="n">
-        <v>7061306</v>
+        <v>7061176</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6757,22 +6685,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119839228</v>
+        <v>119835531</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6785,37 +6713,37 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>563061</v>
+        <v>562827</v>
       </c>
       <c r="R59" t="n">
-        <v>7061025</v>
+        <v>7061302</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6842,24 +6770,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6874,22 +6787,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119838327</v>
+        <v>119840391</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6898,25 +6811,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6926,13 +6839,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562870</v>
+        <v>562861</v>
       </c>
       <c r="R60" t="n">
-        <v>7061110</v>
+        <v>7061439</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6976,22 +6889,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119838865</v>
+        <v>119837761</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -7000,25 +6913,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -7028,13 +6941,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562942</v>
+        <v>562816</v>
       </c>
       <c r="R61" t="n">
-        <v>7061029</v>
+        <v>7061089</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7078,22 +6991,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119836491</v>
+        <v>119840300</v>
       </c>
       <c r="B62" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7102,25 +7015,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7130,13 +7043,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>563040</v>
+        <v>562938</v>
       </c>
       <c r="R62" t="n">
-        <v>7061203</v>
+        <v>7061384</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7192,10 +7105,10 @@
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119839243</v>
+        <v>119835344</v>
       </c>
       <c r="B63" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7204,42 +7117,38 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I63" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>563074</v>
+        <v>562790</v>
       </c>
       <c r="R63" t="n">
-        <v>7061022</v>
+        <v>7061258</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7271,7 +7180,7 @@
       </c>
       <c r="Z63" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
@@ -7281,7 +7190,7 @@
       </c>
       <c r="AB63" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7308,10 +7217,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119838571</v>
+        <v>119840392</v>
       </c>
       <c r="B64" t="n">
-        <v>91884</v>
+        <v>57310</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7324,34 +7233,34 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>100109</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562856</v>
+        <v>562878</v>
       </c>
       <c r="R64" t="n">
-        <v>7061099</v>
+        <v>7061442</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7383,7 +7292,7 @@
       </c>
       <c r="Z64" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA64" t="inlineStr">
@@ -7393,7 +7302,12 @@
       </c>
       <c r="AB64" t="inlineStr">
         <is>
-          <t>17:44</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7420,10 +7334,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119835968</v>
+        <v>119836311</v>
       </c>
       <c r="B65" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7432,25 +7346,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7460,13 +7374,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562856</v>
+        <v>562972</v>
       </c>
       <c r="R65" t="n">
-        <v>7061341</v>
+        <v>7061274</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7496,6 +7410,11 @@
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7522,10 +7441,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119835259</v>
+        <v>119836491</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7534,25 +7453,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7562,10 +7481,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562815</v>
+        <v>563040</v>
       </c>
       <c r="R66" t="n">
-        <v>7061302</v>
+        <v>7061203</v>
       </c>
       <c r="S66" t="n">
         <v>15</v>
@@ -7624,10 +7543,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119835654</v>
+        <v>119838864</v>
       </c>
       <c r="B67" t="n">
-        <v>79636</v>
+        <v>78263</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7636,41 +7555,41 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6462</v>
+        <v>228912</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562838</v>
+        <v>562940</v>
       </c>
       <c r="R67" t="n">
-        <v>7061333</v>
+        <v>7061021</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7697,9 +7616,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7714,22 +7643,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119837999</v>
+        <v>119837181</v>
       </c>
       <c r="B68" t="n">
-        <v>79144</v>
+        <v>90527</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7738,25 +7667,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6453</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7766,13 +7695,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562848</v>
+        <v>562872</v>
       </c>
       <c r="R68" t="n">
-        <v>7061083</v>
+        <v>7061246</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7828,10 +7757,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119836373</v>
+        <v>119835516</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7840,42 +7769,38 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562910</v>
+        <v>562795</v>
       </c>
       <c r="R69" t="n">
-        <v>7061306</v>
+        <v>7061238</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7907,7 +7832,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7917,7 +7842,12 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7944,10 +7874,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119836533</v>
+        <v>119837298</v>
       </c>
       <c r="B70" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7956,45 +7886,41 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562927</v>
+        <v>562841</v>
       </c>
       <c r="R70" t="n">
-        <v>7061314</v>
+        <v>7061196</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -8021,19 +7947,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8048,19 +7964,19 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119837298</v>
+        <v>119840354</v>
       </c>
       <c r="B71" t="n">
         <v>78526</v>
@@ -8100,13 +8016,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562841</v>
+        <v>562893</v>
       </c>
       <c r="R71" t="n">
-        <v>7061196</v>
+        <v>7061427</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8150,19 +8066,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119835500</v>
+        <v>119835697</v>
       </c>
       <c r="B72" t="n">
         <v>79607</v>
@@ -8202,13 +8118,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562824</v>
+        <v>562826</v>
       </c>
       <c r="R72" t="n">
-        <v>7061319</v>
+        <v>7061341</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8264,10 +8180,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119837399</v>
+        <v>119835968</v>
       </c>
       <c r="B73" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8280,21 +8196,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8304,10 +8220,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562767</v>
+        <v>562856</v>
       </c>
       <c r="R73" t="n">
-        <v>7061188</v>
+        <v>7061341</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8366,7 +8282,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119840328</v>
+        <v>119835796</v>
       </c>
       <c r="B74" t="n">
         <v>79607</v>
@@ -8406,10 +8322,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562922</v>
+        <v>562830</v>
       </c>
       <c r="R74" t="n">
-        <v>7061399</v>
+        <v>7061321</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8468,10 +8384,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119838030</v>
+        <v>119837344</v>
       </c>
       <c r="B75" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8484,39 +8400,43 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M75" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P75" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562828</v>
+        <v>562829</v>
       </c>
       <c r="R75" t="n">
-        <v>7061089</v>
+        <v>7061182</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8548,7 +8468,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8558,7 +8478,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8585,10 +8505,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119836807</v>
+        <v>119835350</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>78263</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8601,21 +8521,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8625,13 +8545,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562926</v>
+        <v>562801</v>
       </c>
       <c r="R76" t="n">
-        <v>7061340</v>
+        <v>7061274</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8658,24 +8578,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8690,22 +8595,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119835344</v>
+        <v>119837858</v>
       </c>
       <c r="B77" t="n">
-        <v>90582</v>
+        <v>91840</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8714,25 +8619,25 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8742,10 +8647,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562790</v>
+        <v>562847</v>
       </c>
       <c r="R77" t="n">
-        <v>7061258</v>
+        <v>7061096</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8775,19 +8680,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8802,22 +8697,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119838967</v>
+        <v>119837856</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8826,42 +8721,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562990</v>
+        <v>562803</v>
       </c>
       <c r="R78" t="n">
-        <v>7061060</v>
+        <v>7061104</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8893,7 +8784,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8903,7 +8794,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8930,10 +8826,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119836632</v>
+        <v>119838030</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8942,45 +8838,46 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
+      <c r="M79" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562948</v>
+        <v>562828</v>
       </c>
       <c r="R79" t="n">
-        <v>7061323</v>
+        <v>7061089</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -9007,9 +8904,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z79" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB79" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -9024,22 +8931,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119838064</v>
+        <v>119836632</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9048,38 +8955,42 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P80" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562850</v>
+        <v>562948</v>
       </c>
       <c r="R80" t="n">
-        <v>7061098</v>
+        <v>7061323</v>
       </c>
       <c r="S80" t="n">
         <v>15</v>
@@ -9126,22 +9037,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119837858</v>
+        <v>119837074</v>
       </c>
       <c r="B81" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9150,38 +9061,42 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>562847</v>
+        <v>562940</v>
       </c>
       <c r="R81" t="n">
-        <v>7061096</v>
+        <v>7061272</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9211,9 +9126,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9228,22 +9153,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119836367</v>
+        <v>119836358</v>
       </c>
       <c r="B82" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9256,21 +9181,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9280,10 +9205,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>562983</v>
+        <v>562901</v>
       </c>
       <c r="R82" t="n">
-        <v>7061268</v>
+        <v>7061289</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9330,22 +9255,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119837181</v>
+        <v>119837366</v>
       </c>
       <c r="B83" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9354,25 +9279,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9382,13 +9307,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562872</v>
+        <v>562815</v>
       </c>
       <c r="R83" t="n">
-        <v>7061246</v>
+        <v>7061177</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9432,22 +9357,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119835495</v>
+        <v>119835654</v>
       </c>
       <c r="B84" t="n">
-        <v>79607</v>
+        <v>79636</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9456,25 +9381,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9484,10 +9409,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562822</v>
+        <v>562838</v>
       </c>
       <c r="R84" t="n">
-        <v>7061305</v>
+        <v>7061333</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9546,10 +9471,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119837344</v>
+        <v>119836952</v>
       </c>
       <c r="B85" t="n">
-        <v>57463</v>
+        <v>82305</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9562,43 +9487,34 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>103021</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>562829</v>
+        <v>562955</v>
       </c>
       <c r="R85" t="n">
-        <v>7061182</v>
+        <v>7061332</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9630,7 +9546,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9640,7 +9556,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9667,10 +9583,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119838957</v>
+        <v>119838327</v>
       </c>
       <c r="B86" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9679,25 +9595,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9707,13 +9623,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>562888</v>
+        <v>562870</v>
       </c>
       <c r="R86" t="n">
-        <v>7061052</v>
+        <v>7061110</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9757,22 +9673,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119837856</v>
+        <v>119837999</v>
       </c>
       <c r="B87" t="n">
-        <v>57310</v>
+        <v>79144</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9785,37 +9701,37 @@
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>6453</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>562803</v>
+        <v>562848</v>
       </c>
       <c r="R87" t="n">
-        <v>7061104</v>
+        <v>7061083</v>
       </c>
       <c r="S87" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9842,24 +9758,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9874,22 +9775,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119835108</v>
+        <v>119838179</v>
       </c>
       <c r="B88" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9902,21 +9803,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9926,10 +9827,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562802</v>
+        <v>562854</v>
       </c>
       <c r="R88" t="n">
-        <v>7061280</v>
+        <v>7061121</v>
       </c>
       <c r="S88" t="n">
         <v>15</v>
@@ -9988,10 +9889,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119835535</v>
+        <v>119838957</v>
       </c>
       <c r="B89" t="n">
-        <v>91840</v>
+        <v>91834</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -10000,25 +9901,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -10028,10 +9929,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>562795</v>
+        <v>562888</v>
       </c>
       <c r="R89" t="n">
-        <v>7061238</v>
+        <v>7061052</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10061,19 +9962,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10088,22 +9979,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119838872</v>
+        <v>119836533</v>
       </c>
       <c r="B90" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10112,41 +10003,45 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562893</v>
+        <v>562927</v>
       </c>
       <c r="R90" t="n">
-        <v>7061059</v>
+        <v>7061314</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10173,9 +10068,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10190,22 +10095,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119837543</v>
+        <v>119836512</v>
       </c>
       <c r="B91" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10214,38 +10119,42 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562745</v>
+        <v>562925</v>
       </c>
       <c r="R91" t="n">
-        <v>7061152</v>
+        <v>7061308</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10277,7 +10186,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10287,7 +10196,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10314,10 +10223,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119835796</v>
+        <v>119838885</v>
       </c>
       <c r="B92" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10326,38 +10235,42 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562830</v>
+        <v>562977</v>
       </c>
       <c r="R92" t="n">
-        <v>7061321</v>
+        <v>7061045</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10387,9 +10300,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10404,22 +10327,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119835631</v>
+        <v>119839212</v>
       </c>
       <c r="B93" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10432,34 +10355,34 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>562785</v>
+        <v>563063</v>
       </c>
       <c r="R93" t="n">
-        <v>7061238</v>
+        <v>7061037</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10491,7 +10414,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10501,12 +10424,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10533,10 +10451,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119836358</v>
+        <v>119838872</v>
       </c>
       <c r="B94" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10549,21 +10467,21 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10573,10 +10491,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562901</v>
+        <v>562893</v>
       </c>
       <c r="R94" t="n">
-        <v>7061289</v>
+        <v>7061059</v>
       </c>
       <c r="S94" t="n">
         <v>15</v>
@@ -10623,22 +10541,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119838709</v>
+        <v>119836284</v>
       </c>
       <c r="B95" t="n">
-        <v>91883</v>
+        <v>97907</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10647,41 +10565,45 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562892</v>
+        <v>562903</v>
       </c>
       <c r="R95" t="n">
-        <v>7061086</v>
+        <v>7061259</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10708,9 +10630,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10725,22 +10657,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119840373</v>
+        <v>119835763</v>
       </c>
       <c r="B96" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10753,21 +10685,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10777,10 +10709,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>562875</v>
+        <v>562859</v>
       </c>
       <c r="R96" t="n">
-        <v>7061433</v>
+        <v>7061254</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10810,9 +10742,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10827,19 +10769,19 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119840391</v>
+        <v>119835495</v>
       </c>
       <c r="B97" t="n">
         <v>79607</v>
@@ -10879,13 +10821,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562861</v>
+        <v>562822</v>
       </c>
       <c r="R97" t="n">
-        <v>7061439</v>
+        <v>7061305</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10941,10 +10883,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119836952</v>
+        <v>119836807</v>
       </c>
       <c r="B98" t="n">
-        <v>82305</v>
+        <v>57310</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10957,34 +10899,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562955</v>
+        <v>562926</v>
       </c>
       <c r="R98" t="n">
-        <v>7061332</v>
+        <v>7061340</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11016,7 +10958,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -11026,7 +10968,12 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11053,10 +11000,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119838606</v>
+        <v>119838242</v>
       </c>
       <c r="B99" t="n">
-        <v>78262</v>
+        <v>57310</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11069,21 +11016,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>100109</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11093,10 +11040,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562879</v>
+        <v>562827</v>
       </c>
       <c r="R99" t="n">
-        <v>7061091</v>
+        <v>7061123</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11126,9 +11073,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11143,19 +11105,19 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119835638</v>
+        <v>119835897</v>
       </c>
       <c r="B100" t="n">
         <v>79607</v>
@@ -11195,10 +11157,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562838</v>
+        <v>562851</v>
       </c>
       <c r="R100" t="n">
-        <v>7061326</v>
+        <v>7061350</v>
       </c>
       <c r="S100" t="n">
         <v>15</v>
@@ -11257,10 +11219,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119837761</v>
+        <v>119836629</v>
       </c>
       <c r="B101" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11273,34 +11235,39 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
+      <c r="M101" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562816</v>
+        <v>562935</v>
       </c>
       <c r="R101" t="n">
-        <v>7061089</v>
+        <v>7061315</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11330,9 +11297,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11347,19 +11324,19 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119837424</v>
+        <v>119837899</v>
       </c>
       <c r="B102" t="n">
         <v>91840</v>
@@ -11399,13 +11376,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562774</v>
+        <v>562848</v>
       </c>
       <c r="R102" t="n">
-        <v>7061178</v>
+        <v>7061087</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11449,22 +11426,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119836512</v>
+        <v>119839184</v>
       </c>
       <c r="B103" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11473,45 +11450,41 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562925</v>
+        <v>563009</v>
       </c>
       <c r="R103" t="n">
-        <v>7061308</v>
+        <v>7061040</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11538,19 +11511,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11565,22 +11528,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119839757</v>
+        <v>119839135</v>
       </c>
       <c r="B104" t="n">
-        <v>57326</v>
+        <v>78262</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11593,37 +11556,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>563104</v>
+        <v>562982</v>
       </c>
       <c r="R104" t="n">
-        <v>7061110</v>
+        <v>7061063</v>
       </c>
       <c r="S104" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11650,14 +11613,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11672,22 +11640,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119840392</v>
+        <v>119835108</v>
       </c>
       <c r="B105" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11700,21 +11668,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11724,13 +11692,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562878</v>
+        <v>562802</v>
       </c>
       <c r="R105" t="n">
-        <v>7061442</v>
+        <v>7061280</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11757,24 +11725,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11789,22 +11742,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119835516</v>
+        <v>119836367</v>
       </c>
       <c r="B106" t="n">
-        <v>57310</v>
+        <v>95455</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11817,21 +11770,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>100109</v>
+        <v>53</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11841,13 +11794,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562795</v>
+        <v>562983</v>
       </c>
       <c r="R106" t="n">
-        <v>7061238</v>
+        <v>7061268</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11874,24 +11827,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11906,22 +11844,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119838242</v>
+        <v>119838625</v>
       </c>
       <c r="B107" t="n">
-        <v>57310</v>
+        <v>91884</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11934,34 +11872,34 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>562827</v>
+        <v>562899</v>
       </c>
       <c r="R107" t="n">
-        <v>7061123</v>
+        <v>7061101</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -11993,7 +11931,7 @@
       </c>
       <c r="Z107" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
@@ -12003,12 +11941,7 @@
       </c>
       <c r="AB107" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12035,10 +11968,10 @@
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119837966</v>
+        <v>119836179</v>
       </c>
       <c r="B108" t="n">
-        <v>78171</v>
+        <v>78526</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12051,21 +11984,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12075,13 +12008,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>562845</v>
+        <v>562966</v>
       </c>
       <c r="R108" t="n">
-        <v>7061093</v>
+        <v>7061336</v>
       </c>
       <c r="S108" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12137,10 +12070,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119836521</v>
+        <v>119838865</v>
       </c>
       <c r="B109" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12149,25 +12082,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12177,10 +12110,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>562928</v>
+        <v>562942</v>
       </c>
       <c r="R109" t="n">
-        <v>7061305</v>
+        <v>7061029</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12239,10 +12172,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119838179</v>
+        <v>119839757</v>
       </c>
       <c r="B110" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12255,21 +12188,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12279,13 +12212,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>562854</v>
+        <v>563104</v>
       </c>
       <c r="R110" t="n">
-        <v>7061121</v>
+        <v>7061110</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12315,6 +12248,11 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC110" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12329,22 +12267,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119838102</v>
+        <v>119836424</v>
       </c>
       <c r="B111" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12353,31 +12291,30 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
@@ -12386,13 +12323,13 @@
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562863</v>
+        <v>562902</v>
       </c>
       <c r="R111" t="n">
-        <v>7061098</v>
+        <v>7061306</v>
       </c>
       <c r="S111" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12436,22 +12373,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119837084</v>
+        <v>119839243</v>
       </c>
       <c r="B112" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12460,41 +12397,45 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>562905</v>
+        <v>563074</v>
       </c>
       <c r="R112" t="n">
-        <v>7061251</v>
+        <v>7061022</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12521,9 +12462,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12538,22 +12489,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119837216</v>
+        <v>119837306</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12566,21 +12517,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12590,13 +12541,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562857</v>
+        <v>562793</v>
       </c>
       <c r="R113" t="n">
-        <v>7061235</v>
+        <v>7061251</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12630,7 +12581,7 @@
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12657,10 +12608,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119836896</v>
+        <v>119837299</v>
       </c>
       <c r="B114" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12673,21 +12624,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12697,10 +12648,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>562930</v>
+        <v>562843</v>
       </c>
       <c r="R114" t="n">
-        <v>7061333</v>
+        <v>7061204</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12730,14 +12681,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12752,19 +12708,19 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119839212</v>
+        <v>119835470</v>
       </c>
       <c r="B115" t="n">
         <v>78526</v>
@@ -12800,17 +12756,17 @@
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>563063</v>
+        <v>562839</v>
       </c>
       <c r="R115" t="n">
-        <v>7061037</v>
+        <v>7061260</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12837,19 +12793,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12864,22 +12810,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119835360</v>
+        <v>119835431</v>
       </c>
       <c r="B116" t="n">
-        <v>4766</v>
+        <v>79607</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12888,25 +12834,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>100299</v>
+        <v>6458</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12916,10 +12862,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562801</v>
+        <v>562853</v>
       </c>
       <c r="R116" t="n">
-        <v>7061292</v>
+        <v>7061293</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12954,11 +12900,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -12971,22 +12912,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119837193</v>
+        <v>119835742</v>
       </c>
       <c r="B117" t="n">
-        <v>57310</v>
+        <v>56522</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12995,25 +12936,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13023,10 +12964,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562864</v>
+        <v>562853</v>
       </c>
       <c r="R117" t="n">
-        <v>7061224</v>
+        <v>7061243</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13059,11 +13000,6 @@
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13090,10 +13026,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119837560</v>
+        <v>119836923</v>
       </c>
       <c r="B118" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13106,37 +13042,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562746</v>
+        <v>562958</v>
       </c>
       <c r="R118" t="n">
-        <v>7061142</v>
+        <v>7061345</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13163,9 +13099,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC118" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13180,22 +13131,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119837992</v>
+        <v>119835535</v>
       </c>
       <c r="B119" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13204,25 +13155,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13232,13 +13183,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>562845</v>
+        <v>562795</v>
       </c>
       <c r="R119" t="n">
-        <v>7061115</v>
+        <v>7061238</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13265,9 +13216,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13282,22 +13243,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119835531</v>
+        <v>119838571</v>
       </c>
       <c r="B120" t="n">
-        <v>79607</v>
+        <v>91884</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13310,37 +13271,37 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>5449</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562827</v>
+        <v>562856</v>
       </c>
       <c r="R120" t="n">
-        <v>7061302</v>
+        <v>7061099</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13367,9 +13328,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13384,19 +13355,19 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119835514</v>
+        <v>119837399</v>
       </c>
       <c r="B121" t="n">
         <v>79607</v>
@@ -13436,13 +13407,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562849</v>
+        <v>562767</v>
       </c>
       <c r="R121" t="n">
-        <v>7061244</v>
+        <v>7061188</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13486,22 +13457,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119835751</v>
+        <v>119835631</v>
       </c>
       <c r="B122" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13514,21 +13485,21 @@
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13538,10 +13509,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>562833</v>
+        <v>562785</v>
       </c>
       <c r="R122" t="n">
-        <v>7061339</v>
+        <v>7061238</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13571,9 +13542,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC122" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13588,22 +13574,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119836005</v>
+        <v>119836373</v>
       </c>
       <c r="B123" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13612,41 +13598,45 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>562898</v>
+        <v>562910</v>
       </c>
       <c r="R123" t="n">
-        <v>7061215</v>
+        <v>7061306</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13673,9 +13663,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13690,22 +13690,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119840300</v>
+        <v>119836521</v>
       </c>
       <c r="B124" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13714,25 +13714,25 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13742,13 +13742,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>562938</v>
+        <v>562928</v>
       </c>
       <c r="R124" t="n">
-        <v>7061384</v>
+        <v>7061305</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13792,12 +13792,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119838967</v>
+        <v>119837992</v>
       </c>
       <c r="B22" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,45 +2811,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562990</v>
+        <v>562845</v>
       </c>
       <c r="R22" t="n">
-        <v>7061060</v>
+        <v>7061115</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2876,19 +2872,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2903,12 +2889,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
@@ -3119,10 +3105,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119837992</v>
+        <v>119837543</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3135,21 +3121,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3159,13 +3145,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562845</v>
+        <v>562745</v>
       </c>
       <c r="R25" t="n">
-        <v>7061115</v>
+        <v>7061152</v>
       </c>
       <c r="S25" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3192,9 +3178,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3209,22 +3205,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119837543</v>
+        <v>119838967</v>
       </c>
       <c r="B26" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3233,38 +3229,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562745</v>
+        <v>562990</v>
       </c>
       <c r="R26" t="n">
-        <v>7061152</v>
+        <v>7061060</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3296,7 +3296,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3552,7 +3552,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119836896</v>
+        <v>119835805</v>
       </c>
       <c r="B29" t="n">
         <v>78526</v>
@@ -3592,13 +3592,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562930</v>
+        <v>562873</v>
       </c>
       <c r="R29" t="n">
-        <v>7061333</v>
+        <v>7061226</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3628,11 +3628,6 @@
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3647,19 +3642,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119835259</v>
+        <v>119836896</v>
       </c>
       <c r="B30" t="n">
         <v>78526</v>
@@ -3699,13 +3694,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562815</v>
+        <v>562930</v>
       </c>
       <c r="R30" t="n">
-        <v>7061302</v>
+        <v>7061333</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3735,6 +3730,11 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC30" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3761,7 +3761,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119835805</v>
+        <v>119835259</v>
       </c>
       <c r="B31" t="n">
         <v>78526</v>
@@ -3801,10 +3801,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562873</v>
+        <v>562815</v>
       </c>
       <c r="R31" t="n">
-        <v>7061226</v>
+        <v>7061302</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3851,12 +3851,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4291,10 +4291,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119837560</v>
+        <v>119836719</v>
       </c>
       <c r="B36" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4307,21 +4307,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4331,10 +4331,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562746</v>
+        <v>562937</v>
       </c>
       <c r="R36" t="n">
-        <v>7061142</v>
+        <v>7061312</v>
       </c>
       <c r="S36" t="n">
         <v>15</v>
@@ -4393,7 +4393,7 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119835500</v>
+        <v>119837560</v>
       </c>
       <c r="B37" t="n">
         <v>79607</v>
@@ -4433,10 +4433,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562824</v>
+        <v>562746</v>
       </c>
       <c r="R37" t="n">
-        <v>7061319</v>
+        <v>7061142</v>
       </c>
       <c r="S37" t="n">
         <v>15</v>
@@ -4483,22 +4483,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119837966</v>
+        <v>119835500</v>
       </c>
       <c r="B38" t="n">
-        <v>78171</v>
+        <v>79607</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4511,21 +4511,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>353</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4535,13 +4535,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562845</v>
+        <v>562824</v>
       </c>
       <c r="R38" t="n">
-        <v>7061093</v>
+        <v>7061319</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4597,10 +4597,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119836719</v>
+        <v>119839228</v>
       </c>
       <c r="B39" t="n">
-        <v>90562</v>
+        <v>57310</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4613,37 +4613,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562937</v>
+        <v>563061</v>
       </c>
       <c r="R39" t="n">
-        <v>7061312</v>
+        <v>7061025</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4670,9 +4670,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4687,22 +4702,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119839228</v>
+        <v>119835360</v>
       </c>
       <c r="B40" t="n">
-        <v>57310</v>
+        <v>4766</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4711,41 +4726,41 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100109</v>
+        <v>100299</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
       <c r="P40" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>563061</v>
+        <v>562801</v>
       </c>
       <c r="R40" t="n">
-        <v>7061025</v>
+        <v>7061292</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4772,24 +4787,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z40" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB40" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AC40" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4804,22 +4809,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119835360</v>
+        <v>119837966</v>
       </c>
       <c r="B41" t="n">
-        <v>4766</v>
+        <v>78171</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4828,25 +4833,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>100299</v>
+        <v>353</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4856,13 +4861,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562801</v>
+        <v>562845</v>
       </c>
       <c r="R41" t="n">
-        <v>7061292</v>
+        <v>7061093</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4892,11 +4897,6 @@
       <c r="AA41" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC41" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD41" t="b">
@@ -5157,10 +5157,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119837494</v>
+        <v>119837066</v>
       </c>
       <c r="B44" t="n">
-        <v>89633</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5169,25 +5169,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5197,13 +5197,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562773</v>
+        <v>562940</v>
       </c>
       <c r="R44" t="n">
-        <v>7061158</v>
+        <v>7061261</v>
       </c>
       <c r="S44" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5247,22 +5247,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119839227</v>
+        <v>119837494</v>
       </c>
       <c r="B45" t="n">
-        <v>91840</v>
+        <v>89633</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5271,25 +5271,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>4364</v>
+        <v>1962</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5299,13 +5299,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>563080</v>
+        <v>562773</v>
       </c>
       <c r="R45" t="n">
-        <v>7061030</v>
+        <v>7061158</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5667,10 +5667,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119836005</v>
+        <v>119839227</v>
       </c>
       <c r="B49" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5679,25 +5679,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,13 +5707,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562898</v>
+        <v>563080</v>
       </c>
       <c r="R49" t="n">
-        <v>7061215</v>
+        <v>7061030</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5757,22 +5757,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119837066</v>
+        <v>119836005</v>
       </c>
       <c r="B50" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5781,25 +5781,25 @@
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E50" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5809,10 +5809,10 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562940</v>
+        <v>562898</v>
       </c>
       <c r="R50" t="n">
-        <v>7061261</v>
+        <v>7061215</v>
       </c>
       <c r="S50" t="n">
         <v>15</v>
@@ -6386,10 +6386,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119835638</v>
+        <v>119837216</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6402,21 +6402,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6426,10 +6426,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562838</v>
+        <v>562857</v>
       </c>
       <c r="R56" t="n">
-        <v>7061326</v>
+        <v>7061235</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6462,6 +6462,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6488,7 +6493,7 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119837216</v>
+        <v>119837383</v>
       </c>
       <c r="B57" t="n">
         <v>78526</v>
@@ -6528,13 +6533,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562857</v>
+        <v>562779</v>
       </c>
       <c r="R57" t="n">
-        <v>7061235</v>
+        <v>7061176</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6564,11 +6569,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6595,10 +6595,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119837383</v>
+        <v>119835638</v>
       </c>
       <c r="B58" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6611,21 +6611,21 @@
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6635,13 +6635,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562779</v>
+        <v>562838</v>
       </c>
       <c r="R58" t="n">
-        <v>7061176</v>
+        <v>7061326</v>
       </c>
       <c r="S58" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -7334,10 +7334,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119836311</v>
+        <v>119835516</v>
       </c>
       <c r="B65" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7346,25 +7346,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7374,13 +7374,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562972</v>
+        <v>562795</v>
       </c>
       <c r="R65" t="n">
-        <v>7061274</v>
+        <v>7061238</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7407,14 +7407,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>Spridd i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7429,22 +7439,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119836491</v>
+        <v>119837181</v>
       </c>
       <c r="B66" t="n">
-        <v>97907</v>
+        <v>90527</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7453,25 +7463,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>5447</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7481,13 +7491,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>563040</v>
+        <v>562872</v>
       </c>
       <c r="R66" t="n">
-        <v>7061203</v>
+        <v>7061246</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7543,10 +7553,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119838864</v>
+        <v>119837298</v>
       </c>
       <c r="B67" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7559,37 +7569,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562940</v>
+        <v>562841</v>
       </c>
       <c r="R67" t="n">
-        <v>7061021</v>
+        <v>7061196</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7616,19 +7626,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>18:00</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7643,22 +7643,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119837181</v>
+        <v>119840354</v>
       </c>
       <c r="B68" t="n">
-        <v>90527</v>
+        <v>78526</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7667,25 +7667,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7695,10 +7695,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562872</v>
+        <v>562893</v>
       </c>
       <c r="R68" t="n">
-        <v>7061246</v>
+        <v>7061427</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7757,10 +7757,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119835516</v>
+        <v>119835697</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7773,21 +7773,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7797,10 +7797,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562795</v>
+        <v>562826</v>
       </c>
       <c r="R69" t="n">
-        <v>7061238</v>
+        <v>7061341</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7830,24 +7830,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7862,22 +7847,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119837298</v>
+        <v>119838864</v>
       </c>
       <c r="B70" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7890,37 +7875,37 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562841</v>
+        <v>562940</v>
       </c>
       <c r="R70" t="n">
-        <v>7061196</v>
+        <v>7061021</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7947,9 +7932,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7964,22 +7959,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119840354</v>
+        <v>119836311</v>
       </c>
       <c r="B71" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7988,25 +7983,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8016,13 +8011,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562893</v>
+        <v>562972</v>
       </c>
       <c r="R71" t="n">
-        <v>7061427</v>
+        <v>7061274</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8052,6 +8047,11 @@
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8078,10 +8078,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119835697</v>
+        <v>119836491</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8090,25 +8090,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8118,13 +8118,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562826</v>
+        <v>563040</v>
       </c>
       <c r="R72" t="n">
-        <v>7061341</v>
+        <v>7061203</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -9369,10 +9369,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119835654</v>
+        <v>119836952</v>
       </c>
       <c r="B84" t="n">
-        <v>79636</v>
+        <v>82305</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9381,41 +9381,41 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6462</v>
+        <v>1312</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562838</v>
+        <v>562955</v>
       </c>
       <c r="R84" t="n">
-        <v>7061333</v>
+        <v>7061332</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9442,9 +9442,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9459,22 +9469,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119836952</v>
+        <v>119838327</v>
       </c>
       <c r="B85" t="n">
-        <v>82305</v>
+        <v>91840</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9483,41 +9493,41 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>562955</v>
+        <v>562870</v>
       </c>
       <c r="R85" t="n">
-        <v>7061332</v>
+        <v>7061110</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9544,19 +9554,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>16:35</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>16:35</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9571,22 +9571,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119838327</v>
+        <v>119837999</v>
       </c>
       <c r="B86" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9595,25 +9595,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9623,10 +9623,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>562870</v>
+        <v>562848</v>
       </c>
       <c r="R86" t="n">
-        <v>7061110</v>
+        <v>7061083</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9673,22 +9673,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119837999</v>
+        <v>119835654</v>
       </c>
       <c r="B87" t="n">
-        <v>79144</v>
+        <v>79636</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9697,25 +9697,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6453</v>
+        <v>6462</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9725,10 +9725,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>562848</v>
+        <v>562838</v>
       </c>
       <c r="R87" t="n">
-        <v>7061083</v>
+        <v>7061333</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -10339,10 +10339,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119839212</v>
+        <v>119838872</v>
       </c>
       <c r="B93" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10355,37 +10355,37 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>563063</v>
+        <v>562893</v>
       </c>
       <c r="R93" t="n">
-        <v>7061037</v>
+        <v>7061059</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10412,19 +10412,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10439,22 +10429,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119838872</v>
+        <v>119836284</v>
       </c>
       <c r="B94" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10463,41 +10453,45 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562893</v>
+        <v>562903</v>
       </c>
       <c r="R94" t="n">
-        <v>7061059</v>
+        <v>7061259</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10524,9 +10518,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10541,22 +10545,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119836284</v>
+        <v>119839212</v>
       </c>
       <c r="B95" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10565,42 +10569,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562903</v>
+        <v>563063</v>
       </c>
       <c r="R95" t="n">
-        <v>7061259</v>
+        <v>7061037</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10632,7 +10632,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10642,7 +10642,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10781,10 +10781,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119835495</v>
+        <v>119838242</v>
       </c>
       <c r="B97" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10797,21 +10797,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10821,13 +10821,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562822</v>
+        <v>562827</v>
       </c>
       <c r="R97" t="n">
-        <v>7061305</v>
+        <v>7061123</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10854,9 +10854,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10871,22 +10886,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119836807</v>
+        <v>119835495</v>
       </c>
       <c r="B98" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10899,21 +10914,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10923,13 +10938,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562926</v>
+        <v>562822</v>
       </c>
       <c r="R98" t="n">
-        <v>7061340</v>
+        <v>7061305</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10956,24 +10971,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10988,19 +10988,19 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119838242</v>
+        <v>119836807</v>
       </c>
       <c r="B99" t="n">
         <v>57310</v>
@@ -11040,10 +11040,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562827</v>
+        <v>562926</v>
       </c>
       <c r="R99" t="n">
-        <v>7061123</v>
+        <v>7061340</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11075,7 +11075,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11085,7 +11085,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AC99" t="inlineStr">
@@ -11117,10 +11117,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119835897</v>
+        <v>119837899</v>
       </c>
       <c r="B100" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11129,25 +11129,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11157,13 +11157,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562851</v>
+        <v>562848</v>
       </c>
       <c r="R100" t="n">
-        <v>7061350</v>
+        <v>7061087</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11219,10 +11219,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119836629</v>
+        <v>119839184</v>
       </c>
       <c r="B101" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11231,46 +11231,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
-      <c r="M101" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562935</v>
+        <v>563009</v>
       </c>
       <c r="R101" t="n">
-        <v>7061315</v>
+        <v>7061040</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11297,19 +11292,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11324,22 +11309,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119837899</v>
+        <v>119835897</v>
       </c>
       <c r="B102" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11348,25 +11333,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11376,13 +11361,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562848</v>
+        <v>562851</v>
       </c>
       <c r="R102" t="n">
-        <v>7061087</v>
+        <v>7061350</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11438,10 +11423,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119839184</v>
+        <v>119839135</v>
       </c>
       <c r="B103" t="n">
-        <v>91840</v>
+        <v>78262</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11450,41 +11435,41 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>563009</v>
+        <v>562982</v>
       </c>
       <c r="R103" t="n">
-        <v>7061040</v>
+        <v>7061063</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11511,9 +11496,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11528,22 +11523,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119839135</v>
+        <v>119835108</v>
       </c>
       <c r="B104" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11556,37 +11551,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562982</v>
+        <v>562802</v>
       </c>
       <c r="R104" t="n">
-        <v>7061063</v>
+        <v>7061280</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11613,19 +11608,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>18:21</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11640,22 +11625,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119835108</v>
+        <v>119836629</v>
       </c>
       <c r="B105" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11668,37 +11653,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562802</v>
+        <v>562935</v>
       </c>
       <c r="R105" t="n">
-        <v>7061280</v>
+        <v>7061315</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11725,9 +11715,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11742,12 +11742,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -13255,10 +13255,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119838571</v>
+        <v>119837399</v>
       </c>
       <c r="B120" t="n">
-        <v>91884</v>
+        <v>79607</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13271,34 +13271,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562856</v>
+        <v>562767</v>
       </c>
       <c r="R120" t="n">
-        <v>7061099</v>
+        <v>7061188</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13328,19 +13328,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>17:44</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13355,22 +13345,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119837399</v>
+        <v>119835631</v>
       </c>
       <c r="B121" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13383,21 +13373,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13407,10 +13397,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562767</v>
+        <v>562785</v>
       </c>
       <c r="R121" t="n">
-        <v>7061188</v>
+        <v>7061238</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13440,9 +13430,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13457,22 +13462,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119835631</v>
+        <v>119836373</v>
       </c>
       <c r="B122" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13481,38 +13486,42 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>562785</v>
+        <v>562910</v>
       </c>
       <c r="R122" t="n">
-        <v>7061238</v>
+        <v>7061306</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13544,7 +13553,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13554,12 +13563,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13586,7 +13590,7 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119836373</v>
+        <v>119836521</v>
       </c>
       <c r="B123" t="n">
         <v>97907</v>
@@ -13619,24 +13623,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>562910</v>
+        <v>562928</v>
       </c>
       <c r="R123" t="n">
-        <v>7061306</v>
+        <v>7061305</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13663,19 +13663,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13690,22 +13680,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119836521</v>
+        <v>119838571</v>
       </c>
       <c r="B124" t="n">
-        <v>97907</v>
+        <v>91884</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13714,41 +13704,41 @@
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>562928</v>
+        <v>562856</v>
       </c>
       <c r="R124" t="n">
-        <v>7061305</v>
+        <v>7061099</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13775,9 +13765,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13792,12 +13792,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119837992</v>
+        <v>119838030</v>
       </c>
       <c r="B22" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2815,37 +2815,42 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562845</v>
+        <v>562828</v>
       </c>
       <c r="R22" t="n">
-        <v>7061115</v>
+        <v>7061089</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2872,9 +2877,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2889,19 +2904,19 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119835751</v>
+        <v>119835514</v>
       </c>
       <c r="B23" t="n">
         <v>79607</v>
@@ -2941,13 +2956,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562833</v>
+        <v>562849</v>
       </c>
       <c r="R23" t="n">
-        <v>7061339</v>
+        <v>7061244</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2991,19 +3006,19 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119840373</v>
+        <v>119837992</v>
       </c>
       <c r="B24" t="n">
         <v>79607</v>
@@ -3043,13 +3058,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562875</v>
+        <v>562845</v>
       </c>
       <c r="R24" t="n">
-        <v>7061433</v>
+        <v>7061115</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3093,22 +3108,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119837543</v>
+        <v>119838957</v>
       </c>
       <c r="B25" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3121,21 +3136,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3145,10 +3160,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562745</v>
+        <v>562888</v>
       </c>
       <c r="R25" t="n">
-        <v>7061152</v>
+        <v>7061052</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3178,19 +3193,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3205,22 +3210,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119838967</v>
+        <v>119838327</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3229,45 +3234,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562990</v>
+        <v>562870</v>
       </c>
       <c r="R26" t="n">
-        <v>7061060</v>
+        <v>7061110</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3294,19 +3295,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3321,22 +3312,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119835980</v>
+        <v>119837966</v>
       </c>
       <c r="B27" t="n">
-        <v>57310</v>
+        <v>78171</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3349,42 +3340,37 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562885</v>
+        <v>562845</v>
       </c>
       <c r="R27" t="n">
-        <v>7061225</v>
+        <v>7061093</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3411,19 +3397,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3438,22 +3414,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119838709</v>
+        <v>119837298</v>
       </c>
       <c r="B28" t="n">
-        <v>91883</v>
+        <v>78526</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3466,21 +3442,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>5448</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3490,10 +3466,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562892</v>
+        <v>562841</v>
       </c>
       <c r="R28" t="n">
-        <v>7061086</v>
+        <v>7061196</v>
       </c>
       <c r="S28" t="n">
         <v>15</v>
@@ -3552,10 +3528,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119835805</v>
+        <v>119838625</v>
       </c>
       <c r="B29" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3568,37 +3544,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562873</v>
+        <v>562899</v>
       </c>
       <c r="R29" t="n">
-        <v>7061226</v>
+        <v>7061101</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3625,9 +3601,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,19 +3628,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119836896</v>
+        <v>119835470</v>
       </c>
       <c r="B30" t="n">
         <v>78526</v>
@@ -3694,13 +3680,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562930</v>
+        <v>562839</v>
       </c>
       <c r="R30" t="n">
-        <v>7061333</v>
+        <v>7061260</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3730,11 +3716,6 @@
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC30" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3749,22 +3730,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119835259</v>
+        <v>119840328</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3777,21 +3758,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3801,13 +3782,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562815</v>
+        <v>562922</v>
       </c>
       <c r="R31" t="n">
-        <v>7061302</v>
+        <v>7061399</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3863,10 +3844,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119837193</v>
+        <v>119835742</v>
       </c>
       <c r="B32" t="n">
-        <v>57310</v>
+        <v>56522</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3875,25 +3856,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>100138</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3903,10 +3884,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562864</v>
+        <v>562853</v>
       </c>
       <c r="R32" t="n">
-        <v>7061224</v>
+        <v>7061243</v>
       </c>
       <c r="S32" t="n">
         <v>15</v>
@@ -3939,11 +3920,6 @@
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3970,10 +3946,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119837427</v>
+        <v>119836373</v>
       </c>
       <c r="B33" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3982,38 +3958,42 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562772</v>
+        <v>562910</v>
       </c>
       <c r="R33" t="n">
-        <v>7061165</v>
+        <v>7061306</v>
       </c>
       <c r="S33" t="n">
         <v>10</v>
@@ -4045,7 +4025,7 @@
       </c>
       <c r="Z33" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA33" t="inlineStr">
@@ -4055,7 +4035,7 @@
       </c>
       <c r="AB33" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4082,10 +4062,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119838859</v>
+        <v>119838967</v>
       </c>
       <c r="B34" t="n">
-        <v>91883</v>
+        <v>97907</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4094,38 +4074,42 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562897</v>
+        <v>562990</v>
       </c>
       <c r="R34" t="n">
-        <v>7061087</v>
+        <v>7061060</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4155,9 +4139,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z34" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB34" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4172,22 +4166,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119838102</v>
+        <v>119836521</v>
       </c>
       <c r="B35" t="n">
-        <v>57463</v>
+        <v>97907</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4196,46 +4190,41 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
-      <c r="M35" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P35" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562863</v>
+        <v>562928</v>
       </c>
       <c r="R35" t="n">
-        <v>7061098</v>
+        <v>7061305</v>
       </c>
       <c r="S35" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T35" t="inlineStr">
         <is>
@@ -4279,22 +4268,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119836719</v>
+        <v>119838153</v>
       </c>
       <c r="B36" t="n">
-        <v>90562</v>
+        <v>91840</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4303,25 +4292,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>1202</v>
+        <v>4364</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4331,13 +4320,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562937</v>
+        <v>562865</v>
       </c>
       <c r="R36" t="n">
-        <v>7061312</v>
+        <v>7061107</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4367,6 +4356,11 @@
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC36" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4381,22 +4375,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119837560</v>
+        <v>119837899</v>
       </c>
       <c r="B37" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4405,25 +4399,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4433,13 +4427,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562746</v>
+        <v>562848</v>
       </c>
       <c r="R37" t="n">
-        <v>7061142</v>
+        <v>7061087</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4483,22 +4477,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119835500</v>
+        <v>119837216</v>
       </c>
       <c r="B38" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4511,21 +4505,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4535,10 +4529,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562824</v>
+        <v>562857</v>
       </c>
       <c r="R38" t="n">
-        <v>7061319</v>
+        <v>7061235</v>
       </c>
       <c r="S38" t="n">
         <v>15</v>
@@ -4571,6 +4565,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4597,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119839228</v>
+        <v>119838709</v>
       </c>
       <c r="B39" t="n">
-        <v>57310</v>
+        <v>91883</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4613,37 +4612,37 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100109</v>
+        <v>5448</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563061</v>
+        <v>562892</v>
       </c>
       <c r="R39" t="n">
-        <v>7061025</v>
+        <v>7061086</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4670,24 +4669,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4702,22 +4686,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119835360</v>
+        <v>119837383</v>
       </c>
       <c r="B40" t="n">
-        <v>4766</v>
+        <v>78526</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4726,25 +4710,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4754,13 +4738,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562801</v>
+        <v>562779</v>
       </c>
       <c r="R40" t="n">
-        <v>7061292</v>
+        <v>7061176</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4790,11 +4774,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4821,10 +4800,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119837966</v>
+        <v>119838865</v>
       </c>
       <c r="B41" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4833,25 +4812,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4861,13 +4840,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562845</v>
+        <v>562942</v>
       </c>
       <c r="R41" t="n">
-        <v>7061093</v>
+        <v>7061029</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4911,22 +4890,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119840261</v>
+        <v>119836005</v>
       </c>
       <c r="B42" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4939,37 +4918,37 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
       <c r="P42" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563003</v>
+        <v>562898</v>
       </c>
       <c r="R42" t="n">
-        <v>7061318</v>
+        <v>7061215</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4996,24 +4975,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC42" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5028,22 +4992,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119837512</v>
+        <v>119835108</v>
       </c>
       <c r="B43" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5056,21 +5020,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5080,13 +5044,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562769</v>
+        <v>562802</v>
       </c>
       <c r="R43" t="n">
-        <v>7061157</v>
+        <v>7061280</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5113,24 +5077,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC43" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5145,22 +5094,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119837066</v>
+        <v>119835805</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5169,25 +5118,25 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5197,10 +5146,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562940</v>
+        <v>562873</v>
       </c>
       <c r="R44" t="n">
-        <v>7061261</v>
+        <v>7061226</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5259,10 +5208,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119837494</v>
+        <v>119838242</v>
       </c>
       <c r="B45" t="n">
-        <v>89633</v>
+        <v>57310</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5275,21 +5224,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5299,13 +5248,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562773</v>
+        <v>562827</v>
       </c>
       <c r="R45" t="n">
-        <v>7061158</v>
+        <v>7061123</v>
       </c>
       <c r="S45" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5332,9 +5281,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC45" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5349,22 +5313,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119838606</v>
+        <v>119837306</v>
       </c>
       <c r="B46" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5377,21 +5341,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5401,10 +5365,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562879</v>
+        <v>562793</v>
       </c>
       <c r="R46" t="n">
-        <v>7061091</v>
+        <v>7061251</v>
       </c>
       <c r="S46" t="n">
         <v>10</v>
@@ -5437,6 +5401,11 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC46" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5463,10 +5432,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119835514</v>
+        <v>119836952</v>
       </c>
       <c r="B47" t="n">
-        <v>79607</v>
+        <v>82305</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5479,37 +5448,37 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6458</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562849</v>
+        <v>562955</v>
       </c>
       <c r="R47" t="n">
-        <v>7061244</v>
+        <v>7061332</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5536,9 +5505,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5553,22 +5532,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119840328</v>
+        <v>119836629</v>
       </c>
       <c r="B48" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5581,34 +5560,39 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562922</v>
+        <v>562935</v>
       </c>
       <c r="R48" t="n">
-        <v>7061399</v>
+        <v>7061315</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5638,9 +5622,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5655,22 +5649,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119839227</v>
+        <v>119835631</v>
       </c>
       <c r="B49" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5679,25 +5673,25 @@
       </c>
       <c r="D49" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E49" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5707,10 +5701,10 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>563080</v>
+        <v>562785</v>
       </c>
       <c r="R49" t="n">
-        <v>7061030</v>
+        <v>7061238</v>
       </c>
       <c r="S49" t="n">
         <v>10</v>
@@ -5740,9 +5734,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5757,22 +5766,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119836005</v>
+        <v>119838571</v>
       </c>
       <c r="B50" t="n">
-        <v>78526</v>
+        <v>91884</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5785,37 +5794,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>5449</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562898</v>
+        <v>562856</v>
       </c>
       <c r="R50" t="n">
-        <v>7061215</v>
+        <v>7061099</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5842,9 +5851,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5859,22 +5878,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119838064</v>
+        <v>119836512</v>
       </c>
       <c r="B51" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5883,41 +5902,45 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562850</v>
+        <v>562925</v>
       </c>
       <c r="R51" t="n">
-        <v>7061098</v>
+        <v>7061308</v>
       </c>
       <c r="S51" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5944,9 +5967,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5961,22 +5994,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119838597</v>
+        <v>119840300</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5985,25 +6018,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6013,13 +6046,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562861</v>
+        <v>562938</v>
       </c>
       <c r="R52" t="n">
-        <v>7061099</v>
+        <v>7061384</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6063,19 +6096,19 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119838153</v>
+        <v>119839184</v>
       </c>
       <c r="B53" t="n">
         <v>91840</v>
@@ -6115,13 +6148,13 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562865</v>
+        <v>563009</v>
       </c>
       <c r="R53" t="n">
-        <v>7061107</v>
+        <v>7061040</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6151,11 +6184,6 @@
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6182,10 +6210,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119837424</v>
+        <v>119835431</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6194,25 +6222,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6222,10 +6250,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562774</v>
+        <v>562853</v>
       </c>
       <c r="R54" t="n">
-        <v>7061178</v>
+        <v>7061293</v>
       </c>
       <c r="S54" t="n">
         <v>15</v>
@@ -6284,10 +6312,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119837084</v>
+        <v>119837366</v>
       </c>
       <c r="B55" t="n">
-        <v>90582</v>
+        <v>78526</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6300,21 +6328,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6324,10 +6352,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562905</v>
+        <v>562815</v>
       </c>
       <c r="R55" t="n">
-        <v>7061251</v>
+        <v>7061177</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6374,22 +6402,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119837216</v>
+        <v>119840392</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6402,21 +6430,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6426,13 +6454,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562857</v>
+        <v>562878</v>
       </c>
       <c r="R56" t="n">
-        <v>7061235</v>
+        <v>7061442</v>
       </c>
       <c r="S56" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6459,14 +6487,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z56" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB56" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
       <c r="AC56" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6481,22 +6519,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119837383</v>
+        <v>119837193</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6509,21 +6547,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6533,13 +6571,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562779</v>
+        <v>562864</v>
       </c>
       <c r="R57" t="n">
-        <v>7061176</v>
+        <v>7061224</v>
       </c>
       <c r="S57" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6569,6 +6607,11 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6583,19 +6626,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119835638</v>
+        <v>119835500</v>
       </c>
       <c r="B58" t="n">
         <v>79607</v>
@@ -6635,10 +6678,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562838</v>
+        <v>562824</v>
       </c>
       <c r="R58" t="n">
-        <v>7061326</v>
+        <v>7061319</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6697,10 +6740,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119835531</v>
+        <v>119835968</v>
       </c>
       <c r="B59" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6713,21 +6756,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6737,13 +6780,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562827</v>
+        <v>562856</v>
       </c>
       <c r="R59" t="n">
-        <v>7061302</v>
+        <v>7061341</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6799,10 +6842,10 @@
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119840391</v>
+        <v>119837427</v>
       </c>
       <c r="B60" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6811,25 +6854,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6839,10 +6882,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562861</v>
+        <v>562772</v>
       </c>
       <c r="R60" t="n">
-        <v>7061439</v>
+        <v>7061165</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6872,9 +6915,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6889,22 +6942,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119837761</v>
+        <v>119838872</v>
       </c>
       <c r="B61" t="n">
-        <v>78526</v>
+        <v>91834</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6917,21 +6970,21 @@
         </is>
       </c>
       <c r="E61" t="n">
-        <v>6425</v>
+        <v>4362</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6941,13 +6994,13 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562816</v>
+        <v>562893</v>
       </c>
       <c r="R61" t="n">
-        <v>7061089</v>
+        <v>7061059</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7003,10 +7056,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119840300</v>
+        <v>119837074</v>
       </c>
       <c r="B62" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7015,38 +7068,42 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562938</v>
+        <v>562940</v>
       </c>
       <c r="R62" t="n">
-        <v>7061384</v>
+        <v>7061272</v>
       </c>
       <c r="S62" t="n">
         <v>10</v>
@@ -7076,9 +7133,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7093,22 +7160,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119835344</v>
+        <v>119835531</v>
       </c>
       <c r="B63" t="n">
-        <v>90582</v>
+        <v>79607</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7121,21 +7188,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7145,13 +7212,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562790</v>
+        <v>562827</v>
       </c>
       <c r="R63" t="n">
-        <v>7061258</v>
+        <v>7061302</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7178,19 +7245,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7205,22 +7262,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119840392</v>
+        <v>119837494</v>
       </c>
       <c r="B64" t="n">
-        <v>57310</v>
+        <v>89633</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7233,21 +7290,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7257,13 +7314,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562878</v>
+        <v>562773</v>
       </c>
       <c r="R64" t="n">
-        <v>7061442</v>
+        <v>7061158</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7290,24 +7347,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7322,19 +7364,19 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119835516</v>
+        <v>119839228</v>
       </c>
       <c r="B65" t="n">
         <v>57310</v>
@@ -7370,14 +7412,14 @@
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562795</v>
+        <v>563061</v>
       </c>
       <c r="R65" t="n">
-        <v>7061238</v>
+        <v>7061025</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7409,7 +7451,7 @@
       </c>
       <c r="Z65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA65" t="inlineStr">
@@ -7419,7 +7461,7 @@
       </c>
       <c r="AB65" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AC65" t="inlineStr">
@@ -7451,10 +7493,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119837181</v>
+        <v>119840391</v>
       </c>
       <c r="B66" t="n">
-        <v>90527</v>
+        <v>79607</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7463,25 +7505,25 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7491,10 +7533,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562872</v>
+        <v>562861</v>
       </c>
       <c r="R66" t="n">
-        <v>7061246</v>
+        <v>7061439</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7553,7 +7595,7 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119837298</v>
+        <v>119840354</v>
       </c>
       <c r="B67" t="n">
         <v>78526</v>
@@ -7593,13 +7635,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562841</v>
+        <v>562893</v>
       </c>
       <c r="R67" t="n">
-        <v>7061196</v>
+        <v>7061427</v>
       </c>
       <c r="S67" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7643,22 +7685,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119840354</v>
+        <v>119835360</v>
       </c>
       <c r="B68" t="n">
-        <v>78526</v>
+        <v>4766</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7667,25 +7709,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7695,13 +7737,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562893</v>
+        <v>562801</v>
       </c>
       <c r="R68" t="n">
-        <v>7061427</v>
+        <v>7061292</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7731,6 +7773,11 @@
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7757,10 +7804,10 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119835697</v>
+        <v>119835516</v>
       </c>
       <c r="B69" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7773,21 +7820,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7797,10 +7844,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562826</v>
+        <v>562795</v>
       </c>
       <c r="R69" t="n">
-        <v>7061341</v>
+        <v>7061238</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7830,9 +7877,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7847,22 +7909,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119838864</v>
+        <v>119837856</v>
       </c>
       <c r="B70" t="n">
-        <v>78263</v>
+        <v>57310</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7875,34 +7937,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562940</v>
+        <v>562803</v>
       </c>
       <c r="R70" t="n">
-        <v>7061021</v>
+        <v>7061104</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7934,7 +7996,7 @@
       </c>
       <c r="Z70" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
@@ -7944,7 +8006,12 @@
       </c>
       <c r="AB70" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7971,10 +8038,10 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119836311</v>
+        <v>119837512</v>
       </c>
       <c r="B71" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7983,25 +8050,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8011,13 +8078,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562972</v>
+        <v>562769</v>
       </c>
       <c r="R71" t="n">
-        <v>7061274</v>
+        <v>7061157</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8044,14 +8111,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AC71" t="inlineStr">
         <is>
-          <t>Spridd i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8066,22 +8143,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119836491</v>
+        <v>119837560</v>
       </c>
       <c r="B72" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8090,25 +8167,25 @@
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8118,10 +8195,10 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>563040</v>
+        <v>562746</v>
       </c>
       <c r="R72" t="n">
-        <v>7061203</v>
+        <v>7061142</v>
       </c>
       <c r="S72" t="n">
         <v>15</v>
@@ -8168,19 +8245,19 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119835968</v>
+        <v>119837543</v>
       </c>
       <c r="B73" t="n">
         <v>78526</v>
@@ -8220,10 +8297,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562856</v>
+        <v>562745</v>
       </c>
       <c r="R73" t="n">
-        <v>7061341</v>
+        <v>7061152</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8253,9 +8330,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8270,22 +8357,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119835796</v>
+        <v>119836719</v>
       </c>
       <c r="B74" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8298,21 +8385,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8322,13 +8409,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562830</v>
+        <v>562937</v>
       </c>
       <c r="R74" t="n">
-        <v>7061321</v>
+        <v>7061312</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8372,22 +8459,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119837344</v>
+        <v>119837424</v>
       </c>
       <c r="B75" t="n">
-        <v>57463</v>
+        <v>91840</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8396,50 +8483,41 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>103021</v>
+        <v>4364</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I75" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr"/>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562829</v>
+        <v>562774</v>
       </c>
       <c r="R75" t="n">
-        <v>7061182</v>
+        <v>7061178</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8466,19 +8544,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8493,22 +8561,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119835350</v>
+        <v>119839227</v>
       </c>
       <c r="B76" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8517,25 +8585,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8545,13 +8613,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562801</v>
+        <v>563080</v>
       </c>
       <c r="R76" t="n">
-        <v>7061274</v>
+        <v>7061030</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8595,22 +8663,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119837858</v>
+        <v>119836632</v>
       </c>
       <c r="B77" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8619,41 +8687,45 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562847</v>
+        <v>562948</v>
       </c>
       <c r="R77" t="n">
-        <v>7061096</v>
+        <v>7061323</v>
       </c>
       <c r="S77" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8697,22 +8769,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119837856</v>
+        <v>119836284</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8721,38 +8793,42 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562803</v>
+        <v>562903</v>
       </c>
       <c r="R78" t="n">
-        <v>7061104</v>
+        <v>7061259</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8784,7 +8860,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8794,12 +8870,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8826,10 +8897,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119838030</v>
+        <v>119836424</v>
       </c>
       <c r="B79" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8838,46 +8909,45 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr"/>
-      <c r="M79" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr">
+        <is>
+          <t>70</t>
         </is>
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562828</v>
+        <v>562902</v>
       </c>
       <c r="R79" t="n">
-        <v>7061089</v>
+        <v>7061306</v>
       </c>
       <c r="S79" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8904,19 +8974,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z79" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB79" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8931,22 +8991,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119836632</v>
+        <v>119838859</v>
       </c>
       <c r="B80" t="n">
-        <v>97907</v>
+        <v>91883</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8955,45 +9015,41 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I80" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562948</v>
+        <v>562897</v>
       </c>
       <c r="R80" t="n">
-        <v>7061323</v>
+        <v>7061087</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9037,22 +9093,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119837074</v>
+        <v>119839212</v>
       </c>
       <c r="B81" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9061,42 +9117,38 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>562940</v>
+        <v>563063</v>
       </c>
       <c r="R81" t="n">
-        <v>7061272</v>
+        <v>7061037</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9128,7 +9180,7 @@
       </c>
       <c r="Z81" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
@@ -9138,7 +9190,7 @@
       </c>
       <c r="AB81" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9165,10 +9217,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119836358</v>
+        <v>119837399</v>
       </c>
       <c r="B82" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9181,21 +9233,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9205,13 +9257,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>562901</v>
+        <v>562767</v>
       </c>
       <c r="R82" t="n">
-        <v>7061289</v>
+        <v>7061188</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9255,19 +9307,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119837366</v>
+        <v>119836179</v>
       </c>
       <c r="B83" t="n">
         <v>78526</v>
@@ -9307,13 +9359,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562815</v>
+        <v>562966</v>
       </c>
       <c r="R83" t="n">
-        <v>7061177</v>
+        <v>7061336</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9357,22 +9409,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119836952</v>
+        <v>119835638</v>
       </c>
       <c r="B84" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9385,37 +9437,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562955</v>
+        <v>562838</v>
       </c>
       <c r="R84" t="n">
-        <v>7061332</v>
+        <v>7061326</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9442,19 +9494,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>16:35</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>16:35</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9469,22 +9511,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119838327</v>
+        <v>119837299</v>
       </c>
       <c r="B85" t="n">
-        <v>91840</v>
+        <v>82305</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9493,25 +9535,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9521,13 +9563,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>562870</v>
+        <v>562843</v>
       </c>
       <c r="R85" t="n">
-        <v>7061110</v>
+        <v>7061204</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9554,9 +9596,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9571,22 +9623,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119837999</v>
+        <v>119838597</v>
       </c>
       <c r="B86" t="n">
-        <v>79144</v>
+        <v>91840</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9595,25 +9647,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6453</v>
+        <v>4364</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9623,10 +9675,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>562848</v>
+        <v>562861</v>
       </c>
       <c r="R86" t="n">
-        <v>7061083</v>
+        <v>7061099</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9673,22 +9725,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119835654</v>
+        <v>119836491</v>
       </c>
       <c r="B87" t="n">
-        <v>79636</v>
+        <v>97907</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9697,25 +9749,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6462</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9725,10 +9777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>562838</v>
+        <v>563040</v>
       </c>
       <c r="R87" t="n">
-        <v>7061333</v>
+        <v>7061203</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9787,10 +9839,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119838179</v>
+        <v>119835751</v>
       </c>
       <c r="B88" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9803,21 +9855,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9827,13 +9879,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562854</v>
+        <v>562833</v>
       </c>
       <c r="R88" t="n">
-        <v>7061121</v>
+        <v>7061339</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9877,22 +9929,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119838957</v>
+        <v>119837181</v>
       </c>
       <c r="B89" t="n">
-        <v>91834</v>
+        <v>90527</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9901,25 +9953,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>4362</v>
+        <v>5447</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9929,10 +9981,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>562888</v>
+        <v>562872</v>
       </c>
       <c r="R89" t="n">
-        <v>7061052</v>
+        <v>7061246</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9991,10 +10043,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119836533</v>
+        <v>119837761</v>
       </c>
       <c r="B90" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10003,42 +10055,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562927</v>
+        <v>562816</v>
       </c>
       <c r="R90" t="n">
-        <v>7061314</v>
+        <v>7061089</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10068,19 +10116,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10095,22 +10133,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119836512</v>
+        <v>119840373</v>
       </c>
       <c r="B91" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10119,42 +10157,38 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562925</v>
+        <v>562875</v>
       </c>
       <c r="R91" t="n">
-        <v>7061308</v>
+        <v>7061433</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10184,19 +10218,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10211,22 +10235,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119838885</v>
+        <v>119838179</v>
       </c>
       <c r="B92" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10235,45 +10259,41 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562977</v>
+        <v>562854</v>
       </c>
       <c r="R92" t="n">
-        <v>7061045</v>
+        <v>7061121</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10300,19 +10320,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10327,22 +10337,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119838872</v>
+        <v>119837858</v>
       </c>
       <c r="B93" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10351,25 +10361,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10379,13 +10389,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>562893</v>
+        <v>562847</v>
       </c>
       <c r="R93" t="n">
-        <v>7061059</v>
+        <v>7061096</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10441,10 +10451,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119836284</v>
+        <v>119836923</v>
       </c>
       <c r="B94" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10453,42 +10463,38 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562903</v>
+        <v>562958</v>
       </c>
       <c r="R94" t="n">
-        <v>7061259</v>
+        <v>7061345</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10520,7 +10526,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:32</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10530,7 +10536,12 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10557,10 +10568,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119839212</v>
+        <v>119836533</v>
       </c>
       <c r="B95" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10569,38 +10580,42 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>563063</v>
+        <v>562927</v>
       </c>
       <c r="R95" t="n">
-        <v>7061037</v>
+        <v>7061314</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10632,7 +10647,7 @@
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
@@ -10642,7 +10657,7 @@
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10669,10 +10684,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119835763</v>
+        <v>119838885</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10681,38 +10696,42 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>562859</v>
+        <v>562977</v>
       </c>
       <c r="R96" t="n">
-        <v>7061254</v>
+        <v>7061045</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10744,7 +10763,7 @@
       </c>
       <c r="Z96" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
@@ -10754,7 +10773,7 @@
       </c>
       <c r="AB96" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10781,10 +10800,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119838242</v>
+        <v>119835350</v>
       </c>
       <c r="B97" t="n">
-        <v>57310</v>
+        <v>78263</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10797,21 +10816,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10821,13 +10840,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562827</v>
+        <v>562801</v>
       </c>
       <c r="R97" t="n">
-        <v>7061123</v>
+        <v>7061274</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10854,24 +10873,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC97" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10886,22 +10890,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119835495</v>
+        <v>119839757</v>
       </c>
       <c r="B98" t="n">
-        <v>79607</v>
+        <v>57326</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10914,21 +10918,21 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10938,13 +10942,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562822</v>
+        <v>563104</v>
       </c>
       <c r="R98" t="n">
-        <v>7061305</v>
+        <v>7061110</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10974,6 +10978,11 @@
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC98" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11000,10 +11009,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119836807</v>
+        <v>119839135</v>
       </c>
       <c r="B99" t="n">
-        <v>57310</v>
+        <v>78262</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11016,34 +11025,34 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562926</v>
+        <v>562982</v>
       </c>
       <c r="R99" t="n">
-        <v>7061340</v>
+        <v>7061063</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11075,7 +11084,7 @@
       </c>
       <c r="Z99" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
@@ -11085,12 +11094,7 @@
       </c>
       <c r="AB99" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11117,10 +11121,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119837899</v>
+        <v>119835980</v>
       </c>
       <c r="B100" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11129,38 +11133,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562848</v>
+        <v>562885</v>
       </c>
       <c r="R100" t="n">
-        <v>7061087</v>
+        <v>7061225</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11190,9 +11199,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11207,22 +11226,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119839184</v>
+        <v>119835344</v>
       </c>
       <c r="B101" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11231,25 +11250,25 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11259,13 +11278,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>563009</v>
+        <v>562790</v>
       </c>
       <c r="R101" t="n">
-        <v>7061040</v>
+        <v>7061258</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11292,9 +11311,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11309,22 +11338,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119835897</v>
+        <v>119837066</v>
       </c>
       <c r="B102" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11333,25 +11362,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11361,10 +11390,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562851</v>
+        <v>562940</v>
       </c>
       <c r="R102" t="n">
-        <v>7061350</v>
+        <v>7061261</v>
       </c>
       <c r="S102" t="n">
         <v>15</v>
@@ -11411,22 +11440,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119839135</v>
+        <v>119838864</v>
       </c>
       <c r="B103" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11439,21 +11468,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11463,10 +11492,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562982</v>
+        <v>562940</v>
       </c>
       <c r="R103" t="n">
-        <v>7061063</v>
+        <v>7061021</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11498,7 +11527,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11508,7 +11537,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11535,10 +11564,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119835108</v>
+        <v>119840261</v>
       </c>
       <c r="B104" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11551,37 +11580,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562802</v>
+        <v>563003</v>
       </c>
       <c r="R104" t="n">
-        <v>7061280</v>
+        <v>7061318</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11608,9 +11637,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11625,22 +11669,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119836629</v>
+        <v>119837344</v>
       </c>
       <c r="B105" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11653,27 +11697,31 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="M105" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P105" t="inlineStr">
@@ -11682,10 +11730,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562935</v>
+        <v>562829</v>
       </c>
       <c r="R105" t="n">
-        <v>7061315</v>
+        <v>7061182</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11717,7 +11765,7 @@
       </c>
       <c r="Z105" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
@@ -11727,7 +11775,7 @@
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11754,10 +11802,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119836367</v>
+        <v>119836311</v>
       </c>
       <c r="B106" t="n">
-        <v>95455</v>
+        <v>97907</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11766,25 +11814,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11794,10 +11842,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562983</v>
+        <v>562972</v>
       </c>
       <c r="R106" t="n">
-        <v>7061268</v>
+        <v>7061274</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11830,6 +11878,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11856,10 +11909,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119838625</v>
+        <v>119837999</v>
       </c>
       <c r="B107" t="n">
-        <v>91884</v>
+        <v>79144</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11872,37 +11925,37 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>5449</v>
+        <v>6453</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>562899</v>
+        <v>562848</v>
       </c>
       <c r="R107" t="n">
-        <v>7061101</v>
+        <v>7061083</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11929,19 +11982,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11956,22 +11999,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119836179</v>
+        <v>119835697</v>
       </c>
       <c r="B108" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11984,21 +12027,21 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
@@ -12008,10 +12051,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>562966</v>
+        <v>562826</v>
       </c>
       <c r="R108" t="n">
-        <v>7061336</v>
+        <v>7061341</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12070,10 +12113,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119838865</v>
+        <v>119835763</v>
       </c>
       <c r="B109" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12082,25 +12125,25 @@
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12110,13 +12153,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>562942</v>
+        <v>562859</v>
       </c>
       <c r="R109" t="n">
-        <v>7061029</v>
+        <v>7061254</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12143,9 +12186,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12160,22 +12213,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119839757</v>
+        <v>119837084</v>
       </c>
       <c r="B110" t="n">
-        <v>57326</v>
+        <v>90582</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12188,21 +12241,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>5442</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12212,13 +12265,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>563104</v>
+        <v>562905</v>
       </c>
       <c r="R110" t="n">
-        <v>7061110</v>
+        <v>7061251</v>
       </c>
       <c r="S110" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12248,11 +12301,6 @@
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12279,10 +12327,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119836424</v>
+        <v>119838064</v>
       </c>
       <c r="B111" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12291,42 +12339,38 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562902</v>
+        <v>562850</v>
       </c>
       <c r="R111" t="n">
-        <v>7061306</v>
+        <v>7061098</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12373,22 +12417,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119839243</v>
+        <v>119835495</v>
       </c>
       <c r="B112" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12397,45 +12441,41 @@
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563074</v>
+        <v>562822</v>
       </c>
       <c r="R112" t="n">
-        <v>7061022</v>
+        <v>7061305</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12462,19 +12502,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12489,22 +12519,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119837306</v>
+        <v>119835259</v>
       </c>
       <c r="B113" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12517,21 +12547,21 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12541,13 +12571,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562793</v>
+        <v>562815</v>
       </c>
       <c r="R113" t="n">
-        <v>7061251</v>
+        <v>7061302</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12577,11 +12607,6 @@
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12608,10 +12633,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119837299</v>
+        <v>119836896</v>
       </c>
       <c r="B114" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12624,21 +12649,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12648,10 +12673,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>562843</v>
+        <v>562930</v>
       </c>
       <c r="R114" t="n">
-        <v>7061204</v>
+        <v>7061333</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12681,19 +12706,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>16:52</t>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12708,22 +12728,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119835470</v>
+        <v>119835654</v>
       </c>
       <c r="B115" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12732,25 +12752,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12760,10 +12780,10 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>562839</v>
+        <v>562838</v>
       </c>
       <c r="R115" t="n">
-        <v>7061260</v>
+        <v>7061333</v>
       </c>
       <c r="S115" t="n">
         <v>15</v>
@@ -12810,19 +12830,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119835431</v>
+        <v>119835796</v>
       </c>
       <c r="B116" t="n">
         <v>79607</v>
@@ -12862,13 +12882,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562853</v>
+        <v>562830</v>
       </c>
       <c r="R116" t="n">
-        <v>7061293</v>
+        <v>7061321</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12912,22 +12932,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119835742</v>
+        <v>119835897</v>
       </c>
       <c r="B117" t="n">
-        <v>56522</v>
+        <v>79607</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12936,25 +12956,25 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12964,10 +12984,10 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562853</v>
+        <v>562851</v>
       </c>
       <c r="R117" t="n">
-        <v>7061243</v>
+        <v>7061350</v>
       </c>
       <c r="S117" t="n">
         <v>15</v>
@@ -13014,22 +13034,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119836923</v>
+        <v>119838606</v>
       </c>
       <c r="B118" t="n">
-        <v>57310</v>
+        <v>78262</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13042,34 +13062,34 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562958</v>
+        <v>562879</v>
       </c>
       <c r="R118" t="n">
-        <v>7061345</v>
+        <v>7061091</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13099,24 +13119,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC118" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13131,22 +13136,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119835535</v>
+        <v>119836807</v>
       </c>
       <c r="B119" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13155,25 +13160,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13183,10 +13188,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>562795</v>
+        <v>562926</v>
       </c>
       <c r="R119" t="n">
-        <v>7061238</v>
+        <v>7061340</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13218,7 +13223,7 @@
       </c>
       <c r="Z119" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
@@ -13228,7 +13233,12 @@
       </c>
       <c r="AB119" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC119" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13255,10 +13265,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119837399</v>
+        <v>119835535</v>
       </c>
       <c r="B120" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13267,25 +13277,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13295,10 +13305,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562767</v>
+        <v>562795</v>
       </c>
       <c r="R120" t="n">
-        <v>7061188</v>
+        <v>7061238</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13328,9 +13338,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13345,22 +13365,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119835631</v>
+        <v>119838102</v>
       </c>
       <c r="B121" t="n">
-        <v>57310</v>
+        <v>57463</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13373,37 +13393,42 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562785</v>
+        <v>562863</v>
       </c>
       <c r="R121" t="n">
-        <v>7061238</v>
+        <v>7061098</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13430,24 +13455,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13462,19 +13472,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119836373</v>
+        <v>119839243</v>
       </c>
       <c r="B122" t="n">
         <v>97907</v>
@@ -13509,19 +13519,19 @@
       </c>
       <c r="I122" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>562910</v>
+        <v>563074</v>
       </c>
       <c r="R122" t="n">
-        <v>7061306</v>
+        <v>7061022</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13553,7 +13563,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13563,7 +13573,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>16:07</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13590,10 +13600,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119836521</v>
+        <v>119836367</v>
       </c>
       <c r="B123" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13602,25 +13612,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13630,10 +13640,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>562928</v>
+        <v>562983</v>
       </c>
       <c r="R123" t="n">
-        <v>7061305</v>
+        <v>7061268</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>
@@ -13680,22 +13690,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119838571</v>
+        <v>119836358</v>
       </c>
       <c r="B124" t="n">
-        <v>91884</v>
+        <v>78526</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13708,37 +13718,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>562856</v>
+        <v>562901</v>
       </c>
       <c r="R124" t="n">
-        <v>7061099</v>
+        <v>7061289</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13765,19 +13775,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>17:44</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13792,12 +13792,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -6006,10 +6006,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119840300</v>
+        <v>119839184</v>
       </c>
       <c r="B52" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6018,25 +6018,25 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6046,13 +6046,13 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562938</v>
+        <v>563009</v>
       </c>
       <c r="R52" t="n">
-        <v>7061384</v>
+        <v>7061040</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6108,10 +6108,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119839184</v>
+        <v>119835431</v>
       </c>
       <c r="B53" t="n">
-        <v>91840</v>
+        <v>79607</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6120,25 +6120,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6148,10 +6148,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>563009</v>
+        <v>562853</v>
       </c>
       <c r="R53" t="n">
-        <v>7061040</v>
+        <v>7061293</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6198,22 +6198,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119835431</v>
+        <v>119840300</v>
       </c>
       <c r="B54" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6226,21 +6226,21 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6250,13 +6250,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562853</v>
+        <v>562938</v>
       </c>
       <c r="R54" t="n">
-        <v>7061293</v>
+        <v>7061384</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6300,22 +6300,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119837366</v>
+        <v>119835500</v>
       </c>
       <c r="B55" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6328,21 +6328,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6352,10 +6352,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562815</v>
+        <v>562824</v>
       </c>
       <c r="R55" t="n">
-        <v>7061177</v>
+        <v>7061319</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6402,22 +6402,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119840392</v>
+        <v>119835968</v>
       </c>
       <c r="B56" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6430,21 +6430,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6454,10 +6454,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562878</v>
+        <v>562856</v>
       </c>
       <c r="R56" t="n">
-        <v>7061442</v>
+        <v>7061341</v>
       </c>
       <c r="S56" t="n">
         <v>10</v>
@@ -6487,24 +6487,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC56" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6519,22 +6504,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119837193</v>
+        <v>119837366</v>
       </c>
       <c r="B57" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6547,21 +6532,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6571,10 +6556,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562864</v>
+        <v>562815</v>
       </c>
       <c r="R57" t="n">
-        <v>7061224</v>
+        <v>7061177</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6607,11 +6592,6 @@
       <c r="AA57" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6638,10 +6618,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119835500</v>
+        <v>119837427</v>
       </c>
       <c r="B58" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6650,25 +6630,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6678,13 +6658,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562824</v>
+        <v>562772</v>
       </c>
       <c r="R58" t="n">
-        <v>7061319</v>
+        <v>7061165</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6711,9 +6691,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6728,22 +6718,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119835968</v>
+        <v>119840392</v>
       </c>
       <c r="B59" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6756,21 +6746,21 @@
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6780,10 +6770,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562856</v>
+        <v>562878</v>
       </c>
       <c r="R59" t="n">
-        <v>7061341</v>
+        <v>7061442</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6813,9 +6803,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6830,22 +6835,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119837427</v>
+        <v>119837193</v>
       </c>
       <c r="B60" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6854,25 +6859,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6882,13 +6887,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562772</v>
+        <v>562864</v>
       </c>
       <c r="R60" t="n">
-        <v>7061165</v>
+        <v>7061224</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6915,19 +6920,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>17:03</t>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6942,22 +6942,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119838872</v>
+        <v>119837074</v>
       </c>
       <c r="B61" t="n">
-        <v>91834</v>
+        <v>97907</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6966,41 +6966,45 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562893</v>
+        <v>562940</v>
       </c>
       <c r="R61" t="n">
-        <v>7061059</v>
+        <v>7061272</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7027,9 +7031,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7044,22 +7058,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119837074</v>
+        <v>119838872</v>
       </c>
       <c r="B62" t="n">
-        <v>97907</v>
+        <v>91834</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7068,45 +7082,41 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562940</v>
+        <v>562893</v>
       </c>
       <c r="R62" t="n">
-        <v>7061272</v>
+        <v>7061059</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7133,19 +7143,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>16:40</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7160,12 +7160,12 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
@@ -9319,10 +9319,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119836179</v>
+        <v>119835751</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9335,21 +9335,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9359,10 +9359,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562966</v>
+        <v>562833</v>
       </c>
       <c r="R83" t="n">
-        <v>7061336</v>
+        <v>7061339</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9421,10 +9421,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119835638</v>
+        <v>119836179</v>
       </c>
       <c r="B84" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9437,21 +9437,21 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9461,13 +9461,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562838</v>
+        <v>562966</v>
       </c>
       <c r="R84" t="n">
-        <v>7061326</v>
+        <v>7061336</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9523,10 +9523,10 @@
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119837299</v>
+        <v>119835638</v>
       </c>
       <c r="B85" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9539,21 +9539,21 @@
         </is>
       </c>
       <c r="E85" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9563,13 +9563,13 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>562843</v>
+        <v>562838</v>
       </c>
       <c r="R85" t="n">
-        <v>7061204</v>
+        <v>7061326</v>
       </c>
       <c r="S85" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9596,19 +9596,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z85" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB85" t="inlineStr">
-        <is>
-          <t>16:52</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9623,22 +9613,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119838597</v>
+        <v>119837299</v>
       </c>
       <c r="B86" t="n">
-        <v>91840</v>
+        <v>82305</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9647,25 +9637,25 @@
       </c>
       <c r="D86" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E86" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9675,13 +9665,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>562861</v>
+        <v>562843</v>
       </c>
       <c r="R86" t="n">
-        <v>7061099</v>
+        <v>7061204</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9708,9 +9698,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9725,22 +9725,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119836491</v>
+        <v>119838597</v>
       </c>
       <c r="B87" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9749,25 +9749,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9777,10 +9777,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>563040</v>
+        <v>562861</v>
       </c>
       <c r="R87" t="n">
-        <v>7061203</v>
+        <v>7061099</v>
       </c>
       <c r="S87" t="n">
         <v>15</v>
@@ -9827,22 +9827,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119835751</v>
+        <v>119836491</v>
       </c>
       <c r="B88" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9851,25 +9851,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9879,13 +9879,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562833</v>
+        <v>563040</v>
       </c>
       <c r="R88" t="n">
-        <v>7061339</v>
+        <v>7061203</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -10902,10 +10902,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119839757</v>
+        <v>119835980</v>
       </c>
       <c r="B98" t="n">
-        <v>57326</v>
+        <v>57310</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10918,16 +10918,16 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100049</v>
+        <v>100109</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -10936,19 +10936,24 @@
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
+      <c r="M98" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P98" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>563104</v>
+        <v>562885</v>
       </c>
       <c r="R98" t="n">
-        <v>7061110</v>
+        <v>7061225</v>
       </c>
       <c r="S98" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -10975,14 +10980,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC98" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10997,22 +11007,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119839135</v>
+        <v>119839757</v>
       </c>
       <c r="B99" t="n">
-        <v>78262</v>
+        <v>57326</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11025,37 +11035,37 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6446</v>
+        <v>100049</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
       <c r="P99" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562982</v>
+        <v>563104</v>
       </c>
       <c r="R99" t="n">
-        <v>7061063</v>
+        <v>7061110</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11082,19 +11092,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>18:21</t>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11109,22 +11114,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119835980</v>
+        <v>119837066</v>
       </c>
       <c r="B100" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11133,46 +11138,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562885</v>
+        <v>562940</v>
       </c>
       <c r="R100" t="n">
-        <v>7061225</v>
+        <v>7061261</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11199,19 +11199,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11226,22 +11216,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119835344</v>
+        <v>119838864</v>
       </c>
       <c r="B101" t="n">
-        <v>90582</v>
+        <v>78263</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11254,34 +11244,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>5442</v>
+        <v>228912</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562790</v>
+        <v>562940</v>
       </c>
       <c r="R101" t="n">
-        <v>7061258</v>
+        <v>7061021</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11313,7 +11303,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11323,7 +11313,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11350,10 +11340,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119837066</v>
+        <v>119835344</v>
       </c>
       <c r="B102" t="n">
-        <v>97907</v>
+        <v>90582</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11362,25 +11352,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>5442</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11390,13 +11380,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562940</v>
+        <v>562790</v>
       </c>
       <c r="R102" t="n">
-        <v>7061261</v>
+        <v>7061258</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11423,9 +11413,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11440,22 +11440,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119838864</v>
+        <v>119839135</v>
       </c>
       <c r="B103" t="n">
-        <v>78263</v>
+        <v>78262</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11468,21 +11468,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11492,10 +11492,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562940</v>
+        <v>562982</v>
       </c>
       <c r="R103" t="n">
-        <v>7061021</v>
+        <v>7061063</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11527,7 +11527,7 @@
       </c>
       <c r="Z103" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
@@ -11537,7 +11537,7 @@
       </c>
       <c r="AB103" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -12633,10 +12633,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119836896</v>
+        <v>119835654</v>
       </c>
       <c r="B114" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12645,25 +12645,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12673,13 +12673,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>562930</v>
+        <v>562838</v>
       </c>
       <c r="R114" t="n">
         <v>7061333</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12709,11 +12709,6 @@
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12740,10 +12735,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119835654</v>
+        <v>119835796</v>
       </c>
       <c r="B115" t="n">
-        <v>79636</v>
+        <v>79607</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12752,25 +12747,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12780,13 +12775,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>562838</v>
+        <v>562830</v>
       </c>
       <c r="R115" t="n">
-        <v>7061333</v>
+        <v>7061321</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12842,10 +12837,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119835796</v>
+        <v>119836896</v>
       </c>
       <c r="B116" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12858,21 +12853,21 @@
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12882,10 +12877,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562830</v>
+        <v>562930</v>
       </c>
       <c r="R116" t="n">
-        <v>7061321</v>
+        <v>7061333</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12918,6 +12913,11 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC116" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12944,10 +12944,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119835897</v>
+        <v>119838606</v>
       </c>
       <c r="B117" t="n">
-        <v>79607</v>
+        <v>78262</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12960,21 +12960,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -12984,13 +12984,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562851</v>
+        <v>562879</v>
       </c>
       <c r="R117" t="n">
-        <v>7061350</v>
+        <v>7061091</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13046,10 +13046,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119838606</v>
+        <v>119835897</v>
       </c>
       <c r="B118" t="n">
-        <v>78262</v>
+        <v>79607</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13062,21 +13062,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13086,13 +13086,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562879</v>
+        <v>562851</v>
       </c>
       <c r="R118" t="n">
-        <v>7061091</v>
+        <v>7061350</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119838030</v>
+        <v>119837424</v>
       </c>
       <c r="B22" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,46 +2811,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562828</v>
+        <v>562774</v>
       </c>
       <c r="R22" t="n">
-        <v>7061089</v>
+        <v>7061178</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2877,19 +2872,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2904,22 +2889,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119835514</v>
+        <v>119839227</v>
       </c>
       <c r="B23" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2928,25 +2913,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2956,13 +2941,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562849</v>
+        <v>563080</v>
       </c>
       <c r="R23" t="n">
-        <v>7061244</v>
+        <v>7061030</v>
       </c>
       <c r="S23" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -3006,22 +2991,22 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119837992</v>
+        <v>119837366</v>
       </c>
       <c r="B24" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3034,21 +3019,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3058,10 +3043,10 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562845</v>
+        <v>562815</v>
       </c>
       <c r="R24" t="n">
-        <v>7061115</v>
+        <v>7061177</v>
       </c>
       <c r="S24" t="n">
         <v>15</v>
@@ -3120,10 +3105,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119838957</v>
+        <v>119840328</v>
       </c>
       <c r="B25" t="n">
-        <v>91834</v>
+        <v>79607</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3136,21 +3121,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4362</v>
+        <v>6458</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3160,10 +3145,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562888</v>
+        <v>562922</v>
       </c>
       <c r="R25" t="n">
-        <v>7061052</v>
+        <v>7061399</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3222,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119838327</v>
+        <v>119837966</v>
       </c>
       <c r="B26" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,25 +3219,25 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3262,13 +3247,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562870</v>
+        <v>562845</v>
       </c>
       <c r="R26" t="n">
-        <v>7061110</v>
+        <v>7061093</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3312,22 +3297,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119837966</v>
+        <v>119838064</v>
       </c>
       <c r="B27" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,25 +3321,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3364,13 +3349,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562845</v>
+        <v>562850</v>
       </c>
       <c r="R27" t="n">
-        <v>7061093</v>
+        <v>7061098</v>
       </c>
       <c r="S27" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3426,10 +3411,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119837298</v>
+        <v>119837858</v>
       </c>
       <c r="B28" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3438,25 +3423,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,13 +3451,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562841</v>
+        <v>562847</v>
       </c>
       <c r="R28" t="n">
-        <v>7061196</v>
+        <v>7061096</v>
       </c>
       <c r="S28" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3516,22 +3501,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119838625</v>
+        <v>119839243</v>
       </c>
       <c r="B29" t="n">
-        <v>91884</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3540,38 +3525,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562899</v>
+        <v>563074</v>
       </c>
       <c r="R29" t="n">
-        <v>7061101</v>
+        <v>7061022</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3603,7 +3592,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3613,7 +3602,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3640,10 +3629,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119835470</v>
+        <v>119838885</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3652,41 +3641,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562839</v>
+        <v>562977</v>
       </c>
       <c r="R30" t="n">
-        <v>7061260</v>
+        <v>7061045</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3713,9 +3706,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3730,22 +3733,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119840328</v>
+        <v>119835805</v>
       </c>
       <c r="B31" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3758,21 +3761,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3782,13 +3785,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562922</v>
+        <v>562873</v>
       </c>
       <c r="R31" t="n">
-        <v>7061399</v>
+        <v>7061226</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3832,22 +3835,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119835742</v>
+        <v>119837761</v>
       </c>
       <c r="B32" t="n">
-        <v>56522</v>
+        <v>78526</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3856,25 +3859,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3884,13 +3887,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562853</v>
+        <v>562816</v>
       </c>
       <c r="R32" t="n">
-        <v>7061243</v>
+        <v>7061089</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3934,22 +3937,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119836373</v>
+        <v>119835742</v>
       </c>
       <c r="B33" t="n">
-        <v>97907</v>
+        <v>56522</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3958,45 +3961,41 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>220787</v>
+        <v>100138</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I33" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I33" t="inlineStr"/>
       <c r="P33" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562910</v>
+        <v>562853</v>
       </c>
       <c r="R33" t="n">
-        <v>7061306</v>
+        <v>7061243</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4023,19 +4022,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z33" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB33" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4050,22 +4039,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119838967</v>
+        <v>119835751</v>
       </c>
       <c r="B34" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4074,42 +4063,38 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I34" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I34" t="inlineStr"/>
       <c r="P34" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562990</v>
+        <v>562833</v>
       </c>
       <c r="R34" t="n">
-        <v>7061060</v>
+        <v>7061339</v>
       </c>
       <c r="S34" t="n">
         <v>10</v>
@@ -4139,19 +4124,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z34" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB34" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4166,22 +4141,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119836521</v>
+        <v>119835495</v>
       </c>
       <c r="B35" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4190,25 +4165,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4218,7 +4193,7 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562928</v>
+        <v>562822</v>
       </c>
       <c r="R35" t="n">
         <v>7061305</v>
@@ -4268,22 +4243,22 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119838153</v>
+        <v>119840392</v>
       </c>
       <c r="B36" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4292,25 +4267,25 @@
       </c>
       <c r="D36" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E36" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4320,10 +4295,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562865</v>
+        <v>562878</v>
       </c>
       <c r="R36" t="n">
-        <v>7061107</v>
+        <v>7061442</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4353,14 +4328,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z36" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB36" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
       <c r="AC36" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4375,22 +4360,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119837899</v>
+        <v>119835980</v>
       </c>
       <c r="B37" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4399,38 +4384,43 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562848</v>
+        <v>562885</v>
       </c>
       <c r="R37" t="n">
-        <v>7061087</v>
+        <v>7061225</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4460,9 +4450,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4477,22 +4477,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119837216</v>
+        <v>119838102</v>
       </c>
       <c r="B38" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,37 +4505,42 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562857</v>
+        <v>562863</v>
       </c>
       <c r="R38" t="n">
-        <v>7061235</v>
+        <v>7061098</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4565,11 +4570,6 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC38" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4596,10 +4596,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119838709</v>
+        <v>119836533</v>
       </c>
       <c r="B39" t="n">
-        <v>91883</v>
+        <v>97907</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4608,41 +4608,45 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>5448</v>
+        <v>220787</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562892</v>
+        <v>562927</v>
       </c>
       <c r="R39" t="n">
-        <v>7061086</v>
+        <v>7061314</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4669,9 +4673,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z39" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB39" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4686,22 +4700,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119837383</v>
+        <v>119837494</v>
       </c>
       <c r="B40" t="n">
-        <v>78526</v>
+        <v>89633</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4714,21 +4728,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>1962</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4738,10 +4752,10 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562779</v>
+        <v>562773</v>
       </c>
       <c r="R40" t="n">
-        <v>7061176</v>
+        <v>7061158</v>
       </c>
       <c r="S40" t="n">
         <v>20</v>
@@ -4800,7 +4814,7 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119838865</v>
+        <v>119839184</v>
       </c>
       <c r="B41" t="n">
         <v>91840</v>
@@ -4840,10 +4854,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562942</v>
+        <v>563009</v>
       </c>
       <c r="R41" t="n">
-        <v>7061029</v>
+        <v>7061040</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4890,19 +4904,19 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119836005</v>
+        <v>119837543</v>
       </c>
       <c r="B42" t="n">
         <v>78526</v>
@@ -4942,13 +4956,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562898</v>
+        <v>562745</v>
       </c>
       <c r="R42" t="n">
-        <v>7061215</v>
+        <v>7061152</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4975,9 +4989,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4992,22 +5016,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119835108</v>
+        <v>119836005</v>
       </c>
       <c r="B43" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5020,21 +5044,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5044,10 +5068,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562802</v>
+        <v>562898</v>
       </c>
       <c r="R43" t="n">
-        <v>7061280</v>
+        <v>7061215</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5106,10 +5130,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119835805</v>
+        <v>119839135</v>
       </c>
       <c r="B44" t="n">
-        <v>78526</v>
+        <v>78262</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5122,37 +5146,37 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562873</v>
+        <v>562982</v>
       </c>
       <c r="R44" t="n">
-        <v>7061226</v>
+        <v>7061063</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5179,9 +5203,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5196,22 +5230,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119838242</v>
+        <v>119835259</v>
       </c>
       <c r="B45" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5224,21 +5258,21 @@
         </is>
       </c>
       <c r="E45" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5248,13 +5282,13 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562827</v>
+        <v>562815</v>
       </c>
       <c r="R45" t="n">
-        <v>7061123</v>
+        <v>7061302</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5281,24 +5315,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC45" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5313,22 +5332,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119837306</v>
+        <v>119838872</v>
       </c>
       <c r="B46" t="n">
-        <v>79607</v>
+        <v>91834</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5341,21 +5360,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5365,13 +5384,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562793</v>
+        <v>562893</v>
       </c>
       <c r="R46" t="n">
-        <v>7061251</v>
+        <v>7061059</v>
       </c>
       <c r="S46" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5401,11 +5420,6 @@
       <c r="AA46" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC46" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD46" t="b">
@@ -5432,10 +5446,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119836952</v>
+        <v>119836512</v>
       </c>
       <c r="B47" t="n">
-        <v>82305</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5444,38 +5458,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562955</v>
+        <v>562925</v>
       </c>
       <c r="R47" t="n">
-        <v>7061332</v>
+        <v>7061308</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5507,7 +5525,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5517,7 +5535,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:35</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5544,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119836629</v>
+        <v>119836521</v>
       </c>
       <c r="B48" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5556,46 +5574,41 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
-      <c r="M48" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P48" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562935</v>
+        <v>562928</v>
       </c>
       <c r="R48" t="n">
-        <v>7061315</v>
+        <v>7061305</v>
       </c>
       <c r="S48" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5622,19 +5635,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z48" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB48" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5649,22 +5652,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119835631</v>
+        <v>119838709</v>
       </c>
       <c r="B49" t="n">
-        <v>57310</v>
+        <v>91883</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5677,21 +5680,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>100109</v>
+        <v>5448</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5701,13 +5704,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562785</v>
+        <v>562892</v>
       </c>
       <c r="R49" t="n">
-        <v>7061238</v>
+        <v>7061086</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5734,24 +5737,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z49" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB49" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC49" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5766,12 +5754,12 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
@@ -5890,10 +5878,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119836512</v>
+        <v>119838859</v>
       </c>
       <c r="B51" t="n">
-        <v>97907</v>
+        <v>91883</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5902,42 +5890,38 @@
       </c>
       <c r="D51" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E51" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I51" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562925</v>
+        <v>562897</v>
       </c>
       <c r="R51" t="n">
-        <v>7061308</v>
+        <v>7061087</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5967,19 +5951,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5994,22 +5968,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119839184</v>
+        <v>119835360</v>
       </c>
       <c r="B52" t="n">
-        <v>91840</v>
+        <v>4766</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -6022,21 +5996,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>4364</v>
+        <v>100299</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -6046,10 +6020,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>563009</v>
+        <v>562801</v>
       </c>
       <c r="R52" t="n">
-        <v>7061040</v>
+        <v>7061292</v>
       </c>
       <c r="S52" t="n">
         <v>15</v>
@@ -6082,6 +6056,11 @@
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6108,10 +6087,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119835431</v>
+        <v>119838864</v>
       </c>
       <c r="B53" t="n">
-        <v>79607</v>
+        <v>78263</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6124,37 +6103,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6458</v>
+        <v>228912</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562853</v>
+        <v>562940</v>
       </c>
       <c r="R53" t="n">
-        <v>7061293</v>
+        <v>7061021</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6181,9 +6160,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6198,22 +6187,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119840300</v>
+        <v>119836424</v>
       </c>
       <c r="B54" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6222,41 +6211,45 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562938</v>
+        <v>562902</v>
       </c>
       <c r="R54" t="n">
-        <v>7061384</v>
+        <v>7061306</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6300,19 +6293,19 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119835500</v>
+        <v>119837560</v>
       </c>
       <c r="B55" t="n">
         <v>79607</v>
@@ -6352,10 +6345,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562824</v>
+        <v>562746</v>
       </c>
       <c r="R55" t="n">
-        <v>7061319</v>
+        <v>7061142</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6402,22 +6395,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119835968</v>
+        <v>119835108</v>
       </c>
       <c r="B56" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6430,21 +6423,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6454,13 +6447,13 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562856</v>
+        <v>562802</v>
       </c>
       <c r="R56" t="n">
-        <v>7061341</v>
+        <v>7061280</v>
       </c>
       <c r="S56" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6504,19 +6497,19 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119837366</v>
+        <v>119837216</v>
       </c>
       <c r="B57" t="n">
         <v>78526</v>
@@ -6556,10 +6549,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562815</v>
+        <v>562857</v>
       </c>
       <c r="R57" t="n">
-        <v>7061177</v>
+        <v>7061235</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6594,6 +6587,11 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC57" t="inlineStr">
+        <is>
+          <t>På tall</t>
+        </is>
+      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6606,19 +6604,19 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119837427</v>
+        <v>119837899</v>
       </c>
       <c r="B58" t="n">
         <v>91840</v>
@@ -6658,10 +6656,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562772</v>
+        <v>562848</v>
       </c>
       <c r="R58" t="n">
-        <v>7061165</v>
+        <v>7061087</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6691,19 +6689,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6718,22 +6706,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119840392</v>
+        <v>119838153</v>
       </c>
       <c r="B59" t="n">
-        <v>57310</v>
+        <v>91840</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6742,25 +6730,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6770,10 +6758,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562878</v>
+        <v>562865</v>
       </c>
       <c r="R59" t="n">
-        <v>7061442</v>
+        <v>7061107</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6803,24 +6791,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
       <c r="AC59" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6835,12 +6813,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -6954,10 +6932,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119837074</v>
+        <v>119838327</v>
       </c>
       <c r="B61" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6966,45 +6944,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562940</v>
+        <v>562870</v>
       </c>
       <c r="R61" t="n">
-        <v>7061272</v>
+        <v>7061110</v>
       </c>
       <c r="S61" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7031,19 +7005,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>16:40</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7058,22 +7022,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119838872</v>
+        <v>119838597</v>
       </c>
       <c r="B62" t="n">
-        <v>91834</v>
+        <v>91840</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7082,25 +7046,25 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4362</v>
+        <v>4364</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7110,10 +7074,10 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562893</v>
+        <v>562861</v>
       </c>
       <c r="R62" t="n">
-        <v>7061059</v>
+        <v>7061099</v>
       </c>
       <c r="S62" t="n">
         <v>15</v>
@@ -7160,22 +7124,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119835531</v>
+        <v>119838865</v>
       </c>
       <c r="B63" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7184,25 +7148,25 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7212,10 +7176,10 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562827</v>
+        <v>562942</v>
       </c>
       <c r="R63" t="n">
-        <v>7061302</v>
+        <v>7061029</v>
       </c>
       <c r="S63" t="n">
         <v>15</v>
@@ -7262,22 +7226,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119837494</v>
+        <v>119838625</v>
       </c>
       <c r="B64" t="n">
-        <v>89633</v>
+        <v>91884</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7290,37 +7254,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>1962</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562773</v>
+        <v>562899</v>
       </c>
       <c r="R64" t="n">
-        <v>7061158</v>
+        <v>7061101</v>
       </c>
       <c r="S64" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7347,9 +7311,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7364,22 +7338,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119839228</v>
+        <v>119835431</v>
       </c>
       <c r="B65" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7392,37 +7366,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>563061</v>
+        <v>562853</v>
       </c>
       <c r="R65" t="n">
-        <v>7061025</v>
+        <v>7061293</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7449,24 +7423,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7481,22 +7440,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119840391</v>
+        <v>119838179</v>
       </c>
       <c r="B66" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7509,21 +7468,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7533,13 +7492,13 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562861</v>
+        <v>562854</v>
       </c>
       <c r="R66" t="n">
-        <v>7061439</v>
+        <v>7061121</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7583,22 +7542,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119840354</v>
+        <v>119838242</v>
       </c>
       <c r="B67" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7611,21 +7570,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7635,10 +7594,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562893</v>
+        <v>562827</v>
       </c>
       <c r="R67" t="n">
-        <v>7061427</v>
+        <v>7061123</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7668,9 +7627,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7685,22 +7659,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119835360</v>
+        <v>119837299</v>
       </c>
       <c r="B68" t="n">
-        <v>4766</v>
+        <v>82305</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7709,25 +7683,25 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100299</v>
+        <v>1312</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7737,13 +7711,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562801</v>
+        <v>562843</v>
       </c>
       <c r="R68" t="n">
-        <v>7061292</v>
+        <v>7061204</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7770,14 +7744,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7792,22 +7771,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119835516</v>
+        <v>119836373</v>
       </c>
       <c r="B69" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7816,38 +7795,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562795</v>
+        <v>562910</v>
       </c>
       <c r="R69" t="n">
-        <v>7061238</v>
+        <v>7061306</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7879,7 +7862,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7889,12 +7872,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7921,10 +7899,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119837856</v>
+        <v>119835796</v>
       </c>
       <c r="B70" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7937,34 +7915,34 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562803</v>
+        <v>562830</v>
       </c>
       <c r="R70" t="n">
-        <v>7061104</v>
+        <v>7061321</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -7994,24 +7972,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC70" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8026,22 +7989,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119837512</v>
+        <v>119835344</v>
       </c>
       <c r="B71" t="n">
-        <v>57310</v>
+        <v>90582</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8054,21 +8017,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8078,10 +8041,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562769</v>
+        <v>562790</v>
       </c>
       <c r="R71" t="n">
-        <v>7061157</v>
+        <v>7061258</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8113,7 +8076,7 @@
       </c>
       <c r="Z71" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
@@ -8123,12 +8086,7 @@
       </c>
       <c r="AB71" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8155,7 +8113,7 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119837560</v>
+        <v>119840391</v>
       </c>
       <c r="B72" t="n">
         <v>79607</v>
@@ -8195,13 +8153,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562746</v>
+        <v>562861</v>
       </c>
       <c r="R72" t="n">
-        <v>7061142</v>
+        <v>7061439</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8245,22 +8203,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119837543</v>
+        <v>119835638</v>
       </c>
       <c r="B73" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8273,21 +8231,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8297,13 +8255,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562745</v>
+        <v>562838</v>
       </c>
       <c r="R73" t="n">
-        <v>7061152</v>
+        <v>7061326</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8330,19 +8288,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8357,22 +8305,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119836719</v>
+        <v>119837306</v>
       </c>
       <c r="B74" t="n">
-        <v>90562</v>
+        <v>79607</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8385,21 +8333,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8409,13 +8357,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562937</v>
+        <v>562793</v>
       </c>
       <c r="R74" t="n">
-        <v>7061312</v>
+        <v>7061251</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8445,6 +8393,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8459,22 +8412,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119837424</v>
+        <v>119837999</v>
       </c>
       <c r="B75" t="n">
-        <v>91840</v>
+        <v>79144</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8483,25 +8436,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>4364</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8511,10 +8464,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562774</v>
+        <v>562848</v>
       </c>
       <c r="R75" t="n">
-        <v>7061178</v>
+        <v>7061083</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8561,22 +8514,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119839227</v>
+        <v>119836632</v>
       </c>
       <c r="B76" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8585,41 +8538,45 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P76" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>563080</v>
+        <v>562948</v>
       </c>
       <c r="R76" t="n">
-        <v>7061030</v>
+        <v>7061323</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8663,22 +8620,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119836632</v>
+        <v>119836629</v>
       </c>
       <c r="B77" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8687,30 +8644,31 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P77" t="inlineStr">
@@ -8719,13 +8677,13 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562948</v>
+        <v>562935</v>
       </c>
       <c r="R77" t="n">
-        <v>7061323</v>
+        <v>7061315</v>
       </c>
       <c r="S77" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T77" t="inlineStr">
         <is>
@@ -8752,9 +8710,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8769,22 +8737,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119836284</v>
+        <v>119836807</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8793,42 +8761,38 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562903</v>
+        <v>562926</v>
       </c>
       <c r="R78" t="n">
-        <v>7061259</v>
+        <v>7061340</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8860,7 +8824,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8870,7 +8834,12 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8897,10 +8866,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119836424</v>
+        <v>119835531</v>
       </c>
       <c r="B79" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8909,42 +8878,38 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I79" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I79" t="inlineStr"/>
       <c r="P79" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562902</v>
+        <v>562827</v>
       </c>
       <c r="R79" t="n">
-        <v>7061306</v>
+        <v>7061302</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8991,22 +8956,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119838859</v>
+        <v>119837084</v>
       </c>
       <c r="B80" t="n">
-        <v>91883</v>
+        <v>90582</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -9019,21 +8984,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9043,13 +9008,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562897</v>
+        <v>562905</v>
       </c>
       <c r="R80" t="n">
-        <v>7061087</v>
+        <v>7061251</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9105,10 +9070,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119839212</v>
+        <v>119839757</v>
       </c>
       <c r="B81" t="n">
-        <v>78526</v>
+        <v>57326</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9121,37 +9086,37 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6425</v>
+        <v>100049</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563063</v>
+        <v>563104</v>
       </c>
       <c r="R81" t="n">
-        <v>7061037</v>
+        <v>7061110</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9178,19 +9143,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>18:26</t>
+      <c r="AC81" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9205,22 +9165,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119837399</v>
+        <v>119836719</v>
       </c>
       <c r="B82" t="n">
-        <v>79607</v>
+        <v>90562</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9233,21 +9193,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9257,13 +9217,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>562767</v>
+        <v>562937</v>
       </c>
       <c r="R82" t="n">
-        <v>7061188</v>
+        <v>7061312</v>
       </c>
       <c r="S82" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9307,22 +9267,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119835751</v>
+        <v>119836358</v>
       </c>
       <c r="B83" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9335,21 +9295,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9359,13 +9319,13 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562833</v>
+        <v>562901</v>
       </c>
       <c r="R83" t="n">
-        <v>7061339</v>
+        <v>7061289</v>
       </c>
       <c r="S83" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9409,22 +9369,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119836179</v>
+        <v>119835535</v>
       </c>
       <c r="B84" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9433,25 +9393,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9461,10 +9421,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562966</v>
+        <v>562795</v>
       </c>
       <c r="R84" t="n">
-        <v>7061336</v>
+        <v>7061238</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9494,9 +9454,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9511,22 +9481,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119835638</v>
+        <v>119836491</v>
       </c>
       <c r="B85" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9535,25 +9505,25 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I85" t="inlineStr"/>
@@ -9563,10 +9533,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>562838</v>
+        <v>563040</v>
       </c>
       <c r="R85" t="n">
-        <v>7061326</v>
+        <v>7061203</v>
       </c>
       <c r="S85" t="n">
         <v>15</v>
@@ -9625,10 +9595,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119837299</v>
+        <v>119837992</v>
       </c>
       <c r="B86" t="n">
-        <v>82305</v>
+        <v>79607</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9641,21 +9611,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9665,13 +9635,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>562843</v>
+        <v>562845</v>
       </c>
       <c r="R86" t="n">
-        <v>7061204</v>
+        <v>7061115</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9698,19 +9668,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>16:52</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9725,22 +9685,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119838597</v>
+        <v>119836923</v>
       </c>
       <c r="B87" t="n">
-        <v>91840</v>
+        <v>57310</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9749,41 +9709,41 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>562861</v>
+        <v>562958</v>
       </c>
       <c r="R87" t="n">
-        <v>7061099</v>
+        <v>7061345</v>
       </c>
       <c r="S87" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T87" t="inlineStr">
         <is>
@@ -9810,9 +9770,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9827,22 +9802,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119836491</v>
+        <v>119838606</v>
       </c>
       <c r="B88" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9851,25 +9826,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9879,13 +9854,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>563040</v>
+        <v>562879</v>
       </c>
       <c r="R88" t="n">
-        <v>7061203</v>
+        <v>7061091</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9941,10 +9916,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119837181</v>
+        <v>119835631</v>
       </c>
       <c r="B89" t="n">
-        <v>90527</v>
+        <v>57310</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9953,25 +9928,25 @@
       </c>
       <c r="D89" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9981,10 +9956,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>562872</v>
+        <v>562785</v>
       </c>
       <c r="R89" t="n">
-        <v>7061246</v>
+        <v>7061238</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10014,9 +9989,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10031,22 +10021,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119837761</v>
+        <v>119837066</v>
       </c>
       <c r="B90" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10055,25 +10045,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10083,13 +10073,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562816</v>
+        <v>562940</v>
       </c>
       <c r="R90" t="n">
-        <v>7061089</v>
+        <v>7061261</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10133,22 +10123,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119840373</v>
+        <v>119837298</v>
       </c>
       <c r="B91" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10161,21 +10151,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10185,13 +10175,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562875</v>
+        <v>562841</v>
       </c>
       <c r="R91" t="n">
-        <v>7061433</v>
+        <v>7061196</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10235,22 +10225,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119838179</v>
+        <v>119837399</v>
       </c>
       <c r="B92" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10263,21 +10253,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10287,13 +10277,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562854</v>
+        <v>562767</v>
       </c>
       <c r="R92" t="n">
-        <v>7061121</v>
+        <v>7061188</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10337,19 +10327,19 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119837858</v>
+        <v>119837427</v>
       </c>
       <c r="B93" t="n">
         <v>91840</v>
@@ -10389,10 +10379,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>562847</v>
+        <v>562772</v>
       </c>
       <c r="R93" t="n">
-        <v>7061096</v>
+        <v>7061165</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10422,9 +10412,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10439,22 +10439,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119836923</v>
+        <v>119835500</v>
       </c>
       <c r="B94" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10467,37 +10467,37 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562958</v>
+        <v>562824</v>
       </c>
       <c r="R94" t="n">
-        <v>7061345</v>
+        <v>7061319</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10524,24 +10524,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10556,22 +10541,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119836533</v>
+        <v>119840373</v>
       </c>
       <c r="B95" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10580,42 +10565,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562927</v>
+        <v>562875</v>
       </c>
       <c r="R95" t="n">
-        <v>7061314</v>
+        <v>7061433</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10645,19 +10626,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10672,22 +10643,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119838885</v>
+        <v>119836179</v>
       </c>
       <c r="B96" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10696,42 +10667,38 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>562977</v>
+        <v>562966</v>
       </c>
       <c r="R96" t="n">
-        <v>7061045</v>
+        <v>7061336</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10761,19 +10728,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10788,22 +10745,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119835350</v>
+        <v>119835968</v>
       </c>
       <c r="B97" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10816,21 +10773,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10840,13 +10797,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562801</v>
+        <v>562856</v>
       </c>
       <c r="R97" t="n">
-        <v>7061274</v>
+        <v>7061341</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10890,22 +10847,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119835980</v>
+        <v>119836952</v>
       </c>
       <c r="B98" t="n">
-        <v>57310</v>
+        <v>82305</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10918,39 +10875,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562885</v>
+        <v>562955</v>
       </c>
       <c r="R98" t="n">
-        <v>7061225</v>
+        <v>7061332</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10982,7 +10934,7 @@
       </c>
       <c r="Z98" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
@@ -10992,7 +10944,7 @@
       </c>
       <c r="AB98" t="inlineStr">
         <is>
-          <t>15:46</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11019,10 +10971,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119839757</v>
+        <v>119840300</v>
       </c>
       <c r="B99" t="n">
-        <v>57326</v>
+        <v>78526</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11035,21 +10987,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11059,13 +11011,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>563104</v>
+        <v>562938</v>
       </c>
       <c r="R99" t="n">
-        <v>7061110</v>
+        <v>7061384</v>
       </c>
       <c r="S99" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11095,11 +11047,6 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11126,10 +11073,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119837066</v>
+        <v>119835516</v>
       </c>
       <c r="B100" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11138,25 +11085,25 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11166,13 +11113,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562940</v>
+        <v>562795</v>
       </c>
       <c r="R100" t="n">
-        <v>7061261</v>
+        <v>7061238</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11199,9 +11146,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11216,22 +11178,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119838864</v>
+        <v>119837074</v>
       </c>
       <c r="B101" t="n">
-        <v>78263</v>
+        <v>97907</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11240,28 +11202,32 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
@@ -11271,7 +11237,7 @@
         <v>562940</v>
       </c>
       <c r="R101" t="n">
-        <v>7061021</v>
+        <v>7061272</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11303,7 +11269,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11313,7 +11279,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11340,10 +11306,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119835344</v>
+        <v>119838967</v>
       </c>
       <c r="B102" t="n">
-        <v>90582</v>
+        <v>97907</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11352,38 +11318,42 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562790</v>
+        <v>562990</v>
       </c>
       <c r="R102" t="n">
-        <v>7061258</v>
+        <v>7061060</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11415,7 +11385,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11425,7 +11395,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11452,10 +11422,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119839135</v>
+        <v>119835350</v>
       </c>
       <c r="B103" t="n">
-        <v>78262</v>
+        <v>78263</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11468,37 +11438,37 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6446</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
       <c r="P103" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562982</v>
+        <v>562801</v>
       </c>
       <c r="R103" t="n">
-        <v>7061063</v>
+        <v>7061274</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11525,19 +11495,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>18:21</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11552,22 +11512,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119840261</v>
+        <v>119836896</v>
       </c>
       <c r="B104" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11580,34 +11540,34 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>563003</v>
+        <v>562930</v>
       </c>
       <c r="R104" t="n">
-        <v>7061318</v>
+        <v>7061333</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11637,24 +11597,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
       <c r="AC104" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11669,22 +11619,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119837344</v>
+        <v>119835897</v>
       </c>
       <c r="B105" t="n">
-        <v>57463</v>
+        <v>79607</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11697,46 +11647,37 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562829</v>
+        <v>562851</v>
       </c>
       <c r="R105" t="n">
-        <v>7061182</v>
+        <v>7061350</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11763,19 +11704,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11790,22 +11721,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119836311</v>
+        <v>119835697</v>
       </c>
       <c r="B106" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11814,25 +11745,25 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11842,13 +11773,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562972</v>
+        <v>562826</v>
       </c>
       <c r="R106" t="n">
-        <v>7061274</v>
+        <v>7061341</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11878,11 +11809,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11909,10 +11835,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119837999</v>
+        <v>119835763</v>
       </c>
       <c r="B107" t="n">
-        <v>79144</v>
+        <v>78526</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11925,21 +11851,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6453</v>
+        <v>6425</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11949,13 +11875,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>562848</v>
+        <v>562859</v>
       </c>
       <c r="R107" t="n">
-        <v>7061083</v>
+        <v>7061254</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11982,9 +11908,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11999,22 +11935,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119835697</v>
+        <v>119838030</v>
       </c>
       <c r="B108" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12027,34 +11963,39 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>562826</v>
+        <v>562828</v>
       </c>
       <c r="R108" t="n">
-        <v>7061341</v>
+        <v>7061089</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12084,9 +12025,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12101,22 +12052,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119835763</v>
+        <v>119837344</v>
       </c>
       <c r="B109" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12129,34 +12080,43 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M109" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>562859</v>
+        <v>562829</v>
       </c>
       <c r="R109" t="n">
-        <v>7061254</v>
+        <v>7061182</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12188,7 +12148,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12198,7 +12158,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12225,10 +12185,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119837084</v>
+        <v>119835654</v>
       </c>
       <c r="B110" t="n">
-        <v>90582</v>
+        <v>79636</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12237,25 +12197,25 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5442</v>
+        <v>6462</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12265,10 +12225,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>562905</v>
+        <v>562838</v>
       </c>
       <c r="R110" t="n">
-        <v>7061251</v>
+        <v>7061333</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -12327,10 +12287,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119838064</v>
+        <v>119839212</v>
       </c>
       <c r="B111" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12339,41 +12299,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562850</v>
+        <v>563063</v>
       </c>
       <c r="R111" t="n">
-        <v>7061098</v>
+        <v>7061037</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12400,9 +12360,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12417,22 +12387,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119835495</v>
+        <v>119840354</v>
       </c>
       <c r="B112" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12445,21 +12415,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12469,13 +12439,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>562822</v>
+        <v>562893</v>
       </c>
       <c r="R112" t="n">
-        <v>7061305</v>
+        <v>7061427</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12531,10 +12501,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119835259</v>
+        <v>119837856</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12547,37 +12517,37 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562815</v>
+        <v>562803</v>
       </c>
       <c r="R113" t="n">
-        <v>7061302</v>
+        <v>7061104</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12604,9 +12574,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC113" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12621,22 +12606,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119835654</v>
+        <v>119837512</v>
       </c>
       <c r="B114" t="n">
-        <v>79636</v>
+        <v>57310</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12645,25 +12630,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12673,13 +12658,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>562838</v>
+        <v>562769</v>
       </c>
       <c r="R114" t="n">
-        <v>7061333</v>
+        <v>7061157</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12706,9 +12691,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12723,22 +12723,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119835796</v>
+        <v>119835470</v>
       </c>
       <c r="B115" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12751,21 +12751,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12775,13 +12775,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>562830</v>
+        <v>562839</v>
       </c>
       <c r="R115" t="n">
-        <v>7061321</v>
+        <v>7061260</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12825,22 +12825,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119836896</v>
+        <v>119836311</v>
       </c>
       <c r="B116" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12849,25 +12849,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12877,13 +12877,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562930</v>
+        <v>562972</v>
       </c>
       <c r="R116" t="n">
-        <v>7061333</v>
+        <v>7061274</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12917,7 +12917,7 @@
       </c>
       <c r="AC116" t="inlineStr">
         <is>
-          <t>På tall</t>
+          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12944,10 +12944,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119838606</v>
+        <v>119836284</v>
       </c>
       <c r="B117" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12956,38 +12956,42 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562879</v>
+        <v>562903</v>
       </c>
       <c r="R117" t="n">
-        <v>7061091</v>
+        <v>7061259</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13017,9 +13021,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13034,22 +13048,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119835897</v>
+        <v>119836367</v>
       </c>
       <c r="B118" t="n">
-        <v>79607</v>
+        <v>95455</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13062,21 +13076,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13086,10 +13100,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562851</v>
+        <v>562983</v>
       </c>
       <c r="R118" t="n">
-        <v>7061350</v>
+        <v>7061268</v>
       </c>
       <c r="S118" t="n">
         <v>15</v>
@@ -13148,10 +13162,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119836807</v>
+        <v>119835514</v>
       </c>
       <c r="B119" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13164,21 +13178,21 @@
         </is>
       </c>
       <c r="E119" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13188,13 +13202,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>562926</v>
+        <v>562849</v>
       </c>
       <c r="R119" t="n">
-        <v>7061340</v>
+        <v>7061244</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13221,24 +13235,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC119" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13253,22 +13252,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119835535</v>
+        <v>119837383</v>
       </c>
       <c r="B120" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13277,25 +13276,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13305,13 +13304,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562795</v>
+        <v>562779</v>
       </c>
       <c r="R120" t="n">
-        <v>7061238</v>
+        <v>7061176</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13338,19 +13337,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13365,22 +13354,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119838102</v>
+        <v>119837181</v>
       </c>
       <c r="B121" t="n">
-        <v>57463</v>
+        <v>90527</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13389,46 +13378,41 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>103021</v>
+        <v>5447</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="M121" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562863</v>
+        <v>562872</v>
       </c>
       <c r="R121" t="n">
-        <v>7061098</v>
+        <v>7061246</v>
       </c>
       <c r="S121" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13484,10 +13468,10 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119839243</v>
+        <v>119838957</v>
       </c>
       <c r="B122" t="n">
-        <v>97907</v>
+        <v>91834</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13496,42 +13480,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>4362</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Hornem.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563074</v>
+        <v>562888</v>
       </c>
       <c r="R122" t="n">
-        <v>7061022</v>
+        <v>7061052</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13561,19 +13541,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13588,22 +13558,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119836367</v>
+        <v>119840261</v>
       </c>
       <c r="B123" t="n">
-        <v>95455</v>
+        <v>57310</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13616,37 +13586,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>53</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>562983</v>
+        <v>563003</v>
       </c>
       <c r="R123" t="n">
-        <v>7061268</v>
+        <v>7061318</v>
       </c>
       <c r="S123" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13673,9 +13643,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z123" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB123" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC123" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13690,22 +13675,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119836358</v>
+        <v>119839228</v>
       </c>
       <c r="B124" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13718,37 +13703,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>562901</v>
+        <v>563061</v>
       </c>
       <c r="R124" t="n">
-        <v>7061289</v>
+        <v>7061025</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13775,9 +13760,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13792,12 +13792,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -3207,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119837966</v>
+        <v>119839243</v>
       </c>
       <c r="B26" t="n">
-        <v>78171</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,41 +3219,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562845</v>
+        <v>563074</v>
       </c>
       <c r="R26" t="n">
-        <v>7061093</v>
+        <v>7061022</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3280,9 +3284,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3297,22 +3311,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119838064</v>
+        <v>119838885</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,41 +3335,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562850</v>
+        <v>562977</v>
       </c>
       <c r="R27" t="n">
-        <v>7061098</v>
+        <v>7061045</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3382,9 +3400,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3399,22 +3427,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119837858</v>
+        <v>119837966</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,25 +3451,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3451,13 +3479,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562847</v>
+        <v>562845</v>
       </c>
       <c r="R28" t="n">
-        <v>7061096</v>
+        <v>7061093</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3513,10 +3541,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839243</v>
+        <v>119838064</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,45 +3553,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563074</v>
+        <v>562850</v>
       </c>
       <c r="R29" t="n">
-        <v>7061022</v>
+        <v>7061098</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3590,19 +3614,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3617,22 +3631,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119838885</v>
+        <v>119835805</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3641,45 +3655,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562977</v>
+        <v>562873</v>
       </c>
       <c r="R30" t="n">
-        <v>7061045</v>
+        <v>7061226</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,19 +3716,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,22 +3733,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119835805</v>
+        <v>119837858</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562873</v>
+        <v>562847</v>
       </c>
       <c r="R31" t="n">
-        <v>7061226</v>
+        <v>7061096</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3835,12 +3835,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119839135</v>
+        <v>119836512</v>
       </c>
       <c r="B44" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5142,38 +5142,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562982</v>
+        <v>562925</v>
       </c>
       <c r="R44" t="n">
-        <v>7061063</v>
+        <v>7061308</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5205,7 +5209,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5215,7 +5219,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5242,10 +5246,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119835259</v>
+        <v>119836521</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5254,25 +5258,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5282,10 +5286,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562815</v>
+        <v>562928</v>
       </c>
       <c r="R45" t="n">
-        <v>7061302</v>
+        <v>7061305</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5332,12 +5336,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5446,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119836512</v>
+        <v>119839135</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5458,42 +5462,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562925</v>
+        <v>562982</v>
       </c>
       <c r="R47" t="n">
-        <v>7061308</v>
+        <v>7061063</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119836521</v>
+        <v>119835259</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5574,25 +5574,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562928</v>
+        <v>562815</v>
       </c>
       <c r="R48" t="n">
-        <v>7061305</v>
+        <v>7061302</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5652,12 +5652,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119838625</v>
+        <v>119835431</v>
       </c>
       <c r="B64" t="n">
-        <v>91884</v>
+        <v>79607</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7254,37 +7254,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562899</v>
+        <v>562853</v>
       </c>
       <c r="R64" t="n">
-        <v>7061101</v>
+        <v>7061293</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7311,19 +7311,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7338,22 +7328,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119835431</v>
+        <v>119838625</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>91884</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7366,37 +7356,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562853</v>
+        <v>562899</v>
       </c>
       <c r="R65" t="n">
-        <v>7061293</v>
+        <v>7061101</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7423,9 +7413,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7440,12 +7440,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119840391</v>
+        <v>119837999</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>79144</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8129,21 +8129,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562861</v>
+        <v>562848</v>
       </c>
       <c r="R72" t="n">
-        <v>7061439</v>
+        <v>7061083</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119835638</v>
+        <v>119840391</v>
       </c>
       <c r="B73" t="n">
         <v>79607</v>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562838</v>
+        <v>562861</v>
       </c>
       <c r="R73" t="n">
-        <v>7061326</v>
+        <v>7061439</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119837306</v>
+        <v>119835638</v>
       </c>
       <c r="B74" t="n">
         <v>79607</v>
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562793</v>
+        <v>562838</v>
       </c>
       <c r="R74" t="n">
-        <v>7061251</v>
+        <v>7061326</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8393,11 +8393,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8424,10 +8419,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119837999</v>
+        <v>119837306</v>
       </c>
       <c r="B75" t="n">
-        <v>79144</v>
+        <v>79607</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8440,21 +8435,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,13 +8459,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562848</v>
+        <v>562793</v>
       </c>
       <c r="R75" t="n">
-        <v>7061083</v>
+        <v>7061251</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8500,6 +8495,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8526,10 +8526,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119836632</v>
+        <v>119836629</v>
       </c>
       <c r="B76" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8538,30 +8538,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8570,13 +8571,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562948</v>
+        <v>562935</v>
       </c>
       <c r="R76" t="n">
-        <v>7061323</v>
+        <v>7061315</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8603,9 +8604,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8620,19 +8631,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119836629</v>
+        <v>119836807</v>
       </c>
       <c r="B77" t="n">
         <v>57310</v>
@@ -8666,21 +8677,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562935</v>
+        <v>562926</v>
       </c>
       <c r="R77" t="n">
-        <v>7061315</v>
+        <v>7061340</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8712,7 +8718,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8722,7 +8728,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8749,10 +8760,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119836807</v>
+        <v>119836632</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8761,41 +8772,45 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562926</v>
+        <v>562948</v>
       </c>
       <c r="R78" t="n">
-        <v>7061340</v>
+        <v>7061323</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8822,24 +8837,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8854,12 +8854,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119838606</v>
+        <v>119837066</v>
       </c>
       <c r="B88" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9826,25 +9826,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562879</v>
+        <v>562940</v>
       </c>
       <c r="R88" t="n">
-        <v>7061091</v>
+        <v>7061261</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9904,22 +9904,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119835631</v>
+        <v>119837298</v>
       </c>
       <c r="B89" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9932,21 +9932,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9956,13 +9956,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>562785</v>
+        <v>562841</v>
       </c>
       <c r="R89" t="n">
-        <v>7061238</v>
+        <v>7061196</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9989,24 +9989,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10021,22 +10006,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119837066</v>
+        <v>119838606</v>
       </c>
       <c r="B90" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10045,25 +10030,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10073,13 +10058,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562940</v>
+        <v>562879</v>
       </c>
       <c r="R90" t="n">
-        <v>7061261</v>
+        <v>7061091</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10123,22 +10108,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119837298</v>
+        <v>119835631</v>
       </c>
       <c r="B91" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10151,21 +10136,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10175,13 +10160,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562841</v>
+        <v>562785</v>
       </c>
       <c r="R91" t="n">
-        <v>7061196</v>
+        <v>7061238</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10208,9 +10193,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10225,12 +10225,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11524,10 +11524,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119836896</v>
+        <v>119835897</v>
       </c>
       <c r="B104" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11540,21 +11540,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11564,13 +11564,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562930</v>
+        <v>562851</v>
       </c>
       <c r="R104" t="n">
-        <v>7061333</v>
+        <v>7061350</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11600,11 +11600,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11631,7 +11626,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119835897</v>
+        <v>119835697</v>
       </c>
       <c r="B105" t="n">
         <v>79607</v>
@@ -11671,13 +11666,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562851</v>
+        <v>562826</v>
       </c>
       <c r="R105" t="n">
-        <v>7061350</v>
+        <v>7061341</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11733,10 +11728,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119835697</v>
+        <v>119836896</v>
       </c>
       <c r="B106" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11749,21 +11744,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11773,10 +11768,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562826</v>
+        <v>562930</v>
       </c>
       <c r="R106" t="n">
-        <v>7061341</v>
+        <v>7061333</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11809,6 +11804,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12064,10 +12064,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119837344</v>
+        <v>119835470</v>
       </c>
       <c r="B109" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12080,46 +12080,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M109" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>562829</v>
+        <v>562839</v>
       </c>
       <c r="R109" t="n">
-        <v>7061182</v>
+        <v>7061260</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12146,19 +12137,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12173,22 +12154,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119835654</v>
+        <v>119837344</v>
       </c>
       <c r="B110" t="n">
-        <v>79636</v>
+        <v>57463</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12197,41 +12178,50 @@
       </c>
       <c r="D110" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>562838</v>
+        <v>562829</v>
       </c>
       <c r="R110" t="n">
-        <v>7061333</v>
+        <v>7061182</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12258,9 +12248,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12275,22 +12275,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119839212</v>
+        <v>119835654</v>
       </c>
       <c r="B111" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12299,41 +12299,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>563063</v>
+        <v>562838</v>
       </c>
       <c r="R111" t="n">
-        <v>7061037</v>
+        <v>7061333</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12360,19 +12360,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12387,19 +12377,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119840354</v>
+        <v>119839212</v>
       </c>
       <c r="B112" t="n">
         <v>78526</v>
@@ -12435,14 +12425,14 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>562893</v>
+        <v>563063</v>
       </c>
       <c r="R112" t="n">
-        <v>7061427</v>
+        <v>7061037</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12472,9 +12462,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12489,22 +12489,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119837856</v>
+        <v>119840354</v>
       </c>
       <c r="B113" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12517,34 +12517,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562803</v>
+        <v>562893</v>
       </c>
       <c r="R113" t="n">
-        <v>7061104</v>
+        <v>7061427</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12574,24 +12574,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC113" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12606,19 +12591,19 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119837512</v>
+        <v>119837856</v>
       </c>
       <c r="B114" t="n">
         <v>57310</v>
@@ -12654,14 +12639,14 @@
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>562769</v>
+        <v>562803</v>
       </c>
       <c r="R114" t="n">
-        <v>7061157</v>
+        <v>7061104</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -12693,7 +12678,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -12703,7 +12688,7 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
@@ -12735,10 +12720,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119835470</v>
+        <v>119837512</v>
       </c>
       <c r="B115" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12751,21 +12736,21 @@
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12775,13 +12760,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>562839</v>
+        <v>562769</v>
       </c>
       <c r="R115" t="n">
-        <v>7061260</v>
+        <v>7061157</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12808,9 +12793,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12825,12 +12825,12 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -3207,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839243</v>
+        <v>119837966</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>78171</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,45 +3219,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563074</v>
+        <v>562845</v>
       </c>
       <c r="R26" t="n">
-        <v>7061022</v>
+        <v>7061093</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3284,19 +3280,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3311,22 +3297,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119838885</v>
+        <v>119838064</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,45 +3321,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562977</v>
+        <v>562850</v>
       </c>
       <c r="R27" t="n">
-        <v>7061045</v>
+        <v>7061098</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3400,19 +3382,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,22 +3399,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119837966</v>
+        <v>119837858</v>
       </c>
       <c r="B28" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,25 +3423,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3479,13 +3451,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562845</v>
+        <v>562847</v>
       </c>
       <c r="R28" t="n">
-        <v>7061093</v>
+        <v>7061096</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3541,10 +3513,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119838064</v>
+        <v>119839243</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,41 +3525,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562850</v>
+        <v>563074</v>
       </c>
       <c r="R29" t="n">
-        <v>7061098</v>
+        <v>7061022</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3614,9 +3590,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,22 +3617,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119835805</v>
+        <v>119838885</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3655,41 +3641,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562873</v>
+        <v>562977</v>
       </c>
       <c r="R30" t="n">
-        <v>7061226</v>
+        <v>7061045</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3716,9 +3706,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,22 +3733,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119837858</v>
+        <v>119835805</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562847</v>
+        <v>562873</v>
       </c>
       <c r="R31" t="n">
-        <v>7061096</v>
+        <v>7061226</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3835,12 +3835,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119839184</v>
+        <v>119836005</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4826,25 +4826,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563009</v>
+        <v>562898</v>
       </c>
       <c r="R41" t="n">
-        <v>7061040</v>
+        <v>7061215</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4904,22 +4904,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119837543</v>
+        <v>119839184</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4928,25 +4928,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4956,13 +4956,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562745</v>
+        <v>563009</v>
       </c>
       <c r="R42" t="n">
-        <v>7061152</v>
+        <v>7061040</v>
       </c>
       <c r="S42" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4989,19 +4989,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5016,19 +5006,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119836005</v>
+        <v>119837543</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5068,13 +5058,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562898</v>
+        <v>562745</v>
       </c>
       <c r="R43" t="n">
-        <v>7061215</v>
+        <v>7061152</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5101,9 +5091,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z43" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB43" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5118,22 +5118,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119836512</v>
+        <v>119839135</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5142,42 +5142,38 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562925</v>
+        <v>562982</v>
       </c>
       <c r="R44" t="n">
-        <v>7061308</v>
+        <v>7061063</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,7 +5205,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5219,7 +5215,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5246,10 +5242,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119836521</v>
+        <v>119835259</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5258,25 +5254,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5286,10 +5282,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562928</v>
+        <v>562815</v>
       </c>
       <c r="R45" t="n">
-        <v>7061305</v>
+        <v>7061302</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5336,12 +5332,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5450,10 +5446,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119839135</v>
+        <v>119836512</v>
       </c>
       <c r="B47" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5462,38 +5458,42 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562982</v>
+        <v>562925</v>
       </c>
       <c r="R47" t="n">
-        <v>7061063</v>
+        <v>7061308</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119835259</v>
+        <v>119836521</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5574,25 +5574,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562815</v>
+        <v>562928</v>
       </c>
       <c r="R48" t="n">
-        <v>7061302</v>
+        <v>7061305</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5652,12 +5652,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119835431</v>
+        <v>119838625</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>91884</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7254,37 +7254,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562853</v>
+        <v>562899</v>
       </c>
       <c r="R64" t="n">
-        <v>7061293</v>
+        <v>7061101</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7311,9 +7311,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7328,22 +7338,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119838625</v>
+        <v>119835431</v>
       </c>
       <c r="B65" t="n">
-        <v>91884</v>
+        <v>79607</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7356,37 +7366,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562899</v>
+        <v>562853</v>
       </c>
       <c r="R65" t="n">
-        <v>7061101</v>
+        <v>7061293</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7413,19 +7423,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7440,12 +7440,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119837999</v>
+        <v>119840391</v>
       </c>
       <c r="B72" t="n">
-        <v>79144</v>
+        <v>79607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8129,21 +8129,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562848</v>
+        <v>562861</v>
       </c>
       <c r="R72" t="n">
-        <v>7061083</v>
+        <v>7061439</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119840391</v>
+        <v>119835638</v>
       </c>
       <c r="B73" t="n">
         <v>79607</v>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562861</v>
+        <v>562838</v>
       </c>
       <c r="R73" t="n">
-        <v>7061439</v>
+        <v>7061326</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119835638</v>
+        <v>119837306</v>
       </c>
       <c r="B74" t="n">
         <v>79607</v>
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562838</v>
+        <v>562793</v>
       </c>
       <c r="R74" t="n">
-        <v>7061326</v>
+        <v>7061251</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8393,6 +8393,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8419,10 +8424,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119837306</v>
+        <v>119837999</v>
       </c>
       <c r="B75" t="n">
-        <v>79607</v>
+        <v>79144</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8435,21 +8440,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8459,13 +8464,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562793</v>
+        <v>562848</v>
       </c>
       <c r="R75" t="n">
-        <v>7061251</v>
+        <v>7061083</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8495,11 +8500,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8526,10 +8526,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119836629</v>
+        <v>119836632</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8538,31 +8538,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8571,13 +8570,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562935</v>
+        <v>562948</v>
       </c>
       <c r="R76" t="n">
-        <v>7061315</v>
+        <v>7061323</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8604,19 +8603,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8631,19 +8620,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119836807</v>
+        <v>119836629</v>
       </c>
       <c r="B77" t="n">
         <v>57310</v>
@@ -8677,16 +8666,21 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562926</v>
+        <v>562935</v>
       </c>
       <c r="R77" t="n">
-        <v>7061340</v>
+        <v>7061315</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8718,7 +8712,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8728,12 +8722,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8760,10 +8749,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119836632</v>
+        <v>119836807</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8772,45 +8761,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562948</v>
+        <v>562926</v>
       </c>
       <c r="R78" t="n">
-        <v>7061323</v>
+        <v>7061340</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8837,9 +8822,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8854,12 +8854,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119837066</v>
+        <v>119838606</v>
       </c>
       <c r="B88" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9826,25 +9826,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562940</v>
+        <v>562879</v>
       </c>
       <c r="R88" t="n">
-        <v>7061261</v>
+        <v>7061091</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9904,22 +9904,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119837298</v>
+        <v>119835631</v>
       </c>
       <c r="B89" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9932,21 +9932,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9956,13 +9956,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>562841</v>
+        <v>562785</v>
       </c>
       <c r="R89" t="n">
-        <v>7061196</v>
+        <v>7061238</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9989,9 +9989,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10006,22 +10021,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119838606</v>
+        <v>119837066</v>
       </c>
       <c r="B90" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10030,25 +10045,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10058,13 +10073,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562879</v>
+        <v>562940</v>
       </c>
       <c r="R90" t="n">
-        <v>7061091</v>
+        <v>7061261</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10108,22 +10123,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119835631</v>
+        <v>119837298</v>
       </c>
       <c r="B91" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10136,21 +10151,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10160,13 +10175,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562785</v>
+        <v>562841</v>
       </c>
       <c r="R91" t="n">
-        <v>7061238</v>
+        <v>7061196</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10193,24 +10208,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10225,12 +10225,12 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
@@ -11524,10 +11524,10 @@
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119835897</v>
+        <v>119836896</v>
       </c>
       <c r="B104" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11540,21 +11540,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11564,13 +11564,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562851</v>
+        <v>562930</v>
       </c>
       <c r="R104" t="n">
-        <v>7061350</v>
+        <v>7061333</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11600,6 +11600,11 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11626,7 +11631,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119835697</v>
+        <v>119835897</v>
       </c>
       <c r="B105" t="n">
         <v>79607</v>
@@ -11666,13 +11671,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562826</v>
+        <v>562851</v>
       </c>
       <c r="R105" t="n">
-        <v>7061341</v>
+        <v>7061350</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11728,10 +11733,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119836896</v>
+        <v>119835697</v>
       </c>
       <c r="B106" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11744,21 +11749,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11768,10 +11773,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562930</v>
+        <v>562826</v>
       </c>
       <c r="R106" t="n">
-        <v>7061333</v>
+        <v>7061341</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11804,11 +11809,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD106" t="b">

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -3207,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119837966</v>
+        <v>119839243</v>
       </c>
       <c r="B26" t="n">
-        <v>78171</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,41 +3219,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562845</v>
+        <v>563074</v>
       </c>
       <c r="R26" t="n">
-        <v>7061093</v>
+        <v>7061022</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3280,9 +3284,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3297,22 +3311,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119838064</v>
+        <v>119838885</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,41 +3335,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562850</v>
+        <v>562977</v>
       </c>
       <c r="R27" t="n">
-        <v>7061098</v>
+        <v>7061045</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3382,9 +3400,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3399,22 +3427,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119837858</v>
+        <v>119837966</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,25 +3451,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3451,13 +3479,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562847</v>
+        <v>562845</v>
       </c>
       <c r="R28" t="n">
-        <v>7061096</v>
+        <v>7061093</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3513,10 +3541,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839243</v>
+        <v>119838064</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,45 +3553,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563074</v>
+        <v>562850</v>
       </c>
       <c r="R29" t="n">
-        <v>7061022</v>
+        <v>7061098</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3590,19 +3614,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3617,22 +3631,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119838885</v>
+        <v>119835805</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3641,45 +3655,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562977</v>
+        <v>562873</v>
       </c>
       <c r="R30" t="n">
-        <v>7061045</v>
+        <v>7061226</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,19 +3716,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,22 +3733,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119835805</v>
+        <v>119837858</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562873</v>
+        <v>562847</v>
       </c>
       <c r="R31" t="n">
-        <v>7061226</v>
+        <v>7061096</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3835,12 +3835,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4814,10 +4814,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119836005</v>
+        <v>119839184</v>
       </c>
       <c r="B41" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4826,25 +4826,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4854,10 +4854,10 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562898</v>
+        <v>563009</v>
       </c>
       <c r="R41" t="n">
-        <v>7061215</v>
+        <v>7061040</v>
       </c>
       <c r="S41" t="n">
         <v>15</v>
@@ -4904,22 +4904,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119839184</v>
+        <v>119837543</v>
       </c>
       <c r="B42" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4928,25 +4928,25 @@
       </c>
       <c r="D42" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E42" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4956,13 +4956,13 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>563009</v>
+        <v>562745</v>
       </c>
       <c r="R42" t="n">
-        <v>7061040</v>
+        <v>7061152</v>
       </c>
       <c r="S42" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T42" t="inlineStr">
         <is>
@@ -4989,9 +4989,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5006,19 +5016,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119837543</v>
+        <v>119836005</v>
       </c>
       <c r="B43" t="n">
         <v>78526</v>
@@ -5058,13 +5068,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562745</v>
+        <v>562898</v>
       </c>
       <c r="R43" t="n">
-        <v>7061152</v>
+        <v>7061215</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5091,19 +5101,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z43" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA43" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB43" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD43" t="b">
@@ -5118,12 +5118,12 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119838625</v>
+        <v>119835431</v>
       </c>
       <c r="B64" t="n">
-        <v>91884</v>
+        <v>79607</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7254,37 +7254,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562899</v>
+        <v>562853</v>
       </c>
       <c r="R64" t="n">
-        <v>7061101</v>
+        <v>7061293</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7311,19 +7311,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7338,22 +7328,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119835431</v>
+        <v>119838625</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>91884</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7366,37 +7356,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>5449</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562853</v>
+        <v>562899</v>
       </c>
       <c r="R65" t="n">
-        <v>7061293</v>
+        <v>7061101</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7423,9 +7413,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7440,12 +7440,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8866,10 +8866,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119835531</v>
+        <v>119836358</v>
       </c>
       <c r="B79" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8882,21 +8882,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8906,10 +8906,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562827</v>
+        <v>562901</v>
       </c>
       <c r="R79" t="n">
-        <v>7061302</v>
+        <v>7061289</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8956,22 +8956,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119837084</v>
+        <v>119835535</v>
       </c>
       <c r="B80" t="n">
-        <v>90582</v>
+        <v>91840</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8980,25 +8980,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562905</v>
+        <v>562795</v>
       </c>
       <c r="R80" t="n">
-        <v>7061251</v>
+        <v>7061238</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9041,9 +9041,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9058,12 +9068,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9279,10 +9289,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119836358</v>
+        <v>119835531</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9295,21 +9305,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9319,10 +9329,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562901</v>
+        <v>562827</v>
       </c>
       <c r="R83" t="n">
-        <v>7061289</v>
+        <v>7061302</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9369,22 +9379,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119835535</v>
+        <v>119837084</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9393,25 +9403,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9421,13 +9431,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562795</v>
+        <v>562905</v>
       </c>
       <c r="R84" t="n">
-        <v>7061238</v>
+        <v>7061251</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9454,19 +9464,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9481,12 +9481,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -9814,10 +9814,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119838606</v>
+        <v>119837066</v>
       </c>
       <c r="B88" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9826,25 +9826,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9854,13 +9854,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562879</v>
+        <v>562940</v>
       </c>
       <c r="R88" t="n">
-        <v>7061091</v>
+        <v>7061261</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9904,22 +9904,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119835631</v>
+        <v>119837298</v>
       </c>
       <c r="B89" t="n">
-        <v>57310</v>
+        <v>78526</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9932,21 +9932,21 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
@@ -9956,13 +9956,13 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>562785</v>
+        <v>562841</v>
       </c>
       <c r="R89" t="n">
-        <v>7061238</v>
+        <v>7061196</v>
       </c>
       <c r="S89" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9989,24 +9989,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10021,22 +10006,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119837066</v>
+        <v>119838606</v>
       </c>
       <c r="B90" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10045,25 +10030,25 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10073,13 +10058,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562940</v>
+        <v>562879</v>
       </c>
       <c r="R90" t="n">
-        <v>7061261</v>
+        <v>7061091</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10123,22 +10108,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119837298</v>
+        <v>119835631</v>
       </c>
       <c r="B91" t="n">
-        <v>78526</v>
+        <v>57310</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10151,21 +10136,21 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
@@ -10175,13 +10160,13 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562841</v>
+        <v>562785</v>
       </c>
       <c r="R91" t="n">
-        <v>7061196</v>
+        <v>7061238</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10208,9 +10193,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10225,22 +10225,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119837399</v>
+        <v>119835516</v>
       </c>
       <c r="B92" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10253,21 +10253,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10277,10 +10277,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562767</v>
+        <v>562795</v>
       </c>
       <c r="R92" t="n">
-        <v>7061188</v>
+        <v>7061238</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10310,9 +10310,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10327,22 +10342,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119837427</v>
+        <v>119835350</v>
       </c>
       <c r="B93" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10351,25 +10366,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10379,13 +10394,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>562772</v>
+        <v>562801</v>
       </c>
       <c r="R93" t="n">
-        <v>7061165</v>
+        <v>7061274</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10412,19 +10427,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10439,22 +10444,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119835500</v>
+        <v>119837074</v>
       </c>
       <c r="B94" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10463,41 +10468,45 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562824</v>
+        <v>562940</v>
       </c>
       <c r="R94" t="n">
-        <v>7061319</v>
+        <v>7061272</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10524,9 +10533,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z94" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB94" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10541,22 +10560,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119840373</v>
+        <v>119838967</v>
       </c>
       <c r="B95" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10565,38 +10584,42 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562875</v>
+        <v>562990</v>
       </c>
       <c r="R95" t="n">
-        <v>7061433</v>
+        <v>7061060</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10626,9 +10649,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10643,22 +10676,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119836179</v>
+        <v>119836952</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10671,34 +10704,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>562966</v>
+        <v>562955</v>
       </c>
       <c r="R96" t="n">
-        <v>7061336</v>
+        <v>7061332</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10728,9 +10761,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10745,22 +10788,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119835968</v>
+        <v>119837427</v>
       </c>
       <c r="B97" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10769,25 +10812,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10797,10 +10840,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562856</v>
+        <v>562772</v>
       </c>
       <c r="R97" t="n">
-        <v>7061341</v>
+        <v>7061165</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10830,9 +10873,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10847,22 +10900,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119836952</v>
+        <v>119840300</v>
       </c>
       <c r="B98" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10875,34 +10928,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562955</v>
+        <v>562938</v>
       </c>
       <c r="R98" t="n">
-        <v>7061332</v>
+        <v>7061384</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10932,19 +10985,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>16:35</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>16:35</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10959,22 +11002,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119840300</v>
+        <v>119837399</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10987,21 +11030,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11011,10 +11054,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562938</v>
+        <v>562767</v>
       </c>
       <c r="R99" t="n">
-        <v>7061384</v>
+        <v>7061188</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11073,10 +11116,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119835516</v>
+        <v>119835500</v>
       </c>
       <c r="B100" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11089,21 +11132,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11113,13 +11156,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562795</v>
+        <v>562824</v>
       </c>
       <c r="R100" t="n">
-        <v>7061238</v>
+        <v>7061319</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11146,24 +11189,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11178,22 +11206,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119837074</v>
+        <v>119840373</v>
       </c>
       <c r="B101" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11202,42 +11230,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562940</v>
+        <v>562875</v>
       </c>
       <c r="R101" t="n">
-        <v>7061272</v>
+        <v>7061433</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11267,19 +11291,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>16:40</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11294,22 +11308,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119838967</v>
+        <v>119836179</v>
       </c>
       <c r="B102" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11318,42 +11332,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562990</v>
+        <v>562966</v>
       </c>
       <c r="R102" t="n">
-        <v>7061060</v>
+        <v>7061336</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11383,19 +11393,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11410,22 +11410,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119835350</v>
+        <v>119835968</v>
       </c>
       <c r="B103" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11438,21 +11438,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11462,13 +11462,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562801</v>
+        <v>562856</v>
       </c>
       <c r="R103" t="n">
-        <v>7061274</v>
+        <v>7061341</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11512,12 +11512,12 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119835470</v>
+        <v>119839212</v>
       </c>
       <c r="B109" t="n">
         <v>78526</v>
@@ -12100,17 +12100,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>562839</v>
+        <v>563063</v>
       </c>
       <c r="R109" t="n">
-        <v>7061260</v>
+        <v>7061037</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12137,9 +12137,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12154,22 +12164,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119837344</v>
+        <v>119840354</v>
       </c>
       <c r="B110" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12182,43 +12192,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>562829</v>
+        <v>562893</v>
       </c>
       <c r="R110" t="n">
-        <v>7061182</v>
+        <v>7061427</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12248,19 +12249,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12275,22 +12266,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119835654</v>
+        <v>119837344</v>
       </c>
       <c r="B111" t="n">
-        <v>79636</v>
+        <v>57463</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12299,41 +12290,50 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562838</v>
+        <v>562829</v>
       </c>
       <c r="R111" t="n">
-        <v>7061333</v>
+        <v>7061182</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12360,9 +12360,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12377,19 +12387,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119839212</v>
+        <v>119835470</v>
       </c>
       <c r="B112" t="n">
         <v>78526</v>
@@ -12425,17 +12435,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563063</v>
+        <v>562839</v>
       </c>
       <c r="R112" t="n">
-        <v>7061037</v>
+        <v>7061260</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12462,19 +12472,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12489,22 +12489,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119840354</v>
+        <v>119835654</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12513,25 +12513,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562893</v>
+        <v>562838</v>
       </c>
       <c r="R113" t="n">
-        <v>7061427</v>
+        <v>7061333</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -3207,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839243</v>
+        <v>119837966</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>78171</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,45 +3219,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563074</v>
+        <v>562845</v>
       </c>
       <c r="R26" t="n">
-        <v>7061022</v>
+        <v>7061093</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3284,19 +3280,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3311,22 +3297,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119838885</v>
+        <v>119838064</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,45 +3321,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562977</v>
+        <v>562850</v>
       </c>
       <c r="R27" t="n">
-        <v>7061045</v>
+        <v>7061098</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3400,19 +3382,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,22 +3399,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119837966</v>
+        <v>119837858</v>
       </c>
       <c r="B28" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,25 +3423,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3479,13 +3451,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562845</v>
+        <v>562847</v>
       </c>
       <c r="R28" t="n">
-        <v>7061093</v>
+        <v>7061096</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3541,10 +3513,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119838064</v>
+        <v>119839243</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,41 +3525,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562850</v>
+        <v>563074</v>
       </c>
       <c r="R29" t="n">
-        <v>7061098</v>
+        <v>7061022</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3614,9 +3590,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,22 +3617,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119835805</v>
+        <v>119838885</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3655,41 +3641,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562873</v>
+        <v>562977</v>
       </c>
       <c r="R30" t="n">
-        <v>7061226</v>
+        <v>7061045</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3716,9 +3706,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,22 +3733,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119837858</v>
+        <v>119835805</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562847</v>
+        <v>562873</v>
       </c>
       <c r="R31" t="n">
-        <v>7061096</v>
+        <v>7061226</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3835,12 +3835,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -6087,10 +6087,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119838864</v>
+        <v>119837216</v>
       </c>
       <c r="B53" t="n">
-        <v>78263</v>
+        <v>78526</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6103,37 +6103,37 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
       <c r="P53" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562940</v>
+        <v>562857</v>
       </c>
       <c r="R53" t="n">
-        <v>7061021</v>
+        <v>7061235</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6160,19 +6160,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC53" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6187,22 +6182,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119836424</v>
+        <v>119837899</v>
       </c>
       <c r="B54" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6211,45 +6206,41 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562902</v>
+        <v>562848</v>
       </c>
       <c r="R54" t="n">
-        <v>7061306</v>
+        <v>7061087</v>
       </c>
       <c r="S54" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6293,22 +6284,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119837560</v>
+        <v>119838153</v>
       </c>
       <c r="B55" t="n">
-        <v>79607</v>
+        <v>91840</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6317,25 +6308,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6345,13 +6336,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562746</v>
+        <v>562865</v>
       </c>
       <c r="R55" t="n">
-        <v>7061142</v>
+        <v>7061107</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6381,6 +6372,11 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6395,19 +6391,19 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119835108</v>
+        <v>119837560</v>
       </c>
       <c r="B56" t="n">
         <v>79607</v>
@@ -6447,10 +6443,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562802</v>
+        <v>562746</v>
       </c>
       <c r="R56" t="n">
-        <v>7061280</v>
+        <v>7061142</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6509,10 +6505,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119837216</v>
+        <v>119835108</v>
       </c>
       <c r="B57" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6525,21 +6521,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6549,10 +6545,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562857</v>
+        <v>562802</v>
       </c>
       <c r="R57" t="n">
-        <v>7061235</v>
+        <v>7061280</v>
       </c>
       <c r="S57" t="n">
         <v>15</v>
@@ -6587,11 +6583,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC57" t="inlineStr">
-        <is>
-          <t>På tall</t>
-        </is>
-      </c>
       <c r="AD57" t="b">
         <v>0</v>
       </c>
@@ -6604,22 +6595,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119837899</v>
+        <v>119838864</v>
       </c>
       <c r="B58" t="n">
-        <v>91840</v>
+        <v>78263</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6628,38 +6619,38 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562848</v>
+        <v>562940</v>
       </c>
       <c r="R58" t="n">
-        <v>7061087</v>
+        <v>7061021</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6689,9 +6680,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z58" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB58" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6706,22 +6707,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119838153</v>
+        <v>119836424</v>
       </c>
       <c r="B59" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6730,41 +6731,45 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562865</v>
+        <v>562902</v>
       </c>
       <c r="R59" t="n">
-        <v>7061107</v>
+        <v>7061306</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6794,11 +6799,6 @@
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC59" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6813,12 +6813,12 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119840391</v>
+        <v>119837999</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>79144</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8129,21 +8129,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562861</v>
+        <v>562848</v>
       </c>
       <c r="R72" t="n">
-        <v>7061439</v>
+        <v>7061083</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119835638</v>
+        <v>119840391</v>
       </c>
       <c r="B73" t="n">
         <v>79607</v>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562838</v>
+        <v>562861</v>
       </c>
       <c r="R73" t="n">
-        <v>7061326</v>
+        <v>7061439</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119837306</v>
+        <v>119835638</v>
       </c>
       <c r="B74" t="n">
         <v>79607</v>
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562793</v>
+        <v>562838</v>
       </c>
       <c r="R74" t="n">
-        <v>7061251</v>
+        <v>7061326</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8393,11 +8393,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8424,10 +8419,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119837999</v>
+        <v>119837306</v>
       </c>
       <c r="B75" t="n">
-        <v>79144</v>
+        <v>79607</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8440,21 +8435,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,13 +8459,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562848</v>
+        <v>562793</v>
       </c>
       <c r="R75" t="n">
-        <v>7061083</v>
+        <v>7061251</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8500,6 +8495,11 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8526,10 +8526,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119836632</v>
+        <v>119836629</v>
       </c>
       <c r="B76" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8538,30 +8538,31 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
+      <c r="M76" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8570,13 +8571,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562948</v>
+        <v>562935</v>
       </c>
       <c r="R76" t="n">
-        <v>7061323</v>
+        <v>7061315</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8603,9 +8604,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8620,19 +8631,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119836629</v>
+        <v>119836807</v>
       </c>
       <c r="B77" t="n">
         <v>57310</v>
@@ -8666,21 +8677,16 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562935</v>
+        <v>562926</v>
       </c>
       <c r="R77" t="n">
-        <v>7061315</v>
+        <v>7061340</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8712,7 +8718,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8722,7 +8728,12 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8749,10 +8760,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119836807</v>
+        <v>119836632</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8761,41 +8772,45 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562926</v>
+        <v>562948</v>
       </c>
       <c r="R78" t="n">
-        <v>7061340</v>
+        <v>7061323</v>
       </c>
       <c r="S78" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8822,24 +8837,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8854,22 +8854,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119836358</v>
+        <v>119835531</v>
       </c>
       <c r="B79" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8882,21 +8882,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8906,10 +8906,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562901</v>
+        <v>562827</v>
       </c>
       <c r="R79" t="n">
-        <v>7061289</v>
+        <v>7061302</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8956,22 +8956,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119835535</v>
+        <v>119837084</v>
       </c>
       <c r="B80" t="n">
-        <v>91840</v>
+        <v>90582</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8980,25 +8980,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9008,13 +9008,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562795</v>
+        <v>562905</v>
       </c>
       <c r="R80" t="n">
-        <v>7061238</v>
+        <v>7061251</v>
       </c>
       <c r="S80" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9041,19 +9041,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9068,12 +9058,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9289,10 +9279,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119835531</v>
+        <v>119836358</v>
       </c>
       <c r="B83" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9305,21 +9295,21 @@
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9329,10 +9319,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562827</v>
+        <v>562901</v>
       </c>
       <c r="R83" t="n">
-        <v>7061302</v>
+        <v>7061289</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9379,22 +9369,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119837084</v>
+        <v>119835535</v>
       </c>
       <c r="B84" t="n">
-        <v>90582</v>
+        <v>91840</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9403,25 +9393,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9431,13 +9421,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562905</v>
+        <v>562795</v>
       </c>
       <c r="R84" t="n">
-        <v>7061251</v>
+        <v>7061238</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9464,9 +9454,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9481,12 +9481,12 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
@@ -10237,10 +10237,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119835516</v>
+        <v>119837399</v>
       </c>
       <c r="B92" t="n">
-        <v>57310</v>
+        <v>79607</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10253,21 +10253,21 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10277,10 +10277,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562795</v>
+        <v>562767</v>
       </c>
       <c r="R92" t="n">
-        <v>7061238</v>
+        <v>7061188</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10310,24 +10310,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10342,22 +10327,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119835350</v>
+        <v>119837427</v>
       </c>
       <c r="B93" t="n">
-        <v>78263</v>
+        <v>91840</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10366,25 +10351,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10394,13 +10379,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>562801</v>
+        <v>562772</v>
       </c>
       <c r="R93" t="n">
-        <v>7061274</v>
+        <v>7061165</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10427,9 +10412,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10444,22 +10439,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119837074</v>
+        <v>119835500</v>
       </c>
       <c r="B94" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10468,45 +10463,41 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562940</v>
+        <v>562824</v>
       </c>
       <c r="R94" t="n">
-        <v>7061272</v>
+        <v>7061319</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10533,19 +10524,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z94" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB94" t="inlineStr">
-        <is>
-          <t>16:40</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10560,22 +10541,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119838967</v>
+        <v>119840373</v>
       </c>
       <c r="B95" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10584,42 +10565,38 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562990</v>
+        <v>562875</v>
       </c>
       <c r="R95" t="n">
-        <v>7061060</v>
+        <v>7061433</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10649,19 +10626,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10676,22 +10643,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119836952</v>
+        <v>119836179</v>
       </c>
       <c r="B96" t="n">
-        <v>82305</v>
+        <v>78526</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10704,34 +10671,34 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>1312</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>562955</v>
+        <v>562966</v>
       </c>
       <c r="R96" t="n">
-        <v>7061332</v>
+        <v>7061336</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10761,19 +10728,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>16:35</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>16:35</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10788,22 +10745,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119837427</v>
+        <v>119835968</v>
       </c>
       <c r="B97" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10812,25 +10769,25 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10840,10 +10797,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562772</v>
+        <v>562856</v>
       </c>
       <c r="R97" t="n">
-        <v>7061165</v>
+        <v>7061341</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10873,19 +10830,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10900,22 +10847,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119840300</v>
+        <v>119836952</v>
       </c>
       <c r="B98" t="n">
-        <v>78526</v>
+        <v>82305</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10928,34 +10875,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562938</v>
+        <v>562955</v>
       </c>
       <c r="R98" t="n">
-        <v>7061384</v>
+        <v>7061332</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10985,9 +10932,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11002,22 +10959,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119837399</v>
+        <v>119840300</v>
       </c>
       <c r="B99" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11030,21 +10987,21 @@
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11054,10 +11011,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562767</v>
+        <v>562938</v>
       </c>
       <c r="R99" t="n">
-        <v>7061188</v>
+        <v>7061384</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11116,10 +11073,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119835500</v>
+        <v>119835516</v>
       </c>
       <c r="B100" t="n">
-        <v>79607</v>
+        <v>57310</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11132,21 +11089,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11156,13 +11113,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562824</v>
+        <v>562795</v>
       </c>
       <c r="R100" t="n">
-        <v>7061319</v>
+        <v>7061238</v>
       </c>
       <c r="S100" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11189,9 +11146,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z100" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB100" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC100" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11206,22 +11178,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119840373</v>
+        <v>119837074</v>
       </c>
       <c r="B101" t="n">
-        <v>79607</v>
+        <v>97907</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11230,38 +11202,42 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562875</v>
+        <v>562940</v>
       </c>
       <c r="R101" t="n">
-        <v>7061433</v>
+        <v>7061272</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11291,9 +11267,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11308,22 +11294,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119836179</v>
+        <v>119838967</v>
       </c>
       <c r="B102" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11332,38 +11318,42 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562966</v>
+        <v>562990</v>
       </c>
       <c r="R102" t="n">
-        <v>7061336</v>
+        <v>7061060</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11393,9 +11383,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11410,22 +11410,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119835968</v>
+        <v>119835350</v>
       </c>
       <c r="B103" t="n">
-        <v>78526</v>
+        <v>78263</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11438,21 +11438,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11462,13 +11462,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562856</v>
+        <v>562801</v>
       </c>
       <c r="R103" t="n">
-        <v>7061341</v>
+        <v>7061274</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11512,22 +11512,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119836896</v>
+        <v>119835897</v>
       </c>
       <c r="B104" t="n">
-        <v>78526</v>
+        <v>79607</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11540,21 +11540,21 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11564,13 +11564,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562930</v>
+        <v>562851</v>
       </c>
       <c r="R104" t="n">
-        <v>7061333</v>
+        <v>7061350</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11600,11 +11600,6 @@
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11631,7 +11626,7 @@
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119835897</v>
+        <v>119835697</v>
       </c>
       <c r="B105" t="n">
         <v>79607</v>
@@ -11671,13 +11666,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562851</v>
+        <v>562826</v>
       </c>
       <c r="R105" t="n">
-        <v>7061350</v>
+        <v>7061341</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11733,10 +11728,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119835697</v>
+        <v>119836896</v>
       </c>
       <c r="B106" t="n">
-        <v>79607</v>
+        <v>78526</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11749,21 +11744,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11773,10 +11768,10 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562826</v>
+        <v>562930</v>
       </c>
       <c r="R106" t="n">
-        <v>7061341</v>
+        <v>7061333</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -11809,6 +11804,11 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC106" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12064,7 +12064,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119839212</v>
+        <v>119835470</v>
       </c>
       <c r="B109" t="n">
         <v>78526</v>
@@ -12100,17 +12100,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>563063</v>
+        <v>562839</v>
       </c>
       <c r="R109" t="n">
-        <v>7061037</v>
+        <v>7061260</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12137,19 +12137,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12164,22 +12154,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119840354</v>
+        <v>119837344</v>
       </c>
       <c r="B110" t="n">
-        <v>78526</v>
+        <v>57463</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12192,34 +12182,43 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M110" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P110" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>562893</v>
+        <v>562829</v>
       </c>
       <c r="R110" t="n">
-        <v>7061427</v>
+        <v>7061182</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12249,9 +12248,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12266,22 +12275,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119837344</v>
+        <v>119835654</v>
       </c>
       <c r="B111" t="n">
-        <v>57463</v>
+        <v>79636</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12290,50 +12299,41 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103021</v>
+        <v>6462</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562829</v>
+        <v>562838</v>
       </c>
       <c r="R111" t="n">
-        <v>7061182</v>
+        <v>7061333</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12360,19 +12360,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12387,19 +12377,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119835470</v>
+        <v>119839212</v>
       </c>
       <c r="B112" t="n">
         <v>78526</v>
@@ -12435,17 +12425,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>562839</v>
+        <v>563063</v>
       </c>
       <c r="R112" t="n">
-        <v>7061260</v>
+        <v>7061037</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12472,9 +12462,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12489,22 +12489,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119835654</v>
+        <v>119840354</v>
       </c>
       <c r="B113" t="n">
-        <v>79636</v>
+        <v>78526</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12513,25 +12513,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>6425</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562838</v>
+        <v>562893</v>
       </c>
       <c r="R113" t="n">
-        <v>7061333</v>
+        <v>7061427</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12837,10 +12837,10 @@
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119836311</v>
+        <v>119836367</v>
       </c>
       <c r="B116" t="n">
-        <v>97907</v>
+        <v>95455</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12849,25 +12849,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12877,10 +12877,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562972</v>
+        <v>562983</v>
       </c>
       <c r="R116" t="n">
-        <v>7061274</v>
+        <v>7061268</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -12913,11 +12913,6 @@
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12944,10 +12939,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119836284</v>
+        <v>119835514</v>
       </c>
       <c r="B117" t="n">
-        <v>97907</v>
+        <v>79607</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12956,45 +12951,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562903</v>
+        <v>562849</v>
       </c>
       <c r="R117" t="n">
-        <v>7061259</v>
+        <v>7061244</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13021,19 +13012,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13048,22 +13029,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119836367</v>
+        <v>119837383</v>
       </c>
       <c r="B118" t="n">
-        <v>95455</v>
+        <v>78526</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13076,21 +13057,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>53</v>
+        <v>6425</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13100,13 +13081,13 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562983</v>
+        <v>562779</v>
       </c>
       <c r="R118" t="n">
-        <v>7061268</v>
+        <v>7061176</v>
       </c>
       <c r="S118" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13162,10 +13143,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119835514</v>
+        <v>119837181</v>
       </c>
       <c r="B119" t="n">
-        <v>79607</v>
+        <v>90527</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13174,25 +13155,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13202,13 +13183,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>562849</v>
+        <v>562872</v>
       </c>
       <c r="R119" t="n">
-        <v>7061244</v>
+        <v>7061246</v>
       </c>
       <c r="S119" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13252,22 +13233,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119837383</v>
+        <v>119836311</v>
       </c>
       <c r="B120" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13276,25 +13257,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13304,13 +13285,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562779</v>
+        <v>562972</v>
       </c>
       <c r="R120" t="n">
-        <v>7061176</v>
+        <v>7061274</v>
       </c>
       <c r="S120" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13340,6 +13321,11 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC120" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13366,10 +13352,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119837181</v>
+        <v>119836284</v>
       </c>
       <c r="B121" t="n">
-        <v>90527</v>
+        <v>97907</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13378,38 +13364,42 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562872</v>
+        <v>562903</v>
       </c>
       <c r="R121" t="n">
-        <v>7061246</v>
+        <v>7061259</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13439,9 +13429,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13456,12 +13456,12 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -3207,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119837966</v>
+        <v>119839243</v>
       </c>
       <c r="B26" t="n">
-        <v>78171</v>
+        <v>97907</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,41 +3219,45 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562845</v>
+        <v>563074</v>
       </c>
       <c r="R26" t="n">
-        <v>7061093</v>
+        <v>7061022</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3280,9 +3284,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3297,22 +3311,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119838064</v>
+        <v>119838885</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,41 +3335,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562850</v>
+        <v>562977</v>
       </c>
       <c r="R27" t="n">
-        <v>7061098</v>
+        <v>7061045</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3382,9 +3400,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z27" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB27" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3399,22 +3427,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119837858</v>
+        <v>119837966</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>78171</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,25 +3451,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3451,13 +3479,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562847</v>
+        <v>562845</v>
       </c>
       <c r="R28" t="n">
-        <v>7061096</v>
+        <v>7061093</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3513,10 +3541,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839243</v>
+        <v>119838064</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,45 +3553,41 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563074</v>
+        <v>562850</v>
       </c>
       <c r="R29" t="n">
-        <v>7061022</v>
+        <v>7061098</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3590,19 +3614,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3617,22 +3631,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119838885</v>
+        <v>119835805</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3641,45 +3655,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562977</v>
+        <v>562873</v>
       </c>
       <c r="R30" t="n">
-        <v>7061045</v>
+        <v>7061226</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,19 +3716,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,22 +3733,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119835805</v>
+        <v>119837858</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>91840</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562873</v>
+        <v>562847</v>
       </c>
       <c r="R31" t="n">
-        <v>7061226</v>
+        <v>7061096</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3835,12 +3835,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -5130,10 +5130,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119839135</v>
+        <v>119836512</v>
       </c>
       <c r="B44" t="n">
-        <v>78262</v>
+        <v>97907</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5142,38 +5142,42 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P44" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562982</v>
+        <v>562925</v>
       </c>
       <c r="R44" t="n">
-        <v>7061063</v>
+        <v>7061308</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5205,7 +5209,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5215,7 +5219,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>18:21</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5242,10 +5246,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119835259</v>
+        <v>119836521</v>
       </c>
       <c r="B45" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5254,25 +5258,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5282,10 +5286,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562815</v>
+        <v>562928</v>
       </c>
       <c r="R45" t="n">
-        <v>7061302</v>
+        <v>7061305</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5332,12 +5336,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -5446,10 +5450,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119836512</v>
+        <v>119839135</v>
       </c>
       <c r="B47" t="n">
-        <v>97907</v>
+        <v>78262</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5458,42 +5462,38 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6446</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I47" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562925</v>
+        <v>562982</v>
       </c>
       <c r="R47" t="n">
-        <v>7061308</v>
+        <v>7061063</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5525,7 +5525,7 @@
       </c>
       <c r="Z47" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA47" t="inlineStr">
@@ -5535,7 +5535,7 @@
       </c>
       <c r="AB47" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5562,10 +5562,10 @@
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119836521</v>
+        <v>119835259</v>
       </c>
       <c r="B48" t="n">
-        <v>97907</v>
+        <v>78526</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5574,25 +5574,25 @@
       </c>
       <c r="D48" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E48" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5602,10 +5602,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562928</v>
+        <v>562815</v>
       </c>
       <c r="R48" t="n">
-        <v>7061305</v>
+        <v>7061302</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5652,12 +5652,12 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
@@ -7238,10 +7238,10 @@
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119835431</v>
+        <v>119838625</v>
       </c>
       <c r="B64" t="n">
-        <v>79607</v>
+        <v>91884</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7254,37 +7254,37 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>5449</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562853</v>
+        <v>562899</v>
       </c>
       <c r="R64" t="n">
-        <v>7061293</v>
+        <v>7061101</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7311,9 +7311,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z64" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB64" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7328,22 +7338,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119838625</v>
+        <v>119835431</v>
       </c>
       <c r="B65" t="n">
-        <v>91884</v>
+        <v>79607</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7356,37 +7366,37 @@
         </is>
       </c>
       <c r="E65" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
       <c r="P65" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562899</v>
+        <v>562853</v>
       </c>
       <c r="R65" t="n">
-        <v>7061101</v>
+        <v>7061293</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7413,19 +7423,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7440,12 +7440,12 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
@@ -8113,10 +8113,10 @@
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119837999</v>
+        <v>119840391</v>
       </c>
       <c r="B72" t="n">
-        <v>79144</v>
+        <v>79607</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8129,21 +8129,21 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6453</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
@@ -8153,13 +8153,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562848</v>
+        <v>562861</v>
       </c>
       <c r="R72" t="n">
-        <v>7061083</v>
+        <v>7061439</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8215,7 +8215,7 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119840391</v>
+        <v>119835638</v>
       </c>
       <c r="B73" t="n">
         <v>79607</v>
@@ -8255,13 +8255,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562861</v>
+        <v>562838</v>
       </c>
       <c r="R73" t="n">
-        <v>7061439</v>
+        <v>7061326</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8317,7 +8317,7 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119835638</v>
+        <v>119837306</v>
       </c>
       <c r="B74" t="n">
         <v>79607</v>
@@ -8357,13 +8357,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562838</v>
+        <v>562793</v>
       </c>
       <c r="R74" t="n">
-        <v>7061326</v>
+        <v>7061251</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8393,6 +8393,11 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC74" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8419,10 +8424,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119837306</v>
+        <v>119837999</v>
       </c>
       <c r="B75" t="n">
-        <v>79607</v>
+        <v>79144</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8435,21 +8440,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8459,13 +8464,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562793</v>
+        <v>562848</v>
       </c>
       <c r="R75" t="n">
-        <v>7061251</v>
+        <v>7061083</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8495,11 +8500,6 @@
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC75" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8526,10 +8526,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119836629</v>
+        <v>119836632</v>
       </c>
       <c r="B76" t="n">
-        <v>57310</v>
+        <v>97907</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8538,31 +8538,30 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr">
+        <is>
+          <t>30</t>
         </is>
       </c>
       <c r="P76" t="inlineStr">
@@ -8571,13 +8570,13 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562935</v>
+        <v>562948</v>
       </c>
       <c r="R76" t="n">
-        <v>7061315</v>
+        <v>7061323</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8604,19 +8603,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8631,19 +8620,19 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119836807</v>
+        <v>119836629</v>
       </c>
       <c r="B77" t="n">
         <v>57310</v>
@@ -8677,16 +8666,21 @@
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
+      <c r="M77" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562926</v>
+        <v>562935</v>
       </c>
       <c r="R77" t="n">
-        <v>7061340</v>
+        <v>7061315</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8718,7 +8712,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8728,12 +8722,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8760,10 +8749,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119836632</v>
+        <v>119836807</v>
       </c>
       <c r="B78" t="n">
-        <v>97907</v>
+        <v>57310</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8772,45 +8761,41 @@
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I78" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I78" t="inlineStr"/>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562948</v>
+        <v>562926</v>
       </c>
       <c r="R78" t="n">
-        <v>7061323</v>
+        <v>7061340</v>
       </c>
       <c r="S78" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T78" t="inlineStr">
         <is>
@@ -8837,9 +8822,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8854,12 +8854,12 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
@@ -12064,7 +12064,7 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119835470</v>
+        <v>119839212</v>
       </c>
       <c r="B109" t="n">
         <v>78526</v>
@@ -12100,17 +12100,17 @@
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>562839</v>
+        <v>563063</v>
       </c>
       <c r="R109" t="n">
-        <v>7061260</v>
+        <v>7061037</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12137,9 +12137,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12154,22 +12164,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119837344</v>
+        <v>119840354</v>
       </c>
       <c r="B110" t="n">
-        <v>57463</v>
+        <v>78526</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12182,43 +12192,34 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>562829</v>
+        <v>562893</v>
       </c>
       <c r="R110" t="n">
-        <v>7061182</v>
+        <v>7061427</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12248,19 +12249,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12275,22 +12266,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119835654</v>
+        <v>119837344</v>
       </c>
       <c r="B111" t="n">
-        <v>79636</v>
+        <v>57463</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12299,41 +12290,50 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6462</v>
+        <v>103021</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562838</v>
+        <v>562829</v>
       </c>
       <c r="R111" t="n">
-        <v>7061333</v>
+        <v>7061182</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12360,9 +12360,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12377,19 +12387,19 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119839212</v>
+        <v>119835470</v>
       </c>
       <c r="B112" t="n">
         <v>78526</v>
@@ -12425,17 +12435,17 @@
       <c r="I112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>563063</v>
+        <v>562839</v>
       </c>
       <c r="R112" t="n">
-        <v>7061037</v>
+        <v>7061260</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12462,19 +12472,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12489,22 +12489,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119840354</v>
+        <v>119835654</v>
       </c>
       <c r="B113" t="n">
-        <v>78526</v>
+        <v>79636</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12513,25 +12513,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6425</v>
+        <v>6462</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12541,13 +12541,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562893</v>
+        <v>562838</v>
       </c>
       <c r="R113" t="n">
-        <v>7061427</v>
+        <v>7061333</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -3207,10 +3207,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839243</v>
+        <v>119837966</v>
       </c>
       <c r="B26" t="n">
-        <v>97907</v>
+        <v>78171</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3219,45 +3219,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>353</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Hoffm.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563074</v>
+        <v>562845</v>
       </c>
       <c r="R26" t="n">
-        <v>7061022</v>
+        <v>7061093</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3284,19 +3280,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3311,22 +3297,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119838885</v>
+        <v>119838064</v>
       </c>
       <c r="B27" t="n">
-        <v>97907</v>
+        <v>91840</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3335,45 +3321,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562977</v>
+        <v>562850</v>
       </c>
       <c r="R27" t="n">
-        <v>7061045</v>
+        <v>7061098</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3400,19 +3382,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z27" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB27" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3427,22 +3399,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119837966</v>
+        <v>119837858</v>
       </c>
       <c r="B28" t="n">
-        <v>78171</v>
+        <v>91840</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3451,25 +3423,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>353</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3479,13 +3451,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562845</v>
+        <v>562847</v>
       </c>
       <c r="R28" t="n">
-        <v>7061093</v>
+        <v>7061096</v>
       </c>
       <c r="S28" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3541,10 +3513,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119838064</v>
+        <v>119839243</v>
       </c>
       <c r="B29" t="n">
-        <v>91840</v>
+        <v>97907</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3553,41 +3525,45 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562850</v>
+        <v>563074</v>
       </c>
       <c r="R29" t="n">
-        <v>7061098</v>
+        <v>7061022</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3614,9 +3590,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3631,22 +3617,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119835805</v>
+        <v>119838885</v>
       </c>
       <c r="B30" t="n">
-        <v>78526</v>
+        <v>97907</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3655,41 +3641,45 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562873</v>
+        <v>562977</v>
       </c>
       <c r="R30" t="n">
-        <v>7061226</v>
+        <v>7061045</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3716,9 +3706,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z30" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB30" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,22 +3733,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119837858</v>
+        <v>119835805</v>
       </c>
       <c r="B31" t="n">
-        <v>91840</v>
+        <v>78526</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3757,25 +3757,25 @@
       </c>
       <c r="D31" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E31" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3785,13 +3785,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562847</v>
+        <v>562873</v>
       </c>
       <c r="R31" t="n">
-        <v>7061096</v>
+        <v>7061226</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3835,12 +3835,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119837424</v>
+        <v>119839212</v>
       </c>
       <c r="B22" t="n">
-        <v>91840</v>
+        <v>78542</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,41 +2811,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562774</v>
+        <v>563063</v>
       </c>
       <c r="R22" t="n">
-        <v>7061178</v>
+        <v>7061037</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2872,9 +2872,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2889,22 +2899,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119839227</v>
+        <v>119835796</v>
       </c>
       <c r="B23" t="n">
-        <v>91840</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2913,25 +2923,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2941,10 +2951,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>563080</v>
+        <v>562830</v>
       </c>
       <c r="R23" t="n">
-        <v>7061030</v>
+        <v>7061321</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3003,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119837366</v>
+        <v>119835344</v>
       </c>
       <c r="B24" t="n">
-        <v>78526</v>
+        <v>90600</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3019,21 +3029,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3043,13 +3053,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562815</v>
+        <v>562790</v>
       </c>
       <c r="R24" t="n">
-        <v>7061177</v>
+        <v>7061258</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3076,9 +3086,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3093,22 +3113,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119840328</v>
+        <v>119838153</v>
       </c>
       <c r="B25" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3117,25 +3137,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3145,10 +3165,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562922</v>
+        <v>562865</v>
       </c>
       <c r="R25" t="n">
-        <v>7061399</v>
+        <v>7061107</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3181,6 +3201,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3207,10 +3232,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119837966</v>
+        <v>119838709</v>
       </c>
       <c r="B26" t="n">
-        <v>78171</v>
+        <v>91901</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3223,21 +3248,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>353</v>
+        <v>5448</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3247,13 +3272,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562845</v>
+        <v>562892</v>
       </c>
       <c r="R26" t="n">
-        <v>7061093</v>
+        <v>7061086</v>
       </c>
       <c r="S26" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3297,22 +3322,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119838064</v>
+        <v>119836424</v>
       </c>
       <c r="B27" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3321,38 +3346,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562850</v>
+        <v>562902</v>
       </c>
       <c r="R27" t="n">
-        <v>7061098</v>
+        <v>7061306</v>
       </c>
       <c r="S27" t="n">
         <v>15</v>
@@ -3399,22 +3428,22 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119837858</v>
+        <v>119838864</v>
       </c>
       <c r="B28" t="n">
-        <v>91840</v>
+        <v>78279</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3423,38 +3452,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562847</v>
+        <v>562940</v>
       </c>
       <c r="R28" t="n">
-        <v>7061096</v>
+        <v>7061021</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3484,9 +3513,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z28" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB28" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3501,22 +3540,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119839243</v>
+        <v>119837399</v>
       </c>
       <c r="B29" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3525,42 +3564,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>563074</v>
+        <v>562767</v>
       </c>
       <c r="R29" t="n">
-        <v>7061022</v>
+        <v>7061188</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3590,19 +3625,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>18:30</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>18:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3617,22 +3642,22 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119838885</v>
+        <v>119835431</v>
       </c>
       <c r="B30" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3641,45 +3666,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562977</v>
+        <v>562853</v>
       </c>
       <c r="R30" t="n">
-        <v>7061045</v>
+        <v>7061293</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3706,19 +3727,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z30" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA30" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB30" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3733,22 +3744,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119835805</v>
+        <v>119835259</v>
       </c>
       <c r="B31" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3785,10 +3796,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562873</v>
+        <v>562815</v>
       </c>
       <c r="R31" t="n">
-        <v>7061226</v>
+        <v>7061302</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3835,22 +3846,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119837761</v>
+        <v>119837858</v>
       </c>
       <c r="B32" t="n">
-        <v>78526</v>
+        <v>91858</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3859,25 +3870,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3887,10 +3898,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562816</v>
+        <v>562847</v>
       </c>
       <c r="R32" t="n">
-        <v>7061089</v>
+        <v>7061096</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3949,10 +3960,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119835742</v>
+        <v>119835697</v>
       </c>
       <c r="B33" t="n">
-        <v>56522</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3961,25 +3972,25 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E33" t="n">
-        <v>100138</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -3989,13 +4000,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562853</v>
+        <v>562826</v>
       </c>
       <c r="R33" t="n">
-        <v>7061243</v>
+        <v>7061341</v>
       </c>
       <c r="S33" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4039,22 +4050,22 @@
       <c r="AT33" t="inlineStr"/>
       <c r="AW33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX33" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119835751</v>
+        <v>119835360</v>
       </c>
       <c r="B34" t="n">
-        <v>79607</v>
+        <v>4766</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4063,25 +4074,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6458</v>
+        <v>100299</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4091,13 +4102,13 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562833</v>
+        <v>562801</v>
       </c>
       <c r="R34" t="n">
-        <v>7061339</v>
+        <v>7061292</v>
       </c>
       <c r="S34" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T34" t="inlineStr">
         <is>
@@ -4127,6 +4138,11 @@
       <c r="AA34" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC34" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD34" t="b">
@@ -4153,10 +4169,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119835495</v>
+        <v>119835654</v>
       </c>
       <c r="B35" t="n">
-        <v>79607</v>
+        <v>79652</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4165,25 +4181,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4193,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562822</v>
+        <v>562838</v>
       </c>
       <c r="R35" t="n">
-        <v>7061305</v>
+        <v>7061333</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4255,10 +4271,10 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119840392</v>
+        <v>119835495</v>
       </c>
       <c r="B36" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C36" t="inlineStr">
         <is>
@@ -4271,21 +4287,21 @@
         </is>
       </c>
       <c r="E36" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H36" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I36" t="inlineStr"/>
@@ -4295,13 +4311,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562878</v>
+        <v>562822</v>
       </c>
       <c r="R36" t="n">
-        <v>7061442</v>
+        <v>7061305</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4328,24 +4344,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z36" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
       <c r="AA36" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB36" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC36" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD36" t="b">
@@ -4360,22 +4361,22 @@
       <c r="AT36" t="inlineStr"/>
       <c r="AW36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX36" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119835980</v>
+        <v>119840373</v>
       </c>
       <c r="B37" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4388,39 +4389,34 @@
         </is>
       </c>
       <c r="E37" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
-      <c r="M37" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P37" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562885</v>
+        <v>562875</v>
       </c>
       <c r="R37" t="n">
-        <v>7061225</v>
+        <v>7061433</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4450,19 +4446,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z37" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB37" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4477,22 +4463,22 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119838102</v>
+        <v>119835350</v>
       </c>
       <c r="B38" t="n">
-        <v>57463</v>
+        <v>78279</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4505,42 +4491,37 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>103021</v>
+        <v>228912</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
-      <c r="M38" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P38" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562863</v>
+        <v>562801</v>
       </c>
       <c r="R38" t="n">
-        <v>7061098</v>
+        <v>7061274</v>
       </c>
       <c r="S38" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4584,22 +4565,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119836533</v>
+        <v>119839757</v>
       </c>
       <c r="B39" t="n">
-        <v>97907</v>
+        <v>57336</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4608,45 +4589,41 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I39" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I39" t="inlineStr"/>
       <c r="P39" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562927</v>
+        <v>563104</v>
       </c>
       <c r="R39" t="n">
-        <v>7061314</v>
+        <v>7061110</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4673,19 +4650,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z39" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB39" t="inlineStr">
-        <is>
-          <t>16:17</t>
+      <c r="AC39" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4700,22 +4672,22 @@
       <c r="AT39" t="inlineStr"/>
       <c r="AW39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX39" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119837494</v>
+        <v>119836896</v>
       </c>
       <c r="B40" t="n">
-        <v>89633</v>
+        <v>78542</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4728,21 +4700,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>1962</v>
+        <v>6425</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4752,13 +4724,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562773</v>
+        <v>562930</v>
       </c>
       <c r="R40" t="n">
-        <v>7061158</v>
+        <v>7061333</v>
       </c>
       <c r="S40" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4788,6 +4760,11 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC40" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4814,10 +4791,10 @@
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119839184</v>
+        <v>119840391</v>
       </c>
       <c r="B41" t="n">
-        <v>91840</v>
+        <v>79623</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4826,25 +4803,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4854,13 +4831,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>563009</v>
+        <v>562861</v>
       </c>
       <c r="R41" t="n">
-        <v>7061040</v>
+        <v>7061439</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4916,10 +4893,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119837543</v>
+        <v>119836179</v>
       </c>
       <c r="B42" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4956,10 +4933,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562745</v>
+        <v>562966</v>
       </c>
       <c r="R42" t="n">
-        <v>7061152</v>
+        <v>7061336</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4989,19 +4966,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z42" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB42" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -5016,22 +4983,22 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119836005</v>
+        <v>119840354</v>
       </c>
       <c r="B43" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5068,13 +5035,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562898</v>
+        <v>562893</v>
       </c>
       <c r="R43" t="n">
-        <v>7061215</v>
+        <v>7061427</v>
       </c>
       <c r="S43" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5118,22 +5085,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119836512</v>
+        <v>119836533</v>
       </c>
       <c r="B44" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5165,7 +5132,7 @@
       </c>
       <c r="I44" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P44" t="inlineStr">
@@ -5174,10 +5141,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562925</v>
+        <v>562927</v>
       </c>
       <c r="R44" t="n">
-        <v>7061308</v>
+        <v>7061314</v>
       </c>
       <c r="S44" t="n">
         <v>10</v>
@@ -5209,7 +5176,7 @@
       </c>
       <c r="Z44" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AA44" t="inlineStr">
@@ -5219,7 +5186,7 @@
       </c>
       <c r="AB44" t="inlineStr">
         <is>
-          <t>16:16</t>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5246,10 +5213,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119836521</v>
+        <v>119836512</v>
       </c>
       <c r="B45" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5279,20 +5246,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562928</v>
+        <v>562925</v>
       </c>
       <c r="R45" t="n">
-        <v>7061305</v>
+        <v>7061308</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5319,9 +5290,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>16:16</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5336,22 +5317,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119838872</v>
+        <v>119836491</v>
       </c>
       <c r="B46" t="n">
-        <v>91834</v>
+        <v>97930</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5360,25 +5341,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5388,10 +5369,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562893</v>
+        <v>563040</v>
       </c>
       <c r="R46" t="n">
-        <v>7061059</v>
+        <v>7061203</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5450,10 +5431,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119839135</v>
+        <v>119837066</v>
       </c>
       <c r="B47" t="n">
-        <v>78262</v>
+        <v>97930</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5462,41 +5443,41 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6446</v>
+        <v>220787</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562982</v>
+        <v>562940</v>
       </c>
       <c r="R47" t="n">
-        <v>7061063</v>
+        <v>7061261</v>
       </c>
       <c r="S47" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5523,19 +5504,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z47" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB47" t="inlineStr">
-        <is>
-          <t>18:21</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5550,22 +5521,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119835259</v>
+        <v>119837216</v>
       </c>
       <c r="B48" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5602,10 +5573,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562815</v>
+        <v>562857</v>
       </c>
       <c r="R48" t="n">
-        <v>7061302</v>
+        <v>7061235</v>
       </c>
       <c r="S48" t="n">
         <v>15</v>
@@ -5638,6 +5609,11 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5664,10 +5640,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119838709</v>
+        <v>119837761</v>
       </c>
       <c r="B49" t="n">
-        <v>91883</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5680,21 +5656,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>5448</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5704,13 +5680,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562892</v>
+        <v>562816</v>
       </c>
       <c r="R49" t="n">
-        <v>7061086</v>
+        <v>7061089</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5754,22 +5730,22 @@
       <c r="AT49" t="inlineStr"/>
       <c r="AW49" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX49" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119838571</v>
+        <v>119836358</v>
       </c>
       <c r="B50" t="n">
-        <v>91884</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5782,37 +5758,37 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>5449</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
       <c r="P50" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562856</v>
+        <v>562901</v>
       </c>
       <c r="R50" t="n">
-        <v>7061099</v>
+        <v>7061289</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5839,19 +5815,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z50" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA50" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB50" t="inlineStr">
-        <is>
-          <t>17:44</t>
         </is>
       </c>
       <c r="AD50" t="b">
@@ -5866,22 +5832,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119838859</v>
+        <v>119837543</v>
       </c>
       <c r="B51" t="n">
-        <v>91883</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5894,21 +5860,21 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>5448</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
@@ -5918,10 +5884,10 @@
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562897</v>
+        <v>562745</v>
       </c>
       <c r="R51" t="n">
-        <v>7061087</v>
+        <v>7061152</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5951,9 +5917,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z51" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB51" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5968,22 +5944,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119835360</v>
+        <v>119836923</v>
       </c>
       <c r="B52" t="n">
-        <v>4766</v>
+        <v>57320</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5992,41 +5968,41 @@
       </c>
       <c r="D52" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100299</v>
+        <v>100109</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562801</v>
+        <v>562958</v>
       </c>
       <c r="R52" t="n">
-        <v>7061292</v>
+        <v>7061345</v>
       </c>
       <c r="S52" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6053,14 +6029,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z52" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB52" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AC52" t="inlineStr">
         <is>
-          <t>Gnaggångar</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6075,22 +6061,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119837216</v>
+        <v>119835980</v>
       </c>
       <c r="B53" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6103,37 +6089,42 @@
         </is>
       </c>
       <c r="E53" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562857</v>
+        <v>562885</v>
       </c>
       <c r="R53" t="n">
-        <v>7061235</v>
+        <v>7061225</v>
       </c>
       <c r="S53" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6160,14 +6151,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z53" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC53" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB53" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6182,22 +6178,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119837899</v>
+        <v>119836807</v>
       </c>
       <c r="B54" t="n">
-        <v>91840</v>
+        <v>57320</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6206,25 +6202,25 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
@@ -6234,10 +6230,10 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562848</v>
+        <v>562926</v>
       </c>
       <c r="R54" t="n">
-        <v>7061087</v>
+        <v>7061340</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6267,9 +6263,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC54" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6284,22 +6295,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119838153</v>
+        <v>119837193</v>
       </c>
       <c r="B55" t="n">
-        <v>91840</v>
+        <v>57320</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6308,25 +6319,25 @@
       </c>
       <c r="D55" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E55" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6336,13 +6347,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562865</v>
+        <v>562864</v>
       </c>
       <c r="R55" t="n">
-        <v>7061107</v>
+        <v>7061224</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6376,7 +6387,7 @@
       </c>
       <c r="AC55" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6391,22 +6402,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119837560</v>
+        <v>119838064</v>
       </c>
       <c r="B56" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6415,25 +6426,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6443,10 +6454,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562746</v>
+        <v>562850</v>
       </c>
       <c r="R56" t="n">
-        <v>7061142</v>
+        <v>7061098</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6493,22 +6504,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119835108</v>
+        <v>119838957</v>
       </c>
       <c r="B57" t="n">
-        <v>79607</v>
+        <v>91852</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6521,21 +6532,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6545,13 +6556,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562802</v>
+        <v>562888</v>
       </c>
       <c r="R57" t="n">
-        <v>7061280</v>
+        <v>7061052</v>
       </c>
       <c r="S57" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6595,22 +6606,22 @@
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119838864</v>
+        <v>119838865</v>
       </c>
       <c r="B58" t="n">
-        <v>78263</v>
+        <v>91858</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6619,41 +6630,41 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562940</v>
+        <v>562942</v>
       </c>
       <c r="R58" t="n">
-        <v>7061021</v>
+        <v>7061029</v>
       </c>
       <c r="S58" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6680,19 +6691,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z58" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB58" t="inlineStr">
-        <is>
-          <t>18:00</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6707,22 +6708,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119836424</v>
+        <v>119838859</v>
       </c>
       <c r="B59" t="n">
-        <v>97907</v>
+        <v>91901</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6731,45 +6732,41 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562902</v>
+        <v>562897</v>
       </c>
       <c r="R59" t="n">
-        <v>7061306</v>
+        <v>7061087</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6813,22 +6810,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119837193</v>
+        <v>119838885</v>
       </c>
       <c r="B60" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6837,41 +6834,45 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562864</v>
+        <v>562977</v>
       </c>
       <c r="R60" t="n">
-        <v>7061224</v>
+        <v>7061045</v>
       </c>
       <c r="S60" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6898,14 +6899,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6920,22 +6926,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119838327</v>
+        <v>119836632</v>
       </c>
       <c r="B61" t="n">
-        <v>91840</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6944,38 +6950,42 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562870</v>
+        <v>562948</v>
       </c>
       <c r="R61" t="n">
-        <v>7061110</v>
+        <v>7061323</v>
       </c>
       <c r="S61" t="n">
         <v>15</v>
@@ -7034,10 +7044,10 @@
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119838597</v>
+        <v>119836629</v>
       </c>
       <c r="B62" t="n">
-        <v>91840</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7046,41 +7056,46 @@
       </c>
       <c r="D62" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E62" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562861</v>
+        <v>562935</v>
       </c>
       <c r="R62" t="n">
-        <v>7061099</v>
+        <v>7061315</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7107,9 +7122,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7124,22 +7149,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119838865</v>
+        <v>119839228</v>
       </c>
       <c r="B63" t="n">
-        <v>91840</v>
+        <v>57320</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7148,41 +7173,41 @@
       </c>
       <c r="D63" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E63" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562942</v>
+        <v>563061</v>
       </c>
       <c r="R63" t="n">
-        <v>7061029</v>
+        <v>7061025</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7209,9 +7234,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC63" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7226,22 +7266,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119838625</v>
+        <v>119838597</v>
       </c>
       <c r="B64" t="n">
-        <v>91884</v>
+        <v>91858</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7250,41 +7290,41 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>5449</v>
+        <v>4364</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
       <c r="P64" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562899</v>
+        <v>562861</v>
       </c>
       <c r="R64" t="n">
-        <v>7061101</v>
+        <v>7061099</v>
       </c>
       <c r="S64" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7311,19 +7351,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z64" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB64" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7338,22 +7368,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119835431</v>
+        <v>119838327</v>
       </c>
       <c r="B65" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7362,25 +7392,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7390,10 +7420,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562853</v>
+        <v>562870</v>
       </c>
       <c r="R65" t="n">
-        <v>7061293</v>
+        <v>7061110</v>
       </c>
       <c r="S65" t="n">
         <v>15</v>
@@ -7452,10 +7482,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119838179</v>
+        <v>119836373</v>
       </c>
       <c r="B66" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7464,41 +7494,45 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562854</v>
+        <v>562910</v>
       </c>
       <c r="R66" t="n">
-        <v>7061121</v>
+        <v>7061306</v>
       </c>
       <c r="S66" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7525,9 +7559,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7542,22 +7586,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119838242</v>
+        <v>119837494</v>
       </c>
       <c r="B67" t="n">
-        <v>57310</v>
+        <v>89650</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7570,21 +7614,21 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>1962</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
@@ -7594,13 +7638,13 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562827</v>
+        <v>562773</v>
       </c>
       <c r="R67" t="n">
-        <v>7061123</v>
+        <v>7061158</v>
       </c>
       <c r="S67" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7627,24 +7671,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7659,22 +7688,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119837299</v>
+        <v>119835531</v>
       </c>
       <c r="B68" t="n">
-        <v>82305</v>
+        <v>79623</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7687,21 +7716,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1312</v>
+        <v>6458</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7711,13 +7740,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562843</v>
+        <v>562827</v>
       </c>
       <c r="R68" t="n">
-        <v>7061204</v>
+        <v>7061302</v>
       </c>
       <c r="S68" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7744,19 +7773,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>16:52</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7771,22 +7790,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119836373</v>
+        <v>119836005</v>
       </c>
       <c r="B69" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7795,45 +7814,41 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562910</v>
+        <v>562898</v>
       </c>
       <c r="R69" t="n">
-        <v>7061306</v>
+        <v>7061215</v>
       </c>
       <c r="S69" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7860,19 +7875,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z69" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB69" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7887,22 +7892,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119835796</v>
+        <v>119835108</v>
       </c>
       <c r="B70" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7939,13 +7944,13 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562830</v>
+        <v>562802</v>
       </c>
       <c r="R70" t="n">
-        <v>7061321</v>
+        <v>7061280</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7989,22 +7994,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119835344</v>
+        <v>119835638</v>
       </c>
       <c r="B71" t="n">
-        <v>90582</v>
+        <v>79623</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8017,21 +8022,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>5442</v>
+        <v>6458</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8041,13 +8046,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562790</v>
+        <v>562838</v>
       </c>
       <c r="R71" t="n">
-        <v>7061258</v>
+        <v>7061326</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8074,19 +8079,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8101,22 +8096,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119840391</v>
+        <v>119840261</v>
       </c>
       <c r="B72" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8129,34 +8124,34 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562861</v>
+        <v>563003</v>
       </c>
       <c r="R72" t="n">
-        <v>7061439</v>
+        <v>7061318</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8186,9 +8181,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z72" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB72" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC72" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8203,22 +8213,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119835638</v>
+        <v>119835631</v>
       </c>
       <c r="B73" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8231,21 +8241,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8255,13 +8265,13 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562838</v>
+        <v>562785</v>
       </c>
       <c r="R73" t="n">
-        <v>7061326</v>
+        <v>7061238</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8288,9 +8298,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC73" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8305,22 +8330,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119837306</v>
+        <v>119836367</v>
       </c>
       <c r="B74" t="n">
-        <v>79607</v>
+        <v>95478</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8333,21 +8358,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8357,13 +8382,13 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562793</v>
+        <v>562983</v>
       </c>
       <c r="R74" t="n">
-        <v>7061251</v>
+        <v>7061268</v>
       </c>
       <c r="S74" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8393,11 +8418,6 @@
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8424,10 +8444,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119837999</v>
+        <v>119835742</v>
       </c>
       <c r="B75" t="n">
-        <v>79144</v>
+        <v>56532</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8436,25 +8456,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6453</v>
+        <v>100138</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8464,10 +8484,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562848</v>
+        <v>562853</v>
       </c>
       <c r="R75" t="n">
-        <v>7061083</v>
+        <v>7061243</v>
       </c>
       <c r="S75" t="n">
         <v>15</v>
@@ -8514,22 +8534,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119836632</v>
+        <v>119836952</v>
       </c>
       <c r="B76" t="n">
-        <v>97907</v>
+        <v>82321</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8538,45 +8558,41 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562948</v>
+        <v>562955</v>
       </c>
       <c r="R76" t="n">
-        <v>7061323</v>
+        <v>7061332</v>
       </c>
       <c r="S76" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8603,9 +8619,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z76" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB76" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8620,22 +8646,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119836629</v>
+        <v>119838606</v>
       </c>
       <c r="B77" t="n">
-        <v>57310</v>
+        <v>78278</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8648,39 +8674,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
-      <c r="M77" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P77" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562935</v>
+        <v>562879</v>
       </c>
       <c r="R77" t="n">
-        <v>7061315</v>
+        <v>7061091</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8710,19 +8731,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z77" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB77" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8737,22 +8748,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119836807</v>
+        <v>119835968</v>
       </c>
       <c r="B78" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8765,21 +8776,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8789,10 +8800,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562926</v>
+        <v>562856</v>
       </c>
       <c r="R78" t="n">
-        <v>7061340</v>
+        <v>7061341</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8822,24 +8833,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC78" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8854,22 +8850,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119835531</v>
+        <v>119836521</v>
       </c>
       <c r="B79" t="n">
-        <v>79607</v>
+        <v>97930</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8878,25 +8874,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8906,10 +8902,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562827</v>
+        <v>562928</v>
       </c>
       <c r="R79" t="n">
-        <v>7061302</v>
+        <v>7061305</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8956,22 +8952,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119837084</v>
+        <v>119837427</v>
       </c>
       <c r="B80" t="n">
-        <v>90582</v>
+        <v>91858</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8980,25 +8976,25 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9008,13 +9004,13 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562905</v>
+        <v>562772</v>
       </c>
       <c r="R80" t="n">
-        <v>7061251</v>
+        <v>7061165</v>
       </c>
       <c r="S80" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T80" t="inlineStr">
         <is>
@@ -9041,9 +9037,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z80" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB80" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9058,22 +9064,22 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119839757</v>
+        <v>119837999</v>
       </c>
       <c r="B81" t="n">
-        <v>57326</v>
+        <v>79160</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9086,21 +9092,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>100049</v>
+        <v>6453</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9110,13 +9116,13 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>563104</v>
+        <v>562848</v>
       </c>
       <c r="R81" t="n">
-        <v>7061110</v>
+        <v>7061083</v>
       </c>
       <c r="S81" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9146,11 +9152,6 @@
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC81" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9177,10 +9178,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119836719</v>
+        <v>119835500</v>
       </c>
       <c r="B82" t="n">
-        <v>90562</v>
+        <v>79623</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9193,21 +9194,21 @@
         </is>
       </c>
       <c r="E82" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9217,10 +9218,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>562937</v>
+        <v>562824</v>
       </c>
       <c r="R82" t="n">
-        <v>7061312</v>
+        <v>7061319</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9267,22 +9268,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119836358</v>
+        <v>119837298</v>
       </c>
       <c r="B83" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9319,10 +9320,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562901</v>
+        <v>562841</v>
       </c>
       <c r="R83" t="n">
-        <v>7061289</v>
+        <v>7061196</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9381,10 +9382,10 @@
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119835535</v>
+        <v>119837560</v>
       </c>
       <c r="B84" t="n">
-        <v>91840</v>
+        <v>79623</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9393,25 +9394,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9421,13 +9422,13 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562795</v>
+        <v>562746</v>
       </c>
       <c r="R84" t="n">
-        <v>7061238</v>
+        <v>7061142</v>
       </c>
       <c r="S84" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9454,19 +9455,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z84" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB84" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9481,22 +9472,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119836491</v>
+        <v>119837074</v>
       </c>
       <c r="B85" t="n">
-        <v>97907</v>
+        <v>97930</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9526,20 +9517,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I85" t="inlineStr"/>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563040</v>
+        <v>562940</v>
       </c>
       <c r="R85" t="n">
-        <v>7061203</v>
+        <v>7061272</v>
       </c>
       <c r="S85" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T85" t="inlineStr">
         <is>
@@ -9566,9 +9561,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z85" t="inlineStr">
+        <is>
+          <t>16:40</t>
+        </is>
+      </c>
       <c r="AA85" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB85" t="inlineStr">
+        <is>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9583,22 +9588,22 @@
       <c r="AT85" t="inlineStr"/>
       <c r="AW85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX85" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119837992</v>
+        <v>119838102</v>
       </c>
       <c r="B86" t="n">
-        <v>79607</v>
+        <v>57473</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9611,37 +9616,42 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>562845</v>
+        <v>562863</v>
       </c>
       <c r="R86" t="n">
-        <v>7061115</v>
+        <v>7061098</v>
       </c>
       <c r="S86" t="n">
-        <v>15</v>
+        <v>25</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9685,22 +9695,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119836923</v>
+        <v>119840392</v>
       </c>
       <c r="B87" t="n">
-        <v>57310</v>
+        <v>57320</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9733,14 +9743,14 @@
       <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>562958</v>
+        <v>562878</v>
       </c>
       <c r="R87" t="n">
-        <v>7061345</v>
+        <v>7061442</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9772,7 +9782,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9782,7 +9792,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>16:32</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AC87" t="inlineStr">
@@ -9814,10 +9824,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119837066</v>
+        <v>119835516</v>
       </c>
       <c r="B88" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9826,25 +9836,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9854,13 +9864,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562940</v>
+        <v>562795</v>
       </c>
       <c r="R88" t="n">
-        <v>7061261</v>
+        <v>7061238</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9887,9 +9897,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC88" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9904,22 +9929,22 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119837298</v>
+        <v>119835470</v>
       </c>
       <c r="B89" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9956,10 +9981,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>562841</v>
+        <v>562839</v>
       </c>
       <c r="R89" t="n">
-        <v>7061196</v>
+        <v>7061260</v>
       </c>
       <c r="S89" t="n">
         <v>15</v>
@@ -10018,10 +10043,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119838606</v>
+        <v>119837366</v>
       </c>
       <c r="B90" t="n">
-        <v>78262</v>
+        <v>78542</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10034,21 +10059,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6446</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10058,13 +10083,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562879</v>
+        <v>562815</v>
       </c>
       <c r="R90" t="n">
-        <v>7061091</v>
+        <v>7061177</v>
       </c>
       <c r="S90" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10108,22 +10133,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119835631</v>
+        <v>119838571</v>
       </c>
       <c r="B91" t="n">
-        <v>57310</v>
+        <v>91902</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10136,34 +10161,34 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562785</v>
+        <v>562856</v>
       </c>
       <c r="R91" t="n">
-        <v>7061238</v>
+        <v>7061099</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10195,7 +10220,7 @@
       </c>
       <c r="Z91" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
@@ -10205,12 +10230,7 @@
       </c>
       <c r="AB91" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10237,10 +10257,10 @@
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119837399</v>
+        <v>119837992</v>
       </c>
       <c r="B92" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10277,13 +10297,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562767</v>
+        <v>562845</v>
       </c>
       <c r="R92" t="n">
-        <v>7061188</v>
+        <v>7061115</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10327,22 +10347,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119837427</v>
+        <v>119835535</v>
       </c>
       <c r="B93" t="n">
-        <v>91840</v>
+        <v>91858</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10379,10 +10399,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>562772</v>
+        <v>562795</v>
       </c>
       <c r="R93" t="n">
-        <v>7061165</v>
+        <v>7061238</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10414,7 +10434,7 @@
       </c>
       <c r="Z93" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
@@ -10424,7 +10444,7 @@
       </c>
       <c r="AB93" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10451,10 +10471,10 @@
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119835500</v>
+        <v>119837899</v>
       </c>
       <c r="B94" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10463,25 +10483,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10491,13 +10511,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562824</v>
+        <v>562848</v>
       </c>
       <c r="R94" t="n">
-        <v>7061319</v>
+        <v>7061087</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10553,10 +10573,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119840373</v>
+        <v>119835897</v>
       </c>
       <c r="B95" t="n">
-        <v>79607</v>
+        <v>79623</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10593,13 +10613,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562875</v>
+        <v>562851</v>
       </c>
       <c r="R95" t="n">
-        <v>7061433</v>
+        <v>7061350</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10655,10 +10675,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119836179</v>
+        <v>119835763</v>
       </c>
       <c r="B96" t="n">
-        <v>78526</v>
+        <v>78542</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10695,10 +10715,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>562966</v>
+        <v>562859</v>
       </c>
       <c r="R96" t="n">
-        <v>7061336</v>
+        <v>7061254</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10728,9 +10748,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10745,22 +10775,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119835968</v>
+        <v>119838030</v>
       </c>
       <c r="B97" t="n">
-        <v>78526</v>
+        <v>57320</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10773,34 +10803,39 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562856</v>
+        <v>562828</v>
       </c>
       <c r="R97" t="n">
-        <v>7061341</v>
+        <v>7061089</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10830,9 +10865,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10847,22 +10892,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119836952</v>
+        <v>119837181</v>
       </c>
       <c r="B98" t="n">
-        <v>82305</v>
+        <v>90545</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10871,38 +10916,38 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>1312</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562955</v>
+        <v>562872</v>
       </c>
       <c r="R98" t="n">
-        <v>7061332</v>
+        <v>7061246</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10932,19 +10977,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>16:35</t>
-        </is>
-      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>16:35</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10959,22 +10994,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119840300</v>
+        <v>119836311</v>
       </c>
       <c r="B99" t="n">
-        <v>78526</v>
+        <v>97930</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10983,25 +11018,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11011,13 +11046,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562938</v>
+        <v>562972</v>
       </c>
       <c r="R99" t="n">
-        <v>7061384</v>
+        <v>7061274</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11047,6 +11082,11 @@
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC99" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11073,10 +11113,10 @@
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119835516</v>
+        <v>119836284</v>
       </c>
       <c r="B100" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11085,38 +11125,42 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P100" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562795</v>
+        <v>562903</v>
       </c>
       <c r="R100" t="n">
-        <v>7061238</v>
+        <v>7061259</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11148,7 +11192,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:30</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11158,12 +11202,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC100" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11190,10 +11229,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119837074</v>
+        <v>119837512</v>
       </c>
       <c r="B101" t="n">
-        <v>97907</v>
+        <v>57320</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11202,42 +11241,38 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562940</v>
+        <v>562769</v>
       </c>
       <c r="R101" t="n">
-        <v>7061272</v>
+        <v>7061157</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11269,7 +11304,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11279,7 +11314,12 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC101" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11306,10 +11346,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119838967</v>
+        <v>119837344</v>
       </c>
       <c r="B102" t="n">
-        <v>97907</v>
+        <v>57473</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11318,42 +11358,47 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M102" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562990</v>
+        <v>562829</v>
       </c>
       <c r="R102" t="n">
-        <v>7061060</v>
+        <v>7061182</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11385,7 +11430,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11395,7 +11440,7 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11422,10 +11467,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119835350</v>
+        <v>119838242</v>
       </c>
       <c r="B103" t="n">
-        <v>78263</v>
+        <v>57320</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11438,21 +11483,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11462,13 +11507,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562801</v>
+        <v>562827</v>
       </c>
       <c r="R103" t="n">
-        <v>7061274</v>
+        <v>7061123</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11495,9 +11540,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC103" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11512,22 +11572,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119835897</v>
+        <v>119837424</v>
       </c>
       <c r="B104" t="n">
-        <v>79607</v>
+        <v>91858</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11536,25 +11596,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11564,10 +11624,10 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562851</v>
+        <v>562774</v>
       </c>
       <c r="R104" t="n">
-        <v>7061350</v>
+        <v>7061178</v>
       </c>
       <c r="S104" t="n">
         <v>15</v>
@@ -11614,22 +11674,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119835697</v>
+        <v>119838872</v>
       </c>
       <c r="B105" t="n">
-        <v>79607</v>
+        <v>91852</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11642,21 +11702,21 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>4362</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -11666,13 +11726,13 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562826</v>
+        <v>562893</v>
       </c>
       <c r="R105" t="n">
-        <v>7061341</v>
+        <v>7061059</v>
       </c>
       <c r="S105" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11728,10 +11788,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119836896</v>
+        <v>119837084</v>
       </c>
       <c r="B106" t="n">
-        <v>78526</v>
+        <v>90600</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11744,21 +11804,21 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -11768,13 +11828,13 @@
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562930</v>
+        <v>562905</v>
       </c>
       <c r="R106" t="n">
-        <v>7061333</v>
+        <v>7061251</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11804,11 +11864,6 @@
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC106" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11835,10 +11890,10 @@
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119835763</v>
+        <v>119836719</v>
       </c>
       <c r="B107" t="n">
-        <v>78526</v>
+        <v>90580</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11851,21 +11906,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -11875,13 +11930,13 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>562859</v>
+        <v>562937</v>
       </c>
       <c r="R107" t="n">
-        <v>7061254</v>
+        <v>7061312</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11908,19 +11963,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11935,22 +11980,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119838030</v>
+        <v>119840328</v>
       </c>
       <c r="B108" t="n">
-        <v>57310</v>
+        <v>79623</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -11963,39 +12008,34 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
-      <c r="M108" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>562828</v>
+        <v>562922</v>
       </c>
       <c r="R108" t="n">
-        <v>7061089</v>
+        <v>7061399</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12025,19 +12065,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z108" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB108" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12052,22 +12082,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119839212</v>
+        <v>119839135</v>
       </c>
       <c r="B109" t="n">
-        <v>78526</v>
+        <v>78278</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12080,21 +12110,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>6446</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12104,10 +12134,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>563063</v>
+        <v>562982</v>
       </c>
       <c r="R109" t="n">
-        <v>7061037</v>
+        <v>7061063</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12139,7 +12169,7 @@
       </c>
       <c r="Z109" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
@@ -12149,7 +12179,7 @@
       </c>
       <c r="AB109" t="inlineStr">
         <is>
-          <t>18:26</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12176,10 +12206,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119840354</v>
+        <v>119835514</v>
       </c>
       <c r="B110" t="n">
-        <v>78526</v>
+        <v>79623</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12192,21 +12222,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12216,13 +12246,13 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>562893</v>
+        <v>562849</v>
       </c>
       <c r="R110" t="n">
-        <v>7061427</v>
+        <v>7061244</v>
       </c>
       <c r="S110" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12266,22 +12296,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119837344</v>
+        <v>119835805</v>
       </c>
       <c r="B111" t="n">
-        <v>57463</v>
+        <v>78542</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12294,46 +12324,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562829</v>
+        <v>562873</v>
       </c>
       <c r="R111" t="n">
-        <v>7061182</v>
+        <v>7061226</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12360,19 +12381,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12387,22 +12398,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119835470</v>
+        <v>119837299</v>
       </c>
       <c r="B112" t="n">
-        <v>78526</v>
+        <v>82321</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12415,21 +12426,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12439,13 +12450,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>562839</v>
+        <v>562843</v>
       </c>
       <c r="R112" t="n">
-        <v>7061260</v>
+        <v>7061204</v>
       </c>
       <c r="S112" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12472,9 +12483,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z112" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB112" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12489,22 +12510,22 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119835654</v>
+        <v>119835751</v>
       </c>
       <c r="B113" t="n">
-        <v>79636</v>
+        <v>79623</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12513,25 +12534,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12541,13 +12562,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562838</v>
+        <v>562833</v>
       </c>
       <c r="R113" t="n">
-        <v>7061333</v>
+        <v>7061339</v>
       </c>
       <c r="S113" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12603,10 +12624,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119837856</v>
+        <v>119838179</v>
       </c>
       <c r="B114" t="n">
-        <v>57310</v>
+        <v>78542</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12619,37 +12640,37 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>562803</v>
+        <v>562854</v>
       </c>
       <c r="R114" t="n">
-        <v>7061104</v>
+        <v>7061121</v>
       </c>
       <c r="S114" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12676,24 +12697,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z114" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB114" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12708,22 +12714,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119837512</v>
+        <v>119839184</v>
       </c>
       <c r="B115" t="n">
-        <v>57310</v>
+        <v>91858</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12732,25 +12738,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12760,13 +12766,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>562769</v>
+        <v>563009</v>
       </c>
       <c r="R115" t="n">
-        <v>7061157</v>
+        <v>7061040</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12793,24 +12799,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC115" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12825,22 +12816,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119836367</v>
+        <v>119839227</v>
       </c>
       <c r="B116" t="n">
-        <v>95455</v>
+        <v>91858</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12849,25 +12840,25 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>53</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr"/>
@@ -12877,13 +12868,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562983</v>
+        <v>563080</v>
       </c>
       <c r="R116" t="n">
-        <v>7061268</v>
+        <v>7061030</v>
       </c>
       <c r="S116" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12939,10 +12930,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119835514</v>
+        <v>119837856</v>
       </c>
       <c r="B117" t="n">
-        <v>79607</v>
+        <v>57320</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12955,37 +12946,37 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562849</v>
+        <v>562803</v>
       </c>
       <c r="R117" t="n">
-        <v>7061244</v>
+        <v>7061104</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13012,9 +13003,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13029,22 +13035,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119837383</v>
+        <v>119837966</v>
       </c>
       <c r="B118" t="n">
-        <v>78526</v>
+        <v>78187</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13057,21 +13063,21 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
@@ -13081,10 +13087,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562779</v>
+        <v>562845</v>
       </c>
       <c r="R118" t="n">
-        <v>7061176</v>
+        <v>7061093</v>
       </c>
       <c r="S118" t="n">
         <v>20</v>
@@ -13143,10 +13149,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119837181</v>
+        <v>119837383</v>
       </c>
       <c r="B119" t="n">
-        <v>90527</v>
+        <v>78542</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13155,25 +13161,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5447</v>
+        <v>6425</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13183,13 +13189,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>562872</v>
+        <v>562779</v>
       </c>
       <c r="R119" t="n">
-        <v>7061246</v>
+        <v>7061176</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13245,10 +13251,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119836311</v>
+        <v>119840300</v>
       </c>
       <c r="B120" t="n">
-        <v>97907</v>
+        <v>78542</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13257,25 +13263,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13285,13 +13291,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562972</v>
+        <v>562938</v>
       </c>
       <c r="R120" t="n">
-        <v>7061274</v>
+        <v>7061384</v>
       </c>
       <c r="S120" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13321,11 +13327,6 @@
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC120" t="inlineStr">
-        <is>
-          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13352,10 +13353,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119836284</v>
+        <v>119837306</v>
       </c>
       <c r="B121" t="n">
-        <v>97907</v>
+        <v>79623</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13364,42 +13365,38 @@
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I121" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562903</v>
+        <v>562793</v>
       </c>
       <c r="R121" t="n">
-        <v>7061259</v>
+        <v>7061251</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13429,19 +13426,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>15:58</t>
+      <c r="AC121" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13456,22 +13448,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119838957</v>
+        <v>119838967</v>
       </c>
       <c r="B122" t="n">
-        <v>91834</v>
+        <v>97930</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13480,38 +13472,42 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4362</v>
+        <v>220787</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>562888</v>
+        <v>562990</v>
       </c>
       <c r="R122" t="n">
-        <v>7061052</v>
+        <v>7061060</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13541,9 +13537,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z122" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB122" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13558,22 +13564,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119840261</v>
+        <v>119839243</v>
       </c>
       <c r="B123" t="n">
-        <v>57310</v>
+        <v>97930</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13582,38 +13588,42 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>563003</v>
+        <v>563074</v>
       </c>
       <c r="R123" t="n">
-        <v>7061318</v>
+        <v>7061022</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13645,7 +13655,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13655,12 +13665,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13687,10 +13692,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119839228</v>
+        <v>119838625</v>
       </c>
       <c r="B124" t="n">
-        <v>57310</v>
+        <v>91902</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13703,21 +13708,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13727,10 +13732,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>563061</v>
+        <v>562899</v>
       </c>
       <c r="R124" t="n">
-        <v>7061025</v>
+        <v>7061101</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13762,7 +13767,7 @@
       </c>
       <c r="Z124" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
@@ -13772,12 +13777,7 @@
       </c>
       <c r="AB124" t="inlineStr">
         <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13807,7 +13807,7 @@
         <v>119838919</v>
       </c>
       <c r="B125" t="n">
-        <v>79115</v>
+        <v>79131</v>
       </c>
       <c r="C125" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119839212</v>
+        <v>119836424</v>
       </c>
       <c r="B22" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,41 +2811,45 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>563063</v>
+        <v>562902</v>
       </c>
       <c r="R22" t="n">
-        <v>7061037</v>
+        <v>7061306</v>
       </c>
       <c r="S22" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2872,19 +2876,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,22 +2893,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119835796</v>
+        <v>119838153</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2923,25 +2917,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2951,10 +2945,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562830</v>
+        <v>562865</v>
       </c>
       <c r="R23" t="n">
-        <v>7061321</v>
+        <v>7061107</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -2987,6 +2981,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,10 +3012,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119835344</v>
+        <v>119838709</v>
       </c>
       <c r="B24" t="n">
-        <v>90600</v>
+        <v>91901</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3029,21 +3028,21 @@
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5442</v>
+        <v>5448</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3053,13 +3052,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562790</v>
+        <v>562892</v>
       </c>
       <c r="R24" t="n">
-        <v>7061258</v>
+        <v>7061086</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3086,19 +3085,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z24" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA24" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB24" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD24" t="b">
@@ -3113,22 +3102,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119838153</v>
+        <v>119835344</v>
       </c>
       <c r="B25" t="n">
-        <v>91858</v>
+        <v>90600</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3137,25 +3126,25 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>4364</v>
+        <v>5442</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3165,10 +3154,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562865</v>
+        <v>562790</v>
       </c>
       <c r="R25" t="n">
-        <v>7061107</v>
+        <v>7061258</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3198,14 +3187,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z25" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC25" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
+      <c r="AB25" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3220,22 +3214,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119838709</v>
+        <v>119839212</v>
       </c>
       <c r="B26" t="n">
-        <v>91901</v>
+        <v>78542</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3248,37 +3242,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>5448</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>562892</v>
+        <v>563063</v>
       </c>
       <c r="R26" t="n">
-        <v>7061086</v>
+        <v>7061037</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3305,9 +3299,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3322,22 +3326,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119836424</v>
+        <v>119835796</v>
       </c>
       <c r="B27" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3346,45 +3350,41 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562902</v>
+        <v>562830</v>
       </c>
       <c r="R27" t="n">
-        <v>7061306</v>
+        <v>7061321</v>
       </c>
       <c r="S27" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3428,12 +3428,12 @@
       <c r="AT27" t="inlineStr"/>
       <c r="AW27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX27" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
@@ -3552,10 +3552,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119837399</v>
+        <v>119837858</v>
       </c>
       <c r="B29" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3564,25 +3564,25 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
@@ -3592,10 +3592,10 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562767</v>
+        <v>562847</v>
       </c>
       <c r="R29" t="n">
-        <v>7061188</v>
+        <v>7061096</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3654,7 +3654,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119835431</v>
+        <v>119837399</v>
       </c>
       <c r="B30" t="n">
         <v>79623</v>
@@ -3694,13 +3694,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562853</v>
+        <v>562767</v>
       </c>
       <c r="R30" t="n">
-        <v>7061293</v>
+        <v>7061188</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3744,22 +3744,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119835259</v>
+        <v>119835431</v>
       </c>
       <c r="B31" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3772,21 +3772,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -3796,10 +3796,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562815</v>
+        <v>562853</v>
       </c>
       <c r="R31" t="n">
-        <v>7061302</v>
+        <v>7061293</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3846,22 +3846,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119837858</v>
+        <v>119835259</v>
       </c>
       <c r="B32" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3870,25 +3870,25 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3898,13 +3898,13 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562847</v>
+        <v>562815</v>
       </c>
       <c r="R32" t="n">
-        <v>7061096</v>
+        <v>7061302</v>
       </c>
       <c r="S32" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -4169,10 +4169,10 @@
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119835654</v>
+        <v>119835495</v>
       </c>
       <c r="B35" t="n">
-        <v>79652</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4181,25 +4181,25 @@
       </c>
       <c r="D35" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6462</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4209,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562838</v>
+        <v>562822</v>
       </c>
       <c r="R35" t="n">
-        <v>7061333</v>
+        <v>7061305</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4271,7 +4271,7 @@
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119835495</v>
+        <v>119840373</v>
       </c>
       <c r="B36" t="n">
         <v>79623</v>
@@ -4311,13 +4311,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562822</v>
+        <v>562875</v>
       </c>
       <c r="R36" t="n">
-        <v>7061305</v>
+        <v>7061433</v>
       </c>
       <c r="S36" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4373,10 +4373,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119840373</v>
+        <v>119835654</v>
       </c>
       <c r="B37" t="n">
-        <v>79623</v>
+        <v>79652</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4385,25 +4385,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6458</v>
+        <v>6462</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4413,13 +4413,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562875</v>
+        <v>562838</v>
       </c>
       <c r="R37" t="n">
-        <v>7061433</v>
+        <v>7061333</v>
       </c>
       <c r="S37" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -7482,10 +7482,10 @@
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119836373</v>
+        <v>119837494</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>89650</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7494,45 +7494,41 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>1962</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(Parmasto) Bondartseva</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562910</v>
+        <v>562773</v>
       </c>
       <c r="R66" t="n">
-        <v>7061306</v>
+        <v>7061158</v>
       </c>
       <c r="S66" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7559,19 +7555,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7586,22 +7572,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119837494</v>
+        <v>119840261</v>
       </c>
       <c r="B67" t="n">
-        <v>89650</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7614,37 +7600,37 @@
         </is>
       </c>
       <c r="E67" t="n">
-        <v>1962</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562773</v>
+        <v>563003</v>
       </c>
       <c r="R67" t="n">
-        <v>7061158</v>
+        <v>7061318</v>
       </c>
       <c r="S67" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T67" t="inlineStr">
         <is>
@@ -7671,9 +7657,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7688,22 +7689,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119835531</v>
+        <v>119835631</v>
       </c>
       <c r="B68" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7716,21 +7717,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7740,13 +7741,13 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562827</v>
+        <v>562785</v>
       </c>
       <c r="R68" t="n">
-        <v>7061302</v>
+        <v>7061238</v>
       </c>
       <c r="S68" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T68" t="inlineStr">
         <is>
@@ -7773,9 +7774,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC68" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7790,22 +7806,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119836005</v>
+        <v>119835531</v>
       </c>
       <c r="B69" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7818,21 +7834,21 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -7842,10 +7858,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562898</v>
+        <v>562827</v>
       </c>
       <c r="R69" t="n">
-        <v>7061215</v>
+        <v>7061302</v>
       </c>
       <c r="S69" t="n">
         <v>15</v>
@@ -7892,22 +7908,22 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119835108</v>
+        <v>119836005</v>
       </c>
       <c r="B70" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7920,21 +7936,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -7944,10 +7960,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562802</v>
+        <v>562898</v>
       </c>
       <c r="R70" t="n">
-        <v>7061280</v>
+        <v>7061215</v>
       </c>
       <c r="S70" t="n">
         <v>15</v>
@@ -8006,7 +8022,7 @@
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119835638</v>
+        <v>119835108</v>
       </c>
       <c r="B71" t="n">
         <v>79623</v>
@@ -8046,10 +8062,10 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562838</v>
+        <v>562802</v>
       </c>
       <c r="R71" t="n">
-        <v>7061326</v>
+        <v>7061280</v>
       </c>
       <c r="S71" t="n">
         <v>15</v>
@@ -8096,22 +8112,22 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119840261</v>
+        <v>119835638</v>
       </c>
       <c r="B72" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C72" t="inlineStr">
         <is>
@@ -8124,37 +8140,37 @@
         </is>
       </c>
       <c r="E72" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>563003</v>
+        <v>562838</v>
       </c>
       <c r="R72" t="n">
-        <v>7061318</v>
+        <v>7061326</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8181,24 +8197,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
       <c r="AA72" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC72" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8213,22 +8214,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119835631</v>
+        <v>119836373</v>
       </c>
       <c r="B73" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8237,38 +8238,42 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562785</v>
+        <v>562910</v>
       </c>
       <c r="R73" t="n">
-        <v>7061238</v>
+        <v>7061306</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8300,7 +8305,7 @@
       </c>
       <c r="Z73" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
@@ -8310,12 +8315,7 @@
       </c>
       <c r="AB73" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC73" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -10573,10 +10573,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119835897</v>
+        <v>119837181</v>
       </c>
       <c r="B95" t="n">
-        <v>79623</v>
+        <v>90545</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10585,25 +10585,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10613,13 +10613,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562851</v>
+        <v>562872</v>
       </c>
       <c r="R95" t="n">
-        <v>7061350</v>
+        <v>7061246</v>
       </c>
       <c r="S95" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10675,10 +10675,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119835763</v>
+        <v>119836311</v>
       </c>
       <c r="B96" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10687,25 +10687,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10715,13 +10715,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>562859</v>
+        <v>562972</v>
       </c>
       <c r="R96" t="n">
-        <v>7061254</v>
+        <v>7061274</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10748,19 +10748,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z96" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB96" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC96" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10775,22 +10770,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119838030</v>
+        <v>119836284</v>
       </c>
       <c r="B97" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10799,43 +10794,42 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="M97" t="inlineStr">
-        <is>
-          <t>färska spår</t>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>50</t>
         </is>
       </c>
       <c r="P97" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562828</v>
+        <v>562903</v>
       </c>
       <c r="R97" t="n">
-        <v>7061089</v>
+        <v>7061259</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -10867,7 +10861,7 @@
       </c>
       <c r="Z97" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
@@ -10877,7 +10871,7 @@
       </c>
       <c r="AB97" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10904,10 +10898,10 @@
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119837181</v>
+        <v>119835897</v>
       </c>
       <c r="B98" t="n">
-        <v>90545</v>
+        <v>79623</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10916,25 +10910,25 @@
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5447</v>
+        <v>6458</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -10944,13 +10938,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562872</v>
+        <v>562851</v>
       </c>
       <c r="R98" t="n">
-        <v>7061246</v>
+        <v>7061350</v>
       </c>
       <c r="S98" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11006,10 +11000,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119836311</v>
+        <v>119835763</v>
       </c>
       <c r="B99" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11018,25 +11012,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11046,13 +11040,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562972</v>
+        <v>562859</v>
       </c>
       <c r="R99" t="n">
-        <v>7061274</v>
+        <v>7061254</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11079,14 +11073,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC99" t="inlineStr">
-        <is>
-          <t>Spridd i området</t>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11101,22 +11100,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119836284</v>
+        <v>119838030</v>
       </c>
       <c r="B100" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11125,42 +11124,43 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>50</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I100" t="inlineStr"/>
+      <c r="M100" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562903</v>
+        <v>562828</v>
       </c>
       <c r="R100" t="n">
-        <v>7061259</v>
+        <v>7061089</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11192,7 +11192,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11202,7 +11202,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD100" t="b">

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119836424</v>
+        <v>119838571</v>
       </c>
       <c r="B22" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2811,45 +2811,41 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562902</v>
+        <v>562856</v>
       </c>
       <c r="R22" t="n">
-        <v>7061306</v>
+        <v>7061099</v>
       </c>
       <c r="S22" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T22" t="inlineStr">
         <is>
@@ -2876,9 +2872,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2893,22 +2899,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119838153</v>
+        <v>119835654</v>
       </c>
       <c r="B23" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2921,21 +2927,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2945,13 +2951,13 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562865</v>
+        <v>562838</v>
       </c>
       <c r="R23" t="n">
-        <v>7061107</v>
+        <v>7061333</v>
       </c>
       <c r="S23" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T23" t="inlineStr">
         <is>
@@ -2981,11 +2987,6 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3012,10 +3013,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119838709</v>
+        <v>119837899</v>
       </c>
       <c r="B24" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3024,25 +3025,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3052,13 +3053,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562892</v>
+        <v>562848</v>
       </c>
       <c r="R24" t="n">
-        <v>7061086</v>
+        <v>7061087</v>
       </c>
       <c r="S24" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3102,22 +3103,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119835344</v>
+        <v>119838102</v>
       </c>
       <c r="B25" t="n">
-        <v>90600</v>
+        <v>57473</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3130,37 +3131,42 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562790</v>
+        <v>562863</v>
       </c>
       <c r="R25" t="n">
-        <v>7061258</v>
+        <v>7061098</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3187,19 +3193,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z25" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB25" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3214,22 +3210,22 @@
       <c r="AT25" t="inlineStr"/>
       <c r="AW25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX25" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119839212</v>
+        <v>119836491</v>
       </c>
       <c r="B26" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3238,41 +3234,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563063</v>
+        <v>563040</v>
       </c>
       <c r="R26" t="n">
-        <v>7061037</v>
+        <v>7061203</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3299,19 +3295,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z26" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB26" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3326,22 +3312,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119835796</v>
+        <v>119840300</v>
       </c>
       <c r="B27" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3354,21 +3340,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3378,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562830</v>
+        <v>562938</v>
       </c>
       <c r="R27" t="n">
-        <v>7061321</v>
+        <v>7061384</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3440,10 +3426,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119838864</v>
+        <v>119838153</v>
       </c>
       <c r="B28" t="n">
-        <v>78279</v>
+        <v>91858</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3452,38 +3438,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>228912</v>
+        <v>4364</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562940</v>
+        <v>562865</v>
       </c>
       <c r="R28" t="n">
-        <v>7061021</v>
+        <v>7061107</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3513,19 +3499,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z28" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB28" t="inlineStr">
-        <is>
-          <t>18:00</t>
+      <c r="AC28" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3540,22 +3521,22 @@
       <c r="AT28" t="inlineStr"/>
       <c r="AW28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX28" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119837858</v>
+        <v>119836923</v>
       </c>
       <c r="B29" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3564,38 +3545,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562847</v>
+        <v>562958</v>
       </c>
       <c r="R29" t="n">
-        <v>7061096</v>
+        <v>7061345</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3625,9 +3606,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z29" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB29" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC29" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3642,19 +3638,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119837399</v>
+        <v>119837560</v>
       </c>
       <c r="B30" t="n">
         <v>79623</v>
@@ -3694,13 +3690,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562767</v>
+        <v>562746</v>
       </c>
       <c r="R30" t="n">
-        <v>7061188</v>
+        <v>7061142</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3744,19 +3740,19 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119835431</v>
+        <v>119835638</v>
       </c>
       <c r="B31" t="n">
         <v>79623</v>
@@ -3796,10 +3792,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562853</v>
+        <v>562838</v>
       </c>
       <c r="R31" t="n">
-        <v>7061293</v>
+        <v>7061326</v>
       </c>
       <c r="S31" t="n">
         <v>15</v>
@@ -3846,22 +3842,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119835259</v>
+        <v>119839243</v>
       </c>
       <c r="B32" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3870,41 +3866,45 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562815</v>
+        <v>563074</v>
       </c>
       <c r="R32" t="n">
-        <v>7061302</v>
+        <v>7061022</v>
       </c>
       <c r="S32" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T32" t="inlineStr">
         <is>
@@ -3931,9 +3931,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z32" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB32" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3948,22 +3958,22 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119835697</v>
+        <v>119837216</v>
       </c>
       <c r="B33" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3976,21 +3986,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4000,13 +4010,13 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562826</v>
+        <v>562857</v>
       </c>
       <c r="R33" t="n">
-        <v>7061341</v>
+        <v>7061235</v>
       </c>
       <c r="S33" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T33" t="inlineStr">
         <is>
@@ -4036,6 +4046,11 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC33" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4062,10 +4077,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119835360</v>
+        <v>119835805</v>
       </c>
       <c r="B34" t="n">
-        <v>4766</v>
+        <v>78542</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4074,25 +4089,25 @@
       </c>
       <c r="D34" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E34" t="n">
-        <v>100299</v>
+        <v>6425</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4102,10 +4117,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562801</v>
+        <v>562873</v>
       </c>
       <c r="R34" t="n">
-        <v>7061292</v>
+        <v>7061226</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4140,11 +4155,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC34" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
-        </is>
-      </c>
       <c r="AD34" t="b">
         <v>0</v>
       </c>
@@ -4157,22 +4167,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119835495</v>
+        <v>119837366</v>
       </c>
       <c r="B35" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4185,21 +4195,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4209,10 +4219,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562822</v>
+        <v>562815</v>
       </c>
       <c r="R35" t="n">
-        <v>7061305</v>
+        <v>7061177</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4259,19 +4269,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119840373</v>
+        <v>119837399</v>
       </c>
       <c r="B36" t="n">
         <v>79623</v>
@@ -4311,10 +4321,10 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562875</v>
+        <v>562767</v>
       </c>
       <c r="R36" t="n">
-        <v>7061433</v>
+        <v>7061188</v>
       </c>
       <c r="S36" t="n">
         <v>10</v>
@@ -4373,10 +4383,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119835654</v>
+        <v>119837494</v>
       </c>
       <c r="B37" t="n">
-        <v>79652</v>
+        <v>89650</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4385,25 +4395,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>6462</v>
+        <v>1962</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4413,13 +4423,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562838</v>
+        <v>562773</v>
       </c>
       <c r="R37" t="n">
-        <v>7061333</v>
+        <v>7061158</v>
       </c>
       <c r="S37" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4475,10 +4485,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119835350</v>
+        <v>119837383</v>
       </c>
       <c r="B38" t="n">
-        <v>78279</v>
+        <v>78542</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4491,21 +4501,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>228912</v>
+        <v>6425</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4515,13 +4525,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562801</v>
+        <v>562779</v>
       </c>
       <c r="R38" t="n">
-        <v>7061274</v>
+        <v>7061176</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4565,22 +4575,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119839757</v>
+        <v>119838606</v>
       </c>
       <c r="B39" t="n">
-        <v>57336</v>
+        <v>78278</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4593,21 +4603,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>100049</v>
+        <v>6446</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4617,13 +4627,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>563104</v>
+        <v>562879</v>
       </c>
       <c r="R39" t="n">
-        <v>7061110</v>
+        <v>7061091</v>
       </c>
       <c r="S39" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4653,11 +4663,6 @@
       <c r="AA39" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC39" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD39" t="b">
@@ -4684,10 +4689,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119836896</v>
+        <v>119838865</v>
       </c>
       <c r="B40" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4696,25 +4701,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4724,13 +4729,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562930</v>
+        <v>562942</v>
       </c>
       <c r="R40" t="n">
-        <v>7061333</v>
+        <v>7061029</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4760,11 +4765,6 @@
       <c r="AA40" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC40" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD40" t="b">
@@ -4779,22 +4779,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119840391</v>
+        <v>119837066</v>
       </c>
       <c r="B41" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4803,25 +4803,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562861</v>
+        <v>562940</v>
       </c>
       <c r="R41" t="n">
-        <v>7061439</v>
+        <v>7061261</v>
       </c>
       <c r="S41" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4881,22 +4881,22 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119836179</v>
+        <v>119838859</v>
       </c>
       <c r="B42" t="n">
-        <v>78542</v>
+        <v>91901</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4909,21 +4909,21 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>6425</v>
+        <v>5448</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I42" t="inlineStr"/>
@@ -4933,10 +4933,10 @@
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562966</v>
+        <v>562897</v>
       </c>
       <c r="R42" t="n">
-        <v>7061336</v>
+        <v>7061087</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4995,10 +4995,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119840354</v>
+        <v>119837992</v>
       </c>
       <c r="B43" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5011,21 +5011,21 @@
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5035,13 +5035,13 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562893</v>
+        <v>562845</v>
       </c>
       <c r="R43" t="n">
-        <v>7061427</v>
+        <v>7061115</v>
       </c>
       <c r="S43" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T43" t="inlineStr">
         <is>
@@ -5085,22 +5085,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119836533</v>
+        <v>119835495</v>
       </c>
       <c r="B44" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5109,45 +5109,41 @@
       </c>
       <c r="D44" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E44" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I44" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I44" t="inlineStr"/>
       <c r="P44" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562927</v>
+        <v>562822</v>
       </c>
       <c r="R44" t="n">
-        <v>7061314</v>
+        <v>7061305</v>
       </c>
       <c r="S44" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5174,19 +5170,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z44" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA44" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB44" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD44" t="b">
@@ -5201,22 +5187,22 @@
       <c r="AT44" t="inlineStr"/>
       <c r="AW44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX44" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119836512</v>
+        <v>119836367</v>
       </c>
       <c r="B45" t="n">
-        <v>97930</v>
+        <v>95478</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5225,45 +5211,41 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>220787</v>
+        <v>53</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I45" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I45" t="inlineStr"/>
       <c r="P45" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562925</v>
+        <v>562983</v>
       </c>
       <c r="R45" t="n">
-        <v>7061308</v>
+        <v>7061268</v>
       </c>
       <c r="S45" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5290,19 +5272,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z45" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB45" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5317,22 +5289,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119836491</v>
+        <v>119837999</v>
       </c>
       <c r="B46" t="n">
-        <v>97930</v>
+        <v>79160</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5341,25 +5313,25 @@
       </c>
       <c r="D46" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E46" t="n">
-        <v>220787</v>
+        <v>6453</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5369,10 +5341,10 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>563040</v>
+        <v>562848</v>
       </c>
       <c r="R46" t="n">
-        <v>7061203</v>
+        <v>7061083</v>
       </c>
       <c r="S46" t="n">
         <v>15</v>
@@ -5431,10 +5403,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119837066</v>
+        <v>119835968</v>
       </c>
       <c r="B47" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5443,25 +5415,25 @@
       </c>
       <c r="D47" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E47" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
@@ -5471,13 +5443,13 @@
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562940</v>
+        <v>562856</v>
       </c>
       <c r="R47" t="n">
-        <v>7061261</v>
+        <v>7061341</v>
       </c>
       <c r="S47" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T47" t="inlineStr">
         <is>
@@ -5521,19 +5493,19 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119837216</v>
+        <v>119840354</v>
       </c>
       <c r="B48" t="n">
         <v>78542</v>
@@ -5573,13 +5545,13 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562857</v>
+        <v>562893</v>
       </c>
       <c r="R48" t="n">
-        <v>7061235</v>
+        <v>7061427</v>
       </c>
       <c r="S48" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T48" t="inlineStr">
         <is>
@@ -5609,11 +5581,6 @@
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC48" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5640,10 +5607,10 @@
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119837761</v>
+        <v>119835531</v>
       </c>
       <c r="B49" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5656,21 +5623,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5680,13 +5647,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562816</v>
+        <v>562827</v>
       </c>
       <c r="R49" t="n">
-        <v>7061089</v>
+        <v>7061302</v>
       </c>
       <c r="S49" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5742,10 +5709,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119836358</v>
+        <v>119835697</v>
       </c>
       <c r="B50" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5758,21 +5725,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5782,13 +5749,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562901</v>
+        <v>562826</v>
       </c>
       <c r="R50" t="n">
-        <v>7061289</v>
+        <v>7061341</v>
       </c>
       <c r="S50" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5832,22 +5799,22 @@
       <c r="AT50" t="inlineStr"/>
       <c r="AW50" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX50" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119837543</v>
+        <v>119839228</v>
       </c>
       <c r="B51" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5860,34 +5827,34 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>562745</v>
+        <v>563061</v>
       </c>
       <c r="R51" t="n">
-        <v>7061152</v>
+        <v>7061025</v>
       </c>
       <c r="S51" t="n">
         <v>10</v>
@@ -5919,7 +5886,7 @@
       </c>
       <c r="Z51" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA51" t="inlineStr">
@@ -5929,7 +5896,12 @@
       </c>
       <c r="AB51" t="inlineStr">
         <is>
-          <t>17:11</t>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC51" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5956,10 +5928,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119836923</v>
+        <v>119837966</v>
       </c>
       <c r="B52" t="n">
-        <v>57320</v>
+        <v>78187</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5972,37 +5944,37 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>100109</v>
+        <v>353</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562958</v>
+        <v>562845</v>
       </c>
       <c r="R52" t="n">
-        <v>7061345</v>
+        <v>7061093</v>
       </c>
       <c r="S52" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T52" t="inlineStr">
         <is>
@@ -6029,24 +6001,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA52" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC52" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6061,22 +6018,22 @@
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119835980</v>
+        <v>119839184</v>
       </c>
       <c r="B53" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6085,46 +6042,41 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
-      <c r="M53" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P53" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>562885</v>
+        <v>563009</v>
       </c>
       <c r="R53" t="n">
-        <v>7061225</v>
+        <v>7061040</v>
       </c>
       <c r="S53" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T53" t="inlineStr">
         <is>
@@ -6151,19 +6103,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z53" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA53" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB53" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6178,22 +6120,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119836807</v>
+        <v>119836512</v>
       </c>
       <c r="B54" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6202,38 +6144,42 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562926</v>
+        <v>562925</v>
       </c>
       <c r="R54" t="n">
-        <v>7061340</v>
+        <v>7061308</v>
       </c>
       <c r="S54" t="n">
         <v>10</v>
@@ -6265,7 +6211,7 @@
       </c>
       <c r="Z54" t="inlineStr">
         <is>
-          <t>16:28</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
@@ -6275,12 +6221,7 @@
       </c>
       <c r="AB54" t="inlineStr">
         <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6307,10 +6248,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119837193</v>
+        <v>119836358</v>
       </c>
       <c r="B55" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6323,21 +6264,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6347,10 +6288,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562864</v>
+        <v>562901</v>
       </c>
       <c r="R55" t="n">
-        <v>7061224</v>
+        <v>7061289</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6383,11 +6324,6 @@
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC55" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6414,10 +6350,10 @@
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119838064</v>
+        <v>119837298</v>
       </c>
       <c r="B56" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6426,25 +6362,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6454,10 +6390,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562850</v>
+        <v>562841</v>
       </c>
       <c r="R56" t="n">
-        <v>7061098</v>
+        <v>7061196</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6504,22 +6440,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119838957</v>
+        <v>119836179</v>
       </c>
       <c r="B57" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6532,21 +6468,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6556,10 +6492,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562888</v>
+        <v>562966</v>
       </c>
       <c r="R57" t="n">
-        <v>7061052</v>
+        <v>7061336</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6618,10 +6554,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119838865</v>
+        <v>119836005</v>
       </c>
       <c r="B58" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6630,25 +6566,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6658,10 +6594,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562942</v>
+        <v>562898</v>
       </c>
       <c r="R58" t="n">
-        <v>7061029</v>
+        <v>7061215</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6720,10 +6656,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119838859</v>
+        <v>119837427</v>
       </c>
       <c r="B59" t="n">
-        <v>91901</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6732,25 +6668,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>5448</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6760,10 +6696,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562897</v>
+        <v>562772</v>
       </c>
       <c r="R59" t="n">
-        <v>7061087</v>
+        <v>7061165</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6793,9 +6729,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6810,22 +6756,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119838885</v>
+        <v>119837858</v>
       </c>
       <c r="B60" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6834,42 +6780,38 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562977</v>
+        <v>562847</v>
       </c>
       <c r="R60" t="n">
-        <v>7061045</v>
+        <v>7061096</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6899,19 +6841,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>18:04</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>18:04</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6926,22 +6858,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119836632</v>
+        <v>119835631</v>
       </c>
       <c r="B61" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6950,45 +6882,41 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562948</v>
+        <v>562785</v>
       </c>
       <c r="R61" t="n">
-        <v>7061323</v>
+        <v>7061238</v>
       </c>
       <c r="S61" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7015,9 +6943,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7032,22 +6975,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119836629</v>
+        <v>119836719</v>
       </c>
       <c r="B62" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7060,42 +7003,37 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P62" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562935</v>
+        <v>562937</v>
       </c>
       <c r="R62" t="n">
-        <v>7061315</v>
+        <v>7061312</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7122,19 +7060,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7149,22 +7077,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119839228</v>
+        <v>119840391</v>
       </c>
       <c r="B63" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7177,34 +7105,34 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>563061</v>
+        <v>562861</v>
       </c>
       <c r="R63" t="n">
-        <v>7061025</v>
+        <v>7061439</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7234,24 +7162,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z63" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB63" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC63" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7266,19 +7179,19 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119838597</v>
+        <v>119838327</v>
       </c>
       <c r="B64" t="n">
         <v>91858</v>
@@ -7318,10 +7231,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562861</v>
+        <v>562870</v>
       </c>
       <c r="R64" t="n">
-        <v>7061099</v>
+        <v>7061110</v>
       </c>
       <c r="S64" t="n">
         <v>15</v>
@@ -7380,10 +7293,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119838327</v>
+        <v>119835516</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7392,25 +7305,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7420,13 +7333,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562870</v>
+        <v>562795</v>
       </c>
       <c r="R65" t="n">
-        <v>7061110</v>
+        <v>7061238</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7453,9 +7366,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7470,22 +7398,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119837494</v>
+        <v>119838885</v>
       </c>
       <c r="B66" t="n">
-        <v>89650</v>
+        <v>97930</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7494,41 +7422,45 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>1962</v>
+        <v>220787</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562773</v>
+        <v>562977</v>
       </c>
       <c r="R66" t="n">
-        <v>7061158</v>
+        <v>7061045</v>
       </c>
       <c r="S66" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T66" t="inlineStr">
         <is>
@@ -7555,9 +7487,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z66" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB66" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7572,22 +7514,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119840261</v>
+        <v>119837181</v>
       </c>
       <c r="B67" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7596,38 +7538,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>563003</v>
+        <v>562872</v>
       </c>
       <c r="R67" t="n">
-        <v>7061318</v>
+        <v>7061246</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7657,24 +7599,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z67" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB67" t="inlineStr">
-        <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC67" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7689,22 +7616,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119835631</v>
+        <v>119838625</v>
       </c>
       <c r="B68" t="n">
-        <v>57320</v>
+        <v>91902</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7717,34 +7644,34 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>100109</v>
+        <v>5449</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562785</v>
+        <v>562899</v>
       </c>
       <c r="R68" t="n">
-        <v>7061238</v>
+        <v>7061101</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7776,7 +7703,7 @@
       </c>
       <c r="Z68" t="inlineStr">
         <is>
-          <t>15:34</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
@@ -7786,12 +7713,7 @@
       </c>
       <c r="AB68" t="inlineStr">
         <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC68" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7818,7 +7740,7 @@
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119835531</v>
+        <v>119837306</v>
       </c>
       <c r="B69" t="n">
         <v>79623</v>
@@ -7858,13 +7780,13 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562827</v>
+        <v>562793</v>
       </c>
       <c r="R69" t="n">
-        <v>7061302</v>
+        <v>7061251</v>
       </c>
       <c r="S69" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T69" t="inlineStr">
         <is>
@@ -7894,6 +7816,11 @@
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC69" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7920,7 +7847,7 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119836005</v>
+        <v>119839212</v>
       </c>
       <c r="B70" t="n">
         <v>78542</v>
@@ -7956,17 +7883,17 @@
       <c r="I70" t="inlineStr"/>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>562898</v>
+        <v>563063</v>
       </c>
       <c r="R70" t="n">
-        <v>7061215</v>
+        <v>7061037</v>
       </c>
       <c r="S70" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7993,9 +7920,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z70" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB70" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8010,22 +7947,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119835108</v>
+        <v>119836807</v>
       </c>
       <c r="B71" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -8038,21 +7975,21 @@
         </is>
       </c>
       <c r="E71" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8062,13 +7999,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562802</v>
+        <v>562926</v>
       </c>
       <c r="R71" t="n">
-        <v>7061280</v>
+        <v>7061340</v>
       </c>
       <c r="S71" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8095,9 +8032,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z71" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB71" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC71" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8112,19 +8064,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119835638</v>
+        <v>119840328</v>
       </c>
       <c r="B72" t="n">
         <v>79623</v>
@@ -8164,13 +8116,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562838</v>
+        <v>562922</v>
       </c>
       <c r="R72" t="n">
-        <v>7061326</v>
+        <v>7061399</v>
       </c>
       <c r="S72" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8226,10 +8178,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119836373</v>
+        <v>119835500</v>
       </c>
       <c r="B73" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8238,45 +8190,41 @@
       </c>
       <c r="D73" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E73" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I73" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562910</v>
+        <v>562824</v>
       </c>
       <c r="R73" t="n">
-        <v>7061306</v>
+        <v>7061319</v>
       </c>
       <c r="S73" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8303,19 +8251,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z73" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB73" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8330,22 +8268,22 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119836367</v>
+        <v>119838872</v>
       </c>
       <c r="B74" t="n">
-        <v>95478</v>
+        <v>91852</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8358,21 +8296,21 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>53</v>
+        <v>4362</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
@@ -8382,10 +8320,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562983</v>
+        <v>562893</v>
       </c>
       <c r="R74" t="n">
-        <v>7061268</v>
+        <v>7061059</v>
       </c>
       <c r="S74" t="n">
         <v>15</v>
@@ -8444,10 +8382,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119835742</v>
+        <v>119835763</v>
       </c>
       <c r="B75" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8456,25 +8394,25 @@
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8484,13 +8422,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562853</v>
+        <v>562859</v>
       </c>
       <c r="R75" t="n">
-        <v>7061243</v>
+        <v>7061254</v>
       </c>
       <c r="S75" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -8517,9 +8455,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z75" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB75" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8534,22 +8482,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119836952</v>
+        <v>119837084</v>
       </c>
       <c r="B76" t="n">
-        <v>82321</v>
+        <v>90600</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8562,37 +8510,37 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
       <c r="P76" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562955</v>
+        <v>562905</v>
       </c>
       <c r="R76" t="n">
-        <v>7061332</v>
+        <v>7061251</v>
       </c>
       <c r="S76" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T76" t="inlineStr">
         <is>
@@ -8619,19 +8567,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z76" t="inlineStr">
-        <is>
-          <t>16:35</t>
-        </is>
-      </c>
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB76" t="inlineStr">
-        <is>
-          <t>16:35</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8646,22 +8584,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119838606</v>
+        <v>119838957</v>
       </c>
       <c r="B77" t="n">
-        <v>78278</v>
+        <v>91852</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8674,21 +8612,21 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>6446</v>
+        <v>4362</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
@@ -8698,10 +8636,10 @@
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562879</v>
+        <v>562888</v>
       </c>
       <c r="R77" t="n">
-        <v>7061091</v>
+        <v>7061052</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8760,10 +8698,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119835968</v>
+        <v>119836629</v>
       </c>
       <c r="B78" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8776,34 +8714,39 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
+      <c r="M78" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562856</v>
+        <v>562935</v>
       </c>
       <c r="R78" t="n">
-        <v>7061341</v>
+        <v>7061315</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8833,9 +8776,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z78" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB78" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8850,22 +8803,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119836521</v>
+        <v>119837193</v>
       </c>
       <c r="B79" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8874,25 +8827,25 @@
       </c>
       <c r="D79" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E79" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8902,10 +8855,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562928</v>
+        <v>562864</v>
       </c>
       <c r="R79" t="n">
-        <v>7061305</v>
+        <v>7061224</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8938,6 +8891,11 @@
       <c r="AA79" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC79" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD79" t="b">
@@ -8964,10 +8922,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119837427</v>
+        <v>119837856</v>
       </c>
       <c r="B80" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8976,38 +8934,38 @@
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562772</v>
+        <v>562803</v>
       </c>
       <c r="R80" t="n">
-        <v>7061165</v>
+        <v>7061104</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9039,7 +8997,7 @@
       </c>
       <c r="Z80" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
@@ -9049,7 +9007,12 @@
       </c>
       <c r="AB80" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC80" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9076,10 +9039,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119837999</v>
+        <v>119838967</v>
       </c>
       <c r="B81" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9088,41 +9051,45 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>562848</v>
+        <v>562990</v>
       </c>
       <c r="R81" t="n">
-        <v>7061083</v>
+        <v>7061060</v>
       </c>
       <c r="S81" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9149,9 +9116,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z81" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB81" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9166,22 +9143,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119835500</v>
+        <v>119835742</v>
       </c>
       <c r="B82" t="n">
-        <v>79623</v>
+        <v>56532</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9190,25 +9167,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6458</v>
+        <v>100138</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9218,10 +9195,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>562824</v>
+        <v>562853</v>
       </c>
       <c r="R82" t="n">
-        <v>7061319</v>
+        <v>7061243</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9268,19 +9245,19 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119837298</v>
+        <v>119835259</v>
       </c>
       <c r="B83" t="n">
         <v>78542</v>
@@ -9320,10 +9297,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562841</v>
+        <v>562815</v>
       </c>
       <c r="R83" t="n">
-        <v>7061196</v>
+        <v>7061302</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9370,22 +9347,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119837560</v>
+        <v>119838064</v>
       </c>
       <c r="B84" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9394,25 +9371,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9422,10 +9399,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562746</v>
+        <v>562850</v>
       </c>
       <c r="R84" t="n">
-        <v>7061142</v>
+        <v>7061098</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9472,22 +9449,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119837074</v>
+        <v>119840261</v>
       </c>
       <c r="B85" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9496,42 +9473,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>562940</v>
+        <v>563003</v>
       </c>
       <c r="R85" t="n">
-        <v>7061272</v>
+        <v>7061318</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9563,7 +9536,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9573,7 +9546,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9600,10 +9578,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119838102</v>
+        <v>119838242</v>
       </c>
       <c r="B86" t="n">
-        <v>57473</v>
+        <v>57320</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9616,42 +9594,37 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>103021</v>
+        <v>100109</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P86" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>562863</v>
+        <v>562827</v>
       </c>
       <c r="R86" t="n">
-        <v>7061098</v>
+        <v>7061123</v>
       </c>
       <c r="S86" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9678,9 +9651,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z86" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB86" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC86" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9695,22 +9683,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119840392</v>
+        <v>119837074</v>
       </c>
       <c r="B87" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9719,38 +9707,42 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>562878</v>
+        <v>562940</v>
       </c>
       <c r="R87" t="n">
-        <v>7061442</v>
+        <v>7061272</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9782,7 +9774,7 @@
       </c>
       <c r="Z87" t="inlineStr">
         <is>
-          <t>19:19</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
@@ -9792,12 +9784,7 @@
       </c>
       <c r="AB87" t="inlineStr">
         <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9824,10 +9811,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119835516</v>
+        <v>119836896</v>
       </c>
       <c r="B88" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9840,21 +9827,21 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9864,10 +9851,10 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562795</v>
+        <v>562930</v>
       </c>
       <c r="R88" t="n">
-        <v>7061238</v>
+        <v>7061333</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -9897,24 +9884,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AC88" t="inlineStr">
         <is>
-          <t>Ringhack</t>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9929,12 +9906,12 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
@@ -10043,10 +10020,10 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119837366</v>
+        <v>119835350</v>
       </c>
       <c r="B90" t="n">
-        <v>78542</v>
+        <v>78279</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10059,21 +10036,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6425</v>
+        <v>228912</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10083,10 +10060,10 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562815</v>
+        <v>562801</v>
       </c>
       <c r="R90" t="n">
-        <v>7061177</v>
+        <v>7061274</v>
       </c>
       <c r="S90" t="n">
         <v>15</v>
@@ -10145,10 +10122,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119838571</v>
+        <v>119839757</v>
       </c>
       <c r="B91" t="n">
-        <v>91902</v>
+        <v>57336</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10161,37 +10138,37 @@
         </is>
       </c>
       <c r="E91" t="n">
-        <v>5449</v>
+        <v>100049</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562856</v>
+        <v>563104</v>
       </c>
       <c r="R91" t="n">
-        <v>7061099</v>
+        <v>7061110</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10218,19 +10195,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>17:44</t>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10245,22 +10217,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119837992</v>
+        <v>119836533</v>
       </c>
       <c r="B92" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10269,41 +10241,45 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I92" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562845</v>
+        <v>562927</v>
       </c>
       <c r="R92" t="n">
-        <v>7061115</v>
+        <v>7061314</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10330,9 +10306,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10347,22 +10333,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119835535</v>
+        <v>119836311</v>
       </c>
       <c r="B93" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10371,25 +10357,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10399,13 +10385,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>562795</v>
+        <v>562972</v>
       </c>
       <c r="R93" t="n">
-        <v>7061238</v>
+        <v>7061274</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10432,19 +10418,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>15:32</t>
+      <c r="AC93" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10459,19 +10440,19 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119837899</v>
+        <v>119837424</v>
       </c>
       <c r="B94" t="n">
         <v>91858</v>
@@ -10511,13 +10492,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562848</v>
+        <v>562774</v>
       </c>
       <c r="R94" t="n">
-        <v>7061087</v>
+        <v>7061178</v>
       </c>
       <c r="S94" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10561,22 +10542,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119837181</v>
+        <v>119840392</v>
       </c>
       <c r="B95" t="n">
-        <v>90545</v>
+        <v>57320</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10585,25 +10566,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>100109</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10613,10 +10594,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562872</v>
+        <v>562878</v>
       </c>
       <c r="R95" t="n">
-        <v>7061246</v>
+        <v>7061442</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10646,9 +10627,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z95" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB95" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10663,22 +10659,22 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119836311</v>
+        <v>119837761</v>
       </c>
       <c r="B96" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10687,25 +10683,25 @@
       </c>
       <c r="D96" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E96" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -10715,13 +10711,13 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>562972</v>
+        <v>562816</v>
       </c>
       <c r="R96" t="n">
-        <v>7061274</v>
+        <v>7061089</v>
       </c>
       <c r="S96" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -10751,11 +10747,6 @@
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC96" t="inlineStr">
-        <is>
-          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10782,10 +10773,10 @@
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119836284</v>
+        <v>119838709</v>
       </c>
       <c r="B97" t="n">
-        <v>97930</v>
+        <v>91901</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10794,45 +10785,41 @@
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E97" t="n">
-        <v>220787</v>
+        <v>5448</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Schultz) nom.prov</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562903</v>
+        <v>562892</v>
       </c>
       <c r="R97" t="n">
-        <v>7061259</v>
+        <v>7061086</v>
       </c>
       <c r="S97" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10859,19 +10846,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z97" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB97" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10886,19 +10863,19 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119835897</v>
+        <v>119840373</v>
       </c>
       <c r="B98" t="n">
         <v>79623</v>
@@ -10938,13 +10915,13 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562851</v>
+        <v>562875</v>
       </c>
       <c r="R98" t="n">
-        <v>7061350</v>
+        <v>7061433</v>
       </c>
       <c r="S98" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T98" t="inlineStr">
         <is>
@@ -11000,10 +10977,10 @@
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119835763</v>
+        <v>119838597</v>
       </c>
       <c r="B99" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -11012,25 +10989,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11040,13 +11017,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562859</v>
+        <v>562861</v>
       </c>
       <c r="R99" t="n">
-        <v>7061254</v>
+        <v>7061099</v>
       </c>
       <c r="S99" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11073,19 +11050,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z99" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA99" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB99" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11100,22 +11067,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119838030</v>
+        <v>119836952</v>
       </c>
       <c r="B100" t="n">
-        <v>57320</v>
+        <v>82321</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11128,39 +11095,34 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>100109</v>
+        <v>1312</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
-      <c r="M100" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562828</v>
+        <v>562955</v>
       </c>
       <c r="R100" t="n">
-        <v>7061089</v>
+        <v>7061332</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11192,7 +11154,7 @@
       </c>
       <c r="Z100" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
@@ -11202,7 +11164,7 @@
       </c>
       <c r="AB100" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11229,10 +11191,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119837512</v>
+        <v>119839135</v>
       </c>
       <c r="B101" t="n">
-        <v>57320</v>
+        <v>78278</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11245,34 +11207,34 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100109</v>
+        <v>6446</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562769</v>
+        <v>562982</v>
       </c>
       <c r="R101" t="n">
-        <v>7061157</v>
+        <v>7061063</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11304,7 +11266,7 @@
       </c>
       <c r="Z101" t="inlineStr">
         <is>
-          <t>17:08</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
@@ -11314,12 +11276,7 @@
       </c>
       <c r="AB101" t="inlineStr">
         <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC101" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11346,10 +11303,10 @@
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119837344</v>
+        <v>119838179</v>
       </c>
       <c r="B102" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11362,46 +11319,37 @@
         </is>
       </c>
       <c r="E102" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562829</v>
+        <v>562854</v>
       </c>
       <c r="R102" t="n">
-        <v>7061182</v>
+        <v>7061121</v>
       </c>
       <c r="S102" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11428,19 +11376,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z102" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB102" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11455,22 +11393,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119838242</v>
+        <v>119835514</v>
       </c>
       <c r="B103" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11483,21 +11421,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11507,13 +11445,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562827</v>
+        <v>562849</v>
       </c>
       <c r="R103" t="n">
-        <v>7061123</v>
+        <v>7061244</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11540,24 +11478,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC103" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11572,22 +11495,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119837424</v>
+        <v>119835796</v>
       </c>
       <c r="B104" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11596,25 +11519,25 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
@@ -11624,13 +11547,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562774</v>
+        <v>562830</v>
       </c>
       <c r="R104" t="n">
-        <v>7061178</v>
+        <v>7061321</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11674,22 +11597,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119838872</v>
+        <v>119835980</v>
       </c>
       <c r="B105" t="n">
-        <v>91852</v>
+        <v>57320</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11702,37 +11625,42 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
+      <c r="M105" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562893</v>
+        <v>562885</v>
       </c>
       <c r="R105" t="n">
-        <v>7061059</v>
+        <v>7061225</v>
       </c>
       <c r="S105" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T105" t="inlineStr">
         <is>
@@ -11759,9 +11687,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11776,22 +11714,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119837084</v>
+        <v>119836424</v>
       </c>
       <c r="B106" t="n">
-        <v>90600</v>
+        <v>97930</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11800,38 +11738,42 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>5442</v>
+        <v>220787</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P106" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562905</v>
+        <v>562902</v>
       </c>
       <c r="R106" t="n">
-        <v>7061251</v>
+        <v>7061306</v>
       </c>
       <c r="S106" t="n">
         <v>15</v>
@@ -11878,22 +11820,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119836719</v>
+        <v>119836373</v>
       </c>
       <c r="B107" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11902,41 +11844,45 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>562937</v>
+        <v>562910</v>
       </c>
       <c r="R107" t="n">
-        <v>7061312</v>
+        <v>7061306</v>
       </c>
       <c r="S107" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11963,9 +11909,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z107" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB107" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11980,19 +11936,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119840328</v>
+        <v>119835751</v>
       </c>
       <c r="B108" t="n">
         <v>79623</v>
@@ -12032,10 +11988,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>562922</v>
+        <v>562833</v>
       </c>
       <c r="R108" t="n">
-        <v>7061399</v>
+        <v>7061339</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12094,10 +12050,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119839135</v>
+        <v>119835431</v>
       </c>
       <c r="B109" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12110,37 +12066,37 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>562982</v>
+        <v>562853</v>
       </c>
       <c r="R109" t="n">
-        <v>7061063</v>
+        <v>7061293</v>
       </c>
       <c r="S109" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12167,19 +12123,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>18:21</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12194,19 +12140,19 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119835514</v>
+        <v>119835108</v>
       </c>
       <c r="B110" t="n">
         <v>79623</v>
@@ -12246,10 +12192,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>562849</v>
+        <v>562802</v>
       </c>
       <c r="R110" t="n">
-        <v>7061244</v>
+        <v>7061280</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -12308,10 +12254,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119835805</v>
+        <v>119836632</v>
       </c>
       <c r="B111" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12320,38 +12266,42 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P111" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562873</v>
+        <v>562948</v>
       </c>
       <c r="R111" t="n">
-        <v>7061226</v>
+        <v>7061323</v>
       </c>
       <c r="S111" t="n">
         <v>15</v>
@@ -12410,10 +12360,10 @@
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119837299</v>
+        <v>119835344</v>
       </c>
       <c r="B112" t="n">
-        <v>82321</v>
+        <v>90600</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12426,21 +12376,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>1312</v>
+        <v>5442</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12450,10 +12400,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>562843</v>
+        <v>562790</v>
       </c>
       <c r="R112" t="n">
-        <v>7061204</v>
+        <v>7061258</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12485,7 +12435,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12495,7 +12445,7 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12522,10 +12472,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119835751</v>
+        <v>119835535</v>
       </c>
       <c r="B113" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12534,25 +12484,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12562,10 +12512,10 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562833</v>
+        <v>562795</v>
       </c>
       <c r="R113" t="n">
-        <v>7061339</v>
+        <v>7061238</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12595,9 +12545,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12612,22 +12572,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119838179</v>
+        <v>119835360</v>
       </c>
       <c r="B114" t="n">
-        <v>78542</v>
+        <v>4766</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12636,25 +12596,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>6425</v>
+        <v>100299</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12664,10 +12624,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>562854</v>
+        <v>562801</v>
       </c>
       <c r="R114" t="n">
-        <v>7061121</v>
+        <v>7061292</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12702,6 +12662,11 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
+        </is>
+      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -12714,22 +12679,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119839184</v>
+        <v>119838864</v>
       </c>
       <c r="B115" t="n">
-        <v>91858</v>
+        <v>78279</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12738,41 +12703,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>4364</v>
+        <v>228912</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>563009</v>
+        <v>562940</v>
       </c>
       <c r="R115" t="n">
-        <v>7061040</v>
+        <v>7061021</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12799,9 +12764,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12816,22 +12791,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119839227</v>
+        <v>119837344</v>
       </c>
       <c r="B116" t="n">
-        <v>91858</v>
+        <v>57473</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12840,38 +12815,47 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>4364</v>
+        <v>103021</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M116" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>563080</v>
+        <v>562829</v>
       </c>
       <c r="R116" t="n">
-        <v>7061030</v>
+        <v>7061182</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12901,9 +12885,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z116" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB116" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12918,22 +12912,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119837856</v>
+        <v>119836521</v>
       </c>
       <c r="B117" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12942,41 +12936,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562803</v>
+        <v>562928</v>
       </c>
       <c r="R117" t="n">
-        <v>7061104</v>
+        <v>7061305</v>
       </c>
       <c r="S117" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13003,24 +12997,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z117" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB117" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC117" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13035,22 +13014,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119837966</v>
+        <v>119836284</v>
       </c>
       <c r="B118" t="n">
-        <v>78187</v>
+        <v>97930</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13059,41 +13038,45 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>353</v>
+        <v>220787</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562845</v>
+        <v>562903</v>
       </c>
       <c r="R118" t="n">
-        <v>7061093</v>
+        <v>7061259</v>
       </c>
       <c r="S118" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13120,9 +13103,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13137,22 +13130,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119837383</v>
+        <v>119839227</v>
       </c>
       <c r="B119" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13161,25 +13154,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13189,13 +13182,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>562779</v>
+        <v>563080</v>
       </c>
       <c r="R119" t="n">
-        <v>7061176</v>
+        <v>7061030</v>
       </c>
       <c r="S119" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13251,10 +13244,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119840300</v>
+        <v>119838030</v>
       </c>
       <c r="B120" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13267,34 +13260,39 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
+      <c r="M120" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562938</v>
+        <v>562828</v>
       </c>
       <c r="R120" t="n">
-        <v>7061384</v>
+        <v>7061089</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13324,9 +13322,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z120" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB120" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13341,22 +13349,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119837306</v>
+        <v>119837512</v>
       </c>
       <c r="B121" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13369,21 +13377,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13393,10 +13401,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562793</v>
+        <v>562769</v>
       </c>
       <c r="R121" t="n">
-        <v>7061251</v>
+        <v>7061157</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13426,14 +13434,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z121" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB121" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AC121" t="inlineStr">
         <is>
-          <t>På björkhögstubbe</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13448,22 +13466,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119838967</v>
+        <v>119837543</v>
       </c>
       <c r="B122" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13472,42 +13490,38 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I122" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>562990</v>
+        <v>562745</v>
       </c>
       <c r="R122" t="n">
-        <v>7061060</v>
+        <v>7061152</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13539,7 +13553,7 @@
       </c>
       <c r="Z122" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
@@ -13549,7 +13563,7 @@
       </c>
       <c r="AB122" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13576,10 +13590,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119839243</v>
+        <v>119837299</v>
       </c>
       <c r="B123" t="n">
-        <v>97930</v>
+        <v>82321</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13588,42 +13602,38 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>1312</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Nyl.) Rehm</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>563074</v>
+        <v>562843</v>
       </c>
       <c r="R123" t="n">
-        <v>7061022</v>
+        <v>7061204</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13655,7 +13665,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13665,7 +13675,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13692,10 +13702,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119838625</v>
+        <v>119835897</v>
       </c>
       <c r="B124" t="n">
-        <v>91902</v>
+        <v>79623</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13708,37 +13718,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>5449</v>
+        <v>6458</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>562899</v>
+        <v>562851</v>
       </c>
       <c r="R124" t="n">
-        <v>7061101</v>
+        <v>7061350</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13765,19 +13775,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13792,12 +13792,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -3324,10 +3324,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119840300</v>
+        <v>119838153</v>
       </c>
       <c r="B27" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,25 +3336,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3364,10 +3364,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562938</v>
+        <v>562865</v>
       </c>
       <c r="R27" t="n">
-        <v>7061384</v>
+        <v>7061107</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3400,6 +3400,11 @@
       <c r="AA27" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC27" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3426,10 +3431,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119838153</v>
+        <v>119840300</v>
       </c>
       <c r="B28" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3438,25 +3443,25 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3466,10 +3471,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562865</v>
+        <v>562938</v>
       </c>
       <c r="R28" t="n">
-        <v>7061107</v>
+        <v>7061384</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3502,11 +3507,6 @@
       <c r="AA28" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC28" t="inlineStr">
-        <is>
-          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3533,10 +3533,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119836923</v>
+        <v>119837560</v>
       </c>
       <c r="B29" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3549,37 +3549,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562958</v>
+        <v>562746</v>
       </c>
       <c r="R29" t="n">
-        <v>7061345</v>
+        <v>7061142</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3606,24 +3606,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z29" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA29" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB29" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC29" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3638,19 +3623,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119837560</v>
+        <v>119835638</v>
       </c>
       <c r="B30" t="n">
         <v>79623</v>
@@ -3690,10 +3675,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562746</v>
+        <v>562838</v>
       </c>
       <c r="R30" t="n">
-        <v>7061142</v>
+        <v>7061326</v>
       </c>
       <c r="S30" t="n">
         <v>15</v>
@@ -3740,22 +3725,22 @@
       <c r="AT30" t="inlineStr"/>
       <c r="AW30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX30" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119835638</v>
+        <v>119836923</v>
       </c>
       <c r="B31" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3768,37 +3753,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562838</v>
+        <v>562958</v>
       </c>
       <c r="R31" t="n">
-        <v>7061326</v>
+        <v>7061345</v>
       </c>
       <c r="S31" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3825,9 +3810,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z31" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB31" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC31" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3842,12 +3842,12 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
@@ -4485,10 +4485,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119837383</v>
+        <v>119837992</v>
       </c>
       <c r="B38" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4501,21 +4501,21 @@
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4525,13 +4525,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562779</v>
+        <v>562845</v>
       </c>
       <c r="R38" t="n">
-        <v>7061176</v>
+        <v>7061115</v>
       </c>
       <c r="S38" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4575,22 +4575,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119838606</v>
+        <v>119835495</v>
       </c>
       <c r="B39" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4603,21 +4603,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4627,13 +4627,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562879</v>
+        <v>562822</v>
       </c>
       <c r="R39" t="n">
-        <v>7061091</v>
+        <v>7061305</v>
       </c>
       <c r="S39" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4689,10 +4689,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119838865</v>
+        <v>119838606</v>
       </c>
       <c r="B40" t="n">
-        <v>91858</v>
+        <v>78278</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4701,25 +4701,25 @@
       </c>
       <c r="D40" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E40" t="n">
-        <v>4364</v>
+        <v>6446</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4729,13 +4729,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562942</v>
+        <v>562879</v>
       </c>
       <c r="R40" t="n">
-        <v>7061029</v>
+        <v>7061091</v>
       </c>
       <c r="S40" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4779,22 +4779,22 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119837066</v>
+        <v>119837383</v>
       </c>
       <c r="B41" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C41" t="inlineStr">
         <is>
@@ -4803,25 +4803,25 @@
       </c>
       <c r="D41" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E41" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H41" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I41" t="inlineStr"/>
@@ -4831,13 +4831,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562940</v>
+        <v>562779</v>
       </c>
       <c r="R41" t="n">
-        <v>7061261</v>
+        <v>7061176</v>
       </c>
       <c r="S41" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4881,12 +4881,12 @@
       <c r="AT41" t="inlineStr"/>
       <c r="AW41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX41" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
@@ -4995,10 +4995,10 @@
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119837992</v>
+        <v>119838865</v>
       </c>
       <c r="B43" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C43" t="inlineStr">
         <is>
@@ -5007,25 +5007,25 @@
       </c>
       <c r="D43" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E43" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H43" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I43" t="inlineStr"/>
@@ -5035,10 +5035,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562845</v>
+        <v>562942</v>
       </c>
       <c r="R43" t="n">
-        <v>7061115</v>
+        <v>7061029</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5097,10 +5097,10 @@
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119835495</v>
+        <v>119836367</v>
       </c>
       <c r="B44" t="n">
-        <v>79623</v>
+        <v>95478</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5113,21 +5113,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>6458</v>
+        <v>53</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nees ex Lindenb.) Meyl.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5137,10 +5137,10 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562822</v>
+        <v>562983</v>
       </c>
       <c r="R44" t="n">
-        <v>7061305</v>
+        <v>7061268</v>
       </c>
       <c r="S44" t="n">
         <v>15</v>
@@ -5199,10 +5199,10 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119836367</v>
+        <v>119837066</v>
       </c>
       <c r="B45" t="n">
-        <v>95478</v>
+        <v>97930</v>
       </c>
       <c r="C45" t="inlineStr">
         <is>
@@ -5211,25 +5211,25 @@
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E45" t="n">
-        <v>53</v>
+        <v>220787</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H45" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I45" t="inlineStr"/>
@@ -5239,10 +5239,10 @@
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562983</v>
+        <v>562940</v>
       </c>
       <c r="R45" t="n">
-        <v>7061268</v>
+        <v>7061261</v>
       </c>
       <c r="S45" t="n">
         <v>15</v>
@@ -5289,12 +5289,12 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
@@ -6248,10 +6248,10 @@
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119836358</v>
+        <v>119836719</v>
       </c>
       <c r="B55" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6264,21 +6264,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6288,10 +6288,10 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562901</v>
+        <v>562937</v>
       </c>
       <c r="R55" t="n">
-        <v>7061289</v>
+        <v>7061312</v>
       </c>
       <c r="S55" t="n">
         <v>15</v>
@@ -6656,10 +6656,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119837427</v>
+        <v>119840391</v>
       </c>
       <c r="B59" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6668,25 +6668,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6696,10 +6696,10 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562772</v>
+        <v>562861</v>
       </c>
       <c r="R59" t="n">
-        <v>7061165</v>
+        <v>7061439</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -6729,19 +6729,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>17:03</t>
-        </is>
-      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>17:03</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6756,19 +6746,19 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119837858</v>
+        <v>119837427</v>
       </c>
       <c r="B60" t="n">
         <v>91858</v>
@@ -6808,10 +6798,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562847</v>
+        <v>562772</v>
       </c>
       <c r="R60" t="n">
-        <v>7061096</v>
+        <v>7061165</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6841,9 +6831,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6858,22 +6858,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119835631</v>
+        <v>119837858</v>
       </c>
       <c r="B61" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6882,25 +6882,25 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I61" t="inlineStr"/>
@@ -6910,10 +6910,10 @@
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562785</v>
+        <v>562847</v>
       </c>
       <c r="R61" t="n">
-        <v>7061238</v>
+        <v>7061096</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6943,24 +6943,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z61" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB61" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6975,22 +6960,22 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119836719</v>
+        <v>119835631</v>
       </c>
       <c r="B62" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C62" t="inlineStr">
         <is>
@@ -7003,21 +6988,21 @@
         </is>
       </c>
       <c r="E62" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F62" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H62" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I62" t="inlineStr"/>
@@ -7027,13 +7012,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562937</v>
+        <v>562785</v>
       </c>
       <c r="R62" t="n">
-        <v>7061312</v>
+        <v>7061238</v>
       </c>
       <c r="S62" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7060,9 +7045,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z62" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB62" t="inlineStr">
+        <is>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC62" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7077,22 +7077,22 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119840391</v>
+        <v>119836358</v>
       </c>
       <c r="B63" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C63" t="inlineStr">
         <is>
@@ -7105,21 +7105,21 @@
         </is>
       </c>
       <c r="E63" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F63" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H63" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I63" t="inlineStr"/>
@@ -7129,13 +7129,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562861</v>
+        <v>562901</v>
       </c>
       <c r="R63" t="n">
-        <v>7061439</v>
+        <v>7061289</v>
       </c>
       <c r="S63" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7179,22 +7179,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119838327</v>
+        <v>119837306</v>
       </c>
       <c r="B64" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7203,25 +7203,25 @@
       </c>
       <c r="D64" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E64" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7231,13 +7231,13 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562870</v>
+        <v>562793</v>
       </c>
       <c r="R64" t="n">
-        <v>7061110</v>
+        <v>7061251</v>
       </c>
       <c r="S64" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T64" t="inlineStr">
         <is>
@@ -7267,6 +7267,11 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC64" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7281,22 +7286,22 @@
       <c r="AT64" t="inlineStr"/>
       <c r="AW64" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX64" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119835516</v>
+        <v>119838327</v>
       </c>
       <c r="B65" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7305,25 +7310,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7333,13 +7338,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562795</v>
+        <v>562870</v>
       </c>
       <c r="R65" t="n">
-        <v>7061238</v>
+        <v>7061110</v>
       </c>
       <c r="S65" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7366,24 +7371,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z65" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB65" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC65" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7398,22 +7388,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119838885</v>
+        <v>119835516</v>
       </c>
       <c r="B66" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7422,42 +7412,38 @@
       </c>
       <c r="D66" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E66" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I66" t="inlineStr"/>
       <c r="P66" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562977</v>
+        <v>562795</v>
       </c>
       <c r="R66" t="n">
-        <v>7061045</v>
+        <v>7061238</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7489,7 +7475,7 @@
       </c>
       <c r="Z66" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:30</t>
         </is>
       </c>
       <c r="AA66" t="inlineStr">
@@ -7499,7 +7485,12 @@
       </c>
       <c r="AB66" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC66" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7526,10 +7517,10 @@
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119837181</v>
+        <v>119838885</v>
       </c>
       <c r="B67" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7538,38 +7529,42 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562872</v>
+        <v>562977</v>
       </c>
       <c r="R67" t="n">
-        <v>7061246</v>
+        <v>7061045</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7599,9 +7594,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z67" t="inlineStr">
+        <is>
+          <t>18:04</t>
+        </is>
+      </c>
       <c r="AA67" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB67" t="inlineStr">
+        <is>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7616,22 +7621,22 @@
       <c r="AT67" t="inlineStr"/>
       <c r="AW67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX67" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119838625</v>
+        <v>119837181</v>
       </c>
       <c r="B68" t="n">
-        <v>91902</v>
+        <v>90545</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7640,38 +7645,38 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5449</v>
+        <v>5447</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
       <c r="P68" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562899</v>
+        <v>562872</v>
       </c>
       <c r="R68" t="n">
-        <v>7061101</v>
+        <v>7061246</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7701,19 +7706,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z68" t="inlineStr">
-        <is>
-          <t>17:48</t>
-        </is>
-      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB68" t="inlineStr">
-        <is>
-          <t>17:48</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7728,22 +7723,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119837306</v>
+        <v>119838625</v>
       </c>
       <c r="B69" t="n">
-        <v>79623</v>
+        <v>91902</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7756,34 +7751,34 @@
         </is>
       </c>
       <c r="E69" t="n">
-        <v>6458</v>
+        <v>5449</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
       <c r="P69" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562793</v>
+        <v>562899</v>
       </c>
       <c r="R69" t="n">
-        <v>7061251</v>
+        <v>7061101</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7813,14 +7808,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z69" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA69" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
+      <c r="AB69" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7835,12 +7835,12 @@
       <c r="AT69" t="inlineStr"/>
       <c r="AW69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX69" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
@@ -8382,10 +8382,10 @@
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119835763</v>
+        <v>119836629</v>
       </c>
       <c r="B75" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8398,34 +8398,39 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562859</v>
+        <v>562935</v>
       </c>
       <c r="R75" t="n">
-        <v>7061254</v>
+        <v>7061315</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8457,7 +8462,7 @@
       </c>
       <c r="Z75" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AA75" t="inlineStr">
@@ -8467,7 +8472,7 @@
       </c>
       <c r="AB75" t="inlineStr">
         <is>
-          <t>15:39</t>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8494,10 +8499,10 @@
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119837084</v>
+        <v>119837193</v>
       </c>
       <c r="B76" t="n">
-        <v>90600</v>
+        <v>57320</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8510,21 +8515,21 @@
         </is>
       </c>
       <c r="E76" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8534,10 +8539,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562905</v>
+        <v>562864</v>
       </c>
       <c r="R76" t="n">
-        <v>7061251</v>
+        <v>7061224</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8572,6 +8577,11 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC76" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
+        </is>
+      </c>
       <c r="AD76" t="b">
         <v>0</v>
       </c>
@@ -8584,22 +8594,22 @@
       <c r="AT76" t="inlineStr"/>
       <c r="AW76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX76" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119838957</v>
+        <v>119837856</v>
       </c>
       <c r="B77" t="n">
-        <v>91852</v>
+        <v>57320</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8612,34 +8622,34 @@
         </is>
       </c>
       <c r="E77" t="n">
-        <v>4362</v>
+        <v>100109</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I77" t="inlineStr"/>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562888</v>
+        <v>562803</v>
       </c>
       <c r="R77" t="n">
-        <v>7061052</v>
+        <v>7061104</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8669,9 +8679,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z77" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA77" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB77" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC77" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8686,22 +8711,22 @@
       <c r="AT77" t="inlineStr"/>
       <c r="AW77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX77" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119836629</v>
+        <v>119835763</v>
       </c>
       <c r="B78" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8714,39 +8739,34 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
-      <c r="M78" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P78" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562935</v>
+        <v>562859</v>
       </c>
       <c r="R78" t="n">
-        <v>7061315</v>
+        <v>7061254</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8778,7 +8798,7 @@
       </c>
       <c r="Z78" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
@@ -8788,7 +8808,7 @@
       </c>
       <c r="AB78" t="inlineStr">
         <is>
-          <t>16:20</t>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8815,10 +8835,10 @@
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119837193</v>
+        <v>119837084</v>
       </c>
       <c r="B79" t="n">
-        <v>57320</v>
+        <v>90600</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8831,21 +8851,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>100109</v>
+        <v>5442</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8855,10 +8875,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562864</v>
+        <v>562905</v>
       </c>
       <c r="R79" t="n">
-        <v>7061224</v>
+        <v>7061251</v>
       </c>
       <c r="S79" t="n">
         <v>15</v>
@@ -8893,11 +8913,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC79" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
-        </is>
-      </c>
       <c r="AD79" t="b">
         <v>0</v>
       </c>
@@ -8910,22 +8925,22 @@
       <c r="AT79" t="inlineStr"/>
       <c r="AW79" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX79" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119837856</v>
+        <v>119838957</v>
       </c>
       <c r="B80" t="n">
-        <v>57320</v>
+        <v>91852</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8938,34 +8953,34 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>100109</v>
+        <v>4362</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
       <c r="P80" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562803</v>
+        <v>562888</v>
       </c>
       <c r="R80" t="n">
-        <v>7061104</v>
+        <v>7061052</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -8995,24 +9010,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z80" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA80" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB80" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC80" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9027,12 +9027,12 @@
       <c r="AT80" t="inlineStr"/>
       <c r="AW80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX80" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
@@ -9155,10 +9155,10 @@
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119835742</v>
+        <v>119835259</v>
       </c>
       <c r="B82" t="n">
-        <v>56532</v>
+        <v>78542</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9167,25 +9167,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>100138</v>
+        <v>6425</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9195,10 +9195,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>562853</v>
+        <v>562815</v>
       </c>
       <c r="R82" t="n">
-        <v>7061243</v>
+        <v>7061302</v>
       </c>
       <c r="S82" t="n">
         <v>15</v>
@@ -9245,22 +9245,22 @@
       <c r="AT82" t="inlineStr"/>
       <c r="AW82" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX82" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119835259</v>
+        <v>119835742</v>
       </c>
       <c r="B83" t="n">
-        <v>78542</v>
+        <v>56532</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9269,25 +9269,25 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>6425</v>
+        <v>100138</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I83" t="inlineStr"/>
@@ -9297,10 +9297,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562815</v>
+        <v>562853</v>
       </c>
       <c r="R83" t="n">
-        <v>7061302</v>
+        <v>7061243</v>
       </c>
       <c r="S83" t="n">
         <v>15</v>
@@ -9347,22 +9347,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119838064</v>
+        <v>119835470</v>
       </c>
       <c r="B84" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9371,25 +9371,25 @@
       </c>
       <c r="D84" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E84" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
@@ -9399,10 +9399,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562850</v>
+        <v>562839</v>
       </c>
       <c r="R84" t="n">
-        <v>7061098</v>
+        <v>7061260</v>
       </c>
       <c r="S84" t="n">
         <v>15</v>
@@ -9449,22 +9449,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119840261</v>
+        <v>119837074</v>
       </c>
       <c r="B85" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9473,38 +9473,42 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P85" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>563003</v>
+        <v>562940</v>
       </c>
       <c r="R85" t="n">
-        <v>7061318</v>
+        <v>7061272</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9536,7 +9540,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9546,12 +9550,7 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>19:10</t>
-        </is>
-      </c>
-      <c r="AC85" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9578,10 +9577,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119838242</v>
+        <v>119835350</v>
       </c>
       <c r="B86" t="n">
-        <v>57320</v>
+        <v>78279</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9594,21 +9593,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>100109</v>
+        <v>228912</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9618,13 +9617,13 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>562827</v>
+        <v>562801</v>
       </c>
       <c r="R86" t="n">
-        <v>7061123</v>
+        <v>7061274</v>
       </c>
       <c r="S86" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T86" t="inlineStr">
         <is>
@@ -9651,24 +9650,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z86" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
       <c r="AA86" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB86" t="inlineStr">
-        <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC86" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9683,22 +9667,22 @@
       <c r="AT86" t="inlineStr"/>
       <c r="AW86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX86" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119837074</v>
+        <v>119836896</v>
       </c>
       <c r="B87" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9707,42 +9691,38 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I87" t="inlineStr"/>
       <c r="P87" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>562940</v>
+        <v>562930</v>
       </c>
       <c r="R87" t="n">
-        <v>7061272</v>
+        <v>7061333</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9772,19 +9752,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z87" t="inlineStr">
-        <is>
-          <t>16:40</t>
-        </is>
-      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB87" t="inlineStr">
-        <is>
-          <t>16:40</t>
+      <c r="AC87" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9799,22 +9774,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119836896</v>
+        <v>119838064</v>
       </c>
       <c r="B88" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9823,25 +9798,25 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
@@ -9851,13 +9826,13 @@
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562930</v>
+        <v>562850</v>
       </c>
       <c r="R88" t="n">
-        <v>7061333</v>
+        <v>7061098</v>
       </c>
       <c r="S88" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9887,11 +9862,6 @@
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC88" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9918,10 +9888,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119835470</v>
+        <v>119840261</v>
       </c>
       <c r="B89" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9934,37 +9904,37 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>562839</v>
+        <v>563003</v>
       </c>
       <c r="R89" t="n">
-        <v>7061260</v>
+        <v>7061318</v>
       </c>
       <c r="S89" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T89" t="inlineStr">
         <is>
@@ -9991,9 +9961,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z89" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB89" t="inlineStr">
+        <is>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC89" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10008,22 +9993,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119835350</v>
+        <v>119838242</v>
       </c>
       <c r="B90" t="n">
-        <v>78279</v>
+        <v>57320</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10036,21 +10021,21 @@
         </is>
       </c>
       <c r="E90" t="n">
-        <v>228912</v>
+        <v>100109</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10060,13 +10045,13 @@
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562801</v>
+        <v>562827</v>
       </c>
       <c r="R90" t="n">
-        <v>7061274</v>
+        <v>7061123</v>
       </c>
       <c r="S90" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T90" t="inlineStr">
         <is>
@@ -10093,9 +10078,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10110,22 +10110,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119839757</v>
+        <v>119836533</v>
       </c>
       <c r="B91" t="n">
-        <v>57336</v>
+        <v>97930</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10134,41 +10134,45 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>100049</v>
+        <v>220787</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>563104</v>
+        <v>562927</v>
       </c>
       <c r="R91" t="n">
-        <v>7061110</v>
+        <v>7061314</v>
       </c>
       <c r="S91" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10195,14 +10199,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10217,19 +10226,19 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119836533</v>
+        <v>119836311</v>
       </c>
       <c r="B92" t="n">
         <v>97930</v>
@@ -10262,24 +10271,20 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+      <c r="I92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562927</v>
+        <v>562972</v>
       </c>
       <c r="R92" t="n">
-        <v>7061314</v>
+        <v>7061274</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10306,19 +10311,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z92" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB92" t="inlineStr">
-        <is>
-          <t>16:17</t>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10333,22 +10333,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119836311</v>
+        <v>119840392</v>
       </c>
       <c r="B93" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10357,25 +10357,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10385,13 +10385,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>562972</v>
+        <v>562878</v>
       </c>
       <c r="R93" t="n">
-        <v>7061274</v>
+        <v>7061442</v>
       </c>
       <c r="S93" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -10418,14 +10418,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z93" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB93" t="inlineStr">
+        <is>
+          <t>19:19</t>
+        </is>
+      </c>
       <c r="AC93" t="inlineStr">
         <is>
-          <t>Spridd i området</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10440,22 +10450,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119837424</v>
+        <v>119839757</v>
       </c>
       <c r="B94" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10464,25 +10474,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10492,13 +10502,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>562774</v>
+        <v>563104</v>
       </c>
       <c r="R94" t="n">
-        <v>7061178</v>
+        <v>7061110</v>
       </c>
       <c r="S94" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10528,6 +10538,11 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC94" t="inlineStr">
+        <is>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10542,22 +10557,22 @@
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX94" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119840392</v>
+        <v>119837424</v>
       </c>
       <c r="B95" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10566,25 +10581,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10594,13 +10609,13 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562878</v>
+        <v>562774</v>
       </c>
       <c r="R95" t="n">
-        <v>7061442</v>
+        <v>7061178</v>
       </c>
       <c r="S95" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10627,24 +10642,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z95" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
       <c r="AA95" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB95" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC95" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -10659,12 +10659,12 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
@@ -11405,10 +11405,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119835514</v>
+        <v>119835980</v>
       </c>
       <c r="B103" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11421,37 +11421,42 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
+      <c r="M103" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562849</v>
+        <v>562885</v>
       </c>
       <c r="R103" t="n">
-        <v>7061244</v>
+        <v>7061225</v>
       </c>
       <c r="S103" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11478,9 +11483,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z103" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB103" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11495,19 +11510,19 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119835796</v>
+        <v>119835514</v>
       </c>
       <c r="B104" t="n">
         <v>79623</v>
@@ -11547,13 +11562,13 @@
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562830</v>
+        <v>562849</v>
       </c>
       <c r="R104" t="n">
-        <v>7061321</v>
+        <v>7061244</v>
       </c>
       <c r="S104" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11597,22 +11612,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119835980</v>
+        <v>119835796</v>
       </c>
       <c r="B105" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11625,39 +11640,34 @@
         </is>
       </c>
       <c r="E105" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
-      <c r="M105" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562885</v>
+        <v>562830</v>
       </c>
       <c r="R105" t="n">
-        <v>7061225</v>
+        <v>7061321</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11687,19 +11697,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z105" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB105" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11714,12 +11714,12 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
@@ -12691,10 +12691,10 @@
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119838864</v>
+        <v>119836521</v>
       </c>
       <c r="B115" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12703,41 +12703,41 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>562940</v>
+        <v>562928</v>
       </c>
       <c r="R115" t="n">
-        <v>7061021</v>
+        <v>7061305</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12764,19 +12764,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>18:00</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12791,22 +12781,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119837344</v>
+        <v>119836284</v>
       </c>
       <c r="B116" t="n">
-        <v>57473</v>
+        <v>97930</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12815,35 +12805,30 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>220787</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>50</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12852,10 +12837,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562829</v>
+        <v>562903</v>
       </c>
       <c r="R116" t="n">
-        <v>7061182</v>
+        <v>7061259</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -12887,7 +12872,7 @@
       </c>
       <c r="Z116" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
@@ -12897,7 +12882,7 @@
       </c>
       <c r="AB116" t="inlineStr">
         <is>
-          <t>16:56</t>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12924,10 +12909,10 @@
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119836521</v>
+        <v>119838864</v>
       </c>
       <c r="B117" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12936,41 +12921,41 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562928</v>
+        <v>562940</v>
       </c>
       <c r="R117" t="n">
-        <v>7061305</v>
+        <v>7061021</v>
       </c>
       <c r="S117" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -12997,9 +12982,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z117" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA117" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB117" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13014,22 +13009,22 @@
       <c r="AT117" t="inlineStr"/>
       <c r="AW117" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX117" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119836284</v>
+        <v>119837344</v>
       </c>
       <c r="B118" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13038,30 +13033,35 @@
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M118" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P118" t="inlineStr">
@@ -13070,10 +13070,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562903</v>
+        <v>562829</v>
       </c>
       <c r="R118" t="n">
-        <v>7061259</v>
+        <v>7061182</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13105,7 +13105,7 @@
       </c>
       <c r="Z118" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
@@ -13115,7 +13115,7 @@
       </c>
       <c r="AB118" t="inlineStr">
         <is>
-          <t>15:58</t>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13142,10 +13142,10 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119839227</v>
+        <v>119837299</v>
       </c>
       <c r="B119" t="n">
-        <v>91858</v>
+        <v>82321</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13154,25 +13154,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>4364</v>
+        <v>1312</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13182,10 +13182,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>563080</v>
+        <v>562843</v>
       </c>
       <c r="R119" t="n">
-        <v>7061030</v>
+        <v>7061204</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13215,9 +13215,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z119" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13232,22 +13242,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119838030</v>
+        <v>119837543</v>
       </c>
       <c r="B120" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13260,39 +13270,34 @@
         </is>
       </c>
       <c r="E120" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="M120" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P120" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562828</v>
+        <v>562745</v>
       </c>
       <c r="R120" t="n">
-        <v>7061089</v>
+        <v>7061152</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13324,7 +13329,7 @@
       </c>
       <c r="Z120" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
@@ -13334,7 +13339,7 @@
       </c>
       <c r="AB120" t="inlineStr">
         <is>
-          <t>17:23</t>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13361,10 +13366,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119837512</v>
+        <v>119835897</v>
       </c>
       <c r="B121" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13377,21 +13382,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13401,13 +13406,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562769</v>
+        <v>562851</v>
       </c>
       <c r="R121" t="n">
-        <v>7061157</v>
+        <v>7061350</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13434,24 +13439,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z121" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA121" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB121" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC121" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13466,22 +13456,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119837543</v>
+        <v>119839227</v>
       </c>
       <c r="B122" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13490,25 +13480,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13518,10 +13508,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>562745</v>
+        <v>563080</v>
       </c>
       <c r="R122" t="n">
-        <v>7061152</v>
+        <v>7061030</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13551,19 +13541,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z122" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA122" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB122" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13578,22 +13558,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119837299</v>
+        <v>119838030</v>
       </c>
       <c r="B123" t="n">
-        <v>82321</v>
+        <v>57320</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13606,34 +13586,39 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>1312</v>
+        <v>100109</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>562843</v>
+        <v>562828</v>
       </c>
       <c r="R123" t="n">
-        <v>7061204</v>
+        <v>7061089</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13665,7 +13650,7 @@
       </c>
       <c r="Z123" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
@@ -13675,7 +13660,7 @@
       </c>
       <c r="AB123" t="inlineStr">
         <is>
-          <t>16:52</t>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13702,10 +13687,10 @@
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119835897</v>
+        <v>119837512</v>
       </c>
       <c r="B124" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13718,21 +13703,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13742,13 +13727,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>562851</v>
+        <v>562769</v>
       </c>
       <c r="R124" t="n">
-        <v>7061350</v>
+        <v>7061157</v>
       </c>
       <c r="S124" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13775,9 +13760,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z124" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB124" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13792,12 +13792,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -2799,10 +2799,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>119838571</v>
+        <v>119838606</v>
       </c>
       <c r="B22" t="n">
-        <v>91902</v>
+        <v>78278</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2815,34 +2815,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>5449</v>
+        <v>6446</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>562856</v>
+        <v>562879</v>
       </c>
       <c r="R22" t="n">
-        <v>7061099</v>
+        <v>7061091</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -2872,19 +2872,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>17:44</t>
-        </is>
-      </c>
       <c r="AA22" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>17:44</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -2899,22 +2889,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>119835654</v>
+        <v>119835360</v>
       </c>
       <c r="B23" t="n">
-        <v>79652</v>
+        <v>4766</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -2927,21 +2917,21 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6462</v>
+        <v>100299</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -2951,10 +2941,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>562838</v>
+        <v>562801</v>
       </c>
       <c r="R23" t="n">
-        <v>7061333</v>
+        <v>7061292</v>
       </c>
       <c r="S23" t="n">
         <v>15</v>
@@ -2987,6 +2977,11 @@
       <c r="AA23" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr">
+        <is>
+          <t>Gnaggångar</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3013,10 +3008,10 @@
     </row>
     <row r="24">
       <c r="A24" t="n">
-        <v>119837899</v>
+        <v>119836005</v>
       </c>
       <c r="B24" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C24" t="inlineStr">
         <is>
@@ -3025,25 +3020,25 @@
       </c>
       <c r="D24" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E24" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I24" t="inlineStr"/>
@@ -3053,13 +3048,13 @@
         </is>
       </c>
       <c r="Q24" t="n">
-        <v>562848</v>
+        <v>562898</v>
       </c>
       <c r="R24" t="n">
-        <v>7061087</v>
+        <v>7061215</v>
       </c>
       <c r="S24" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T24" t="inlineStr">
         <is>
@@ -3103,22 +3098,22 @@
       <c r="AT24" t="inlineStr"/>
       <c r="AW24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX24" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>119838102</v>
+        <v>119837216</v>
       </c>
       <c r="B25" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3131,42 +3126,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>562863</v>
+        <v>562857</v>
       </c>
       <c r="R25" t="n">
-        <v>7061098</v>
+        <v>7061235</v>
       </c>
       <c r="S25" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3196,6 +3186,11 @@
       <c r="AA25" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC25" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3222,10 +3217,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>119836491</v>
+        <v>119838571</v>
       </c>
       <c r="B26" t="n">
-        <v>97930</v>
+        <v>91902</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3234,41 +3229,41 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>5449</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>563040</v>
+        <v>562856</v>
       </c>
       <c r="R26" t="n">
-        <v>7061203</v>
+        <v>7061099</v>
       </c>
       <c r="S26" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3295,9 +3290,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z26" t="inlineStr">
+        <is>
+          <t>17:44</t>
+        </is>
+      </c>
       <c r="AA26" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB26" t="inlineStr">
+        <is>
+          <t>17:44</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3312,22 +3317,22 @@
       <c r="AT26" t="inlineStr"/>
       <c r="AW26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX26" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>119838153</v>
+        <v>119839757</v>
       </c>
       <c r="B27" t="n">
-        <v>91858</v>
+        <v>57336</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3336,25 +3341,25 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>4364</v>
+        <v>100049</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3364,13 +3369,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>562865</v>
+        <v>563104</v>
       </c>
       <c r="R27" t="n">
-        <v>7061107</v>
+        <v>7061110</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3404,7 +3409,7 @@
       </c>
       <c r="AC27" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3431,10 +3436,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>119840300</v>
+        <v>119837966</v>
       </c>
       <c r="B28" t="n">
-        <v>78542</v>
+        <v>78187</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3447,21 +3452,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>353</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dvärgbägarlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Cladonia parasitica</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Hoffm.) Hoffm.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3471,13 +3476,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>562938</v>
+        <v>562845</v>
       </c>
       <c r="R28" t="n">
-        <v>7061384</v>
+        <v>7061093</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3533,7 +3538,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>119837560</v>
+        <v>119840391</v>
       </c>
       <c r="B29" t="n">
         <v>79623</v>
@@ -3573,13 +3578,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>562746</v>
+        <v>562861</v>
       </c>
       <c r="R29" t="n">
-        <v>7061142</v>
+        <v>7061439</v>
       </c>
       <c r="S29" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3623,19 +3628,19 @@
       <c r="AT29" t="inlineStr"/>
       <c r="AW29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX29" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>119835638</v>
+        <v>119840328</v>
       </c>
       <c r="B30" t="n">
         <v>79623</v>
@@ -3675,13 +3680,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>562838</v>
+        <v>562922</v>
       </c>
       <c r="R30" t="n">
-        <v>7061326</v>
+        <v>7061399</v>
       </c>
       <c r="S30" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3737,10 +3742,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>119836923</v>
+        <v>119837298</v>
       </c>
       <c r="B31" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3753,37 +3758,37 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>562958</v>
+        <v>562841</v>
       </c>
       <c r="R31" t="n">
-        <v>7061345</v>
+        <v>7061196</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -3810,24 +3815,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z31" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
       <c r="AA31" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB31" t="inlineStr">
-        <is>
-          <t>16:32</t>
-        </is>
-      </c>
-      <c r="AC31" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD31" t="b">
@@ -3842,22 +3832,22 @@
       <c r="AT31" t="inlineStr"/>
       <c r="AW31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX31" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119839243</v>
+        <v>119837512</v>
       </c>
       <c r="B32" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3866,42 +3856,38 @@
       </c>
       <c r="D32" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E32" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I32" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I32" t="inlineStr"/>
       <c r="P32" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>563074</v>
+        <v>562769</v>
       </c>
       <c r="R32" t="n">
-        <v>7061022</v>
+        <v>7061157</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3933,7 +3919,7 @@
       </c>
       <c r="Z32" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:08</t>
         </is>
       </c>
       <c r="AA32" t="inlineStr">
@@ -3943,7 +3929,12 @@
       </c>
       <c r="AB32" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>17:08</t>
+        </is>
+      </c>
+      <c r="AC32" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3970,10 +3961,10 @@
     </row>
     <row r="33">
       <c r="A33" t="n">
-        <v>119837216</v>
+        <v>119835897</v>
       </c>
       <c r="B33" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C33" t="inlineStr">
         <is>
@@ -3986,21 +3977,21 @@
         </is>
       </c>
       <c r="E33" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H33" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I33" t="inlineStr"/>
@@ -4010,10 +4001,10 @@
         </is>
       </c>
       <c r="Q33" t="n">
-        <v>562857</v>
+        <v>562851</v>
       </c>
       <c r="R33" t="n">
-        <v>7061235</v>
+        <v>7061350</v>
       </c>
       <c r="S33" t="n">
         <v>15</v>
@@ -4046,11 +4037,6 @@
       <c r="AA33" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC33" t="inlineStr">
-        <is>
-          <t>På tall</t>
         </is>
       </c>
       <c r="AD33" t="b">
@@ -4077,10 +4063,10 @@
     </row>
     <row r="34">
       <c r="A34" t="n">
-        <v>119835805</v>
+        <v>119835531</v>
       </c>
       <c r="B34" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C34" t="inlineStr">
         <is>
@@ -4093,21 +4079,21 @@
         </is>
       </c>
       <c r="E34" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H34" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I34" t="inlineStr"/>
@@ -4117,10 +4103,10 @@
         </is>
       </c>
       <c r="Q34" t="n">
-        <v>562873</v>
+        <v>562827</v>
       </c>
       <c r="R34" t="n">
-        <v>7061226</v>
+        <v>7061302</v>
       </c>
       <c r="S34" t="n">
         <v>15</v>
@@ -4167,22 +4153,22 @@
       <c r="AT34" t="inlineStr"/>
       <c r="AW34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX34" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" t="n">
-        <v>119837366</v>
+        <v>119835495</v>
       </c>
       <c r="B35" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C35" t="inlineStr">
         <is>
@@ -4195,21 +4181,21 @@
         </is>
       </c>
       <c r="E35" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H35" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I35" t="inlineStr"/>
@@ -4219,10 +4205,10 @@
         </is>
       </c>
       <c r="Q35" t="n">
-        <v>562815</v>
+        <v>562822</v>
       </c>
       <c r="R35" t="n">
-        <v>7061177</v>
+        <v>7061305</v>
       </c>
       <c r="S35" t="n">
         <v>15</v>
@@ -4269,19 +4255,19 @@
       <c r="AT35" t="inlineStr"/>
       <c r="AW35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX35" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" t="n">
-        <v>119837399</v>
+        <v>119835500</v>
       </c>
       <c r="B36" t="n">
         <v>79623</v>
@@ -4321,13 +4307,13 @@
         </is>
       </c>
       <c r="Q36" t="n">
-        <v>562767</v>
+        <v>562824</v>
       </c>
       <c r="R36" t="n">
-        <v>7061188</v>
+        <v>7061319</v>
       </c>
       <c r="S36" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T36" t="inlineStr">
         <is>
@@ -4383,10 +4369,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119837494</v>
+        <v>119838153</v>
       </c>
       <c r="B37" t="n">
-        <v>89650</v>
+        <v>91858</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4395,25 +4381,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>1962</v>
+        <v>4364</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Vaddporing</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Anomoporia kamtschatica</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Parmasto) Bondartseva</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4423,13 +4409,13 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562773</v>
+        <v>562865</v>
       </c>
       <c r="R37" t="n">
-        <v>7061158</v>
+        <v>7061107</v>
       </c>
       <c r="S37" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T37" t="inlineStr">
         <is>
@@ -4459,6 +4445,11 @@
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC37" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4485,10 +4476,10 @@
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119837992</v>
+        <v>119837899</v>
       </c>
       <c r="B38" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C38" t="inlineStr">
         <is>
@@ -4497,25 +4488,25 @@
       </c>
       <c r="D38" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E38" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H38" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I38" t="inlineStr"/>
@@ -4525,13 +4516,13 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562845</v>
+        <v>562848</v>
       </c>
       <c r="R38" t="n">
-        <v>7061115</v>
+        <v>7061087</v>
       </c>
       <c r="S38" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T38" t="inlineStr">
         <is>
@@ -4575,22 +4566,22 @@
       <c r="AT38" t="inlineStr"/>
       <c r="AW38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX38" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119835495</v>
+        <v>119836179</v>
       </c>
       <c r="B39" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4603,21 +4594,21 @@
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4627,13 +4618,13 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562822</v>
+        <v>562966</v>
       </c>
       <c r="R39" t="n">
-        <v>7061305</v>
+        <v>7061336</v>
       </c>
       <c r="S39" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T39" t="inlineStr">
         <is>
@@ -4689,10 +4680,10 @@
     </row>
     <row r="40">
       <c r="A40" t="n">
-        <v>119838606</v>
+        <v>119837560</v>
       </c>
       <c r="B40" t="n">
-        <v>78278</v>
+        <v>79623</v>
       </c>
       <c r="C40" t="inlineStr">
         <is>
@@ -4705,21 +4696,21 @@
         </is>
       </c>
       <c r="E40" t="n">
-        <v>6446</v>
+        <v>6458</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I40" t="inlineStr"/>
@@ -4729,13 +4720,13 @@
         </is>
       </c>
       <c r="Q40" t="n">
-        <v>562879</v>
+        <v>562746</v>
       </c>
       <c r="R40" t="n">
-        <v>7061091</v>
+        <v>7061142</v>
       </c>
       <c r="S40" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T40" t="inlineStr">
         <is>
@@ -4779,19 +4770,19 @@
       <c r="AT40" t="inlineStr"/>
       <c r="AW40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX40" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
-        <v>119837383</v>
+        <v>119840300</v>
       </c>
       <c r="B41" t="n">
         <v>78542</v>
@@ -4831,13 +4822,13 @@
         </is>
       </c>
       <c r="Q41" t="n">
-        <v>562779</v>
+        <v>562938</v>
       </c>
       <c r="R41" t="n">
-        <v>7061176</v>
+        <v>7061384</v>
       </c>
       <c r="S41" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T41" t="inlineStr">
         <is>
@@ -4893,10 +4884,10 @@
     </row>
     <row r="42">
       <c r="A42" t="n">
-        <v>119838859</v>
+        <v>119837344</v>
       </c>
       <c r="B42" t="n">
-        <v>91901</v>
+        <v>57473</v>
       </c>
       <c r="C42" t="inlineStr">
         <is>
@@ -4909,34 +4900,43 @@
         </is>
       </c>
       <c r="E42" t="n">
-        <v>5448</v>
+        <v>103021</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H42" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
-        </is>
-      </c>
-      <c r="I42" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I42" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P42" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q42" t="n">
-        <v>562897</v>
+        <v>562829</v>
       </c>
       <c r="R42" t="n">
-        <v>7061087</v>
+        <v>7061182</v>
       </c>
       <c r="S42" t="n">
         <v>10</v>
@@ -4966,9 +4966,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z42" t="inlineStr">
+        <is>
+          <t>16:56</t>
+        </is>
+      </c>
       <c r="AA42" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB42" t="inlineStr">
+        <is>
+          <t>16:56</t>
         </is>
       </c>
       <c r="AD42" t="b">
@@ -4983,19 +4993,19 @@
       <c r="AT42" t="inlineStr"/>
       <c r="AW42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX42" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
     </row>
     <row r="43">
       <c r="A43" t="n">
-        <v>119838865</v>
+        <v>119838064</v>
       </c>
       <c r="B43" t="n">
         <v>91858</v>
@@ -5035,10 +5045,10 @@
         </is>
       </c>
       <c r="Q43" t="n">
-        <v>562942</v>
+        <v>562850</v>
       </c>
       <c r="R43" t="n">
-        <v>7061029</v>
+        <v>7061098</v>
       </c>
       <c r="S43" t="n">
         <v>15</v>
@@ -5085,22 +5095,22 @@
       <c r="AT43" t="inlineStr"/>
       <c r="AW43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX43" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
-        <v>119836367</v>
+        <v>119838957</v>
       </c>
       <c r="B44" t="n">
-        <v>95478</v>
+        <v>91852</v>
       </c>
       <c r="C44" t="inlineStr">
         <is>
@@ -5113,21 +5123,21 @@
         </is>
       </c>
       <c r="E44" t="n">
-        <v>53</v>
+        <v>4362</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H44" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I44" t="inlineStr"/>
@@ -5137,13 +5147,13 @@
         </is>
       </c>
       <c r="Q44" t="n">
-        <v>562983</v>
+        <v>562888</v>
       </c>
       <c r="R44" t="n">
-        <v>7061268</v>
+        <v>7061052</v>
       </c>
       <c r="S44" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T44" t="inlineStr">
         <is>
@@ -5199,7 +5209,7 @@
     </row>
     <row r="45">
       <c r="A45" t="n">
-        <v>119837066</v>
+        <v>119839243</v>
       </c>
       <c r="B45" t="n">
         <v>97930</v>
@@ -5232,20 +5242,24 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I45" t="inlineStr"/>
+      <c r="I45" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P45" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q45" t="n">
-        <v>562940</v>
+        <v>563074</v>
       </c>
       <c r="R45" t="n">
-        <v>7061261</v>
+        <v>7061022</v>
       </c>
       <c r="S45" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T45" t="inlineStr">
         <is>
@@ -5272,9 +5286,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z45" t="inlineStr">
+        <is>
+          <t>18:30</t>
+        </is>
+      </c>
       <c r="AA45" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB45" t="inlineStr">
+        <is>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD45" t="b">
@@ -5289,22 +5313,22 @@
       <c r="AT45" t="inlineStr"/>
       <c r="AW45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX45" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
     </row>
     <row r="46">
       <c r="A46" t="n">
-        <v>119837999</v>
+        <v>119837494</v>
       </c>
       <c r="B46" t="n">
-        <v>79160</v>
+        <v>89650</v>
       </c>
       <c r="C46" t="inlineStr">
         <is>
@@ -5317,21 +5341,21 @@
         </is>
       </c>
       <c r="E46" t="n">
-        <v>6453</v>
+        <v>1962</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Vaddporing</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Anomoporia kamtschatica</t>
         </is>
       </c>
       <c r="H46" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Parmasto) Bondartseva</t>
         </is>
       </c>
       <c r="I46" t="inlineStr"/>
@@ -5341,13 +5365,13 @@
         </is>
       </c>
       <c r="Q46" t="n">
-        <v>562848</v>
+        <v>562773</v>
       </c>
       <c r="R46" t="n">
-        <v>7061083</v>
+        <v>7061158</v>
       </c>
       <c r="S46" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="T46" t="inlineStr">
         <is>
@@ -5403,10 +5427,10 @@
     </row>
     <row r="47">
       <c r="A47" t="n">
-        <v>119835968</v>
+        <v>119836952</v>
       </c>
       <c r="B47" t="n">
-        <v>78542</v>
+        <v>82321</v>
       </c>
       <c r="C47" t="inlineStr">
         <is>
@@ -5419,34 +5443,34 @@
         </is>
       </c>
       <c r="E47" t="n">
-        <v>6425</v>
+        <v>1312</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H47" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I47" t="inlineStr"/>
       <c r="P47" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q47" t="n">
-        <v>562856</v>
+        <v>562955</v>
       </c>
       <c r="R47" t="n">
-        <v>7061341</v>
+        <v>7061332</v>
       </c>
       <c r="S47" t="n">
         <v>10</v>
@@ -5476,9 +5500,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z47" t="inlineStr">
+        <is>
+          <t>16:35</t>
+        </is>
+      </c>
       <c r="AA47" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB47" t="inlineStr">
+        <is>
+          <t>16:35</t>
         </is>
       </c>
       <c r="AD47" t="b">
@@ -5493,22 +5527,22 @@
       <c r="AT47" t="inlineStr"/>
       <c r="AW47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX47" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="n">
-        <v>119840354</v>
+        <v>119838242</v>
       </c>
       <c r="B48" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C48" t="inlineStr">
         <is>
@@ -5521,21 +5555,21 @@
         </is>
       </c>
       <c r="E48" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H48" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I48" t="inlineStr"/>
@@ -5545,10 +5579,10 @@
         </is>
       </c>
       <c r="Q48" t="n">
-        <v>562893</v>
+        <v>562827</v>
       </c>
       <c r="R48" t="n">
-        <v>7061427</v>
+        <v>7061123</v>
       </c>
       <c r="S48" t="n">
         <v>10</v>
@@ -5578,9 +5612,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z48" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
       <c r="AA48" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB48" t="inlineStr">
+        <is>
+          <t>17:32</t>
+        </is>
+      </c>
+      <c r="AC48" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD48" t="b">
@@ -5595,22 +5644,22 @@
       <c r="AT48" t="inlineStr"/>
       <c r="AW48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX48" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
     </row>
     <row r="49">
       <c r="A49" t="n">
-        <v>119835531</v>
+        <v>119836896</v>
       </c>
       <c r="B49" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C49" t="inlineStr">
         <is>
@@ -5623,21 +5672,21 @@
         </is>
       </c>
       <c r="E49" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H49" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I49" t="inlineStr"/>
@@ -5647,13 +5696,13 @@
         </is>
       </c>
       <c r="Q49" t="n">
-        <v>562827</v>
+        <v>562930</v>
       </c>
       <c r="R49" t="n">
-        <v>7061302</v>
+        <v>7061333</v>
       </c>
       <c r="S49" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T49" t="inlineStr">
         <is>
@@ -5683,6 +5732,11 @@
       <c r="AA49" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>På tall</t>
         </is>
       </c>
       <c r="AD49" t="b">
@@ -5709,10 +5763,10 @@
     </row>
     <row r="50">
       <c r="A50" t="n">
-        <v>119835697</v>
+        <v>119835259</v>
       </c>
       <c r="B50" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C50" t="inlineStr">
         <is>
@@ -5725,21 +5779,21 @@
         </is>
       </c>
       <c r="E50" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H50" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I50" t="inlineStr"/>
@@ -5749,13 +5803,13 @@
         </is>
       </c>
       <c r="Q50" t="n">
-        <v>562826</v>
+        <v>562815</v>
       </c>
       <c r="R50" t="n">
-        <v>7061341</v>
+        <v>7061302</v>
       </c>
       <c r="S50" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T50" t="inlineStr">
         <is>
@@ -5811,10 +5865,10 @@
     </row>
     <row r="51">
       <c r="A51" t="n">
-        <v>119839228</v>
+        <v>119835470</v>
       </c>
       <c r="B51" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C51" t="inlineStr">
         <is>
@@ -5827,37 +5881,37 @@
         </is>
       </c>
       <c r="E51" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H51" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I51" t="inlineStr"/>
       <c r="P51" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q51" t="n">
-        <v>563061</v>
+        <v>562839</v>
       </c>
       <c r="R51" t="n">
-        <v>7061025</v>
+        <v>7061260</v>
       </c>
       <c r="S51" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T51" t="inlineStr">
         <is>
@@ -5884,24 +5938,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z51" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA51" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB51" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC51" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD51" t="b">
@@ -5916,22 +5955,22 @@
       <c r="AT51" t="inlineStr"/>
       <c r="AW51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX51" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>119837966</v>
+        <v>119837383</v>
       </c>
       <c r="B52" t="n">
-        <v>78187</v>
+        <v>78542</v>
       </c>
       <c r="C52" t="inlineStr">
         <is>
@@ -5944,21 +5983,21 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>353</v>
+        <v>6425</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Dvärgbägarlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Cladonia parasitica</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
         <is>
-          <t>(Hoffm.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
@@ -5968,10 +6007,10 @@
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>562845</v>
+        <v>562779</v>
       </c>
       <c r="R52" t="n">
-        <v>7061093</v>
+        <v>7061176</v>
       </c>
       <c r="S52" t="n">
         <v>20</v>
@@ -6030,10 +6069,10 @@
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>119839184</v>
+        <v>119836358</v>
       </c>
       <c r="B53" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C53" t="inlineStr">
         <is>
@@ -6042,25 +6081,25 @@
       </c>
       <c r="D53" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E53" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H53" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I53" t="inlineStr"/>
@@ -6070,10 +6109,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>563009</v>
+        <v>562901</v>
       </c>
       <c r="R53" t="n">
-        <v>7061040</v>
+        <v>7061289</v>
       </c>
       <c r="S53" t="n">
         <v>15</v>
@@ -6120,22 +6159,22 @@
       <c r="AT53" t="inlineStr"/>
       <c r="AW53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX53" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119836512</v>
+        <v>119838102</v>
       </c>
       <c r="B54" t="n">
-        <v>97930</v>
+        <v>57473</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6144,30 +6183,31 @@
       </c>
       <c r="D54" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E54" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I54" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I54" t="inlineStr"/>
+      <c r="M54" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P54" t="inlineStr">
@@ -6176,13 +6216,13 @@
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562925</v>
+        <v>562863</v>
       </c>
       <c r="R54" t="n">
-        <v>7061308</v>
+        <v>7061098</v>
       </c>
       <c r="S54" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6209,19 +6249,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z54" t="inlineStr">
-        <is>
-          <t>16:16</t>
-        </is>
-      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB54" t="inlineStr">
-        <is>
-          <t>16:16</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6236,22 +6266,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119836719</v>
+        <v>119835344</v>
       </c>
       <c r="B55" t="n">
-        <v>90580</v>
+        <v>90600</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6264,21 +6294,21 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>1202</v>
+        <v>5442</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
@@ -6288,13 +6318,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562937</v>
+        <v>562790</v>
       </c>
       <c r="R55" t="n">
-        <v>7061312</v>
+        <v>7061258</v>
       </c>
       <c r="S55" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6321,9 +6351,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z55" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB55" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6338,22 +6378,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119837298</v>
+        <v>119837999</v>
       </c>
       <c r="B56" t="n">
-        <v>78542</v>
+        <v>79160</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6366,21 +6406,21 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6425</v>
+        <v>6453</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6390,10 +6430,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562841</v>
+        <v>562848</v>
       </c>
       <c r="R56" t="n">
-        <v>7061196</v>
+        <v>7061083</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6440,22 +6480,22 @@
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119836179</v>
+        <v>119837399</v>
       </c>
       <c r="B57" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6468,21 +6508,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6492,10 +6532,10 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562966</v>
+        <v>562767</v>
       </c>
       <c r="R57" t="n">
-        <v>7061336</v>
+        <v>7061188</v>
       </c>
       <c r="S57" t="n">
         <v>10</v>
@@ -6554,10 +6594,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119836005</v>
+        <v>119836311</v>
       </c>
       <c r="B58" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6566,25 +6606,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6594,10 +6634,10 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562898</v>
+        <v>562972</v>
       </c>
       <c r="R58" t="n">
-        <v>7061215</v>
+        <v>7061274</v>
       </c>
       <c r="S58" t="n">
         <v>15</v>
@@ -6632,6 +6672,11 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AC58" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
+        </is>
+      </c>
       <c r="AD58" t="b">
         <v>0</v>
       </c>
@@ -6644,22 +6689,22 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119840391</v>
+        <v>119838865</v>
       </c>
       <c r="B59" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6668,25 +6713,25 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
@@ -6696,13 +6741,13 @@
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562861</v>
+        <v>562942</v>
       </c>
       <c r="R59" t="n">
-        <v>7061439</v>
+        <v>7061029</v>
       </c>
       <c r="S59" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6746,22 +6791,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119837427</v>
+        <v>119840392</v>
       </c>
       <c r="B60" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6770,25 +6815,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6798,10 +6843,10 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562772</v>
+        <v>562878</v>
       </c>
       <c r="R60" t="n">
-        <v>7061165</v>
+        <v>7061442</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -6833,7 +6878,7 @@
       </c>
       <c r="Z60" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
@@ -6843,7 +6888,12 @@
       </c>
       <c r="AB60" t="inlineStr">
         <is>
-          <t>17:03</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC60" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6870,10 +6920,10 @@
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119837858</v>
+        <v>119838967</v>
       </c>
       <c r="B61" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6882,38 +6932,42 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562847</v>
+        <v>562990</v>
       </c>
       <c r="R61" t="n">
-        <v>7061096</v>
+        <v>7061060</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6943,9 +6997,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z61" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA61" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB61" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -6960,19 +7024,19 @@
       <c r="AT61" t="inlineStr"/>
       <c r="AW61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX61" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>119835631</v>
+        <v>119837193</v>
       </c>
       <c r="B62" t="n">
         <v>57320</v>
@@ -7012,13 +7076,13 @@
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>562785</v>
+        <v>562864</v>
       </c>
       <c r="R62" t="n">
-        <v>7061238</v>
+        <v>7061224</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7045,19 +7109,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z62" t="inlineStr">
-        <is>
-          <t>15:34</t>
-        </is>
-      </c>
       <c r="AA62" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB62" t="inlineStr">
-        <is>
-          <t>15:34</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
@@ -7077,19 +7131,19 @@
       <c r="AT62" t="inlineStr"/>
       <c r="AW62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX62" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>119836358</v>
+        <v>119837543</v>
       </c>
       <c r="B63" t="n">
         <v>78542</v>
@@ -7129,13 +7183,13 @@
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>562901</v>
+        <v>562745</v>
       </c>
       <c r="R63" t="n">
-        <v>7061289</v>
+        <v>7061152</v>
       </c>
       <c r="S63" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T63" t="inlineStr">
         <is>
@@ -7162,9 +7216,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z63" t="inlineStr">
+        <is>
+          <t>17:11</t>
+        </is>
+      </c>
       <c r="AA63" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB63" t="inlineStr">
+        <is>
+          <t>17:11</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7179,22 +7243,22 @@
       <c r="AT63" t="inlineStr"/>
       <c r="AW63" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX63" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>119837306</v>
+        <v>119835968</v>
       </c>
       <c r="B64" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C64" t="inlineStr">
         <is>
@@ -7207,21 +7271,21 @@
         </is>
       </c>
       <c r="E64" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F64" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H64" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I64" t="inlineStr"/>
@@ -7231,10 +7295,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>562793</v>
+        <v>562856</v>
       </c>
       <c r="R64" t="n">
-        <v>7061251</v>
+        <v>7061341</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7267,11 +7331,6 @@
       <c r="AA64" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC64" t="inlineStr">
-        <is>
-          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7298,10 +7357,10 @@
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>119838327</v>
+        <v>119835516</v>
       </c>
       <c r="B65" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C65" t="inlineStr">
         <is>
@@ -7310,25 +7369,25 @@
       </c>
       <c r="D65" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E65" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H65" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I65" t="inlineStr"/>
@@ -7338,13 +7397,13 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>562870</v>
+        <v>562795</v>
       </c>
       <c r="R65" t="n">
-        <v>7061110</v>
+        <v>7061238</v>
       </c>
       <c r="S65" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T65" t="inlineStr">
         <is>
@@ -7371,9 +7430,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z65" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
       <c r="AA65" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB65" t="inlineStr">
+        <is>
+          <t>15:30</t>
+        </is>
+      </c>
+      <c r="AC65" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7388,22 +7462,22 @@
       <c r="AT65" t="inlineStr"/>
       <c r="AW65" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX65" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>119835516</v>
+        <v>119835697</v>
       </c>
       <c r="B66" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C66" t="inlineStr">
         <is>
@@ -7416,21 +7490,21 @@
         </is>
       </c>
       <c r="E66" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H66" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I66" t="inlineStr"/>
@@ -7440,10 +7514,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>562795</v>
+        <v>562826</v>
       </c>
       <c r="R66" t="n">
-        <v>7061238</v>
+        <v>7061341</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7473,24 +7547,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z66" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
       <c r="AA66" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB66" t="inlineStr">
-        <is>
-          <t>15:30</t>
-        </is>
-      </c>
-      <c r="AC66" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7505,22 +7564,22 @@
       <c r="AT66" t="inlineStr"/>
       <c r="AW66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX66" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>119838885</v>
+        <v>119840261</v>
       </c>
       <c r="B67" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C67" t="inlineStr">
         <is>
@@ -7529,42 +7588,38 @@
       </c>
       <c r="D67" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E67" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H67" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I67" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I67" t="inlineStr"/>
       <c r="P67" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>562977</v>
+        <v>563003</v>
       </c>
       <c r="R67" t="n">
-        <v>7061045</v>
+        <v>7061318</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7596,7 +7651,7 @@
       </c>
       <c r="Z67" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:10</t>
         </is>
       </c>
       <c r="AA67" t="inlineStr">
@@ -7606,7 +7661,12 @@
       </c>
       <c r="AB67" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>19:10</t>
+        </is>
+      </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD67" t="b">
@@ -7633,10 +7693,10 @@
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>119837181</v>
+        <v>119836373</v>
       </c>
       <c r="B68" t="n">
-        <v>90545</v>
+        <v>97930</v>
       </c>
       <c r="C68" t="inlineStr">
         <is>
@@ -7645,38 +7705,42 @@
       </c>
       <c r="D68" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E68" t="n">
-        <v>5447</v>
+        <v>220787</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
-        </is>
-      </c>
-      <c r="I68" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I68" t="inlineStr">
+        <is>
+          <t>60</t>
+        </is>
+      </c>
       <c r="P68" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>562872</v>
+        <v>562910</v>
       </c>
       <c r="R68" t="n">
-        <v>7061246</v>
+        <v>7061306</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -7706,9 +7770,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z68" t="inlineStr">
+        <is>
+          <t>16:07</t>
+        </is>
+      </c>
       <c r="AA68" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB68" t="inlineStr">
+        <is>
+          <t>16:07</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -7723,22 +7797,22 @@
       <c r="AT68" t="inlineStr"/>
       <c r="AW68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX68" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>119838625</v>
+        <v>119837074</v>
       </c>
       <c r="B69" t="n">
-        <v>91902</v>
+        <v>97930</v>
       </c>
       <c r="C69" t="inlineStr">
         <is>
@@ -7747,38 +7821,42 @@
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>5449</v>
+        <v>220787</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Svart taggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellodon niger</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P.Karst.</t>
-        </is>
-      </c>
-      <c r="I69" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I69" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P69" t="inlineStr">
         <is>
           <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>562899</v>
+        <v>562940</v>
       </c>
       <c r="R69" t="n">
-        <v>7061101</v>
+        <v>7061272</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -7810,7 +7888,7 @@
       </c>
       <c r="Z69" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
@@ -7820,7 +7898,7 @@
       </c>
       <c r="AB69" t="inlineStr">
         <is>
-          <t>17:48</t>
+          <t>16:40</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -7847,10 +7925,10 @@
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>119839212</v>
+        <v>119836424</v>
       </c>
       <c r="B70" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C70" t="inlineStr">
         <is>
@@ -7859,41 +7937,45 @@
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E70" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>70</t>
+        </is>
+      </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>563063</v>
+        <v>562902</v>
       </c>
       <c r="R70" t="n">
-        <v>7061037</v>
+        <v>7061306</v>
       </c>
       <c r="S70" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T70" t="inlineStr">
         <is>
@@ -7920,19 +8002,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z70" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA70" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB70" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -7947,22 +8019,22 @@
       <c r="AT70" t="inlineStr"/>
       <c r="AW70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX70" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>119836807</v>
+        <v>119836491</v>
       </c>
       <c r="B71" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C71" t="inlineStr">
         <is>
@@ -7971,25 +8043,25 @@
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -7999,13 +8071,13 @@
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>562926</v>
+        <v>563040</v>
       </c>
       <c r="R71" t="n">
-        <v>7061340</v>
+        <v>7061203</v>
       </c>
       <c r="S71" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T71" t="inlineStr">
         <is>
@@ -8032,24 +8104,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z71" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA71" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB71" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC71" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8064,19 +8121,19 @@
       <c r="AT71" t="inlineStr"/>
       <c r="AW71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX71" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>119840328</v>
+        <v>119837992</v>
       </c>
       <c r="B72" t="n">
         <v>79623</v>
@@ -8116,13 +8173,13 @@
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>562922</v>
+        <v>562845</v>
       </c>
       <c r="R72" t="n">
-        <v>7061399</v>
+        <v>7061115</v>
       </c>
       <c r="S72" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T72" t="inlineStr">
         <is>
@@ -8166,22 +8223,22 @@
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119835500</v>
+        <v>119837084</v>
       </c>
       <c r="B73" t="n">
-        <v>79623</v>
+        <v>90600</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8194,21 +8251,21 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>6458</v>
+        <v>5442</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
@@ -8218,10 +8275,10 @@
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562824</v>
+        <v>562905</v>
       </c>
       <c r="R73" t="n">
-        <v>7061319</v>
+        <v>7061251</v>
       </c>
       <c r="S73" t="n">
         <v>15</v>
@@ -8280,10 +8337,10 @@
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119838872</v>
+        <v>119839212</v>
       </c>
       <c r="B74" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C74" t="inlineStr">
         <is>
@@ -8296,37 +8353,37 @@
         </is>
       </c>
       <c r="E74" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H74" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>562893</v>
+        <v>563063</v>
       </c>
       <c r="R74" t="n">
-        <v>7061059</v>
+        <v>7061037</v>
       </c>
       <c r="S74" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T74" t="inlineStr">
         <is>
@@ -8353,9 +8410,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z74" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB74" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8370,22 +8437,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119836629</v>
+        <v>119840354</v>
       </c>
       <c r="B75" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8398,39 +8465,34 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
-      <c r="M75" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P75" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562935</v>
+        <v>562893</v>
       </c>
       <c r="R75" t="n">
-        <v>7061315</v>
+        <v>7061427</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8460,19 +8522,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z75" t="inlineStr">
-        <is>
-          <t>16:20</t>
-        </is>
-      </c>
       <c r="AA75" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB75" t="inlineStr">
-        <is>
-          <t>16:20</t>
         </is>
       </c>
       <c r="AD75" t="b">
@@ -8487,22 +8539,22 @@
       <c r="AT75" t="inlineStr"/>
       <c r="AW75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX75" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>119837193</v>
+        <v>119837066</v>
       </c>
       <c r="B76" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C76" t="inlineStr">
         <is>
@@ -8511,25 +8563,25 @@
       </c>
       <c r="D76" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E76" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I76" t="inlineStr"/>
@@ -8539,10 +8591,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>562864</v>
+        <v>562940</v>
       </c>
       <c r="R76" t="n">
-        <v>7061224</v>
+        <v>7061261</v>
       </c>
       <c r="S76" t="n">
         <v>15</v>
@@ -8575,11 +8627,6 @@
       <c r="AA76" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC76" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8606,10 +8653,10 @@
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>119837856</v>
+        <v>119838885</v>
       </c>
       <c r="B77" t="n">
-        <v>57320</v>
+        <v>97930</v>
       </c>
       <c r="C77" t="inlineStr">
         <is>
@@ -8618,38 +8665,42 @@
       </c>
       <c r="D77" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E77" t="n">
-        <v>100109</v>
+        <v>220787</v>
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I77" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I77" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q77" t="n">
-        <v>562803</v>
+        <v>562977</v>
       </c>
       <c r="R77" t="n">
-        <v>7061104</v>
+        <v>7061045</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -8681,7 +8732,7 @@
       </c>
       <c r="Z77" t="inlineStr">
         <is>
-          <t>17:21</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA77" t="inlineStr">
@@ -8691,12 +8742,7 @@
       </c>
       <c r="AB77" t="inlineStr">
         <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC77" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD77" t="b">
@@ -8723,10 +8769,10 @@
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>119835763</v>
+        <v>119837306</v>
       </c>
       <c r="B78" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C78" t="inlineStr">
         <is>
@@ -8739,21 +8785,21 @@
         </is>
       </c>
       <c r="E78" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -8763,10 +8809,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>562859</v>
+        <v>562793</v>
       </c>
       <c r="R78" t="n">
-        <v>7061254</v>
+        <v>7061251</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -8796,19 +8842,14 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z78" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA78" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AB78" t="inlineStr">
-        <is>
-          <t>15:39</t>
+      <c r="AC78" t="inlineStr">
+        <is>
+          <t>På björkhögstubbe</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -8823,22 +8864,22 @@
       <c r="AT78" t="inlineStr"/>
       <c r="AW78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX78" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>119837084</v>
+        <v>119838859</v>
       </c>
       <c r="B79" t="n">
-        <v>90600</v>
+        <v>91901</v>
       </c>
       <c r="C79" t="inlineStr">
         <is>
@@ -8851,21 +8892,21 @@
         </is>
       </c>
       <c r="E79" t="n">
-        <v>5442</v>
+        <v>5448</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I79" t="inlineStr"/>
@@ -8875,13 +8916,13 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>562905</v>
+        <v>562897</v>
       </c>
       <c r="R79" t="n">
-        <v>7061251</v>
+        <v>7061087</v>
       </c>
       <c r="S79" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T79" t="inlineStr">
         <is>
@@ -8937,10 +8978,10 @@
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>119838957</v>
+        <v>119837761</v>
       </c>
       <c r="B80" t="n">
-        <v>91852</v>
+        <v>78542</v>
       </c>
       <c r="C80" t="inlineStr">
         <is>
@@ -8953,21 +8994,21 @@
         </is>
       </c>
       <c r="E80" t="n">
-        <v>4362</v>
+        <v>6425</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Blå taggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Hydnellum caeruleum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Hornem.) P.Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -8977,10 +9018,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>562888</v>
+        <v>562816</v>
       </c>
       <c r="R80" t="n">
-        <v>7061052</v>
+        <v>7061089</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9039,10 +9080,10 @@
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>119838967</v>
+        <v>119835350</v>
       </c>
       <c r="B81" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C81" t="inlineStr">
         <is>
@@ -9051,45 +9092,41 @@
       </c>
       <c r="D81" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E81" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I81" t="inlineStr"/>
       <c r="P81" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>562990</v>
+        <v>562801</v>
       </c>
       <c r="R81" t="n">
-        <v>7061060</v>
+        <v>7061274</v>
       </c>
       <c r="S81" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T81" t="inlineStr">
         <is>
@@ -9116,19 +9153,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z81" t="inlineStr">
-        <is>
-          <t>18:11</t>
-        </is>
-      </c>
       <c r="AA81" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB81" t="inlineStr">
-        <is>
-          <t>18:11</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9143,22 +9170,22 @@
       <c r="AT81" t="inlineStr"/>
       <c r="AW81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX81" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>119835259</v>
+        <v>119839227</v>
       </c>
       <c r="B82" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C82" t="inlineStr">
         <is>
@@ -9167,25 +9194,25 @@
       </c>
       <c r="D82" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E82" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H82" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I82" t="inlineStr"/>
@@ -9195,13 +9222,13 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>562815</v>
+        <v>563080</v>
       </c>
       <c r="R82" t="n">
-        <v>7061302</v>
+        <v>7061030</v>
       </c>
       <c r="S82" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T82" t="inlineStr">
         <is>
@@ -9257,10 +9284,10 @@
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>119835742</v>
+        <v>119836533</v>
       </c>
       <c r="B83" t="n">
-        <v>56532</v>
+        <v>97930</v>
       </c>
       <c r="C83" t="inlineStr">
         <is>
@@ -9269,41 +9296,45 @@
       </c>
       <c r="D83" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E83" t="n">
-        <v>100138</v>
+        <v>220787</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I83" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I83" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P83" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>562853</v>
+        <v>562927</v>
       </c>
       <c r="R83" t="n">
-        <v>7061243</v>
+        <v>7061314</v>
       </c>
       <c r="S83" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T83" t="inlineStr">
         <is>
@@ -9330,9 +9361,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z83" t="inlineStr">
+        <is>
+          <t>16:17</t>
+        </is>
+      </c>
       <c r="AA83" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB83" t="inlineStr">
+        <is>
+          <t>16:17</t>
         </is>
       </c>
       <c r="AD83" t="b">
@@ -9347,22 +9388,22 @@
       <c r="AT83" t="inlineStr"/>
       <c r="AW83" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX83" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>119835470</v>
+        <v>119836923</v>
       </c>
       <c r="B84" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C84" t="inlineStr">
         <is>
@@ -9375,37 +9416,37 @@
         </is>
       </c>
       <c r="E84" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H84" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I84" t="inlineStr"/>
       <c r="P84" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>562839</v>
+        <v>562958</v>
       </c>
       <c r="R84" t="n">
-        <v>7061260</v>
+        <v>7061345</v>
       </c>
       <c r="S84" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T84" t="inlineStr">
         <is>
@@ -9432,9 +9473,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z84" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
       <c r="AA84" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB84" t="inlineStr">
+        <is>
+          <t>16:32</t>
+        </is>
+      </c>
+      <c r="AC84" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD84" t="b">
@@ -9449,22 +9505,22 @@
       <c r="AT84" t="inlineStr"/>
       <c r="AW84" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX84" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>119837074</v>
+        <v>119835631</v>
       </c>
       <c r="B85" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C85" t="inlineStr">
         <is>
@@ -9473,42 +9529,38 @@
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E85" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I85" t="inlineStr"/>
       <c r="P85" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>562940</v>
+        <v>562785</v>
       </c>
       <c r="R85" t="n">
-        <v>7061272</v>
+        <v>7061238</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9540,7 +9592,7 @@
       </c>
       <c r="Z85" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:34</t>
         </is>
       </c>
       <c r="AA85" t="inlineStr">
@@ -9550,7 +9602,12 @@
       </c>
       <c r="AB85" t="inlineStr">
         <is>
-          <t>16:40</t>
+          <t>15:34</t>
+        </is>
+      </c>
+      <c r="AC85" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD85" t="b">
@@ -9577,10 +9634,10 @@
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>119835350</v>
+        <v>119835514</v>
       </c>
       <c r="B86" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C86" t="inlineStr">
         <is>
@@ -9593,21 +9650,21 @@
         </is>
       </c>
       <c r="E86" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H86" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I86" t="inlineStr"/>
@@ -9617,10 +9674,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>562801</v>
+        <v>562849</v>
       </c>
       <c r="R86" t="n">
-        <v>7061274</v>
+        <v>7061244</v>
       </c>
       <c r="S86" t="n">
         <v>15</v>
@@ -9679,10 +9736,10 @@
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>119836896</v>
+        <v>119837427</v>
       </c>
       <c r="B87" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C87" t="inlineStr">
         <is>
@@ -9691,25 +9748,25 @@
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -9719,10 +9776,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>562930</v>
+        <v>562772</v>
       </c>
       <c r="R87" t="n">
-        <v>7061333</v>
+        <v>7061165</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -9752,14 +9809,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z87" t="inlineStr">
+        <is>
+          <t>17:03</t>
+        </is>
+      </c>
       <c r="AA87" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC87" t="inlineStr">
-        <is>
-          <t>På tall</t>
+      <c r="AB87" t="inlineStr">
+        <is>
+          <t>17:03</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -9774,22 +9836,22 @@
       <c r="AT87" t="inlineStr"/>
       <c r="AW87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX87" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>119838064</v>
+        <v>119838625</v>
       </c>
       <c r="B88" t="n">
-        <v>91858</v>
+        <v>91902</v>
       </c>
       <c r="C88" t="inlineStr">
         <is>
@@ -9798,41 +9860,41 @@
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>4364</v>
+        <v>5449</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Svart taggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellodon niger</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.:Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>562850</v>
+        <v>562899</v>
       </c>
       <c r="R88" t="n">
-        <v>7061098</v>
+        <v>7061101</v>
       </c>
       <c r="S88" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T88" t="inlineStr">
         <is>
@@ -9859,9 +9921,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z88" t="inlineStr">
+        <is>
+          <t>17:48</t>
+        </is>
+      </c>
       <c r="AA88" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB88" t="inlineStr">
+        <is>
+          <t>17:48</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -9876,19 +9948,19 @@
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119840261</v>
+        <v>119839228</v>
       </c>
       <c r="B89" t="n">
         <v>57320</v>
@@ -9928,10 +10000,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>563003</v>
+        <v>563061</v>
       </c>
       <c r="R89" t="n">
-        <v>7061318</v>
+        <v>7061025</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -9963,7 +10035,7 @@
       </c>
       <c r="Z89" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
@@ -9973,7 +10045,7 @@
       </c>
       <c r="AB89" t="inlineStr">
         <is>
-          <t>19:10</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AC89" t="inlineStr">
@@ -10005,7 +10077,7 @@
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119838242</v>
+        <v>119835980</v>
       </c>
       <c r="B90" t="n">
         <v>57320</v>
@@ -10039,16 +10111,21 @@
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
+      <c r="M90" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562827</v>
+        <v>562885</v>
       </c>
       <c r="R90" t="n">
-        <v>7061123</v>
+        <v>7061225</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10080,7 +10157,7 @@
       </c>
       <c r="Z90" t="inlineStr">
         <is>
-          <t>17:32</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
@@ -10090,12 +10167,7 @@
       </c>
       <c r="AB90" t="inlineStr">
         <is>
-          <t>17:32</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10122,10 +10194,10 @@
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119836533</v>
+        <v>119835654</v>
       </c>
       <c r="B91" t="n">
-        <v>97930</v>
+        <v>79652</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10134,45 +10206,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>220787</v>
+        <v>6462</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
+          <t>(Spreng.) Tuck.</t>
+        </is>
+      </c>
+      <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562927</v>
+        <v>562838</v>
       </c>
       <c r="R91" t="n">
-        <v>7061314</v>
+        <v>7061333</v>
       </c>
       <c r="S91" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10199,19 +10267,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>16:17</t>
-        </is>
-      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>16:17</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10226,22 +10284,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119836311</v>
+        <v>119835796</v>
       </c>
       <c r="B92" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10250,25 +10308,25 @@
       </c>
       <c r="D92" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E92" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
@@ -10278,13 +10336,13 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562972</v>
+        <v>562830</v>
       </c>
       <c r="R92" t="n">
-        <v>7061274</v>
+        <v>7061321</v>
       </c>
       <c r="S92" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10314,11 +10372,6 @@
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC92" t="inlineStr">
-        <is>
-          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10345,10 +10398,10 @@
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119840392</v>
+        <v>119837858</v>
       </c>
       <c r="B93" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10357,25 +10410,25 @@
       </c>
       <c r="D93" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E93" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10385,10 +10438,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>562878</v>
+        <v>562847</v>
       </c>
       <c r="R93" t="n">
-        <v>7061442</v>
+        <v>7061096</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10418,24 +10471,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
       <c r="AA93" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC93" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10450,22 +10488,22 @@
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>119839757</v>
+        <v>119839184</v>
       </c>
       <c r="B94" t="n">
-        <v>57336</v>
+        <v>91858</v>
       </c>
       <c r="C94" t="inlineStr">
         <is>
@@ -10474,25 +10512,25 @@
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>4364</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10502,13 +10540,13 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>563104</v>
+        <v>563009</v>
       </c>
       <c r="R94" t="n">
-        <v>7061110</v>
+        <v>7061040</v>
       </c>
       <c r="S94" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="T94" t="inlineStr">
         <is>
@@ -10538,11 +10576,6 @@
       <c r="AA94" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Födosökshack</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10569,10 +10602,10 @@
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>119837424</v>
+        <v>119835805</v>
       </c>
       <c r="B95" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C95" t="inlineStr">
         <is>
@@ -10581,25 +10614,25 @@
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10609,10 +10642,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>562774</v>
+        <v>562873</v>
       </c>
       <c r="R95" t="n">
-        <v>7061178</v>
+        <v>7061226</v>
       </c>
       <c r="S95" t="n">
         <v>15</v>
@@ -10671,10 +10704,10 @@
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>119837761</v>
+        <v>119836629</v>
       </c>
       <c r="B96" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C96" t="inlineStr">
         <is>
@@ -10687,34 +10720,39 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
+      <c r="M96" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P96" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>562816</v>
+        <v>562935</v>
       </c>
       <c r="R96" t="n">
-        <v>7061089</v>
+        <v>7061315</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -10744,9 +10782,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>16:20</t>
+        </is>
+      </c>
       <c r="AA96" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>16:20</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -10761,22 +10809,22 @@
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>119838709</v>
+        <v>119837299</v>
       </c>
       <c r="B97" t="n">
-        <v>91901</v>
+        <v>82321</v>
       </c>
       <c r="C97" t="inlineStr">
         <is>
@@ -10789,21 +10837,21 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5448</v>
+        <v>1312</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Gammelgransskål</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Pseudographis pinicola</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Nyl.) Rehm</t>
         </is>
       </c>
       <c r="I97" t="inlineStr"/>
@@ -10813,13 +10861,13 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>562892</v>
+        <v>562843</v>
       </c>
       <c r="R97" t="n">
-        <v>7061086</v>
+        <v>7061204</v>
       </c>
       <c r="S97" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T97" t="inlineStr">
         <is>
@@ -10846,9 +10894,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z97" t="inlineStr">
+        <is>
+          <t>16:52</t>
+        </is>
+      </c>
       <c r="AA97" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB97" t="inlineStr">
+        <is>
+          <t>16:52</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -10863,22 +10921,22 @@
       <c r="AT97" t="inlineStr"/>
       <c r="AW97" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX97" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>119840373</v>
+        <v>119839135</v>
       </c>
       <c r="B98" t="n">
-        <v>79623</v>
+        <v>78278</v>
       </c>
       <c r="C98" t="inlineStr">
         <is>
@@ -10891,34 +10949,34 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>6458</v>
+        <v>6446</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>562875</v>
+        <v>562982</v>
       </c>
       <c r="R98" t="n">
-        <v>7061433</v>
+        <v>7061063</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -10948,9 +11006,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z98" t="inlineStr">
+        <is>
+          <t>18:21</t>
+        </is>
+      </c>
       <c r="AA98" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB98" t="inlineStr">
+        <is>
+          <t>18:21</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -10965,22 +11033,22 @@
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>119838597</v>
+        <v>119840373</v>
       </c>
       <c r="B99" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C99" t="inlineStr">
         <is>
@@ -10989,25 +11057,25 @@
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11017,13 +11085,13 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>562861</v>
+        <v>562875</v>
       </c>
       <c r="R99" t="n">
-        <v>7061099</v>
+        <v>7061433</v>
       </c>
       <c r="S99" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T99" t="inlineStr">
         <is>
@@ -11067,22 +11135,22 @@
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>119836952</v>
+        <v>119836521</v>
       </c>
       <c r="B100" t="n">
-        <v>82321</v>
+        <v>97930</v>
       </c>
       <c r="C100" t="inlineStr">
         <is>
@@ -11091,41 +11159,41 @@
       </c>
       <c r="D100" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E100" t="n">
-        <v>1312</v>
+        <v>220787</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
       <c r="P100" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>562955</v>
+        <v>562928</v>
       </c>
       <c r="R100" t="n">
-        <v>7061332</v>
+        <v>7061305</v>
       </c>
       <c r="S100" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11152,19 +11220,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z100" t="inlineStr">
-        <is>
-          <t>16:35</t>
-        </is>
-      </c>
       <c r="AA100" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB100" t="inlineStr">
-        <is>
-          <t>16:35</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11179,22 +11237,22 @@
       <c r="AT100" t="inlineStr"/>
       <c r="AW100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX100" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119839135</v>
+        <v>119835742</v>
       </c>
       <c r="B101" t="n">
-        <v>78278</v>
+        <v>56532</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11203,41 +11261,41 @@
       </c>
       <c r="D101" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E101" t="n">
-        <v>6446</v>
+        <v>100138</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
       <c r="P101" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562982</v>
+        <v>562853</v>
       </c>
       <c r="R101" t="n">
-        <v>7061063</v>
+        <v>7061243</v>
       </c>
       <c r="S101" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11264,19 +11322,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z101" t="inlineStr">
-        <is>
-          <t>18:21</t>
-        </is>
-      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB101" t="inlineStr">
-        <is>
-          <t>18:21</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11291,22 +11339,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119838179</v>
+        <v>119835535</v>
       </c>
       <c r="B102" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11315,25 +11363,25 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
@@ -11343,13 +11391,13 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562854</v>
+        <v>562795</v>
       </c>
       <c r="R102" t="n">
-        <v>7061121</v>
+        <v>7061238</v>
       </c>
       <c r="S102" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T102" t="inlineStr">
         <is>
@@ -11376,9 +11424,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z102" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA102" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB102" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11393,22 +11451,22 @@
       <c r="AT102" t="inlineStr"/>
       <c r="AW102" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX102" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119835980</v>
+        <v>119837181</v>
       </c>
       <c r="B103" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11417,43 +11475,38 @@
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
-      <c r="M103" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P103" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562885</v>
+        <v>562872</v>
       </c>
       <c r="R103" t="n">
-        <v>7061225</v>
+        <v>7061246</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11483,19 +11536,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z103" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA103" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB103" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11510,22 +11553,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119835514</v>
+        <v>119837856</v>
       </c>
       <c r="B104" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11538,37 +11581,37 @@
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562849</v>
+        <v>562803</v>
       </c>
       <c r="R104" t="n">
-        <v>7061244</v>
+        <v>7061104</v>
       </c>
       <c r="S104" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T104" t="inlineStr">
         <is>
@@ -11595,9 +11638,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z104" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB104" t="inlineStr">
+        <is>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC104" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11612,22 +11670,22 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>119835796</v>
+        <v>119836284</v>
       </c>
       <c r="B105" t="n">
-        <v>79623</v>
+        <v>97930</v>
       </c>
       <c r="C105" t="inlineStr">
         <is>
@@ -11636,38 +11694,42 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6458</v>
+        <v>220787</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I105" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
       <c r="P105" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>562830</v>
+        <v>562903</v>
       </c>
       <c r="R105" t="n">
-        <v>7061321</v>
+        <v>7061259</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -11697,9 +11759,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z105" t="inlineStr">
+        <is>
+          <t>15:58</t>
+        </is>
+      </c>
       <c r="AA105" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB105" t="inlineStr">
+        <is>
+          <t>15:58</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -11714,22 +11786,22 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119836424</v>
+        <v>119838864</v>
       </c>
       <c r="B106" t="n">
-        <v>97930</v>
+        <v>78279</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11738,45 +11810,41 @@
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>220787</v>
+        <v>228912</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>70</t>
-        </is>
-      </c>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
+        </is>
+      </c>
+      <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562902</v>
+        <v>562940</v>
       </c>
       <c r="R106" t="n">
-        <v>7061306</v>
+        <v>7061021</v>
       </c>
       <c r="S106" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11803,9 +11871,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z106" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB106" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11820,22 +11898,22 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119836373</v>
+        <v>119835108</v>
       </c>
       <c r="B107" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C107" t="inlineStr">
         <is>
@@ -11844,45 +11922,41 @@
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E107" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>60</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>562910</v>
+        <v>562802</v>
       </c>
       <c r="R107" t="n">
-        <v>7061306</v>
+        <v>7061280</v>
       </c>
       <c r="S107" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -11909,19 +11983,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>16:07</t>
-        </is>
-      </c>
       <c r="AA107" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>16:07</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -11936,19 +12000,19 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119835751</v>
+        <v>119835638</v>
       </c>
       <c r="B108" t="n">
         <v>79623</v>
@@ -11988,13 +12052,13 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>562833</v>
+        <v>562838</v>
       </c>
       <c r="R108" t="n">
-        <v>7061339</v>
+        <v>7061326</v>
       </c>
       <c r="S108" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12050,10 +12114,10 @@
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119835431</v>
+        <v>119838179</v>
       </c>
       <c r="B109" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12066,21 +12130,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12090,10 +12154,10 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>562853</v>
+        <v>562854</v>
       </c>
       <c r="R109" t="n">
-        <v>7061293</v>
+        <v>7061121</v>
       </c>
       <c r="S109" t="n">
         <v>15</v>
@@ -12152,10 +12216,10 @@
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119835108</v>
+        <v>119838709</v>
       </c>
       <c r="B110" t="n">
-        <v>79623</v>
+        <v>91901</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12168,21 +12232,21 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>6458</v>
+        <v>5448</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
@@ -12192,10 +12256,10 @@
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>562802</v>
+        <v>562892</v>
       </c>
       <c r="R110" t="n">
-        <v>7061280</v>
+        <v>7061086</v>
       </c>
       <c r="S110" t="n">
         <v>15</v>
@@ -12254,10 +12318,10 @@
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119836632</v>
+        <v>119838030</v>
       </c>
       <c r="B111" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12266,45 +12330,46 @@
       </c>
       <c r="D111" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E111" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>30</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562948</v>
+        <v>562828</v>
       </c>
       <c r="R111" t="n">
-        <v>7061323</v>
+        <v>7061089</v>
       </c>
       <c r="S111" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12331,9 +12396,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12348,22 +12423,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119835344</v>
+        <v>119836807</v>
       </c>
       <c r="B112" t="n">
-        <v>90600</v>
+        <v>57320</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12376,21 +12451,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>5442</v>
+        <v>100109</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12400,10 +12475,10 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>562790</v>
+        <v>562926</v>
       </c>
       <c r="R112" t="n">
-        <v>7061258</v>
+        <v>7061340</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12435,7 +12510,7 @@
       </c>
       <c r="Z112" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:28</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
@@ -12445,7 +12520,12 @@
       </c>
       <c r="AB112" t="inlineStr">
         <is>
-          <t>15:20</t>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC112" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12472,10 +12552,10 @@
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>119835535</v>
+        <v>119838872</v>
       </c>
       <c r="B113" t="n">
-        <v>91858</v>
+        <v>91852</v>
       </c>
       <c r="C113" t="inlineStr">
         <is>
@@ -12484,25 +12564,25 @@
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>4364</v>
+        <v>4362</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Blå taggsvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Hydnellum caeruleum</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Hornem.) P.Karst.</t>
         </is>
       </c>
       <c r="I113" t="inlineStr"/>
@@ -12512,13 +12592,13 @@
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>562795</v>
+        <v>562893</v>
       </c>
       <c r="R113" t="n">
-        <v>7061238</v>
+        <v>7061059</v>
       </c>
       <c r="S113" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T113" t="inlineStr">
         <is>
@@ -12545,19 +12625,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z113" t="inlineStr">
-        <is>
-          <t>15:32</t>
-        </is>
-      </c>
       <c r="AA113" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB113" t="inlineStr">
-        <is>
-          <t>15:32</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -12572,22 +12642,22 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119835360</v>
+        <v>119838597</v>
       </c>
       <c r="B114" t="n">
-        <v>4766</v>
+        <v>91858</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12600,21 +12670,21 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100299</v>
+        <v>4364</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12624,10 +12694,10 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>562801</v>
+        <v>562861</v>
       </c>
       <c r="R114" t="n">
-        <v>7061292</v>
+        <v>7061099</v>
       </c>
       <c r="S114" t="n">
         <v>15</v>
@@ -12662,11 +12732,6 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="AC114" t="inlineStr">
-        <is>
-          <t>Gnaggångar</t>
-        </is>
-      </c>
       <c r="AD114" t="b">
         <v>0</v>
       </c>
@@ -12679,22 +12744,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119836521</v>
+        <v>119835763</v>
       </c>
       <c r="B115" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12703,25 +12768,25 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
@@ -12731,13 +12796,13 @@
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>562928</v>
+        <v>562859</v>
       </c>
       <c r="R115" t="n">
-        <v>7061305</v>
+        <v>7061254</v>
       </c>
       <c r="S115" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12764,9 +12829,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12781,19 +12856,19 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119836284</v>
+        <v>119836632</v>
       </c>
       <c r="B116" t="n">
         <v>97930</v>
@@ -12828,7 +12903,7 @@
       </c>
       <c r="I116" t="inlineStr">
         <is>
-          <t>50</t>
+          <t>30</t>
         </is>
       </c>
       <c r="P116" t="inlineStr">
@@ -12837,13 +12912,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562903</v>
+        <v>562948</v>
       </c>
       <c r="R116" t="n">
-        <v>7061259</v>
+        <v>7061323</v>
       </c>
       <c r="S116" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -12870,19 +12945,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z116" t="inlineStr">
-        <is>
-          <t>15:58</t>
-        </is>
-      </c>
       <c r="AA116" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB116" t="inlineStr">
-        <is>
-          <t>15:58</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -12897,22 +12962,22 @@
       <c r="AT116" t="inlineStr"/>
       <c r="AW116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX116" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>119838864</v>
+        <v>119836512</v>
       </c>
       <c r="B117" t="n">
-        <v>78279</v>
+        <v>97930</v>
       </c>
       <c r="C117" t="inlineStr">
         <is>
@@ -12921,38 +12986,42 @@
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>228912</v>
+        <v>220787</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>562940</v>
+        <v>562925</v>
       </c>
       <c r="R117" t="n">
-        <v>7061021</v>
+        <v>7061308</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -12984,7 +13053,7 @@
       </c>
       <c r="Z117" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
@@ -12994,7 +13063,7 @@
       </c>
       <c r="AB117" t="inlineStr">
         <is>
-          <t>18:00</t>
+          <t>16:16</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13021,10 +13090,10 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>119837344</v>
+        <v>119836367</v>
       </c>
       <c r="B118" t="n">
-        <v>57473</v>
+        <v>95478</v>
       </c>
       <c r="C118" t="inlineStr">
         <is>
@@ -13037,46 +13106,37 @@
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>53</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M118" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>562829</v>
+        <v>562983</v>
       </c>
       <c r="R118" t="n">
-        <v>7061182</v>
+        <v>7061268</v>
       </c>
       <c r="S118" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13103,19 +13163,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z118" t="inlineStr">
-        <is>
-          <t>16:56</t>
-        </is>
-      </c>
       <c r="AA118" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB118" t="inlineStr">
-        <is>
-          <t>16:56</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13130,22 +13180,22 @@
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>119837299</v>
+        <v>119837424</v>
       </c>
       <c r="B119" t="n">
-        <v>82321</v>
+        <v>91858</v>
       </c>
       <c r="C119" t="inlineStr">
         <is>
@@ -13154,25 +13204,25 @@
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>1312</v>
+        <v>4364</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Gammelgransskål</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Pseudographis pinicola</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Nyl.) Rehm</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I119" t="inlineStr"/>
@@ -13182,13 +13232,13 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>562843</v>
+        <v>562774</v>
       </c>
       <c r="R119" t="n">
-        <v>7061204</v>
+        <v>7061178</v>
       </c>
       <c r="S119" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T119" t="inlineStr">
         <is>
@@ -13215,19 +13265,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z119" t="inlineStr">
-        <is>
-          <t>16:52</t>
-        </is>
-      </c>
       <c r="AA119" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB119" t="inlineStr">
-        <is>
-          <t>16:52</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13242,22 +13282,22 @@
       <c r="AT119" t="inlineStr"/>
       <c r="AW119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX119" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119837543</v>
+        <v>119838327</v>
       </c>
       <c r="B120" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13266,25 +13306,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13294,13 +13334,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562745</v>
+        <v>562870</v>
       </c>
       <c r="R120" t="n">
-        <v>7061152</v>
+        <v>7061110</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13327,19 +13367,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z120" t="inlineStr">
-        <is>
-          <t>17:11</t>
-        </is>
-      </c>
       <c r="AA120" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB120" t="inlineStr">
-        <is>
-          <t>17:11</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13354,22 +13384,22 @@
       <c r="AT120" t="inlineStr"/>
       <c r="AW120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX120" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119835897</v>
+        <v>119836719</v>
       </c>
       <c r="B121" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13382,21 +13412,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13406,10 +13436,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562851</v>
+        <v>562937</v>
       </c>
       <c r="R121" t="n">
-        <v>7061350</v>
+        <v>7061312</v>
       </c>
       <c r="S121" t="n">
         <v>15</v>
@@ -13456,22 +13486,22 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119839227</v>
+        <v>119835751</v>
       </c>
       <c r="B122" t="n">
-        <v>91858</v>
+        <v>79623</v>
       </c>
       <c r="C122" t="inlineStr">
         <is>
@@ -13480,25 +13510,25 @@
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>4364</v>
+        <v>6458</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
@@ -13508,10 +13538,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>563080</v>
+        <v>562833</v>
       </c>
       <c r="R122" t="n">
-        <v>7061030</v>
+        <v>7061339</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13570,10 +13600,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119838030</v>
+        <v>119835431</v>
       </c>
       <c r="B123" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13586,42 +13616,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
-      <c r="M123" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>562828</v>
+        <v>562853</v>
       </c>
       <c r="R123" t="n">
-        <v>7061089</v>
+        <v>7061293</v>
       </c>
       <c r="S123" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T123" t="inlineStr">
         <is>
@@ -13648,19 +13673,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z123" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA123" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB123" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13675,22 +13690,22 @@
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>119837512</v>
+        <v>119837366</v>
       </c>
       <c r="B124" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C124" t="inlineStr">
         <is>
@@ -13703,21 +13718,21 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
@@ -13727,13 +13742,13 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>562769</v>
+        <v>562815</v>
       </c>
       <c r="R124" t="n">
-        <v>7061157</v>
+        <v>7061177</v>
       </c>
       <c r="S124" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T124" t="inlineStr">
         <is>
@@ -13760,24 +13775,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z124" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA124" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB124" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13792,12 +13792,12 @@
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -3844,10 +3844,10 @@
     </row>
     <row r="32">
       <c r="A32" t="n">
-        <v>119837512</v>
+        <v>119836179</v>
       </c>
       <c r="B32" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3860,21 +3860,21 @@
         </is>
       </c>
       <c r="E32" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H32" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I32" t="inlineStr"/>
@@ -3884,10 +3884,10 @@
         </is>
       </c>
       <c r="Q32" t="n">
-        <v>562769</v>
+        <v>562966</v>
       </c>
       <c r="R32" t="n">
-        <v>7061157</v>
+        <v>7061336</v>
       </c>
       <c r="S32" t="n">
         <v>10</v>
@@ -3917,24 +3917,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z32" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
       <c r="AA32" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB32" t="inlineStr">
-        <is>
-          <t>17:08</t>
-        </is>
-      </c>
-      <c r="AC32" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD32" t="b">
@@ -3949,12 +3934,12 @@
       <c r="AT32" t="inlineStr"/>
       <c r="AW32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX32" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
@@ -4369,10 +4354,10 @@
     </row>
     <row r="37">
       <c r="A37" t="n">
-        <v>119838153</v>
+        <v>119837512</v>
       </c>
       <c r="B37" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C37" t="inlineStr">
         <is>
@@ -4381,25 +4366,25 @@
       </c>
       <c r="D37" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E37" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H37" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I37" t="inlineStr"/>
@@ -4409,10 +4394,10 @@
         </is>
       </c>
       <c r="Q37" t="n">
-        <v>562865</v>
+        <v>562769</v>
       </c>
       <c r="R37" t="n">
-        <v>7061107</v>
+        <v>7061157</v>
       </c>
       <c r="S37" t="n">
         <v>10</v>
@@ -4442,14 +4427,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z37" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AA37" t="inlineStr">
         <is>
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="AB37" t="inlineStr">
+        <is>
+          <t>17:08</t>
+        </is>
+      </c>
       <c r="AC37" t="inlineStr">
         <is>
-          <t>Rikligt</t>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD37" t="b">
@@ -4464,19 +4459,19 @@
       <c r="AT37" t="inlineStr"/>
       <c r="AW37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX37" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
     </row>
     <row r="38">
       <c r="A38" t="n">
-        <v>119837899</v>
+        <v>119838153</v>
       </c>
       <c r="B38" t="n">
         <v>91858</v>
@@ -4516,10 +4511,10 @@
         </is>
       </c>
       <c r="Q38" t="n">
-        <v>562848</v>
+        <v>562865</v>
       </c>
       <c r="R38" t="n">
-        <v>7061087</v>
+        <v>7061107</v>
       </c>
       <c r="S38" t="n">
         <v>10</v>
@@ -4552,6 +4547,11 @@
       <c r="AA38" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC38" t="inlineStr">
+        <is>
+          <t>Rikligt</t>
         </is>
       </c>
       <c r="AD38" t="b">
@@ -4578,10 +4578,10 @@
     </row>
     <row r="39">
       <c r="A39" t="n">
-        <v>119836179</v>
+        <v>119837899</v>
       </c>
       <c r="B39" t="n">
-        <v>78542</v>
+        <v>91858</v>
       </c>
       <c r="C39" t="inlineStr">
         <is>
@@ -4590,25 +4590,25 @@
       </c>
       <c r="D39" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E39" t="n">
-        <v>6425</v>
+        <v>4364</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H39" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I39" t="inlineStr"/>
@@ -4618,10 +4618,10 @@
         </is>
       </c>
       <c r="Q39" t="n">
-        <v>562966</v>
+        <v>562848</v>
       </c>
       <c r="R39" t="n">
-        <v>7061336</v>
+        <v>7061087</v>
       </c>
       <c r="S39" t="n">
         <v>10</v>
@@ -6171,10 +6171,10 @@
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>119838102</v>
+        <v>119835344</v>
       </c>
       <c r="B54" t="n">
-        <v>57473</v>
+        <v>90600</v>
       </c>
       <c r="C54" t="inlineStr">
         <is>
@@ -6187,42 +6187,37 @@
         </is>
       </c>
       <c r="E54" t="n">
-        <v>103021</v>
+        <v>5442</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H54" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="P54" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>562863</v>
+        <v>562790</v>
       </c>
       <c r="R54" t="n">
-        <v>7061098</v>
+        <v>7061258</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6249,9 +6244,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>15:20</t>
+        </is>
+      </c>
       <c r="AA54" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>15:20</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6266,22 +6271,22 @@
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>119835344</v>
+        <v>119838102</v>
       </c>
       <c r="B55" t="n">
-        <v>90600</v>
+        <v>57473</v>
       </c>
       <c r="C55" t="inlineStr">
         <is>
@@ -6294,37 +6299,42 @@
         </is>
       </c>
       <c r="E55" t="n">
-        <v>5442</v>
+        <v>103021</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P55" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>562790</v>
+        <v>562863</v>
       </c>
       <c r="R55" t="n">
-        <v>7061258</v>
+        <v>7061098</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6351,19 +6361,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z55" t="inlineStr">
-        <is>
-          <t>15:20</t>
-        </is>
-      </c>
       <c r="AA55" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB55" t="inlineStr">
-        <is>
-          <t>15:20</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6378,22 +6378,22 @@
       <c r="AT55" t="inlineStr"/>
       <c r="AW55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX55" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>119837999</v>
+        <v>119836311</v>
       </c>
       <c r="B56" t="n">
-        <v>79160</v>
+        <v>97930</v>
       </c>
       <c r="C56" t="inlineStr">
         <is>
@@ -6402,25 +6402,25 @@
       </c>
       <c r="D56" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E56" t="n">
-        <v>6453</v>
+        <v>220787</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I56" t="inlineStr"/>
@@ -6430,10 +6430,10 @@
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>562848</v>
+        <v>562972</v>
       </c>
       <c r="R56" t="n">
-        <v>7061083</v>
+        <v>7061274</v>
       </c>
       <c r="S56" t="n">
         <v>15</v>
@@ -6466,6 +6466,11 @@
       <c r="AA56" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AC56" t="inlineStr">
+        <is>
+          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6492,10 +6497,10 @@
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>119837399</v>
+        <v>119837999</v>
       </c>
       <c r="B57" t="n">
-        <v>79623</v>
+        <v>79160</v>
       </c>
       <c r="C57" t="inlineStr">
         <is>
@@ -6508,21 +6513,21 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I57" t="inlineStr"/>
@@ -6532,13 +6537,13 @@
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>562767</v>
+        <v>562848</v>
       </c>
       <c r="R57" t="n">
-        <v>7061188</v>
+        <v>7061083</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6594,10 +6599,10 @@
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>119836311</v>
+        <v>119837399</v>
       </c>
       <c r="B58" t="n">
-        <v>97930</v>
+        <v>79623</v>
       </c>
       <c r="C58" t="inlineStr">
         <is>
@@ -6606,25 +6611,25 @@
       </c>
       <c r="D58" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E58" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H58" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I58" t="inlineStr"/>
@@ -6634,13 +6639,13 @@
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>562972</v>
+        <v>562767</v>
       </c>
       <c r="R58" t="n">
-        <v>7061274</v>
+        <v>7061188</v>
       </c>
       <c r="S58" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T58" t="inlineStr">
         <is>
@@ -6670,11 +6675,6 @@
       <c r="AA58" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>Spridd i området</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6701,10 +6701,10 @@
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>119838865</v>
+        <v>119838967</v>
       </c>
       <c r="B59" t="n">
-        <v>91858</v>
+        <v>97930</v>
       </c>
       <c r="C59" t="inlineStr">
         <is>
@@ -6713,41 +6713,45 @@
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>4364</v>
+        <v>220787</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I59" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>562942</v>
+        <v>562990</v>
       </c>
       <c r="R59" t="n">
-        <v>7061029</v>
+        <v>7061060</v>
       </c>
       <c r="S59" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T59" t="inlineStr">
         <is>
@@ -6774,9 +6778,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z59" t="inlineStr">
+        <is>
+          <t>18:11</t>
+        </is>
+      </c>
       <c r="AA59" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB59" t="inlineStr">
+        <is>
+          <t>18:11</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -6791,22 +6805,22 @@
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>119840392</v>
+        <v>119838865</v>
       </c>
       <c r="B60" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C60" t="inlineStr">
         <is>
@@ -6815,25 +6829,25 @@
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I60" t="inlineStr"/>
@@ -6843,13 +6857,13 @@
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>562878</v>
+        <v>562942</v>
       </c>
       <c r="R60" t="n">
-        <v>7061442</v>
+        <v>7061029</v>
       </c>
       <c r="S60" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T60" t="inlineStr">
         <is>
@@ -6876,24 +6890,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z60" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
       <c r="AA60" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB60" t="inlineStr">
-        <is>
-          <t>19:19</t>
-        </is>
-      </c>
-      <c r="AC60" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -6908,22 +6907,22 @@
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>119838967</v>
+        <v>119840392</v>
       </c>
       <c r="B61" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C61" t="inlineStr">
         <is>
@@ -6932,42 +6931,38 @@
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>562990</v>
+        <v>562878</v>
       </c>
       <c r="R61" t="n">
-        <v>7061060</v>
+        <v>7061442</v>
       </c>
       <c r="S61" t="n">
         <v>10</v>
@@ -6999,7 +6994,7 @@
       </c>
       <c r="Z61" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:19</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
@@ -7009,7 +7004,12 @@
       </c>
       <c r="AB61" t="inlineStr">
         <is>
-          <t>18:11</t>
+          <t>19:19</t>
+        </is>
+      </c>
+      <c r="AC61" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -8235,10 +8235,10 @@
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>119837084</v>
+        <v>119839212</v>
       </c>
       <c r="B73" t="n">
-        <v>90600</v>
+        <v>78542</v>
       </c>
       <c r="C73" t="inlineStr">
         <is>
@@ -8251,37 +8251,37 @@
         </is>
       </c>
       <c r="E73" t="n">
-        <v>5442</v>
+        <v>6425</v>
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H73" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>562905</v>
+        <v>563063</v>
       </c>
       <c r="R73" t="n">
-        <v>7061251</v>
+        <v>7061037</v>
       </c>
       <c r="S73" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T73" t="inlineStr">
         <is>
@@ -8308,9 +8308,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>18:26</t>
+        </is>
+      </c>
       <c r="AA73" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>18:26</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8325,19 +8335,19 @@
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>119839212</v>
+        <v>119840354</v>
       </c>
       <c r="B74" t="n">
         <v>78542</v>
@@ -8373,14 +8383,14 @@
       <c r="I74" t="inlineStr"/>
       <c r="P74" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>563063</v>
+        <v>562893</v>
       </c>
       <c r="R74" t="n">
-        <v>7061037</v>
+        <v>7061427</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8410,19 +8420,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z74" t="inlineStr">
-        <is>
-          <t>18:26</t>
-        </is>
-      </c>
       <c r="AA74" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB74" t="inlineStr">
-        <is>
-          <t>18:26</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8437,22 +8437,22 @@
       <c r="AT74" t="inlineStr"/>
       <c r="AW74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX74" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>119840354</v>
+        <v>119837084</v>
       </c>
       <c r="B75" t="n">
-        <v>78542</v>
+        <v>90600</v>
       </c>
       <c r="C75" t="inlineStr">
         <is>
@@ -8465,21 +8465,21 @@
         </is>
       </c>
       <c r="E75" t="n">
-        <v>6425</v>
+        <v>5442</v>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I75" t="inlineStr"/>
@@ -8489,13 +8489,13 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>562893</v>
+        <v>562905</v>
       </c>
       <c r="R75" t="n">
-        <v>7061427</v>
+        <v>7061251</v>
       </c>
       <c r="S75" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T75" t="inlineStr">
         <is>
@@ -9960,10 +9960,10 @@
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>119839228</v>
+        <v>119835796</v>
       </c>
       <c r="B89" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C89" t="inlineStr">
         <is>
@@ -9976,34 +9976,34 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>563061</v>
+        <v>562830</v>
       </c>
       <c r="R89" t="n">
-        <v>7061025</v>
+        <v>7061321</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10033,24 +10033,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z89" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
       <c r="AA89" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB89" t="inlineStr">
-        <is>
-          <t>18:28</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10065,22 +10050,22 @@
       <c r="AT89" t="inlineStr"/>
       <c r="AW89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX89" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>119835980</v>
+        <v>119837858</v>
       </c>
       <c r="B90" t="n">
-        <v>57320</v>
+        <v>91858</v>
       </c>
       <c r="C90" t="inlineStr">
         <is>
@@ -10089,43 +10074,38 @@
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>100109</v>
+        <v>4364</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
-      <c r="M90" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P90" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>562885</v>
+        <v>562847</v>
       </c>
       <c r="R90" t="n">
-        <v>7061225</v>
+        <v>7061096</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10155,19 +10135,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z90" t="inlineStr">
-        <is>
-          <t>15:46</t>
-        </is>
-      </c>
       <c r="AA90" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB90" t="inlineStr">
-        <is>
-          <t>15:46</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10182,22 +10152,22 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>119835654</v>
+        <v>119839228</v>
       </c>
       <c r="B91" t="n">
-        <v>79652</v>
+        <v>57320</v>
       </c>
       <c r="C91" t="inlineStr">
         <is>
@@ -10206,41 +10176,41 @@
       </c>
       <c r="D91" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E91" t="n">
-        <v>6462</v>
+        <v>100109</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>Stuplav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>Nephroma bellum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
         <is>
-          <t>(Spreng.) Tuck.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>562838</v>
+        <v>563061</v>
       </c>
       <c r="R91" t="n">
-        <v>7061333</v>
+        <v>7061025</v>
       </c>
       <c r="S91" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10267,9 +10237,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z91" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
       <c r="AA91" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB91" t="inlineStr">
+        <is>
+          <t>18:28</t>
+        </is>
+      </c>
+      <c r="AC91" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10284,22 +10269,22 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>119835796</v>
+        <v>119835980</v>
       </c>
       <c r="B92" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C92" t="inlineStr">
         <is>
@@ -10312,34 +10297,39 @@
         </is>
       </c>
       <c r="E92" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H92" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P92" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>562830</v>
+        <v>562885</v>
       </c>
       <c r="R92" t="n">
-        <v>7061321</v>
+        <v>7061225</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10369,9 +10359,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>15:46</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>15:46</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10386,22 +10386,22 @@
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>119837858</v>
+        <v>119835654</v>
       </c>
       <c r="B93" t="n">
-        <v>91858</v>
+        <v>79652</v>
       </c>
       <c r="C93" t="inlineStr">
         <is>
@@ -10414,21 +10414,21 @@
         </is>
       </c>
       <c r="E93" t="n">
-        <v>4364</v>
+        <v>6462</v>
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Stuplav</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Nephroma bellum</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Spreng.) Tuck.</t>
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
@@ -10438,13 +10438,13 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>562847</v>
+        <v>562838</v>
       </c>
       <c r="R93" t="n">
-        <v>7061096</v>
+        <v>7061333</v>
       </c>
       <c r="S93" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T93" t="inlineStr">
         <is>
@@ -11249,10 +11249,10 @@
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>119835742</v>
+        <v>119835535</v>
       </c>
       <c r="B101" t="n">
-        <v>56532</v>
+        <v>91858</v>
       </c>
       <c r="C101" t="inlineStr">
         <is>
@@ -11265,21 +11265,21 @@
         </is>
       </c>
       <c r="E101" t="n">
-        <v>100138</v>
+        <v>4364</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>Tjäder</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>Tetrao urogallus</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I101" t="inlineStr"/>
@@ -11289,13 +11289,13 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>562853</v>
+        <v>562795</v>
       </c>
       <c r="R101" t="n">
-        <v>7061243</v>
+        <v>7061238</v>
       </c>
       <c r="S101" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T101" t="inlineStr">
         <is>
@@ -11322,9 +11322,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z101" t="inlineStr">
+        <is>
+          <t>15:32</t>
+        </is>
+      </c>
       <c r="AA101" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB101" t="inlineStr">
+        <is>
+          <t>15:32</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11339,22 +11349,22 @@
       <c r="AT101" t="inlineStr"/>
       <c r="AW101" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX101" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>119835535</v>
+        <v>119837856</v>
       </c>
       <c r="B102" t="n">
-        <v>91858</v>
+        <v>57320</v>
       </c>
       <c r="C102" t="inlineStr">
         <is>
@@ -11363,38 +11373,38 @@
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E102" t="n">
-        <v>4364</v>
+        <v>100109</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H102" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I102" t="inlineStr"/>
       <c r="P102" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>562795</v>
+        <v>562803</v>
       </c>
       <c r="R102" t="n">
-        <v>7061238</v>
+        <v>7061104</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11426,7 +11436,7 @@
       </c>
       <c r="Z102" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:21</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
@@ -11436,7 +11446,12 @@
       </c>
       <c r="AB102" t="inlineStr">
         <is>
-          <t>15:32</t>
+          <t>17:21</t>
+        </is>
+      </c>
+      <c r="AC102" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11463,10 +11478,10 @@
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>119837181</v>
+        <v>119835742</v>
       </c>
       <c r="B103" t="n">
-        <v>90545</v>
+        <v>56532</v>
       </c>
       <c r="C103" t="inlineStr">
         <is>
@@ -11479,21 +11494,21 @@
         </is>
       </c>
       <c r="E103" t="n">
-        <v>5447</v>
+        <v>100138</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tjäder</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Tetrao urogallus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11503,13 +11518,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>562872</v>
+        <v>562853</v>
       </c>
       <c r="R103" t="n">
-        <v>7061246</v>
+        <v>7061243</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11553,22 +11568,22 @@
       <c r="AT103" t="inlineStr"/>
       <c r="AW103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX103" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>119837856</v>
+        <v>119837181</v>
       </c>
       <c r="B104" t="n">
-        <v>57320</v>
+        <v>90545</v>
       </c>
       <c r="C104" t="inlineStr">
         <is>
@@ -11577,38 +11592,38 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>100109</v>
+        <v>5447</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>562803</v>
+        <v>562872</v>
       </c>
       <c r="R104" t="n">
-        <v>7061104</v>
+        <v>7061246</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11638,24 +11653,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z104" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
       <c r="AA104" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB104" t="inlineStr">
-        <is>
-          <t>17:21</t>
-        </is>
-      </c>
-      <c r="AC104" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11670,12 +11670,12 @@
       <c r="AT104" t="inlineStr"/>
       <c r="AW104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX104" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
@@ -11798,10 +11798,10 @@
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>119838864</v>
+        <v>119835108</v>
       </c>
       <c r="B106" t="n">
-        <v>78279</v>
+        <v>79623</v>
       </c>
       <c r="C106" t="inlineStr">
         <is>
@@ -11814,37 +11814,37 @@
         </is>
       </c>
       <c r="E106" t="n">
-        <v>228912</v>
+        <v>6458</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Sågrået, Sågrået, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>562940</v>
+        <v>562802</v>
       </c>
       <c r="R106" t="n">
-        <v>7061021</v>
+        <v>7061280</v>
       </c>
       <c r="S106" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T106" t="inlineStr">
         <is>
@@ -11871,19 +11871,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z106" t="inlineStr">
-        <is>
-          <t>18:00</t>
-        </is>
-      </c>
       <c r="AA106" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB106" t="inlineStr">
-        <is>
-          <t>18:00</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -11898,19 +11888,19 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>119835108</v>
+        <v>119835638</v>
       </c>
       <c r="B107" t="n">
         <v>79623</v>
@@ -11950,10 +11940,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>562802</v>
+        <v>562838</v>
       </c>
       <c r="R107" t="n">
-        <v>7061280</v>
+        <v>7061326</v>
       </c>
       <c r="S107" t="n">
         <v>15</v>
@@ -12000,22 +11990,22 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>119835638</v>
+        <v>119838030</v>
       </c>
       <c r="B108" t="n">
-        <v>79623</v>
+        <v>57320</v>
       </c>
       <c r="C108" t="inlineStr">
         <is>
@@ -12028,37 +12018,42 @@
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6458</v>
+        <v>100109</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I108" t="inlineStr"/>
+      <c r="M108" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Grössjöflon, Grössjöflon, Ång</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>562838</v>
+        <v>562828</v>
       </c>
       <c r="R108" t="n">
-        <v>7061326</v>
+        <v>7061089</v>
       </c>
       <c r="S108" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T108" t="inlineStr">
         <is>
@@ -12085,9 +12080,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z108" t="inlineStr">
+        <is>
+          <t>17:23</t>
+        </is>
+      </c>
       <c r="AA108" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB108" t="inlineStr">
+        <is>
+          <t>17:23</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12102,22 +12107,22 @@
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>119838179</v>
+        <v>119836807</v>
       </c>
       <c r="B109" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C109" t="inlineStr">
         <is>
@@ -12130,21 +12135,21 @@
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
@@ -12154,13 +12159,13 @@
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>562854</v>
+        <v>562926</v>
       </c>
       <c r="R109" t="n">
-        <v>7061121</v>
+        <v>7061340</v>
       </c>
       <c r="S109" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T109" t="inlineStr">
         <is>
@@ -12187,9 +12192,24 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z109" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
       <c r="AA109" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB109" t="inlineStr">
+        <is>
+          <t>16:28</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12204,22 +12224,22 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>119838709</v>
+        <v>119838864</v>
       </c>
       <c r="B110" t="n">
-        <v>91901</v>
+        <v>78279</v>
       </c>
       <c r="C110" t="inlineStr">
         <is>
@@ -12232,37 +12252,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>5448</v>
+        <v>228912</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Phellodon connatus</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Schultz) nom.prov</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
+          <t>Sågrået, Sågrået, Ång</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>562892</v>
+        <v>562940</v>
       </c>
       <c r="R110" t="n">
-        <v>7061086</v>
+        <v>7061021</v>
       </c>
       <c r="S110" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12289,9 +12309,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z110" t="inlineStr">
+        <is>
+          <t>18:00</t>
+        </is>
+      </c>
       <c r="AA110" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB110" t="inlineStr">
+        <is>
+          <t>18:00</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12306,22 +12336,22 @@
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>119838030</v>
+        <v>119838179</v>
       </c>
       <c r="B111" t="n">
-        <v>57320</v>
+        <v>78542</v>
       </c>
       <c r="C111" t="inlineStr">
         <is>
@@ -12334,42 +12364,37 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100109</v>
+        <v>6425</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
-      <c r="M111" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Grössjöflon, Grössjöflon, Ång</t>
+          <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>562828</v>
+        <v>562854</v>
       </c>
       <c r="R111" t="n">
-        <v>7061089</v>
+        <v>7061121</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12396,19 +12421,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z111" t="inlineStr">
-        <is>
-          <t>17:23</t>
-        </is>
-      </c>
       <c r="AA111" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB111" t="inlineStr">
-        <is>
-          <t>17:23</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12423,22 +12438,22 @@
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>119836807</v>
+        <v>119838709</v>
       </c>
       <c r="B112" t="n">
-        <v>57320</v>
+        <v>91901</v>
       </c>
       <c r="C112" t="inlineStr">
         <is>
@@ -12451,21 +12466,21 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100109</v>
+        <v>5448</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellodon connatus</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Schultz) nom.prov</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
@@ -12475,13 +12490,13 @@
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>562926</v>
+        <v>562892</v>
       </c>
       <c r="R112" t="n">
-        <v>7061340</v>
+        <v>7061086</v>
       </c>
       <c r="S112" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T112" t="inlineStr">
         <is>
@@ -12508,24 +12523,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z112" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
       <c r="AA112" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB112" t="inlineStr">
-        <is>
-          <t>16:28</t>
-        </is>
-      </c>
-      <c r="AC112" t="inlineStr">
-        <is>
-          <t>Ringhack</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12540,12 +12540,12 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
@@ -12654,10 +12654,10 @@
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>119838597</v>
+        <v>119835763</v>
       </c>
       <c r="B114" t="n">
-        <v>91858</v>
+        <v>78542</v>
       </c>
       <c r="C114" t="inlineStr">
         <is>
@@ -12666,25 +12666,25 @@
       </c>
       <c r="D114" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E114" t="n">
-        <v>4364</v>
+        <v>6425</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
@@ -12694,13 +12694,13 @@
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>562861</v>
+        <v>562859</v>
       </c>
       <c r="R114" t="n">
-        <v>7061099</v>
+        <v>7061254</v>
       </c>
       <c r="S114" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T114" t="inlineStr">
         <is>
@@ -12727,9 +12727,19 @@
           <t>2024-09-18</t>
         </is>
       </c>
+      <c r="Z114" t="inlineStr">
+        <is>
+          <t>15:39</t>
+        </is>
+      </c>
       <c r="AA114" t="inlineStr">
         <is>
           <t>2024-09-18</t>
+        </is>
+      </c>
+      <c r="AB114" t="inlineStr">
+        <is>
+          <t>15:39</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -12744,22 +12754,22 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>119835763</v>
+        <v>119836632</v>
       </c>
       <c r="B115" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C115" t="inlineStr">
         <is>
@@ -12768,41 +12778,45 @@
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
       <c r="P115" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>562859</v>
+        <v>562948</v>
       </c>
       <c r="R115" t="n">
-        <v>7061254</v>
+        <v>7061323</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -12829,19 +12843,9 @@
           <t>2024-09-18</t>
         </is>
       </c>
-      <c r="Z115" t="inlineStr">
-        <is>
-          <t>15:39</t>
-        </is>
-      </c>
       <c r="AA115" t="inlineStr">
         <is>
           <t>2024-09-18</t>
-        </is>
-      </c>
-      <c r="AB115" t="inlineStr">
-        <is>
-          <t>15:39</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -12856,22 +12860,22 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>119836632</v>
+        <v>119838597</v>
       </c>
       <c r="B116" t="n">
-        <v>97930</v>
+        <v>91858</v>
       </c>
       <c r="C116" t="inlineStr">
         <is>
@@ -12880,42 +12884,38 @@
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>220787</v>
+        <v>4364</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
           <t>Ottringstjärnen, Ottringstjärnen, Ång</t>
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>562948</v>
+        <v>562861</v>
       </c>
       <c r="R116" t="n">
-        <v>7061323</v>
+        <v>7061099</v>
       </c>
       <c r="S116" t="n">
         <v>15</v>
@@ -13294,10 +13294,10 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>119838327</v>
+        <v>119836719</v>
       </c>
       <c r="B120" t="n">
-        <v>91858</v>
+        <v>90580</v>
       </c>
       <c r="C120" t="inlineStr">
         <is>
@@ -13306,25 +13306,25 @@
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>4364</v>
+        <v>1202</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
@@ -13334,10 +13334,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>562870</v>
+        <v>562937</v>
       </c>
       <c r="R120" t="n">
-        <v>7061110</v>
+        <v>7061312</v>
       </c>
       <c r="S120" t="n">
         <v>15</v>
@@ -13396,10 +13396,10 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>119836719</v>
+        <v>119835751</v>
       </c>
       <c r="B121" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C121" t="inlineStr">
         <is>
@@ -13412,21 +13412,21 @@
         </is>
       </c>
       <c r="E121" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
@@ -13436,13 +13436,13 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>562937</v>
+        <v>562833</v>
       </c>
       <c r="R121" t="n">
-        <v>7061312</v>
+        <v>7061339</v>
       </c>
       <c r="S121" t="n">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13486,19 +13486,19 @@
       <c r="AT121" t="inlineStr"/>
       <c r="AW121" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AX121" t="inlineStr">
         <is>
-          <t>Michaela Ehmann</t>
+          <t>Erland Lindblad</t>
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>119835751</v>
+        <v>119835431</v>
       </c>
       <c r="B122" t="n">
         <v>79623</v>
@@ -13538,13 +13538,13 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>562833</v>
+        <v>562853</v>
       </c>
       <c r="R122" t="n">
-        <v>7061339</v>
+        <v>7061293</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -13588,22 +13588,22 @@
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Erland Lindblad</t>
+          <t>Michaela Ehmann</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>119835431</v>
+        <v>119838327</v>
       </c>
       <c r="B123" t="n">
-        <v>79623</v>
+        <v>91858</v>
       </c>
       <c r="C123" t="inlineStr">
         <is>
@@ -13612,25 +13612,25 @@
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>4364</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
@@ -13640,10 +13640,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>562853</v>
+        <v>562870</v>
       </c>
       <c r="R123" t="n">
-        <v>7061293</v>
+        <v>7061110</v>
       </c>
       <c r="S123" t="n">
         <v>15</v>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -13909,7 +13909,7 @@
         <v>122296685</v>
       </c>
       <c r="B126" t="n">
-        <v>90799</v>
+        <v>90809</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -13909,7 +13909,7 @@
         <v>122296685</v>
       </c>
       <c r="B126" t="n">
-        <v>90809</v>
+        <v>90821</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -13909,7 +13909,7 @@
         <v>122296685</v>
       </c>
       <c r="B126" t="n">
-        <v>90821</v>
+        <v>90828</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -13909,7 +13909,7 @@
         <v>122296685</v>
       </c>
       <c r="B126" t="n">
-        <v>90828</v>
+        <v>90833</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13923,11 +13923,6 @@
       </c>
       <c r="E126" t="n">
         <v>5442</v>
-      </c>
-      <c r="F126" t="inlineStr">
-        <is>
-          <t>Tallticka</t>
-        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -13909,7 +13909,7 @@
         <v>122296685</v>
       </c>
       <c r="B126" t="n">
-        <v>90833</v>
+        <v>90846</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
@@ -13923,6 +13923,11 @@
       </c>
       <c r="E126" t="n">
         <v>5442</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -13909,7 +13909,7 @@
         <v>122296685</v>
       </c>
       <c r="B126" t="n">
-        <v>90846</v>
+        <v>90859</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -13909,7 +13909,7 @@
         <v>122296685</v>
       </c>
       <c r="B126" t="n">
-        <v>90859</v>
+        <v>90853</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -13909,7 +13909,7 @@
         <v>122296685</v>
       </c>
       <c r="B126" t="n">
-        <v>90853</v>
+        <v>90854</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>

--- a/artfynd/A 38186-2024 artfynd.xlsx
+++ b/artfynd/A 38186-2024 artfynd.xlsx
@@ -13909,7 +13909,7 @@
         <v>122296685</v>
       </c>
       <c r="B126" t="n">
-        <v>90854</v>
+        <v>90857</v>
       </c>
       <c r="C126" t="inlineStr">
         <is>
